--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,6 +91,10 @@
     </font>
     <font>
       <color rgb="00595959"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="8">
@@ -163,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -188,6 +192,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -588,7 +594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 19 Juli 2026</t>
+          <t>Hari/Tanggal : 20 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -610,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 06.29 WITA</t>
+          <t>Pukul        : 05.55 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -744,62 +750,62 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4129</v>
+        <v>4131</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1176</v>
+        <v>1162</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
         <v/>
       </c>
       <c r="F7" s="9" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G7" s="10">
         <f>F7/B7</f>
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>162</v>
+        <v>33</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K7" s="10">
         <f>J7/B7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2737</v>
+        <v>2884</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
         <v/>
       </c>
       <c r="N7" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O7" s="10">
         <f>N7/B7</f>
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>2916</v>
+        <v>2935</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -813,27 +819,27 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1413</v>
+        <v>1422</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
@@ -847,28 +853,28 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>698</v>
+        <v>745</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
         <v/>
       </c>
       <c r="N8" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O8" s="10">
         <f>N8/B8</f>
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>717</v>
+        <v>751</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -882,41 +888,41 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6234</v>
+        <v>6244</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1616</v>
+        <v>1583</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>142</v>
+        <v>63</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4283</v>
+        <v>4413</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -930,14 +936,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4524</v>
+        <v>4588</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -951,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3157</v>
+        <v>3171</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>813</v>
+        <v>768</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -971,21 +977,21 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K10" s="10">
         <f>J10/B10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2319</v>
+        <v>2380</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
@@ -999,14 +1005,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2344</v>
+        <v>2403</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1020,27 +1026,27 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
@@ -1054,7 +1060,7 @@
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>658</v>
+        <v>690</v>
       </c>
       <c r="M11" s="10">
         <f>L11/B11</f>
@@ -1068,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>678</v>
+        <v>701</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1095,42 +1101,42 @@
         <v>23</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E12" s="10">
         <f>D12/B12</f>
         <v/>
       </c>
       <c r="F12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="10">
         <f>F12/B12</f>
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
         <v/>
       </c>
       <c r="J12" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12" s="10">
         <f>J12/B12</f>
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="M12" s="10">
         <f>L12/B12</f>
         <v/>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="10">
         <f>N12/B12</f>
@@ -1144,7 +1150,7 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1158,41 +1164,41 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4591</v>
+        <v>4604</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2063</v>
+        <v>2034</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2258</v>
+        <v>2329</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1206,14 +1212,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2494</v>
+        <v>2537</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1227,62 +1233,62 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>5995</v>
+        <v>6005</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2832</v>
+        <v>2798</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>2912</v>
+        <v>3021</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
         <v/>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="10">
         <f>N14/B14</f>
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3127</v>
+        <v>3183</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1296,41 +1302,41 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8049</v>
+        <v>8066</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3577</v>
+        <v>3540</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K15" s="10">
         <f>J15/B15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4283</v>
+        <v>4342</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1344,14 +1350,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4333</v>
+        <v>4399</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1365,62 +1371,62 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5177</v>
+        <v>5180</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2085</v>
+        <v>2067</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>2835</v>
+        <v>2918</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
         <v/>
       </c>
       <c r="N16" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O16" s="10">
         <f>N16/B16</f>
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>2968</v>
+        <v>2999</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1434,41 +1440,41 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2402</v>
+        <v>2407</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1122</v>
+        <v>1104</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1066</v>
+        <v>1133</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
@@ -1482,14 +1488,14 @@
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1256</v>
+        <v>1275</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1503,41 +1509,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9181</v>
+        <v>9227</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2717</v>
+        <v>2628</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>243</v>
+        <v>56</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6104</v>
+        <v>6435</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1551,14 +1557,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>6365</v>
+        <v>6513</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>212</v>
+        <v>148</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1578,7 +1584,7 @@
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1592,21 +1598,21 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
         <v/>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="10">
         <f>J19/B19</f>
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>853</v>
+        <v>887</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1620,14 +1626,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>873</v>
+        <v>896</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1661,21 +1667,21 @@
         <v/>
       </c>
       <c r="H20" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I20" s="10">
         <f>H20/B20</f>
         <v/>
       </c>
       <c r="J20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" s="10">
         <f>J20/B20</f>
         <v/>
       </c>
       <c r="L20" s="9" t="n">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="M20" s="10">
         <f>L20/B20</f>
@@ -1696,7 +1702,7 @@
         <v/>
       </c>
       <c r="R20" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S20" s="10">
         <f>R20/B20</f>
@@ -1710,62 +1716,62 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2796</v>
+        <v>2809</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1176</v>
+        <v>1149</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
         <v/>
       </c>
       <c r="F21" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" s="10">
         <f>F21/B21</f>
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1559</v>
+        <v>1636</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
         <v/>
       </c>
       <c r="N21" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O21" s="10">
         <f>N21/B21</f>
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1616</v>
-      </c>
-      <c r="Q21" s="12">
+        <v>1657</v>
+      </c>
+      <c r="Q21" s="11">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1894,7 +1900,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 19 Juli 2026</t>
+          <t>Hari/Tanggal : 20 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1911,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 06.29 WITA</t>
+          <t>Pukul        : 05.55 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2046,27 +2052,27 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Ayu Lestari Areros</t>
+          <t>Regina Mahoro</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>308</v>
+        <v>417</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>0</v>
@@ -2075,16 +2081,16 @@
         <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>279</v>
+        <v>393</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>281</v>
+        <v>399</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.9123376623376623</v>
+        <v>0.9568345323741008</v>
       </c>
     </row>
     <row r="9">
@@ -2107,31 +2113,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>486</v>
+        <v>519</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.911070780399274</v>
+        <v>0.9402173913043478</v>
       </c>
     </row>
     <row r="10">
@@ -2140,27 +2146,27 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Regina Mahoro</t>
+          <t>Ayu Lestari Areros</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>413</v>
+        <v>308</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="9" t="n">
         <v>0</v>
@@ -2169,16 +2175,16 @@
         <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>370</v>
+        <v>279</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>376</v>
+        <v>281</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.910411622276029</v>
+        <v>0.9123376623376623</v>
       </c>
     </row>
     <row r="11">
@@ -2187,45 +2193,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Merry Christiani Lano</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>364</v>
+        <v>516</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>249</v>
+        <v>443</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>318</v>
+        <v>458</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.8736263736263736</v>
+        <v>0.8875968992248062</v>
       </c>
     </row>
     <row r="12">
@@ -2234,45 +2240,45 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Merry Christiani Lano</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>514</v>
+        <v>364</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>443</v>
+        <v>308</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>444</v>
+        <v>319</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.8638132295719845</v>
+        <v>0.8763736263736264</v>
       </c>
     </row>
     <row r="13">
@@ -2298,28 +2304,28 @@
         <v>377</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.8541114058355439</v>
+        <v>0.8726790450928382</v>
       </c>
     </row>
     <row r="14">
@@ -2328,7 +2334,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Clara Patricia Pangandaheng</t>
+          <t>Fitria Rianti Gorosita</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -2342,31 +2348,31 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.8333333333333335</v>
+        <v>0.8496042216358839</v>
       </c>
     </row>
     <row r="15">
@@ -2375,7 +2381,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Fitria Rianti Gorosita</t>
+          <t>Clara Patricia Pangandaheng</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -2389,31 +2395,31 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.8324468085106383</v>
+        <v>0.841823056300268</v>
       </c>
     </row>
     <row r="16">
@@ -2445,13 +2451,13 @@
         <v>2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
@@ -2486,7 +2492,7 @@
         <v>397</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0</v>
@@ -2498,16 +2504,16 @@
         <v>2</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.7934508816120907</v>
+        <v>0.8110831234256927</v>
       </c>
     </row>
     <row r="18">
@@ -2516,24 +2522,24 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
@@ -2545,16 +2551,16 @@
         <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8032786885245902</v>
       </c>
     </row>
     <row r="19">
@@ -2563,45 +2569,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>372</v>
+        <v>421</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>292</v>
+        <v>335</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.7849462365591396</v>
+        <v>0.7957244655581949</v>
       </c>
     </row>
     <row r="20">
@@ -2610,27 +2616,27 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>495</v>
+        <v>476</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>0</v>
@@ -2639,16 +2645,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.7797979797979798</v>
+        <v>0.7941176470588235</v>
       </c>
     </row>
     <row r="21">
@@ -2657,45 +2663,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.7790973871733968</v>
+        <v>0.7931873479318735</v>
       </c>
     </row>
     <row r="22">
@@ -2704,7 +2710,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -2718,31 +2724,31 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>481</v>
+        <v>376</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>373</v>
+        <v>295</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>374</v>
+        <v>297</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.7775467775467776</v>
+        <v>0.7898936170212765</v>
       </c>
     </row>
     <row r="23">
@@ -2751,45 +2757,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>411</v>
+        <v>499</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>312</v>
+        <v>393</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>317</v>
+        <v>393</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.7712895377128953</v>
+        <v>0.7875751503006012</v>
       </c>
     </row>
     <row r="24">
@@ -2798,45 +2804,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>430</v>
+        <v>495</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>305</v>
+        <v>384</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>329</v>
+        <v>384</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.7651162790697674</v>
+        <v>0.7757575757575758</v>
       </c>
     </row>
     <row r="25">
@@ -2845,45 +2851,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>493</v>
+        <v>430</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>367</v>
+        <v>325</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>375</v>
+        <v>333</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.7606490872210954</v>
+        <v>0.7744186046511627</v>
       </c>
     </row>
     <row r="26">
@@ -2892,45 +2898,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>523</v>
+        <v>388</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>388</v>
+        <v>297</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>397</v>
+        <v>300</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.7590822179732314</v>
+        <v>0.7731958762886599</v>
       </c>
     </row>
     <row r="27">
@@ -2939,45 +2945,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>385</v>
+        <v>524</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>285</v>
+        <v>391</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>286</v>
+        <v>403</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7690839694656488</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J28" s="9" t="n">
         <v>321</v>
@@ -3033,45 +3039,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>257</v>
+        <v>303</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.7356020942408377</v>
+        <v>0.7386091127098321</v>
       </c>
     </row>
     <row r="30">
@@ -3080,7 +3086,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -3094,31 +3100,31 @@
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>552</v>
+        <v>382</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>153</v>
+        <v>101</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>357</v>
+        <v>279</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>399</v>
+        <v>281</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7228260869565217</v>
+        <v>0.7356020942408377</v>
       </c>
     </row>
     <row r="31">
@@ -3127,45 +3133,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7139303482587064</v>
+        <v>0.7294685990338166</v>
       </c>
     </row>
     <row r="32">
@@ -3174,45 +3180,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>496</v>
+        <v>422</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="G32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="J32" s="9" t="n">
-        <v>342</v>
+        <v>306</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>354</v>
+        <v>307</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.7137096774193549</v>
+        <v>0.7274881516587678</v>
       </c>
     </row>
     <row r="33">
@@ -3221,7 +3227,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -3235,31 +3241,31 @@
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J33" s="9" t="n">
+        <v>355</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="9" t="n">
         <v>361</v>
       </c>
-      <c r="K33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="9" t="n">
-        <v>362</v>
-      </c>
       <c r="M33" s="11" t="n">
-        <v>0.7111984282907662</v>
+        <v>0.7248995983935742</v>
       </c>
     </row>
     <row r="34">
@@ -3268,45 +3274,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>407</v>
+        <v>552</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>288</v>
+        <v>398</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>289</v>
+        <v>399</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.71007371007371</v>
+        <v>0.7228260869565217</v>
       </c>
     </row>
     <row r="35">
@@ -3315,45 +3321,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>499</v>
+        <v>535</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.7094188376753507</v>
+        <v>0.7177570093457943</v>
       </c>
     </row>
     <row r="36">
@@ -3362,45 +3368,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>420</v>
+        <v>499</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>289</v>
+        <v>353</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>296</v>
+        <v>358</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7047619047619048</v>
+        <v>0.717434869739479</v>
       </c>
     </row>
     <row r="37">
@@ -3409,24 +3415,24 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0</v>
@@ -3435,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J37" s="9" t="n">
         <v>287</v>
@@ -3444,10 +3450,10 @@
         <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7028985507246377</v>
+        <v>0.7139303482587064</v>
       </c>
     </row>
     <row r="38">
@@ -3456,45 +3462,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>346</v>
+        <v>509</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>242</v>
+        <v>361</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>243</v>
+        <v>362</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.7023121387283237</v>
+        <v>0.7111984282907662</v>
       </c>
     </row>
     <row r="39">
@@ -3503,45 +3509,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>534</v>
+        <v>347</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>367</v>
+        <v>242</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>373</v>
+        <v>246</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.6985018726591761</v>
+        <v>0.7089337175792507</v>
       </c>
     </row>
     <row r="40">
@@ -3550,45 +3556,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>388</v>
+        <v>447</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>223</v>
+        <v>312</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.6829896907216495</v>
+        <v>0.697986577181208</v>
       </c>
     </row>
     <row r="41">
@@ -3597,45 +3603,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>374</v>
+        <v>417</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="G41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I41" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="J41" s="9" t="n">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>254</v>
+        <v>286</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.679144385026738</v>
+        <v>0.6858513189448441</v>
       </c>
     </row>
     <row r="42">
@@ -3644,45 +3650,45 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>417</v>
+        <v>389</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.6762589928057554</v>
+        <v>0.6838046272493572</v>
       </c>
     </row>
     <row r="43">
@@ -3691,45 +3697,45 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G43" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>341</v>
+      </c>
+      <c r="K43" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="J43" s="9" t="n">
-        <v>332</v>
-      </c>
-      <c r="K43" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" s="9" t="n">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.6753507014028056</v>
+        <v>0.6826347305389223</v>
       </c>
     </row>
     <row r="44">
@@ -3738,45 +3744,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>501</v>
+        <v>527</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>311</v>
+        <v>353</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.6686626746506987</v>
+        <v>0.6774193548387096</v>
       </c>
     </row>
     <row r="45">
@@ -3785,45 +3791,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>289</v>
+        <v>374</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>191</v>
+        <v>252</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.6678200692041523</v>
+        <v>0.6764705882352942</v>
       </c>
     </row>
     <row r="46">
@@ -3832,45 +3838,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>522</v>
+        <v>499</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.6753507014028056</v>
       </c>
     </row>
     <row r="47">
@@ -3879,24 +3885,24 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>438</v>
+        <v>289</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
@@ -3905,19 +3911,19 @@
         <v>0</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>292</v>
+        <v>190</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>292</v>
+        <v>193</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.6678200692041523</v>
       </c>
     </row>
     <row r="48">
@@ -3943,28 +3949,28 @@
         <v>345</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.6434782608695652</v>
+        <v>0.6666666666666665</v>
       </c>
     </row>
     <row r="49">
@@ -3973,24 +3979,24 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>0</v>
@@ -3999,19 +4005,19 @@
         <v>0</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.6396396396396397</v>
+        <v>0.6601307189542482</v>
       </c>
     </row>
     <row r="50">
@@ -4037,28 +4043,28 @@
         <v>367</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.6376021798365122</v>
+        <v>0.6566757493188011</v>
       </c>
     </row>
     <row r="51">
@@ -4067,27 +4073,27 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="H51" s="9" t="n">
         <v>0</v>
@@ -4096,16 +4102,16 @@
         <v>1</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.6344827586206897</v>
+        <v>0.652654867256637</v>
       </c>
     </row>
     <row r="52">
@@ -4114,21 +4120,21 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>150</v>
@@ -4137,22 +4143,22 @@
         <v>0</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.6332518337408313</v>
+        <v>0.6462264150943396</v>
       </c>
     </row>
     <row r="53">
@@ -4161,45 +4167,45 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.6318289786223278</v>
+        <v>0.6426966292134831</v>
       </c>
     </row>
     <row r="54">
@@ -4208,7 +4214,7 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
@@ -4222,31 +4228,31 @@
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>513</v>
+        <v>445</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>314</v>
+        <v>281</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>324</v>
+        <v>286</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6426966292134831</v>
       </c>
     </row>
     <row r="55">
@@ -4255,45 +4261,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>464</v>
+        <v>435</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="K55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.6314655172413793</v>
+        <v>0.6413793103448274</v>
       </c>
     </row>
     <row r="56">
@@ -4302,45 +4308,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>452</v>
+        <v>514</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>285</v>
+        <v>329</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.6305309734513275</v>
+        <v>0.6400778210116731</v>
       </c>
     </row>
     <row r="57">
@@ -4349,45 +4355,45 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="I57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.62882096069869</v>
+        <v>0.6379310344827587</v>
       </c>
     </row>
     <row r="58">
@@ -4396,45 +4402,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>429</v>
+        <v>374</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="K58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.627039627039627</v>
+        <v>0.6336898395721925</v>
       </c>
     </row>
     <row r="59">
@@ -4460,7 +4466,7 @@
         <v>622</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G59" s="9" t="n">
         <v>5</v>
@@ -4469,19 +4475,19 @@
         <v>0</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6270096463022508</v>
+        <v>0.6334405144694534</v>
       </c>
     </row>
     <row r="60">
@@ -4490,45 +4496,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>452</v>
+        <v>409</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="G60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.6238938053097345</v>
+        <v>0.6332518337408313</v>
       </c>
     </row>
     <row r="61">
@@ -4537,45 +4543,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.6213151927437641</v>
+        <v>0.6317016317016317</v>
       </c>
     </row>
     <row r="62">
@@ -4601,28 +4607,28 @@
         <v>498</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G62" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6164658634538153</v>
+        <v>0.6244979919678715</v>
       </c>
     </row>
     <row r="63">
@@ -4631,7 +4637,7 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -4645,31 +4651,31 @@
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.6118598382749326</v>
+        <v>0.6239316239316239</v>
       </c>
     </row>
     <row r="64">
@@ -4678,45 +4684,45 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6238938053097345</v>
       </c>
     </row>
     <row r="65">
@@ -4725,45 +4731,45 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>256</v>
+        <v>312</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.61</v>
+        <v>0.6144814090019569</v>
       </c>
     </row>
     <row r="66">
@@ -4789,7 +4795,7 @@
         <v>428</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>0</v>
@@ -4801,16 +4807,16 @@
         <v>0</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K66" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.6098130841121495</v>
+        <v>0.6121495327102804</v>
       </c>
     </row>
     <row r="67">
@@ -4819,45 +4825,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>413</v>
+        <v>450</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>273</v>
+      </c>
+      <c r="K67" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J67" s="9" t="n">
-        <v>245</v>
-      </c>
-      <c r="K67" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L67" s="9" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.6053268765133172</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="68">
@@ -4866,45 +4872,45 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="9" t="n">
         <v>305</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.6039603960396039</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="69">
@@ -4913,45 +4919,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>347</v>
+        <v>414</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" s="9" t="n">
         <v>6</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.6023054755043228</v>
+        <v>0.6086956521739131</v>
       </c>
     </row>
     <row r="70">
@@ -4960,45 +4966,45 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>463</v>
+        <v>399</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>187</v>
+        <v>115</v>
       </c>
       <c r="G70" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="H70" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H70" s="9" t="n">
-        <v>12</v>
-      </c>
       <c r="I70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>263</v>
+        <v>238</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>0.5939524838012959</v>
+        <v>0.6015037593984962</v>
       </c>
     </row>
     <row r="71">
@@ -5024,28 +5030,28 @@
         <v>400</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>0.5925</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="72">
@@ -5054,45 +5060,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I72" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="J72" s="9" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M72" s="11" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.5991379310344828</v>
       </c>
     </row>
     <row r="73">
@@ -5115,10 +5121,10 @@
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>0</v>
@@ -5130,16 +5136,16 @@
         <v>4</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="M73" s="11" t="n">
-        <v>0.5894736842105263</v>
+        <v>0.5984251968503937</v>
       </c>
     </row>
     <row r="74">
@@ -5148,45 +5154,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>557</v>
+        <v>471</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>328</v>
+        <v>273</v>
       </c>
       <c r="K74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>328</v>
+        <v>281</v>
       </c>
       <c r="M74" s="11" t="n">
-        <v>0.5888689407540395</v>
+        <v>0.5966029723991507</v>
       </c>
     </row>
     <row r="75">
@@ -5195,45 +5201,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>361</v>
+        <v>557</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>149</v>
+        <v>201</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>201</v>
+        <v>332</v>
       </c>
       <c r="K75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>212</v>
+        <v>332</v>
       </c>
       <c r="M75" s="11" t="n">
-        <v>0.5872576177285319</v>
+        <v>0.5960502692998204</v>
       </c>
     </row>
     <row r="76">
@@ -5259,28 +5265,28 @@
         <v>426</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="K76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="M76" s="11" t="n">
-        <v>0.5845070422535211</v>
+        <v>0.5938967136150235</v>
       </c>
     </row>
     <row r="77">
@@ -5289,45 +5295,45 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>533</v>
+        <v>361</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>222</v>
+        <v>149</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>291</v>
+        <v>202</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>311</v>
-      </c>
-      <c r="M77" s="12" t="n">
-        <v>0.5834896810506567</v>
+        <v>212</v>
+      </c>
+      <c r="M77" s="11" t="n">
+        <v>0.5872576177285319</v>
       </c>
     </row>
     <row r="78">
@@ -5336,45 +5342,45 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>463</v>
+        <v>533</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>249</v>
+        <v>308</v>
       </c>
       <c r="K78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>268</v>
-      </c>
-      <c r="M78" s="12" t="n">
-        <v>0.5788336933045356</v>
+        <v>313</v>
+      </c>
+      <c r="M78" s="11" t="n">
+        <v>0.5872420262664165</v>
       </c>
     </row>
     <row r="79">
@@ -5383,7 +5389,7 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
@@ -5397,31 +5403,31 @@
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H79" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="K79" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I79" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="9" t="n">
-        <v>260</v>
-      </c>
-      <c r="K79" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L79" s="9" t="n">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.5745614035087719</v>
+        <v>0.5839080459770115</v>
       </c>
     </row>
     <row r="80">
@@ -5430,45 +5436,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>498</v>
+        <v>463</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>7</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>286</v>
+        <v>249</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.5742971887550201</v>
+        <v>0.5831533477321814</v>
       </c>
     </row>
     <row r="81">
@@ -5477,7 +5483,7 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -5491,31 +5497,31 @@
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>433</v>
+        <v>460</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.5727482678983834</v>
+        <v>0.5804347826086956</v>
       </c>
     </row>
     <row r="82">
@@ -5524,45 +5530,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>445</v>
+        <v>400</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.5685393258426966</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="83">
@@ -5571,45 +5577,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F83" s="9" t="n">
         <v>204</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.5668662674650699</v>
+        <v>0.5791583166332666</v>
       </c>
     </row>
     <row r="84">
@@ -5618,45 +5624,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>394</v>
+        <v>504</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>127</v>
+        <v>215</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>219</v>
+        <v>286</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>223</v>
+        <v>289</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.565989847715736</v>
+        <v>0.5734126984126984</v>
       </c>
     </row>
     <row r="85">
@@ -5665,45 +5671,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>364</v>
+        <v>466</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>205</v>
+        <v>267</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.5631868131868132</v>
+        <v>0.572961373390558</v>
       </c>
     </row>
     <row r="86">
@@ -5712,45 +5718,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>466</v>
+        <v>364</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="G86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H86" s="9" t="n">
-        <v>23</v>
-      </c>
       <c r="I86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>262</v>
+        <v>208</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.5622317596566524</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="87">
@@ -5759,7 +5765,7 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
@@ -5773,31 +5779,31 @@
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>397</v>
+        <v>440</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>202</v>
+        <v>247</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.5591939546599496</v>
+        <v>0.5704545454545454</v>
       </c>
     </row>
     <row r="88">
@@ -5806,45 +5812,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>496</v>
+        <v>470</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="K88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.5584677419354839</v>
+        <v>0.5680851063829787</v>
       </c>
     </row>
     <row r="89">
@@ -5853,7 +5859,7 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
@@ -5867,31 +5873,31 @@
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.5574468085106383</v>
+        <v>0.5672645739910314</v>
       </c>
     </row>
     <row r="90">
@@ -5900,45 +5906,45 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="G90" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="H90" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="H90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="J90" s="9" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.5528455284552846</v>
+        <v>0.5668662674650699</v>
       </c>
     </row>
     <row r="91">
@@ -5947,45 +5953,45 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>440</v>
+        <v>492</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.55</v>
+        <v>0.5650406504065041</v>
       </c>
     </row>
     <row r="92">
@@ -6008,31 +6014,31 @@
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="K92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.559748427672956</v>
       </c>
     </row>
     <row r="93">
@@ -6041,45 +6047,45 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.5413043478260869</v>
+        <v>0.5536480686695279</v>
       </c>
     </row>
     <row r="94">
@@ -6088,45 +6094,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>532</v>
+        <v>407</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>282</v>
+        <v>213</v>
       </c>
       <c r="K94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>287</v>
+        <v>225</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.5394736842105263</v>
+        <v>0.5528255528255528</v>
       </c>
     </row>
     <row r="95">
@@ -6135,7 +6141,7 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
@@ -6149,31 +6155,31 @@
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>412</v>
+        <v>544</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>20</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>216</v>
+        <v>298</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>222</v>
+        <v>300</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.5388349514563107</v>
+        <v>0.5514705882352942</v>
       </c>
     </row>
     <row r="96">
@@ -6182,45 +6188,45 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>465</v>
+        <v>426</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.5376344086021505</v>
+        <v>0.5492957746478874</v>
       </c>
     </row>
     <row r="97">
@@ -6229,24 +6235,24 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>1</v>
@@ -6255,19 +6261,19 @@
         <v>0</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.5338345864661654</v>
+        <v>0.547945205479452</v>
       </c>
     </row>
     <row r="98">
@@ -6276,45 +6282,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>437</v>
+        <v>399</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.5331807780320366</v>
+        <v>0.5463659147869674</v>
       </c>
     </row>
     <row r="99">
@@ -6323,45 +6329,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>426</v>
+        <v>460</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.5328638497652582</v>
+        <v>0.5456521739130434</v>
       </c>
     </row>
     <row r="100">
@@ -6370,45 +6376,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="G100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>223</v>
+      </c>
+      <c r="K100" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="9" t="n">
-        <v>214</v>
-      </c>
-      <c r="K100" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L100" s="9" t="n">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.5323383084577115</v>
+        <v>0.539906103286385</v>
       </c>
     </row>
     <row r="101">
@@ -6417,45 +6423,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>454</v>
+        <v>412</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>214</v>
+        <v>170</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.5286343612334802</v>
+        <v>0.5388349514563107</v>
       </c>
     </row>
     <row r="102">
@@ -6464,45 +6470,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>451</v>
+        <v>511</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>208</v>
+        <v>269</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.5254988913525499</v>
+        <v>0.5362035225048923</v>
       </c>
     </row>
     <row r="103">
@@ -6511,45 +6517,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>470</v>
+        <v>394</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>217</v>
+        <v>180</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="K103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.5212765957446809</v>
+        <v>0.5355329949238579</v>
       </c>
     </row>
     <row r="104">
@@ -6558,45 +6564,45 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>438</v>
+        <v>368</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="K104" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.5205479452054794</v>
+        <v>0.5353260869565217</v>
       </c>
     </row>
     <row r="105">
@@ -6605,45 +6611,45 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Ivan Christian Sasenga</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>498</v>
+        <v>454</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="K105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.5200803212851406</v>
+        <v>0.5330396475770925</v>
       </c>
     </row>
     <row r="106">
@@ -6652,45 +6658,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>364</v>
+        <v>402</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5323383084577115</v>
       </c>
     </row>
     <row r="107">
@@ -6699,24 +6705,24 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="G107" s="9" t="n">
         <v>0</v>
@@ -6728,16 +6734,16 @@
         <v>0</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="K107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.518957345971564</v>
+        <v>0.5286343612334802</v>
       </c>
     </row>
     <row r="108">
@@ -6746,45 +6752,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>511</v>
+        <v>470</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I108" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.5185909980430529</v>
+        <v>0.5234042553191489</v>
       </c>
     </row>
     <row r="109">
@@ -6793,45 +6799,45 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Regina Kesya Dumumpe</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.5179856115107914</v>
+        <v>0.5205479452054794</v>
       </c>
     </row>
     <row r="110">
@@ -6840,45 +6846,45 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Regina Kesya Dumumpe</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>323</v>
+        <v>419</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>114</v>
+        <v>201</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>167</v>
+        <v>218</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.5170278637770898</v>
+        <v>0.5202863961813843</v>
       </c>
     </row>
     <row r="111">
@@ -6887,45 +6893,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Ivan Christian Sasenga</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>401</v>
+        <v>498</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>182</v>
+        <v>239</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>199</v>
+        <v>248</v>
       </c>
       <c r="K111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.516209476309227</v>
+        <v>0.5200803212851406</v>
       </c>
     </row>
     <row r="112">
@@ -6934,45 +6940,45 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.5122549019607843</v>
+        <v>0.5180722891566265</v>
       </c>
     </row>
     <row r="113">
@@ -6981,45 +6987,45 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>414</v>
+        <v>323</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="K113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>211</v>
+        <v>167</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.5096618357487923</v>
+        <v>0.5170278637770898</v>
       </c>
     </row>
     <row r="114">
@@ -7028,45 +7034,45 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>474</v>
+        <v>408</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.5063291139240507</v>
+        <v>0.5122549019607843</v>
       </c>
     </row>
     <row r="115">
@@ -7075,7 +7081,7 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
@@ -7089,31 +7095,31 @@
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>389</v>
+        <v>450</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>186</v>
+        <v>224</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.5038560411311054</v>
+        <v>0.5022222222222222</v>
       </c>
     </row>
     <row r="116">
@@ -7122,45 +7128,45 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="K116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.5022222222222222</v>
+        <v>0.5011764705882353</v>
       </c>
     </row>
     <row r="117">
@@ -7169,42 +7175,42 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>346</v>
+        <v>404</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="M117" s="12" t="n">
         <v>0.5</v>
@@ -7216,45 +7222,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>399</v>
+        <v>474</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I118" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>194</v>
+      </c>
+      <c r="K118" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J118" s="9" t="n">
-        <v>197</v>
-      </c>
-      <c r="K118" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L118" s="9" t="n">
-        <v>198</v>
+        <v>237</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.4962406015037594</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="119">
@@ -7263,45 +7269,45 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="G119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H119" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I119" s="9" t="n">
-        <v>11</v>
-      </c>
       <c r="J119" s="9" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="K119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.4950248756218906</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="120">
@@ -7310,45 +7316,45 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>418</v>
+        <v>505</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="G120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>206</v>
+        <v>252</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.4928229665071771</v>
+        <v>0.499009900990099</v>
       </c>
     </row>
     <row r="121">
@@ -7357,45 +7363,45 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0.4847058823529412</v>
+        <v>0.4987468671679198</v>
       </c>
     </row>
     <row r="122">
@@ -7404,45 +7410,45 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>503</v>
+        <v>418</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>260</v>
+        <v>212</v>
       </c>
       <c r="G122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>243</v>
+        <v>206</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.4831013916500994</v>
+        <v>0.4928229665071771</v>
       </c>
     </row>
     <row r="123">
@@ -7451,7 +7457,7 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
@@ -7465,31 +7471,31 @@
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="F123" s="9" t="n">
+        <v>221</v>
+      </c>
+      <c r="G123" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H123" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>202</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="9" t="n">
         <v>213</v>
       </c>
-      <c r="G123" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H123" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="I123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="9" t="n">
-        <v>173</v>
-      </c>
-      <c r="K123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="9" t="n">
-        <v>200</v>
-      </c>
       <c r="M123" s="12" t="n">
-        <v>0.4830917874396136</v>
+        <v>0.4863013698630138</v>
       </c>
     </row>
     <row r="124">
@@ -7498,45 +7504,45 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>437</v>
+        <v>414</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="G124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="K124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.482837528604119</v>
+        <v>0.4830917874396136</v>
       </c>
     </row>
     <row r="125">
@@ -7545,45 +7551,45 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.4794520547945205</v>
+        <v>0.482837528604119</v>
       </c>
     </row>
     <row r="126">
@@ -7592,45 +7598,45 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>181</v>
+        <v>137</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.4629156010230179</v>
+        <v>0.4806763285024155</v>
       </c>
     </row>
     <row r="127">
@@ -7639,7 +7645,7 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -7653,31 +7659,31 @@
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>407</v>
+        <v>448</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.4619164619164619</v>
+        <v>0.4776785714285715</v>
       </c>
     </row>
     <row r="128">
@@ -7686,45 +7692,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.4608501118568233</v>
+        <v>0.4716553287981859</v>
       </c>
     </row>
     <row r="129">
@@ -7750,28 +7756,28 @@
         <v>437</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I129" s="9" t="n">
         <v>19</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.4599542334096111</v>
+        <v>0.4668192219679634</v>
       </c>
     </row>
     <row r="130">
@@ -7780,7 +7786,7 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
@@ -7794,31 +7800,31 @@
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>441</v>
+        <v>391</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="K130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4557823129251701</v>
+        <v>0.4629156010230179</v>
       </c>
     </row>
     <row r="131">
@@ -7827,45 +7833,45 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="G131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="K131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.4514563106796117</v>
+        <v>0.4619164619164619</v>
       </c>
     </row>
     <row r="132">
@@ -7874,45 +7880,45 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>459</v>
+        <v>415</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.4422657952069716</v>
+        <v>0.4506024096385542</v>
       </c>
     </row>
     <row r="133">
@@ -7921,45 +7927,45 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>512</v>
+        <v>418</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.4375</v>
+        <v>0.4473684210526316</v>
       </c>
     </row>
     <row r="134">
@@ -7968,45 +7974,45 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>415</v>
+        <v>513</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>216</v>
+        <v>279</v>
       </c>
       <c r="G134" s="9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H134" s="9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>149</v>
+        <v>202</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.436144578313253</v>
+        <v>0.4463937621832358</v>
       </c>
     </row>
     <row r="135">
@@ -8015,45 +8021,45 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Dince Lahaube</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>417</v>
+        <v>332</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>234</v>
+        <v>8</v>
       </c>
       <c r="G135" s="9" t="n">
+        <v>177</v>
+      </c>
+      <c r="H135" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H135" s="9" t="n">
-        <v>8</v>
-      </c>
       <c r="I135" s="9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.434052757793765</v>
+        <v>0.4427710843373494</v>
       </c>
     </row>
     <row r="136">
@@ -8062,45 +8068,45 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Dince Lahaube</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E136" s="9" t="n">
-        <v>332</v>
+        <v>459</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>8</v>
+        <v>227</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>184</v>
+        <v>29</v>
       </c>
       <c r="H136" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I136" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J136" s="9" t="n">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="K136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>140</v>
+        <v>203</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.4216867469879519</v>
+        <v>0.4422657952069716</v>
       </c>
     </row>
   </sheetData>
@@ -8143,7 +8149,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 19 Juli 2026</t>
+          <t>Hari/Tanggal : 20 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8160,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 06.29 WITA</t>
+          <t>Pukul        : 05.55 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8262,31 +8268,31 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2869</v>
+        <v>2872</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2312</v>
+        <v>2426</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2319</v>
+        <v>2433</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.8082955733705124</v>
+        <v>0.8471448467966574</v>
       </c>
     </row>
     <row r="8">
@@ -8309,31 +8315,31 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1459</v>
+        <v>1526</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>6</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1474</v>
+        <v>1542</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.7275419545903258</v>
+        <v>0.7603550295857988</v>
       </c>
     </row>
     <row r="9">
@@ -8356,31 +8362,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2784</v>
+        <v>2798</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>752</v>
+        <v>709</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2012</v>
+        <v>2073</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2022</v>
+        <v>2084</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.7262931034482759</v>
+        <v>0.74481772694782</v>
       </c>
     </row>
     <row r="10">
@@ -8403,31 +8409,31 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2884</v>
+        <v>2887</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2003</v>
+        <v>2037</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2076</v>
+        <v>2124</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7198335644937586</v>
+        <v>0.735711811569103</v>
       </c>
     </row>
     <row r="11">
@@ -8450,31 +8456,31 @@
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2461</v>
+        <v>2482</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>727</v>
+        <v>688</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1696</v>
+        <v>1780</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1697</v>
+        <v>1781</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.6895570906135717</v>
+        <v>0.7175664786462531</v>
       </c>
     </row>
     <row r="12">
@@ -8497,31 +8503,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2827</v>
+        <v>2833</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>833</v>
+        <v>812</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1892</v>
+        <v>1985</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>1909</v>
+        <v>2010</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.6752741422002121</v>
+        <v>0.7094952347334982</v>
       </c>
     </row>
     <row r="13">
@@ -8530,45 +8536,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Manganitu, Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Erike, Mega</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2381</v>
+        <v>2103</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>903</v>
+        <v>704</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1438</v>
+        <v>1358</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1455</v>
+        <v>1360</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6110877782444352</v>
+        <v>0.6466951973371374</v>
       </c>
     </row>
     <row r="14">
@@ -8577,45 +8583,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2103</v>
+        <v>2758</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>714</v>
+        <v>949</v>
       </c>
       <c r="G14" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="I14" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="9" t="n">
-        <v>102</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="J14" s="9" t="n">
-        <v>1278</v>
+        <v>1711</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1280</v>
+        <v>1722</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6086543033761294</v>
+        <v>0.6243654822335025</v>
       </c>
     </row>
     <row r="15">
@@ -8624,45 +8630,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Kepulauan Marore, Tabukan Utara</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Hendri, Michael</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2148</v>
+        <v>2892</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>821</v>
+        <v>1040</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1278</v>
+        <v>1796</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1285</v>
+        <v>1803</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.5982309124767226</v>
+        <v>0.6234439834024896</v>
       </c>
     </row>
     <row r="16">
@@ -8671,45 +8677,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu, Tamako</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike, Mega</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2747</v>
+        <v>2385</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>979</v>
+        <v>879</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1633</v>
+        <v>1467</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1642</v>
+        <v>1475</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.5977429923552967</v>
+        <v>0.6184486373165619</v>
       </c>
     </row>
     <row r="17">
@@ -8718,45 +8724,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore, Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Hendri, Michael</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2881</v>
+        <v>2156</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>1062</v>
+        <v>802</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1701</v>
+        <v>1321</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1704</v>
+        <v>1326</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.591461298160361</v>
+        <v>0.6150278293135436</v>
       </c>
     </row>
     <row r="18">
@@ -8782,28 +8788,28 @@
         <v>2878</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1640</v>
+        <v>1697</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1663</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>0.5778318276580959</v>
+        <v>1726</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>0.5997220291869354</v>
       </c>
     </row>
     <row r="19">
@@ -8826,31 +8832,31 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2796</v>
+        <v>2809</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1176</v>
+        <v>1149</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1559</v>
+        <v>1636</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1578</v>
-      </c>
-      <c r="M19" s="12" t="n">
-        <v>0.5643776824034334</v>
+        <v>1652</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>0.5881096475614097</v>
       </c>
     </row>
     <row r="20">
@@ -8873,13 +8879,13 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2657</v>
+        <v>2661</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1177</v>
+        <v>1158</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>0</v>
@@ -8888,16 +8894,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1450</v>
+        <v>1477</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1451</v>
+        <v>1478</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.5461046292811441</v>
+        <v>0.5554302893649005</v>
       </c>
     </row>
     <row r="21">
@@ -8906,45 +8912,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2437</v>
+        <v>2694</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>928</v>
+        <v>1152</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1317</v>
+        <v>1476</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1327</v>
+        <v>1479</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.5445219532211736</v>
+        <v>0.5489977728285078</v>
       </c>
     </row>
     <row r="22">
@@ -8953,45 +8959,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2681</v>
+        <v>2443</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>1164</v>
+        <v>910</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>17</v>
+        <v>171</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1444</v>
+        <v>1321</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1448</v>
+        <v>1332</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.5400969787392764</v>
+        <v>0.5452312730249693</v>
       </c>
     </row>
     <row r="23">
@@ -9014,31 +9020,31 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2299</v>
+        <v>2302</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>982</v>
+        <v>968</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1195</v>
+        <v>1221</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1220</v>
+        <v>1245</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.5306655067420618</v>
+        <v>0.5408340573414422</v>
       </c>
     </row>
     <row r="24">
@@ -9047,45 +9053,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Kezia Maralending</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2711</v>
+        <v>1422</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1236</v>
+        <v>406</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>58</v>
+        <v>265</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1389</v>
+        <v>745</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>1395</v>
+        <v>747</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5145702692733308</v>
+        <v>0.5253164556962026</v>
       </c>
     </row>
     <row r="25">
@@ -9094,45 +9100,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Kezia Maralending</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>1413</v>
+        <v>2534</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>422</v>
+        <v>1183</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>274</v>
+        <v>3</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>698</v>
+        <v>1315</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>702</v>
+        <v>1321</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.4968152866242038</v>
+        <v>0.521310181531176</v>
       </c>
     </row>
     <row r="26">
@@ -9141,45 +9147,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2527</v>
+        <v>2711</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1196</v>
+        <v>1230</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1248</v>
+        <v>1389</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1253</v>
+        <v>1394</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.4958448753462604</v>
+        <v>0.5142014016967908</v>
       </c>
     </row>
     <row r="27">
@@ -9188,7 +9194,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Olfira Sicilia Budiman</t>
+          <t>B. Lenskar Diamanis</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -9202,31 +9208,31 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2076</v>
+        <v>2063</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="G27" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="H27" s="9" t="n">
-        <v>27</v>
-      </c>
       <c r="I27" s="9" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>938</v>
+        <v>987</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.4869942196531792</v>
+        <v>0.4910324769752787</v>
       </c>
     </row>
     <row r="28">
@@ -9235,7 +9241,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>B. Lenskar Diamanis</t>
+          <t>Olfira Sicilia Budiman</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -9249,31 +9255,31 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2061</v>
+        <v>2081</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1027</v>
+        <v>1007</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>924</v>
+        <v>958</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>951</v>
+        <v>1014</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.4614264919941775</v>
+        <v>0.4872657376261413</v>
       </c>
     </row>
     <row r="29">
@@ -9292,35 +9298,35 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2402</v>
+        <v>2407</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1122</v>
+        <v>1104</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1066</v>
+        <v>1133</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1108</v>
+        <v>1169</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.4612822647793505</v>
+        <v>0.4856668051516411</v>
       </c>
     </row>
   </sheetData>
@@ -9354,7 +9360,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 19 Juli 2026</t>
+          <t>Hari/Tanggal : 20 Juli 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9371,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 06.29 WITA</t>
+          <t>Pukul        : 05.55 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9418,7 +9424,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.7558441558441558</v>
+        <v>0.7757575757575758</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9436,7 +9442,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7424770351599619</v>
+        <v>0.7578051087984864</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9454,7 +9460,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7256977863330125</v>
+        <v>0.7347853939782191</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9472,7 +9478,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7062242673770889</v>
+        <v>0.7104817235536189</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -9490,7 +9496,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.6932795991722035</v>
+        <v>0.7058632274845561</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9544,7 +9550,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.6005314437555359</v>
+        <v>0.6165347405452947</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
@@ -9561,8 +9567,8 @@
           <t>Kendahe</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
-        <v>0.5779685264663805</v>
+      <c r="C15" s="11" t="n">
+        <v>0.5898896404414382</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -9580,7 +9586,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.5733050028974309</v>
+        <v>0.5789575289575289</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9598,7 +9604,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.5432367675887606</v>
+        <v>0.5510425716768028</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
@@ -9616,7 +9622,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.5383277425767176</v>
+        <v>0.545375650880238</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -9630,15 +9636,15 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.5228975853455454</v>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.5300582847626978</v>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9648,15 +9654,15 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.5216013344453712</v>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.52970502700457</v>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9670,7 +9676,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.5074309978768577</v>
+        <v>0.5281293952180028</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 20 Juli 2026</t>
+          <t>Hari/Tanggal : 21 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -616,32 +616,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 05.55 WITA</t>
+          <t>Pukul        : 10.25 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-35):</t>
+          <t>Target Hari Ini (H-36):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>58.45%</t>
+          <t>60.12%</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Hijau &gt;= 58.45%</t>
+          <t>Hijau &gt;= 60.12%</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Kuning 29.22% - 58.45%</t>
+          <t>Kuning 30.06% - 60.12%</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Merah &lt; 29.22%</t>
+          <t>Merah &lt; 30.06%</t>
         </is>
       </c>
     </row>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4131</v>
+        <v>4143</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1162</v>
+        <v>1116</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
@@ -770,7 +770,7 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
@@ -784,28 +784,28 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2884</v>
+        <v>2907</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
         <v/>
       </c>
       <c r="N7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O7" s="10">
         <f>N7/B7</f>
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>2935</v>
+        <v>2993</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -819,27 +819,27 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1422</v>
+        <v>1433</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>406</v>
+        <v>356</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>745</v>
+        <v>766</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -867,14 +867,14 @@
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>751</v>
+        <v>783</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -888,62 +888,62 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6244</v>
+        <v>6290</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1583</v>
+        <v>1451</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>63</v>
+        <v>190</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4413</v>
+        <v>4451</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
         <v/>
       </c>
       <c r="N9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="10">
         <f>N9/B9</f>
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4588</v>
+        <v>4751</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3171</v>
+        <v>3185</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>768</v>
+        <v>725</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -977,7 +977,7 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
@@ -991,28 +991,28 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2380</v>
+        <v>2383</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
         <v/>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10" s="10">
         <f>N10/B10</f>
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2403</v>
+        <v>2460</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
@@ -1046,7 +1046,7 @@
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
@@ -1060,7 +1060,7 @@
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="M11" s="10">
         <f>L11/B11</f>
@@ -1074,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1095,34 +1095,34 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>23</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E12" s="10">
         <f>D12/B12</f>
         <v/>
       </c>
       <c r="F12" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="10">
         <f>F12/B12</f>
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
         <v/>
       </c>
       <c r="J12" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" s="10">
         <f>J12/B12</f>
@@ -1143,14 +1143,14 @@
         <v/>
       </c>
       <c r="P12" s="9" t="n">
-        <v>634</v>
+        <v>647</v>
       </c>
       <c r="Q12" s="11">
         <f>P12/B12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1164,41 +1164,41 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4604</v>
+        <v>4624</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2034</v>
+        <v>1999</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2329</v>
+        <v>2414</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1212,14 +1212,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2537</v>
+        <v>2588</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1233,27 +1233,27 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6005</v>
+        <v>6028</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2798</v>
+        <v>2770</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
@@ -1267,28 +1267,28 @@
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3021</v>
+        <v>3051</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
         <v/>
       </c>
       <c r="N14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="10">
         <f>N14/B14</f>
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3183</v>
+        <v>3230</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1302,27 +1302,27 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8066</v>
+        <v>8079</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3540</v>
+        <v>3499</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
@@ -1336,7 +1336,7 @@
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4342</v>
+        <v>4406</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1350,14 +1350,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4399</v>
+        <v>4469</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1371,41 +1371,41 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5180</v>
+        <v>5204</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2067</v>
+        <v>2023</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>2918</v>
+        <v>2985</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1419,14 +1419,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>2999</v>
+        <v>3062</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1440,62 +1440,62 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2407</v>
+        <v>2413</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1104</v>
+        <v>1077</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1133</v>
+        <v>1186</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
         <v/>
       </c>
       <c r="N17" s="9" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O17" s="10">
         <f>N17/B17</f>
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1275</v>
+        <v>1310</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1509,41 +1509,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9227</v>
+        <v>9298</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2628</v>
+        <v>2481</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6435</v>
+        <v>6675</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1557,14 +1557,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>6513</v>
+        <v>6746</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>148</v>
+        <v>233</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1598,21 +1598,21 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
         <v/>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="10">
         <f>J19/B19</f>
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>887</v>
+        <v>897</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1626,14 +1626,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>896</v>
+        <v>907</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1647,20 +1647,20 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>8</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E20" s="10">
         <f>D20/B20</f>
         <v/>
       </c>
       <c r="F20" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G20" s="10">
         <f>F20/B20</f>
@@ -1674,14 +1674,14 @@
         <v/>
       </c>
       <c r="J20" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K20" s="10">
         <f>J20/B20</f>
         <v/>
       </c>
       <c r="L20" s="9" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="M20" s="10">
         <f>L20/B20</f>
@@ -1695,14 +1695,14 @@
         <v/>
       </c>
       <c r="P20" s="9" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="Q20" s="11">
         <f>P20/B20</f>
         <v/>
       </c>
       <c r="R20" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S20" s="10">
         <f>R20/B20</f>
@@ -1716,13 +1716,13 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2809</v>
+        <v>2825</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1149</v>
+        <v>1125</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
@@ -1736,21 +1736,21 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1764,14 +1764,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1657</v>
-      </c>
-      <c r="Q21" s="11">
+        <v>1697</v>
+      </c>
+      <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1900,7 +1900,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 20 Juli 2026</t>
+          <t>Hari/Tanggal : 21 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1917,17 +1917,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 05.55 WITA</t>
+          <t>Pukul        : 10.25 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-35):</t>
+          <t>Target Hari Ini (H-36):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>58.45%</t>
+          <t>60.12%</t>
         </is>
       </c>
     </row>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>1</v>
@@ -2081,16 +2081,16 @@
         <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>6</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.9568345323741008</v>
+        <v>0.964200477326969</v>
       </c>
     </row>
     <row r="9">
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
@@ -2128,16 +2128,16 @@
         <v>0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.9402173913043478</v>
+        <v>0.956989247311828</v>
       </c>
     </row>
     <row r="10">
@@ -2146,45 +2146,45 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Ayu Lestari Areros</t>
+          <t>Merry Christiani Lano</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>308</v>
+        <v>520</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>279</v>
+        <v>465</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>281</v>
+        <v>484</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.9123376623376623</v>
+        <v>0.9307692307692308</v>
       </c>
     </row>
     <row r="11">
@@ -2193,45 +2193,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Merry Christiani Lano</t>
+          <t>Ayu Lestari Areros</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>516</v>
+        <v>309</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>443</v>
+        <v>279</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>458</v>
+        <v>283</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.8875968992248062</v>
+        <v>0.9158576051779935</v>
       </c>
     </row>
     <row r="12">
@@ -2257,28 +2257,28 @@
         <v>364</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.8763736263736264</v>
+        <v>0.8818681318681318</v>
       </c>
     </row>
     <row r="13">
@@ -2313,10 +2313,10 @@
         <v>5</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>0</v>
@@ -2348,16 +2348,16 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>0</v>
@@ -2369,10 +2369,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.8496042216358839</v>
+        <v>0.8713910761154857</v>
       </c>
     </row>
     <row r="15">
@@ -2445,28 +2445,28 @@
         <v>426</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.8215962441314554</v>
+        <v>0.8380281690140845</v>
       </c>
     </row>
     <row r="17">
@@ -2489,31 +2489,31 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I17" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8110831234256927</v>
+        <v>0.8304239401496259</v>
       </c>
     </row>
     <row r="18">
@@ -2536,16 +2536,16 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I18" s="9" t="n">
         <v>0</v>
@@ -2557,10 +2557,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8032786885245902</v>
+        <v>0.8255578093306287</v>
       </c>
     </row>
     <row r="19">
@@ -2569,45 +2569,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>421</v>
+        <v>384</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>335</v>
+        <v>314</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.7957244655581949</v>
+        <v>0.8177083333333335</v>
       </c>
     </row>
     <row r="20">
@@ -2630,16 +2630,16 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I20" s="9" t="n">
         <v>0</v>
@@ -2651,10 +2651,10 @@
         <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.8155136268343816</v>
       </c>
     </row>
     <row r="21">
@@ -2663,45 +2663,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.7931873479318735</v>
+        <v>0.8085106382978722</v>
       </c>
     </row>
     <row r="22">
@@ -2710,45 +2710,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>376</v>
+        <v>431</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.7898936170212765</v>
+        <v>0.7981438515081206</v>
       </c>
     </row>
     <row r="23">
@@ -2757,27 +2757,27 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H23" s="9" t="n">
         <v>0</v>
@@ -2786,16 +2786,16 @@
         <v>0</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.7875751503006012</v>
+        <v>0.795959595959596</v>
       </c>
     </row>
     <row r="24">
@@ -2804,45 +2804,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>495</v>
+        <v>389</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>384</v>
+        <v>299</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>384</v>
+        <v>309</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.7757575757575758</v>
+        <v>0.7943444730077122</v>
       </c>
     </row>
     <row r="25">
@@ -2851,45 +2851,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.7744186046511627</v>
+        <v>0.7931873479318735</v>
       </c>
     </row>
     <row r="26">
@@ -2898,45 +2898,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>388</v>
+        <v>499</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>297</v>
+        <v>393</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>300</v>
+        <v>395</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.7731958762886599</v>
+        <v>0.7915831663326653</v>
       </c>
     </row>
     <row r="27">
@@ -2959,31 +2959,31 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.7690839694656488</v>
+        <v>0.7867924528301887</v>
       </c>
     </row>
     <row r="28">
@@ -2992,45 +2992,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Sheryl Jessica Tatontos</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>484</v>
+        <v>384</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>321</v>
+        <v>280</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>359</v>
+        <v>296</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>0.7417355371900827</v>
+        <v>0.7708333333333335</v>
       </c>
     </row>
     <row r="29">
@@ -3039,45 +3039,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Sheryl Jessica Tatontos</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>417</v>
+        <v>490</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>308</v>
+        <v>375</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.7386091127098321</v>
+        <v>0.7653061224489796</v>
       </c>
     </row>
     <row r="30">
@@ -3086,45 +3086,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7356020942408377</v>
+        <v>0.7470449172576832</v>
       </c>
     </row>
     <row r="31">
@@ -3150,13 +3150,13 @@
         <v>414</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I31" s="9" t="n">
         <v>0</v>
@@ -3168,10 +3168,10 @@
         <v>1</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7294685990338166</v>
+        <v>0.7463768115942028</v>
       </c>
     </row>
     <row r="32">
@@ -3197,16 +3197,16 @@
         <v>422</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="9" t="n">
         <v>306</v>
@@ -3215,10 +3215,10 @@
         <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.7274881516587678</v>
+        <v>0.7440758293838863</v>
       </c>
     </row>
     <row r="33">
@@ -3241,31 +3241,31 @@
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.7248995983935742</v>
+        <v>0.7390438247011953</v>
       </c>
     </row>
     <row r="34">
@@ -3288,16 +3288,16 @@
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I34" s="9" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.7228260869565217</v>
+        <v>0.7302158273381295</v>
       </c>
     </row>
     <row r="35">
@@ -3321,45 +3321,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>535</v>
+        <v>512</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.7177570093457943</v>
+        <v>0.724609375</v>
       </c>
     </row>
     <row r="36">
@@ -3368,45 +3368,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>499</v>
+        <v>539</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>358</v>
+        <v>389</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.717434869739479</v>
+        <v>0.7217068645640075</v>
       </c>
     </row>
     <row r="37">
@@ -3432,13 +3432,13 @@
         <v>402</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I37" s="9" t="n">
         <v>0</v>
@@ -3450,10 +3450,10 @@
         <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7139303482587064</v>
+        <v>0.7213930348258707</v>
       </c>
     </row>
     <row r="38">
@@ -3462,45 +3462,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>354</v>
+      </c>
+      <c r="K38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="9" t="n">
+      <c r="L38" s="9" t="n">
         <v>361</v>
       </c>
-      <c r="K38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>362</v>
-      </c>
       <c r="M38" s="11" t="n">
-        <v>0.7111984282907662</v>
+        <v>0.720558882235529</v>
       </c>
     </row>
     <row r="39">
@@ -3526,28 +3526,28 @@
         <v>347</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7089337175792507</v>
+        <v>0.7175792507204612</v>
       </c>
     </row>
     <row r="40">
@@ -3570,10 +3570,10 @@
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>0</v>
@@ -3585,16 +3585,16 @@
         <v>0</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.697986577181208</v>
+        <v>0.7130242825607064</v>
       </c>
     </row>
     <row r="41">
@@ -3617,31 +3617,31 @@
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.6858513189448441</v>
+        <v>0.7095238095238094</v>
       </c>
     </row>
     <row r="42">
@@ -3650,45 +3650,45 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>389</v>
+        <v>503</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>223</v>
+        <v>335</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>266</v>
+        <v>354</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.6838046272493572</v>
+        <v>0.7037773359840955</v>
       </c>
     </row>
     <row r="43">
@@ -3697,45 +3697,45 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>501</v>
+        <v>381</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>341</v>
+        <v>253</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>342</v>
+        <v>267</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.6826347305389223</v>
+        <v>0.7007874015748031</v>
       </c>
     </row>
     <row r="44">
@@ -3744,45 +3744,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H44" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>346</v>
+      </c>
+      <c r="K44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>353</v>
-      </c>
-      <c r="K44" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" s="9" t="n">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.6924603174603174</v>
       </c>
     </row>
     <row r="45">
@@ -3791,45 +3791,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I45" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.6764705882352942</v>
+        <v>0.6838046272493572</v>
       </c>
     </row>
     <row r="46">
@@ -3838,45 +3838,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Ruslan Ginoga</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>499</v>
+        <v>369</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>332</v>
+        <v>247</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>337</v>
+        <v>251</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.6753507014028056</v>
+        <v>0.6802168021680217</v>
       </c>
     </row>
     <row r="47">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
@@ -3899,31 +3899,31 @@
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>289</v>
+        <v>527</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>190</v>
+        <v>354</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>193</v>
+        <v>358</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.6678200692041523</v>
+        <v>0.6793168880455408</v>
       </c>
     </row>
     <row r="48">
@@ -3949,13 +3949,13 @@
         <v>345</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I48" s="9" t="n">
         <v>0</v>
@@ -3967,10 +3967,10 @@
         <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.6782608695652174</v>
       </c>
     </row>
     <row r="49">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
@@ -3993,31 +3993,31 @@
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>459</v>
+        <v>515</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>303</v>
+        <v>342</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>303</v>
+        <v>349</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.6601307189542482</v>
+        <v>0.6776699029126214</v>
       </c>
     </row>
     <row r="50">
@@ -4026,45 +4026,45 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Ruslan Ginoga</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>367</v>
+        <v>455</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="I50" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I50" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J50" s="9" t="n">
-        <v>238</v>
+        <v>287</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>241</v>
+        <v>306</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.6566757493188011</v>
+        <v>0.6725274725274726</v>
       </c>
     </row>
     <row r="51">
@@ -4073,27 +4073,27 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>452</v>
+        <v>289</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H51" s="9" t="n">
         <v>0</v>
@@ -4102,16 +4102,16 @@
         <v>1</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>294</v>
+        <v>191</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>295</v>
+        <v>194</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.652654867256637</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="52">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
@@ -4134,31 +4134,31 @@
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>424</v>
+        <v>460</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>254</v>
+        <v>305</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.6462264150943396</v>
+        <v>0.6630434782608695</v>
       </c>
     </row>
     <row r="53">
@@ -4181,16 +4181,16 @@
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I53" s="9" t="n">
         <v>2</v>
@@ -4202,10 +4202,10 @@
         <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.6426966292134831</v>
+        <v>0.6570155902004454</v>
       </c>
     </row>
     <row r="54">
@@ -4214,45 +4214,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="G54" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="H54" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H54" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="I54" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K54" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.6426966292134831</v>
+        <v>0.6541850220264317</v>
       </c>
     </row>
     <row r="55">
@@ -4261,45 +4261,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.6413793103448274</v>
+        <v>0.6533018867924528</v>
       </c>
     </row>
     <row r="56">
@@ -4308,45 +4308,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>514</v>
+        <v>464</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.6400778210116731</v>
+        <v>0.6530172413793103</v>
       </c>
     </row>
     <row r="57">
@@ -4355,45 +4355,45 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G57" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="H57" s="9" t="n">
-        <v>4</v>
-      </c>
       <c r="I57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.6379310344827587</v>
+        <v>0.6495535714285714</v>
       </c>
     </row>
     <row r="58">
@@ -4402,45 +4402,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>374</v>
+        <v>411</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="I58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="K58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.6336898395721925</v>
+        <v>0.6472019464720195</v>
       </c>
     </row>
     <row r="59">
@@ -4449,45 +4449,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>622</v>
+        <v>376</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>223</v>
+        <v>116</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>391</v>
+        <v>237</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>394</v>
+        <v>243</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6334405144694534</v>
+        <v>0.6462765957446809</v>
       </c>
     </row>
     <row r="60">
@@ -4496,45 +4496,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>197</v>
+        <v>278</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.6332518337408313</v>
+        <v>0.6413793103448274</v>
       </c>
     </row>
     <row r="61">
@@ -4543,45 +4543,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>429</v>
+        <v>625</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>158</v>
+        <v>219</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>271</v>
+        <v>394</v>
       </c>
       <c r="K61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>271</v>
+        <v>399</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.6317016317016317</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="62">
@@ -4590,45 +4590,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>498</v>
+        <v>404</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>183</v>
+        <v>103</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>311</v>
+        <v>257</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6244979919678715</v>
+        <v>0.6361386138613861</v>
       </c>
     </row>
     <row r="63">
@@ -4637,45 +4637,45 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>351</v>
+        <v>429</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>214</v>
+        <v>272</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>219</v>
+        <v>272</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.6239316239316239</v>
+        <v>0.634032634032634</v>
       </c>
     </row>
     <row r="64">
@@ -4684,45 +4684,45 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>452</v>
+        <v>498</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="K64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.6238938053097345</v>
+        <v>0.6285140562248996</v>
       </c>
     </row>
     <row r="65">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>511</v>
+        <v>429</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>0</v>
@@ -4757,19 +4757,19 @@
         <v>0</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>312</v>
+        <v>268</v>
       </c>
       <c r="K65" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>314</v>
+        <v>269</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.6144814090019569</v>
+        <v>0.627039627039627</v>
       </c>
     </row>
     <row r="66">
@@ -4778,24 +4778,24 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>0</v>
@@ -4804,19 +4804,19 @@
         <v>0</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K66" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.6121495327102804</v>
+        <v>0.6247240618101545</v>
       </c>
     </row>
     <row r="67">
@@ -4825,45 +4825,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>450</v>
+        <v>351</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>273</v>
+        <v>214</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>275</v>
+        <v>219</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6239316239316239</v>
       </c>
     </row>
     <row r="68">
@@ -4872,33 +4872,33 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J68" s="9" t="n">
         <v>280</v>
@@ -4907,10 +4907,10 @@
         <v>0</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.61</v>
+        <v>0.6231263383297645</v>
       </c>
     </row>
     <row r="69">
@@ -4919,45 +4919,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>414</v>
+        <v>500</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>252</v>
+        <v>310</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="70">
@@ -4966,45 +4966,45 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>399</v>
+        <v>513</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>115</v>
+        <v>196</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>238</v>
+        <v>301</v>
       </c>
       <c r="K70" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>240</v>
+        <v>317</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>0.6015037593984962</v>
+        <v>0.6179337231968811</v>
       </c>
     </row>
     <row r="71">
@@ -5013,45 +5013,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>400</v>
+        <v>544</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>237</v>
+        <v>308</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>240</v>
+        <v>336</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>0.6</v>
+        <v>0.6176470588235294</v>
       </c>
     </row>
     <row r="72">
@@ -5060,45 +5060,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>464</v>
+        <v>381</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="M72" s="11" t="n">
-        <v>0.5991379310344828</v>
+        <v>0.6089238845144357</v>
       </c>
     </row>
     <row r="73">
@@ -5107,45 +5107,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>381</v>
+        <v>414</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="M73" s="11" t="n">
-        <v>0.5984251968503937</v>
+        <v>0.6086956521739131</v>
       </c>
     </row>
     <row r="74">
@@ -5154,45 +5154,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="K74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="M74" s="11" t="n">
-        <v>0.5966029723991507</v>
+        <v>0.607981220657277</v>
       </c>
     </row>
     <row r="75">
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H75" s="9" t="n">
         <v>0</v>
@@ -5230,16 +5230,16 @@
         <v>0</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="K75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="M75" s="11" t="n">
-        <v>0.5960502692998204</v>
+        <v>0.6057347670250897</v>
       </c>
     </row>
     <row r="76">
@@ -5248,45 +5248,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="H76" s="9" t="n">
+      <c r="I76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>262</v>
+      </c>
+      <c r="K76" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="9" t="n">
-        <v>252</v>
-      </c>
-      <c r="K76" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L76" s="9" t="n">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="M76" s="11" t="n">
-        <v>0.5938967136150235</v>
+        <v>0.6045454545454545</v>
       </c>
     </row>
     <row r="77">
@@ -5295,45 +5295,45 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>361</v>
+        <v>468</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>202</v>
+        <v>273</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>212</v>
-      </c>
-      <c r="M77" s="11" t="n">
-        <v>0.5872576177285319</v>
+        <v>281</v>
+      </c>
+      <c r="M77" s="12" t="n">
+        <v>0.6004273504273504</v>
       </c>
     </row>
     <row r="78">
@@ -5342,45 +5342,45 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>533</v>
+        <v>400</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>308</v>
+        <v>237</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>313</v>
-      </c>
-      <c r="M78" s="11" t="n">
-        <v>0.5872420262664165</v>
+        <v>240</v>
+      </c>
+      <c r="M78" s="12" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="79">
@@ -5389,45 +5389,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>435</v>
+        <v>360</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>254</v>
+        <v>216</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.5839080459770115</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="80">
@@ -5436,45 +5436,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.5831533477321814</v>
+        <v>0.5978947368421053</v>
       </c>
     </row>
     <row r="81">
@@ -5483,45 +5483,45 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>460</v>
+        <v>505</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="K81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.5804347826086956</v>
+        <v>0.596039603960396</v>
       </c>
     </row>
     <row r="82">
@@ -5530,45 +5530,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I82" s="9" t="n">
         <v>3</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="K82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.58</v>
+        <v>0.5942028985507246</v>
       </c>
     </row>
     <row r="83">
@@ -5577,45 +5577,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>499</v>
+        <v>465</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.5791583166332666</v>
+        <v>0.5913978494623656</v>
       </c>
     </row>
     <row r="84">
@@ -5624,45 +5624,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
         <v>504</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.5734126984126984</v>
+        <v>0.5912698412698413</v>
       </c>
     </row>
     <row r="85">
@@ -5671,45 +5671,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>466</v>
+        <v>511</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>267</v>
+        <v>300</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.572961373390558</v>
+        <v>0.5870841487279843</v>
       </c>
     </row>
     <row r="86">
@@ -5718,45 +5718,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>364</v>
+        <v>475</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>207</v>
+        <v>278</v>
       </c>
       <c r="K86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>208</v>
+        <v>278</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5852631578947368</v>
       </c>
     </row>
     <row r="87">
@@ -5765,45 +5765,45 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.5704545454545454</v>
+        <v>0.5829787234042553</v>
       </c>
     </row>
     <row r="88">
@@ -5812,45 +5812,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="K88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.5680851063829787</v>
+        <v>0.5809935205183585</v>
       </c>
     </row>
     <row r="89">
@@ -5859,45 +5859,45 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>446</v>
+        <v>400</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.5672645739910314</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="90">
@@ -5906,45 +5906,45 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>501</v>
+        <v>440</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>284</v>
+        <v>252</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.5668662674650699</v>
+        <v>0.5727272727272728</v>
       </c>
     </row>
     <row r="91">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
@@ -5967,31 +5967,31 @@
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>492</v>
+        <v>547</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>278</v>
+        <v>313</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.5650406504065041</v>
+        <v>0.5722120658135283</v>
       </c>
     </row>
     <row r="92">
@@ -6000,45 +6000,45 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>477</v>
+        <v>364</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>264</v>
+        <v>207</v>
       </c>
       <c r="K92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>267</v>
+        <v>208</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.559748427672956</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="93">
@@ -6047,45 +6047,45 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>466</v>
+        <v>427</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="I93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.5536480686695279</v>
+        <v>0.5690866510538641</v>
       </c>
     </row>
     <row r="94">
@@ -6094,45 +6094,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.5528255528255528</v>
+        <v>0.5672645739910314</v>
       </c>
     </row>
     <row r="95">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
@@ -6155,31 +6155,31 @@
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>544</v>
+        <v>466</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.5514705882352942</v>
+        <v>0.5665236051502146</v>
       </c>
     </row>
     <row r="96">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
@@ -6202,31 +6202,31 @@
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>426</v>
+        <v>493</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="K96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>234</v>
+        <v>279</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.5492957746478874</v>
+        <v>0.565922920892495</v>
       </c>
     </row>
     <row r="97">
@@ -6235,45 +6235,45 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>438</v>
+        <v>467</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="K97" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.547945205479452</v>
+        <v>0.5653104925053534</v>
       </c>
     </row>
     <row r="98">
@@ -6282,45 +6282,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>399</v>
+        <v>443</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.5463659147869674</v>
+        <v>0.5643340857787811</v>
       </c>
     </row>
     <row r="99">
@@ -6329,45 +6329,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>460</v>
+        <v>396</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="K99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.5456521739130434</v>
+        <v>0.5606060606060606</v>
       </c>
     </row>
     <row r="100">
@@ -6390,16 +6390,16 @@
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I100" s="9" t="n">
         <v>0</v>
@@ -6411,10 +6411,10 @@
         <v>2</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.539906103286385</v>
+        <v>0.550351288056206</v>
       </c>
     </row>
     <row r="101">
@@ -6423,45 +6423,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="K101" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.5388349514563107</v>
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="102">
@@ -6470,45 +6470,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>511</v>
+        <v>399</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>269</v>
+        <v>218</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>274</v>
+        <v>218</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.5362035225048923</v>
+        <v>0.5463659147869674</v>
       </c>
     </row>
     <row r="103">
@@ -6517,45 +6517,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>394</v>
+        <v>520</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="G103" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H103" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I103" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>263</v>
+      </c>
+      <c r="K103" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="H103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="9" t="n">
-        <v>211</v>
-      </c>
-      <c r="K103" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L103" s="9" t="n">
-        <v>211</v>
+        <v>284</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.5355329949238579</v>
+        <v>0.5461538461538461</v>
       </c>
     </row>
     <row r="104">
@@ -6564,45 +6564,45 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>368</v>
+        <v>455</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>197</v>
+        <v>248</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.5353260869565217</v>
+        <v>0.545054945054945</v>
       </c>
     </row>
     <row r="105">
@@ -6611,45 +6611,45 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="K105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.5330396475770925</v>
+        <v>0.5394736842105263</v>
       </c>
     </row>
     <row r="106">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
@@ -6672,13 +6672,13 @@
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H106" s="9" t="n">
         <v>0</v>
@@ -6687,16 +6687,16 @@
         <v>0</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.5323383084577115</v>
+        <v>0.5388349514563107</v>
       </c>
     </row>
     <row r="107">
@@ -6705,45 +6705,45 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>454</v>
+        <v>325</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>214</v>
+        <v>79</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>240</v>
+        <v>173</v>
       </c>
       <c r="K107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.5286343612334802</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="108">
@@ -6752,45 +6752,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>470</v>
+        <v>402</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="K108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.5234042553191489</v>
+        <v>0.5323383084577115</v>
       </c>
     </row>
     <row r="109">
@@ -6799,45 +6799,45 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.5205479452054794</v>
+        <v>0.5275779376498801</v>
       </c>
     </row>
     <row r="110">
@@ -6846,45 +6846,45 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Regina Kesya Dumumpe</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>419</v>
+        <v>471</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>198</v>
+        <v>246</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.5202863961813843</v>
+        <v>0.5265392781316348</v>
       </c>
     </row>
     <row r="111">
@@ -6893,45 +6893,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Ivan Christian Sasenga</t>
+          <t>Regina Kesya Dumumpe</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>498</v>
+        <v>420</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="G111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>248</v>
+        <v>204</v>
       </c>
       <c r="K111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>259</v>
+        <v>220</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.5200803212851406</v>
+        <v>0.5238095238095238</v>
       </c>
     </row>
     <row r="112">
@@ -6940,45 +6940,45 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Ivan Christian Sasenga</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>415</v>
+        <v>498</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="G112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>207</v>
+        <v>248</v>
       </c>
       <c r="K112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.5180722891566265</v>
+        <v>0.5220883534136547</v>
       </c>
     </row>
     <row r="113">
@@ -6987,27 +6987,27 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>323</v>
+        <v>438</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>114</v>
+        <v>210</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H113" s="9" t="n">
         <v>0</v>
@@ -7016,16 +7016,16 @@
         <v>0</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>167</v>
+        <v>227</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>167</v>
+        <v>228</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.5170278637770898</v>
+        <v>0.5205479452054794</v>
       </c>
     </row>
     <row r="114">
@@ -7034,45 +7034,45 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>408</v>
+        <v>508</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>198</v>
+        <v>247</v>
       </c>
       <c r="G114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H114" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="I114" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.5122549019607843</v>
+        <v>0.5137795275590551</v>
       </c>
     </row>
     <row r="115">
@@ -7081,45 +7081,45 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.5022222222222222</v>
+        <v>0.5122549019607843</v>
       </c>
     </row>
     <row r="116">
@@ -7128,45 +7128,45 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>425</v>
+        <v>477</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="G116" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H116" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="I116" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>189</v>
+      </c>
+      <c r="K116" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="I116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="9" t="n">
-        <v>207</v>
-      </c>
-      <c r="K116" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L116" s="9" t="n">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.5011764705882353</v>
+        <v>0.5115303983228512</v>
       </c>
     </row>
     <row r="117">
@@ -7175,45 +7175,45 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>404</v>
+        <v>454</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>182</v>
+        <v>231</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.5</v>
+        <v>0.5088105726872246</v>
       </c>
     </row>
     <row r="118">
@@ -7222,45 +7222,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>474</v>
+        <v>405</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.5</v>
+        <v>0.5012345679012346</v>
       </c>
     </row>
     <row r="119">
@@ -7269,24 +7269,24 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>346</v>
+        <v>425</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="G119" s="9" t="n">
         <v>0</v>
@@ -7295,19 +7295,19 @@
         <v>0</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="K119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.5</v>
+        <v>0.5011764705882353</v>
       </c>
     </row>
     <row r="120">
@@ -7316,45 +7316,45 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>505</v>
+        <v>399</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>253</v>
+        <v>191</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>252</v>
+        <v>199</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.499009900990099</v>
+        <v>0.4987468671679198</v>
       </c>
     </row>
     <row r="121">
@@ -7363,45 +7363,45 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>399</v>
+        <v>345</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H121" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I121" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0.4987468671679198</v>
+        <v>0.4985507246376812</v>
       </c>
     </row>
     <row r="122">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
@@ -7424,31 +7424,31 @@
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="G122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I122" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J122" s="9" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="K122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.4928229665071771</v>
+        <v>0.4977168949771689</v>
       </c>
     </row>
     <row r="123">
@@ -7457,45 +7457,45 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I123" s="9" t="n">
-        <v>10</v>
-      </c>
       <c r="J123" s="9" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.4863013698630138</v>
+        <v>0.4928229665071771</v>
       </c>
     </row>
     <row r="124">
@@ -7504,45 +7504,45 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>200</v>
+        <v>147</v>
       </c>
       <c r="K124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.4830917874396136</v>
+        <v>0.4927884615384615</v>
       </c>
     </row>
     <row r="125">
@@ -7551,45 +7551,45 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.482837528604119</v>
+        <v>0.4920273348519363</v>
       </c>
     </row>
     <row r="126">
@@ -7598,45 +7598,45 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>414</v>
+        <v>451</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="G126" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.4806763285024155</v>
+        <v>0.4878048780487805</v>
       </c>
     </row>
     <row r="127">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -7659,31 +7659,31 @@
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>448</v>
+        <v>414</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.4776785714285715</v>
+        <v>0.4830917874396136</v>
       </c>
     </row>
     <row r="128">
@@ -7709,13 +7709,13 @@
         <v>441</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G128" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H128" s="9" t="n">
         <v>16</v>
-      </c>
-      <c r="H128" s="9" t="n">
-        <v>12</v>
       </c>
       <c r="I128" s="9" t="n">
         <v>0</v>
@@ -7727,10 +7727,10 @@
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.4716553287981859</v>
+        <v>0.4807256235827664</v>
       </c>
     </row>
     <row r="129">
@@ -7739,45 +7739,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.4668192219679634</v>
+        <v>0.4717444717444718</v>
       </c>
     </row>
     <row r="130">
@@ -7786,33 +7786,33 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>391</v>
+        <v>442</v>
       </c>
       <c r="F130" s="9" t="n">
         <v>210</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J130" s="9" t="n">
         <v>181</v>
@@ -7821,10 +7821,10 @@
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4629156010230179</v>
+        <v>0.4705882352941176</v>
       </c>
     </row>
     <row r="131">
@@ -7833,45 +7833,45 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>407</v>
+        <v>514</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>219</v>
+        <v>269</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H131" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I131" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>218</v>
+      </c>
+      <c r="K131" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="9" t="n">
-        <v>187</v>
-      </c>
-      <c r="K131" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L131" s="9" t="n">
-        <v>188</v>
+        <v>240</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.4619164619164619</v>
+        <v>0.4669260700389105</v>
       </c>
     </row>
     <row r="132">
@@ -7880,45 +7880,45 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="K132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.4506024096385542</v>
+        <v>0.4629156010230179</v>
       </c>
     </row>
     <row r="133">
@@ -7927,45 +7927,45 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>418</v>
+        <v>459</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="K133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.4596949891067538</v>
       </c>
     </row>
     <row r="134">
@@ -7974,45 +7974,45 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>513</v>
+        <v>417</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>279</v>
+        <v>210</v>
       </c>
       <c r="G134" s="9" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H134" s="9" t="n">
         <v>13</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>202</v>
+        <v>149</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.4463937621832358</v>
+        <v>0.4580335731414868</v>
       </c>
     </row>
     <row r="135">
@@ -8021,45 +8021,45 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Dince Lahaube</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>332</v>
+        <v>422</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>8</v>
+        <v>228</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>177</v>
+        <v>2</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.4427710843373494</v>
+        <v>0.4549763033175356</v>
       </c>
     </row>
     <row r="136">
@@ -8068,45 +8068,45 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Dince Lahaube</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E136" s="9" t="n">
-        <v>459</v>
+        <v>332</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>227</v>
+        <v>8</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>29</v>
+        <v>177</v>
       </c>
       <c r="H136" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I136" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J136" s="9" t="n">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="K136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>203</v>
+        <v>147</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.4422657952069716</v>
+        <v>0.4427710843373494</v>
       </c>
     </row>
   </sheetData>
@@ -8149,7 +8149,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 20 Juli 2026</t>
+          <t>Hari/Tanggal : 21 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8166,17 +8166,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 05.55 WITA</t>
+          <t>Pukul        : 10.25 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-35):</t>
+          <t>Target Hari Ini (H-36):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>58.45%</t>
+          <t>60.12%</t>
         </is>
       </c>
     </row>
@@ -8268,31 +8268,31 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2872</v>
+        <v>2898</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>433</v>
+        <v>385</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2426</v>
+        <v>2496</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2433</v>
+        <v>2505</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.8471448467966574</v>
+        <v>0.8643892339544513</v>
       </c>
     </row>
     <row r="8">
@@ -8315,31 +8315,31 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2028</v>
+        <v>2033</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>27</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L8" s="9" t="n">
         <v>1542</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.7603550295857988</v>
+        <v>0.7584849975405804</v>
       </c>
     </row>
     <row r="9">
@@ -8362,31 +8362,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2798</v>
+        <v>2812</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>709</v>
+        <v>666</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>9</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2084</v>
+        <v>2088</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.74481772694782</v>
+        <v>0.7425320056899004</v>
       </c>
     </row>
     <row r="10">
@@ -8409,31 +8409,31 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2887</v>
+        <v>2906</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>661</v>
+        <v>590</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2037</v>
+        <v>2034</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2124</v>
+        <v>2131</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.735711811569103</v>
+        <v>0.7333103922918101</v>
       </c>
     </row>
     <row r="11">
@@ -8456,31 +8456,31 @@
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2482</v>
+        <v>2505</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>688</v>
+        <v>661</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1780</v>
+        <v>1828</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1781</v>
+        <v>1828</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7175664786462531</v>
+        <v>0.7297405189620758</v>
       </c>
     </row>
     <row r="12">
@@ -8503,31 +8503,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2833</v>
+        <v>2854</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>812</v>
+        <v>755</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1985</v>
+        <v>2007</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7094952347334982</v>
+        <v>0.7060266292922215</v>
       </c>
     </row>
     <row r="13">
@@ -8550,31 +8550,31 @@
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2103</v>
+        <v>2110</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>704</v>
+        <v>676</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>7</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1358</v>
+        <v>1379</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1360</v>
+        <v>1382</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6466951973371374</v>
+        <v>0.6549763033175355</v>
       </c>
     </row>
     <row r="14">
@@ -8597,31 +8597,31 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2758</v>
+        <v>2774</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>949</v>
+        <v>913</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1711</v>
+        <v>1786</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1722</v>
+        <v>1795</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6243654822335025</v>
+        <v>0.6470800288392213</v>
       </c>
     </row>
     <row r="15">
@@ -8644,31 +8644,31 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2892</v>
+        <v>2903</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1040</v>
+        <v>991</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1796</v>
+        <v>1856</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1803</v>
+        <v>1868</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.6234439834024896</v>
+        <v>0.6434722700654496</v>
       </c>
     </row>
     <row r="16">
@@ -8691,31 +8691,31 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2385</v>
+        <v>2403</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="G16" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="H16" s="9" t="n">
-        <v>17</v>
-      </c>
       <c r="I16" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1467</v>
+        <v>1504</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1475</v>
+        <v>1515</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.6184486373165619</v>
+        <v>0.630461922596754</v>
       </c>
     </row>
     <row r="17">
@@ -8738,31 +8738,31 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2156</v>
+        <v>2164</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.6150278293135436</v>
+        <v>0.6136783733826248</v>
       </c>
     </row>
     <row r="18">
@@ -8785,31 +8785,31 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2878</v>
+        <v>2890</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1099</v>
+        <v>1072</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1697</v>
+        <v>1730</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1726</v>
+        <v>1753</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.5997220291869354</v>
+        <v>0.6065743944636678</v>
       </c>
     </row>
     <row r="19">
@@ -8832,31 +8832,31 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2809</v>
+        <v>2825</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1149</v>
+        <v>1125</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>8</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1652</v>
-      </c>
-      <c r="M19" s="11" t="n">
-        <v>0.5881096475614097</v>
+        <v>1679</v>
+      </c>
+      <c r="M19" s="12" t="n">
+        <v>0.5943362831858408</v>
       </c>
     </row>
     <row r="20">
@@ -8879,13 +8879,13 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2661</v>
+        <v>2670</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1158</v>
+        <v>1127</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>0</v>
@@ -8894,16 +8894,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1477</v>
+        <v>1519</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1478</v>
+        <v>1520</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.5554302893649005</v>
+        <v>0.5692883895131086</v>
       </c>
     </row>
     <row r="21">
@@ -8926,31 +8926,31 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2694</v>
+        <v>2697</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1152</v>
+        <v>1145</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1476</v>
+        <v>1498</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1479</v>
+        <v>1501</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.5489977728285078</v>
+        <v>0.5565443084909159</v>
       </c>
     </row>
     <row r="22">
@@ -8973,31 +8973,31 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2443</v>
+        <v>2451</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>910</v>
+        <v>897</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1321</v>
+        <v>1350</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1332</v>
+        <v>1359</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.5452312730249693</v>
+        <v>0.554467564259486</v>
       </c>
     </row>
     <row r="23">
@@ -9020,31 +9020,31 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2302</v>
+        <v>2314</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>968</v>
+        <v>951</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>22</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1221</v>
+        <v>1255</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1245</v>
+        <v>1279</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.5408340573414422</v>
+        <v>0.5527225583405359</v>
       </c>
     </row>
     <row r="24">
@@ -9053,45 +9053,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Kezia Maralending</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>1422</v>
+        <v>2546</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>406</v>
+        <v>1161</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>265</v>
+        <v>2</v>
       </c>
       <c r="H24" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="I24" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" s="9" t="n">
-        <v>745</v>
+        <v>1371</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>747</v>
+        <v>1377</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5253164556962026</v>
+        <v>0.5408483896307934</v>
       </c>
     </row>
     <row r="25">
@@ -9100,45 +9100,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Kezia Maralending</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2534</v>
+        <v>1433</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1183</v>
+        <v>356</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>3</v>
+        <v>294</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1315</v>
+        <v>766</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>1321</v>
+        <v>768</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.521310181531176</v>
+        <v>0.5359385903698535</v>
       </c>
     </row>
     <row r="26">
@@ -9147,45 +9147,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2711</v>
+        <v>2413</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1230</v>
+        <v>1077</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1389</v>
+        <v>1186</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1394</v>
+        <v>1241</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.5142014016967908</v>
+        <v>0.5142975549108993</v>
       </c>
     </row>
     <row r="27">
@@ -9194,45 +9194,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>B. Lenskar Diamanis</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2063</v>
+        <v>2712</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1022</v>
+        <v>1227</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>987</v>
+        <v>1389</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>1013</v>
+        <v>1394</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.4910324769752787</v>
+        <v>0.5140117994100295</v>
       </c>
     </row>
     <row r="28">
@@ -9255,31 +9255,31 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2081</v>
+        <v>2090</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1007</v>
+        <v>996</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>958</v>
+        <v>967</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1014</v>
+        <v>1029</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.4872657376261413</v>
+        <v>0.4923444976076555</v>
       </c>
     </row>
     <row r="29">
@@ -9288,45 +9288,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>B. Lenskar Diamanis</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2407</v>
+        <v>2065</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1104</v>
+        <v>1016</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1133</v>
+        <v>990</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1169</v>
+        <v>1011</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.4856668051516411</v>
+        <v>0.489588377723971</v>
       </c>
     </row>
   </sheetData>
@@ -9360,7 +9360,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 20 Juli 2026</t>
+          <t>Hari/Tanggal : 21 Juli 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9377,17 +9377,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 05.55 WITA</t>
+          <t>Pukul        : 10.25 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-35):</t>
+          <t>Target Hari Ini (H-36):</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>58.45%</t>
+          <t>60.12%</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.7757575757575758</v>
+        <v>0.783923941227312</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7578051087984864</v>
+        <v>0.7723704866562009</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7347853939782191</v>
+        <v>0.7553259141494436</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9474,15 +9474,15 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7104817235536189</v>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.7255323725532372</v>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9492,15 +9492,15 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.7058632274845561</v>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.7224233647115617</v>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.6334405144694534</v>
+        <v>0.6384</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.6221786064769381</v>
+        <v>0.631219512195122</v>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.6165347405452947</v>
+        <v>0.6233538191395961</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
@@ -9567,8 +9567,8 @@
           <t>Kendahe</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>0.5898896404414382</v>
+      <c r="C15" s="12" t="n">
+        <v>0.6007079646017699</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.5789575289575289</v>
+        <v>0.5883935434281322</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.5510425716768028</v>
+        <v>0.5596885813148789</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.545375650880238</v>
+        <v>0.5531625201138755</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -9636,15 +9636,15 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.5300582847626978</v>
+        <v>0.5464061409630147</v>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
     </row>
@@ -9658,11 +9658,11 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.52970502700457</v>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>-1</t>
+        <v>0.5428926647326979</v>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9672,15 +9672,15 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.5281293952180028</v>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.5358327803583278</v>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>-2</t>
         </is>
       </c>
     </row>

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,10 +91,6 @@
     </font>
     <font>
       <color rgb="00595959"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="8">
@@ -167,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -192,8 +188,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -594,7 +588,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 21 Juli 2026</t>
+          <t>Hari/Tanggal : 22 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -616,32 +610,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 10.25 WITA</t>
+          <t>Pukul        : 09.30 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-36):</t>
+          <t>Target Hari Ini (H-37):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>60.12%</t>
+          <t>61.79%</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Hijau &gt;= 60.12%</t>
+          <t>Hijau &gt;= 61.79%</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Kuning 30.06% - 60.12%</t>
+          <t>Kuning 30.89% - 61.79%</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Merah &lt; 30.06%</t>
+          <t>Merah &lt; 30.89%</t>
         </is>
       </c>
     </row>
@@ -805,7 +799,7 @@
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -874,7 +868,7 @@
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -943,7 +937,7 @@
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -1012,7 +1006,7 @@
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1081,7 +1075,7 @@
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1150,7 +1144,7 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1219,7 +1213,7 @@
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1288,7 +1282,7 @@
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1357,7 +1351,7 @@
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1426,7 +1420,7 @@
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1495,7 +1489,7 @@
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1564,7 +1558,7 @@
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1633,7 +1627,7 @@
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1702,7 +1696,7 @@
         <v/>
       </c>
       <c r="R20" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S20" s="10">
         <f>R20/B20</f>
@@ -1771,7 +1765,7 @@
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1900,7 +1894,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 21 Juli 2026</t>
+          <t>Hari/Tanggal : 22 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1917,17 +1911,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 10.25 WITA</t>
+          <t>Pukul        : 09.30 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-36):</t>
+          <t>Target Hari Ini (H-37):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>60.12%</t>
+          <t>61.79%</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5044,7 @@
       <c r="L71" s="9" t="n">
         <v>336</v>
       </c>
-      <c r="M71" s="11" t="n">
+      <c r="M71" s="12" t="n">
         <v>0.6176470588235294</v>
       </c>
     </row>
@@ -5097,7 +5091,7 @@
       <c r="L72" s="9" t="n">
         <v>232</v>
       </c>
-      <c r="M72" s="11" t="n">
+      <c r="M72" s="12" t="n">
         <v>0.6089238845144357</v>
       </c>
     </row>
@@ -5144,7 +5138,7 @@
       <c r="L73" s="9" t="n">
         <v>252</v>
       </c>
-      <c r="M73" s="11" t="n">
+      <c r="M73" s="12" t="n">
         <v>0.6086956521739131</v>
       </c>
     </row>
@@ -5191,7 +5185,7 @@
       <c r="L74" s="9" t="n">
         <v>259</v>
       </c>
-      <c r="M74" s="11" t="n">
+      <c r="M74" s="12" t="n">
         <v>0.607981220657277</v>
       </c>
     </row>
@@ -5238,7 +5232,7 @@
       <c r="L75" s="9" t="n">
         <v>338</v>
       </c>
-      <c r="M75" s="11" t="n">
+      <c r="M75" s="12" t="n">
         <v>0.6057347670250897</v>
       </c>
     </row>
@@ -5285,7 +5279,7 @@
       <c r="L76" s="9" t="n">
         <v>266</v>
       </c>
-      <c r="M76" s="11" t="n">
+      <c r="M76" s="12" t="n">
         <v>0.6045454545454545</v>
       </c>
     </row>
@@ -8149,7 +8143,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 21 Juli 2026</t>
+          <t>Hari/Tanggal : 22 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8166,17 +8160,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 10.25 WITA</t>
+          <t>Pukul        : 09.30 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-36):</t>
+          <t>Target Hari Ini (H-37):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>60.12%</t>
+          <t>61.79%</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8755,7 @@
       <c r="L17" s="9" t="n">
         <v>1328</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" s="12" t="n">
         <v>0.6136783733826248</v>
       </c>
     </row>
@@ -8808,7 +8802,7 @@
       <c r="L18" s="9" t="n">
         <v>1753</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" s="12" t="n">
         <v>0.6065743944636678</v>
       </c>
     </row>
@@ -9360,7 +9354,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 21 Juli 2026</t>
+          <t>Hari/Tanggal : 22 Juli 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9377,17 +9371,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 10.25 WITA</t>
+          <t>Pukul        : 09.30 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-36):</t>
+          <t>Target Hari Ini (H-37):</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>60.12%</t>
+          <t>61.79%</t>
         </is>
       </c>
     </row>
@@ -9480,9 +9474,9 @@
       <c r="C10" s="11" t="n">
         <v>0.7255323725532372</v>
       </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>+1</t>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9498,9 +9492,9 @@
       <c r="C11" s="11" t="n">
         <v>0.7224233647115617</v>
       </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>-1</t>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9642,9 +9636,9 @@
       <c r="C19" s="12" t="n">
         <v>0.5464061409630147</v>
       </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>+2</t>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9678,9 +9672,9 @@
       <c r="C21" s="12" t="n">
         <v>0.5358327803583278</v>
       </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>-2</t>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,6 +91,10 @@
     </font>
     <font>
       <color rgb="00595959"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="8">
@@ -163,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -188,6 +192,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -610,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.30 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -744,62 +750,62 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4143</v>
+        <v>4157</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1116</v>
+        <v>1097</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
         <v/>
       </c>
       <c r="F7" s="9" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G7" s="10">
         <f>F7/B7</f>
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K7" s="10">
         <f>J7/B7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2907</v>
+        <v>2910</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
         <v/>
       </c>
       <c r="N7" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O7" s="10">
         <f>N7/B7</f>
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>2993</v>
+        <v>3032</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -813,41 +819,41 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
         <v/>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="10">
         <f>J8/B8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>766</v>
+        <v>802</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -861,14 +867,14 @@
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>783</v>
+        <v>826</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -882,62 +888,62 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6290</v>
+        <v>6336</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1451</v>
+        <v>1365</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4451</v>
+        <v>4611</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
         <v/>
       </c>
       <c r="N9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="10">
         <f>N9/B9</f>
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4751</v>
+        <v>4877</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -951,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3185</v>
+        <v>3212</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>725</v>
+        <v>680</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -971,42 +977,42 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K10" s="10">
         <f>J10/B10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2383</v>
+        <v>2477</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
         <v/>
       </c>
       <c r="N10" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O10" s="10">
         <f>N10/B10</f>
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2460</v>
+        <v>2532</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1020,41 +1026,41 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1139</v>
+        <v>1146</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
         <v/>
       </c>
       <c r="J11" s="9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K11" s="10">
         <f>J11/B11</f>
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="M11" s="10">
         <f>L11/B11</f>
@@ -1068,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>710</v>
+        <v>739</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1089,13 +1095,13 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>1025</v>
+        <v>1035</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>23</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="E12" s="10">
         <f>D12/B12</f>
@@ -1109,14 +1115,14 @@
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
         <v/>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="10">
         <f>J12/B12</f>
@@ -1137,14 +1143,14 @@
         <v/>
       </c>
       <c r="P12" s="9" t="n">
-        <v>647</v>
+        <v>678</v>
       </c>
       <c r="Q12" s="11">
         <f>P12/B12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1158,13 +1164,13 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4624</v>
+        <v>4650</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1999</v>
+        <v>1946</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
@@ -1178,21 +1184,21 @@
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>164</v>
+        <v>220</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2414</v>
+        <v>2442</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1206,14 +1212,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2588</v>
+        <v>2667</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1227,41 +1233,41 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6028</v>
+        <v>6081</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2770</v>
+        <v>2686</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3051</v>
+        <v>3149</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
@@ -1275,14 +1281,14 @@
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3230</v>
+        <v>3364</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1296,41 +1302,41 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8079</v>
+        <v>8130</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3499</v>
+        <v>3385</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>54</v>
+        <v>143</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="10">
         <f>J15/B15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4406</v>
+        <v>4489</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1344,14 +1350,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4469</v>
+        <v>4642</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1365,41 +1371,41 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5204</v>
+        <v>5222</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2023</v>
+        <v>1949</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>2985</v>
+        <v>3087</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1413,14 +1419,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3062</v>
+        <v>3155</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1434,62 +1440,62 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2413</v>
+        <v>2418</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1077</v>
+        <v>1033</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1186</v>
+        <v>1208</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
         <v/>
       </c>
       <c r="N17" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O17" s="10">
         <f>N17/B17</f>
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1310</v>
+        <v>1362</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1503,62 +1509,62 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9298</v>
+        <v>9380</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2481</v>
+        <v>2310</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>46</v>
+        <v>162</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6675</v>
+        <v>6780</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
         <v/>
       </c>
       <c r="N18" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O18" s="10">
         <f>N18/B18</f>
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>6746</v>
+        <v>6970</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1572,13 +1578,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1592,7 +1598,7 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
@@ -1606,7 +1612,7 @@
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>897</v>
+        <v>907</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1620,14 +1626,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>907</v>
+        <v>932</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1710,13 +1716,13 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2825</v>
+        <v>2835</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1125</v>
+        <v>1090</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
@@ -1730,21 +1736,21 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1632</v>
+        <v>1724</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1758,14 +1764,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1697</v>
+        <v>1742</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1911,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.30 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2060,31 +2066,31 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>6</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.964200477326969</v>
+        <v>0.9929577464788732</v>
       </c>
     </row>
     <row r="9">
@@ -2107,16 +2113,16 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
@@ -2128,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>534</v>
+        <v>556</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.956989247311828</v>
+        <v>0.9737302977232924</v>
       </c>
     </row>
     <row r="10">
@@ -2154,31 +2160,31 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.9307692307692308</v>
+        <v>0.9358490566037736</v>
       </c>
     </row>
     <row r="11">
@@ -2216,10 +2222,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" s="9" t="n">
         <v>283</v>
@@ -2234,45 +2240,45 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Fitria Rianti Gorosita</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.8818681318681318</v>
+        <v>0.8932291666666665</v>
       </c>
     </row>
     <row r="13">
@@ -2281,45 +2287,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Alfred Jonathan</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="I13" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" s="9" t="n">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.8726790450928382</v>
+        <v>0.8818681318681318</v>
       </c>
     </row>
     <row r="14">
@@ -2328,45 +2334,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Fitria Rianti Gorosita</t>
+          <t>Alfred Jonathan</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.8713910761154857</v>
+        <v>0.8726790450928382</v>
       </c>
     </row>
     <row r="15">
@@ -2389,19 +2395,19 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I15" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>5</v>
       </c>
       <c r="J15" s="9" t="n">
         <v>307</v>
@@ -2410,10 +2416,10 @@
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.841823056300268</v>
+        <v>0.8567639257294429</v>
       </c>
     </row>
     <row r="16">
@@ -2422,45 +2428,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Asari Prisilia Antari</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>426</v>
+        <v>507</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>264</v>
+        <v>420</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>357</v>
+        <v>425</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.8380281690140845</v>
+        <v>0.8382642998027613</v>
       </c>
     </row>
     <row r="17">
@@ -2469,45 +2475,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Meisye Fransiska Samau</t>
+          <t>Asari Prisilia Antari</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8304239401496259</v>
+        <v>0.8380281690140845</v>
       </c>
     </row>
     <row r="18">
@@ -2516,45 +2522,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Meisye Fransiska Samau</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>493</v>
+        <v>405</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>392</v>
+        <v>337</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>407</v>
+        <v>339</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8255578093306287</v>
+        <v>0.8370370370370369</v>
       </c>
     </row>
     <row r="19">
@@ -2577,31 +2583,31 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" s="9" t="n">
         <v>4</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.8177083333333335</v>
+        <v>0.8324742268041238</v>
       </c>
     </row>
     <row r="20">
@@ -2610,45 +2616,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>477</v>
+        <v>415</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>377</v>
+        <v>326</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>389</v>
+        <v>345</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.8155136268343816</v>
+        <v>0.8313253012048193</v>
       </c>
     </row>
     <row r="21">
@@ -2657,45 +2663,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>336</v>
+        <v>401</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.8085106382978722</v>
+        <v>0.8216432865731462</v>
       </c>
     </row>
     <row r="22">
@@ -2704,7 +2710,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -2718,31 +2724,31 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.7981438515081206</v>
+        <v>0.8215962441314554</v>
       </c>
     </row>
     <row r="23">
@@ -2751,45 +2757,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>495</v>
+        <v>431</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>394</v>
+        <v>354</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.795959595959596</v>
+        <v>0.8213457076566125</v>
       </c>
     </row>
     <row r="24">
@@ -2798,45 +2804,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>389</v>
+        <v>478</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>299</v>
+        <v>377</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>309</v>
+        <v>392</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.7943444730077122</v>
+        <v>0.8200836820083682</v>
       </c>
     </row>
     <row r="25">
@@ -2845,45 +2851,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>411</v>
+        <v>503</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>326</v>
+        <v>398</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>326</v>
+        <v>407</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.7931873479318735</v>
+        <v>0.8091451292246521</v>
       </c>
     </row>
     <row r="26">
@@ -2892,45 +2898,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>499</v>
+        <v>392</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>393</v>
+        <v>312</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>395</v>
+        <v>316</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.7915831663326653</v>
+        <v>0.8061224489795918</v>
       </c>
     </row>
     <row r="27">
@@ -2953,31 +2959,31 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.7867924528301887</v>
+        <v>0.7879924953095684</v>
       </c>
     </row>
     <row r="28">
@@ -2986,45 +2992,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Sheryl Jessica Tatontos</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>384</v>
+        <v>498</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>296</v>
+        <v>390</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>0.7708333333333335</v>
+        <v>0.7831325301204819</v>
       </c>
     </row>
     <row r="29">
@@ -3033,45 +3039,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Sheryl Jessica Tatontos</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>490</v>
+        <v>386</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>323</v>
+        <v>281</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>375</v>
+        <v>298</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.7653061224489796</v>
+        <v>0.7720207253886009</v>
       </c>
     </row>
     <row r="30">
@@ -3080,7 +3086,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -3094,31 +3100,31 @@
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7470449172576832</v>
+        <v>0.7714285714285716</v>
       </c>
     </row>
     <row r="31">
@@ -3127,7 +3133,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -3141,31 +3147,31 @@
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7463768115942028</v>
+        <v>0.7570754716981132</v>
       </c>
     </row>
     <row r="32">
@@ -3188,31 +3194,31 @@
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.7440758293838863</v>
+        <v>0.7570754716981132</v>
       </c>
     </row>
     <row r="33">
@@ -3221,45 +3227,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>502</v>
+        <v>410</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>356</v>
+        <v>291</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>371</v>
+        <v>310</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.7390438247011953</v>
+        <v>0.7560975609756098</v>
       </c>
     </row>
     <row r="34">
@@ -3268,45 +3274,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>556</v>
+        <v>503</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>406</v>
+        <v>378</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.7302158273381295</v>
+        <v>0.7514910536779325</v>
       </c>
     </row>
     <row r="35">
@@ -3329,31 +3335,31 @@
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>8</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.724609375</v>
+        <v>0.7495183044315994</v>
       </c>
     </row>
     <row r="36">
@@ -3362,45 +3368,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>539</v>
+        <v>560</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7217068645640075</v>
+        <v>0.7392857142857143</v>
       </c>
     </row>
     <row r="37">
@@ -3409,45 +3415,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>402</v>
+        <v>350</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7213930348258707</v>
+        <v>0.7371428571428571</v>
       </c>
     </row>
     <row r="38">
@@ -3456,45 +3462,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>501</v>
+        <v>544</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H38" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="I38" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>354</v>
+        <v>396</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.720558882235529</v>
+        <v>0.7352941176470589</v>
       </c>
     </row>
     <row r="39">
@@ -3503,45 +3509,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>347</v>
+        <v>425</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>244</v>
+        <v>290</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>249</v>
+        <v>312</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7175792507204612</v>
+        <v>0.7341176470588234</v>
       </c>
     </row>
     <row r="40">
@@ -3550,45 +3556,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>453</v>
+        <v>507</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>323</v>
+        <v>364</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>323</v>
+        <v>370</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.7130242825607064</v>
+        <v>0.7297830374753451</v>
       </c>
     </row>
     <row r="41">
@@ -3597,45 +3603,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>420</v>
+        <v>505</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>288</v>
+        <v>349</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>298</v>
+        <v>364</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.7095238095238094</v>
+        <v>0.7207920792079208</v>
       </c>
     </row>
     <row r="42">
@@ -3644,45 +3650,45 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>503</v>
+        <v>453</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>354</v>
+        <v>323</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.7037773359840955</v>
+        <v>0.7130242825607064</v>
       </c>
     </row>
     <row r="43">
@@ -3705,19 +3711,19 @@
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="9" t="n">
         <v>253</v>
@@ -3726,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.7007874015748031</v>
+        <v>0.711340206185567</v>
       </c>
     </row>
     <row r="44">
@@ -3738,45 +3744,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>504</v>
+        <v>458</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H44" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="I44" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I44" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J44" s="9" t="n">
-        <v>346</v>
+        <v>290</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>349</v>
+        <v>323</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.6924603174603174</v>
+        <v>0.7052401746724891</v>
       </c>
     </row>
     <row r="45">
@@ -3785,45 +3791,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>389</v>
+        <v>505</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="G45" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>350</v>
+      </c>
+      <c r="K45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="9" t="n">
-        <v>223</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" s="9" t="n">
-        <v>266</v>
+        <v>354</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.6838046272493572</v>
+        <v>0.7009900990099009</v>
       </c>
     </row>
     <row r="46">
@@ -3846,31 +3852,31 @@
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.6802168021680217</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="47">
@@ -3879,45 +3885,45 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>527</v>
+        <v>469</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.6793168880455408</v>
+        <v>0.697228144989339</v>
       </c>
     </row>
     <row r="48">
@@ -3926,45 +3932,45 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>345</v>
+        <v>520</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>230</v>
+        <v>341</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>234</v>
+        <v>360</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.6782608695652174</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="49">
@@ -3973,45 +3979,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>515</v>
+        <v>347</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>342</v>
+        <v>228</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>349</v>
+        <v>240</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.6776699029126214</v>
+        <v>0.69164265129683</v>
       </c>
     </row>
     <row r="50">
@@ -4020,45 +4026,45 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>455</v>
+        <v>389</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>287</v>
+        <v>223</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>306</v>
+        <v>268</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.6725274725274726</v>
+        <v>0.6889460154241646</v>
       </c>
     </row>
     <row r="51">
@@ -4067,7 +4073,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -4081,10 +4087,10 @@
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>289</v>
+        <v>528</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>95</v>
+        <v>166</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>0</v>
@@ -4093,19 +4099,19 @@
         <v>0</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>191</v>
+        <v>360</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>194</v>
+        <v>362</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.671280276816609</v>
+        <v>0.6856060606060607</v>
       </c>
     </row>
     <row r="52">
@@ -4114,45 +4120,45 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>460</v>
+        <v>380</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>305</v>
+        <v>253</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.6630434782608695</v>
+        <v>0.6815789473684211</v>
       </c>
     </row>
     <row r="53">
@@ -4161,45 +4167,45 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>449</v>
+        <v>416</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>284</v>
+        <v>221</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.6570155902004454</v>
+        <v>0.673076923076923</v>
       </c>
     </row>
     <row r="54">
@@ -4208,45 +4214,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.6541850220264317</v>
+        <v>0.6728971962616822</v>
       </c>
     </row>
     <row r="55">
@@ -4255,45 +4261,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.6533018867924528</v>
+        <v>0.6724890829694323</v>
       </c>
     </row>
     <row r="56">
@@ -4302,45 +4308,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>464</v>
+        <v>289</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="G56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H56" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I56" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J56" s="9" t="n">
-        <v>300</v>
+        <v>191</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>303</v>
+        <v>194</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.6530172413793103</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="57">
@@ -4363,31 +4369,31 @@
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I57" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.6495535714285714</v>
+        <v>0.6703539823008849</v>
       </c>
     </row>
     <row r="58">
@@ -4396,45 +4402,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.6472019464720195</v>
+        <v>0.6674876847290641</v>
       </c>
     </row>
     <row r="59">
@@ -4443,45 +4449,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>376</v>
+        <v>452</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>243</v>
+        <v>300</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6462765957446809</v>
+        <v>0.6637168141592921</v>
       </c>
     </row>
     <row r="60">
@@ -4490,45 +4496,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>435</v>
+        <v>464</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.6413793103448274</v>
+        <v>0.6573275862068965</v>
       </c>
     </row>
     <row r="61">
@@ -4537,45 +4543,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>625</v>
+        <v>459</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>219</v>
+        <v>159</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>394</v>
+        <v>281</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>399</v>
+        <v>300</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.6384</v>
+        <v>0.65359477124183</v>
       </c>
     </row>
     <row r="62">
@@ -4584,45 +4590,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>404</v>
+        <v>502</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>249</v>
+        <v>324</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>257</v>
+        <v>328</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6361386138613861</v>
+        <v>0.6533864541832669</v>
       </c>
     </row>
     <row r="63">
@@ -4631,45 +4637,45 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.634032634032634</v>
+        <v>0.6505747126436782</v>
       </c>
     </row>
     <row r="64">
@@ -4678,45 +4684,45 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.6285140562248996</v>
+        <v>0.6447105788423154</v>
       </c>
     </row>
     <row r="65">
@@ -4739,10 +4745,10 @@
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>0</v>
@@ -4754,16 +4760,16 @@
         <v>0</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="K65" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.627039627039627</v>
+        <v>0.6412037037037037</v>
       </c>
     </row>
     <row r="66">
@@ -4772,45 +4778,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.6247240618101545</v>
+        <v>0.639344262295082</v>
       </c>
     </row>
     <row r="67">
@@ -4819,45 +4825,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>351</v>
+        <v>625</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>132</v>
+        <v>219</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>214</v>
+        <v>394</v>
       </c>
       <c r="K67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>219</v>
+        <v>399</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.6239316239316239</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="68">
@@ -4883,28 +4889,28 @@
         <v>467</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="K68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.6231263383297645</v>
+        <v>0.6381156316916489</v>
       </c>
     </row>
     <row r="69">
@@ -4913,45 +4919,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>500</v>
+        <v>386</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>304</v>
+        <v>233</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>310</v>
+        <v>245</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.62</v>
+        <v>0.6347150259067358</v>
       </c>
     </row>
     <row r="70">
@@ -4960,24 +4966,24 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>513</v>
+        <v>429</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>0</v>
@@ -4986,19 +4992,19 @@
         <v>0</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>301</v>
+        <v>272</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>317</v>
+        <v>272</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>0.6179337231968811</v>
+        <v>0.634032634032634</v>
       </c>
     </row>
     <row r="71">
@@ -5007,45 +5013,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>544</v>
+        <v>352</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>208</v>
+        <v>129</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>308</v>
+        <v>211</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>336</v>
-      </c>
-      <c r="M71" s="12" t="n">
-        <v>0.6176470588235294</v>
+        <v>223</v>
+      </c>
+      <c r="M71" s="11" t="n">
+        <v>0.6335227272727273</v>
       </c>
     </row>
     <row r="72">
@@ -5054,45 +5060,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>381</v>
+        <v>515</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>224</v>
+        <v>324</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>232</v>
-      </c>
-      <c r="M72" s="12" t="n">
-        <v>0.6089238845144357</v>
+        <v>326</v>
+      </c>
+      <c r="M72" s="11" t="n">
+        <v>0.6330097087378641</v>
       </c>
     </row>
     <row r="73">
@@ -5101,45 +5107,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>414</v>
+        <v>572</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="G73" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H73" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="I73" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H73" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I73" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="J73" s="9" t="n">
-        <v>243</v>
+        <v>326</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>252</v>
-      </c>
-      <c r="M73" s="12" t="n">
-        <v>0.6086956521739131</v>
+        <v>360</v>
+      </c>
+      <c r="M73" s="11" t="n">
+        <v>0.6293706293706294</v>
       </c>
     </row>
     <row r="74">
@@ -5148,45 +5154,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>259</v>
-      </c>
-      <c r="M74" s="12" t="n">
-        <v>0.607981220657277</v>
+        <v>277</v>
+      </c>
+      <c r="M74" s="11" t="n">
+        <v>0.6281179138321995</v>
       </c>
     </row>
     <row r="75">
@@ -5195,45 +5201,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>558</v>
+        <v>427</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>338</v>
+        <v>266</v>
       </c>
       <c r="K75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>338</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>0.6057347670250897</v>
+        <v>268</v>
+      </c>
+      <c r="M75" s="11" t="n">
+        <v>0.6276346604215457</v>
       </c>
     </row>
     <row r="76">
@@ -5242,45 +5248,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>440</v>
+        <v>478</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>266</v>
-      </c>
-      <c r="M76" s="12" t="n">
-        <v>0.6045454545454545</v>
+        <v>299</v>
+      </c>
+      <c r="M76" s="11" t="n">
+        <v>0.6255230125523012</v>
       </c>
     </row>
     <row r="77">
@@ -5303,10 +5309,10 @@
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>1</v>
@@ -5315,19 +5321,19 @@
         <v>1</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>281</v>
-      </c>
-      <c r="M77" s="12" t="n">
-        <v>0.6004273504273504</v>
+        <v>293</v>
+      </c>
+      <c r="M77" s="11" t="n">
+        <v>0.6247334754797441</v>
       </c>
     </row>
     <row r="78">
@@ -5336,45 +5342,45 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>400</v>
+        <v>546</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I78" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>237</v>
+        <v>333</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>240</v>
-      </c>
-      <c r="M78" s="12" t="n">
-        <v>0.6</v>
+        <v>341</v>
+      </c>
+      <c r="M78" s="11" t="n">
+        <v>0.6245421245421245</v>
       </c>
     </row>
     <row r="79">
@@ -5383,45 +5389,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>360</v>
+        <v>404</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>216</v>
-      </c>
-      <c r="M79" s="12" t="n">
-        <v>0.6</v>
+        <v>252</v>
+      </c>
+      <c r="M79" s="11" t="n">
+        <v>0.6237623762376238</v>
       </c>
     </row>
     <row r="80">
@@ -5430,45 +5436,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>475</v>
+        <v>415</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>284</v>
-      </c>
-      <c r="M80" s="12" t="n">
-        <v>0.5978947368421053</v>
+        <v>258</v>
+      </c>
+      <c r="M80" s="11" t="n">
+        <v>0.6216867469879518</v>
       </c>
     </row>
     <row r="81">
@@ -5491,31 +5497,31 @@
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="K81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>301</v>
-      </c>
-      <c r="M81" s="12" t="n">
-        <v>0.596039603960396</v>
+        <v>315</v>
+      </c>
+      <c r="M81" s="11" t="n">
+        <v>0.618860510805501</v>
       </c>
     </row>
     <row r="82">
@@ -5524,45 +5530,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="K82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.5942028985507246</v>
+        <v>0.6172248803827751</v>
       </c>
     </row>
     <row r="83">
@@ -5571,45 +5577,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.5913978494623656</v>
+        <v>0.6171548117154811</v>
       </c>
     </row>
     <row r="84">
@@ -5618,45 +5624,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>504</v>
+        <v>559</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>288</v>
+        <v>344</v>
       </c>
       <c r="K84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.5912698412698413</v>
+        <v>0.6153846153846154</v>
       </c>
     </row>
     <row r="85">
@@ -5679,31 +5685,31 @@
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="K85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.5870841487279843</v>
+        <v>0.6143410852713178</v>
       </c>
     </row>
     <row r="86">
@@ -5712,45 +5718,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="K86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.5852631578947368</v>
+        <v>0.610752688172043</v>
       </c>
     </row>
     <row r="87">
@@ -5759,7 +5765,7 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
@@ -5773,31 +5779,31 @@
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="9" t="n">
         <v>274</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.5829787234042553</v>
+        <v>0.6088888888888889</v>
       </c>
     </row>
     <row r="88">
@@ -5806,45 +5812,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>463</v>
+        <v>366</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="K88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>269</v>
+        <v>222</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.5809935205183585</v>
+        <v>0.6065573770491803</v>
       </c>
     </row>
     <row r="89">
@@ -5853,45 +5859,45 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>216</v>
+        <v>256</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.58</v>
+        <v>0.6046511627906976</v>
       </c>
     </row>
     <row r="90">
@@ -5900,45 +5906,45 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>440</v>
+        <v>361</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.5727272727272728</v>
+        <v>0.6011080332409973</v>
       </c>
     </row>
     <row r="91">
@@ -5947,45 +5953,45 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>547</v>
+        <v>450</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>313</v>
+        <v>263</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>313</v>
+        <v>270</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.5722120658135283</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="92">
@@ -5994,45 +6000,45 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>364</v>
+        <v>402</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="I92" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I92" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J92" s="9" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="K92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>208</v>
+        <v>241</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.599502487562189</v>
       </c>
     </row>
     <row r="93">
@@ -6041,7 +6047,7 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
@@ -6055,31 +6061,31 @@
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>427</v>
+        <v>469</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>243</v>
+        <v>280</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.5690866510538641</v>
+        <v>0.5970149253731343</v>
       </c>
     </row>
     <row r="94">
@@ -6088,45 +6094,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>446</v>
+        <v>504</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.5672645739910314</v>
+        <v>0.5952380952380952</v>
       </c>
     </row>
     <row r="95">
@@ -6135,45 +6141,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.5665236051502146</v>
+        <v>0.594017094017094</v>
       </c>
     </row>
     <row r="96">
@@ -6182,45 +6188,45 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>493</v>
+        <v>469</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J96" s="9" t="n">
         <v>269</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.565922920892495</v>
+        <v>0.5906183368869936</v>
       </c>
     </row>
     <row r="97">
@@ -6229,45 +6235,45 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.5653104925053534</v>
+        <v>0.5902335456475584</v>
       </c>
     </row>
     <row r="98">
@@ -6276,45 +6282,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>443</v>
+        <v>325</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>244</v>
+        <v>186</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>250</v>
+        <v>191</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.5643340857787811</v>
+        <v>0.5876923076923077</v>
       </c>
     </row>
     <row r="99">
@@ -6323,45 +6329,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>396</v>
+        <v>445</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="K99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.5606060606060606</v>
+        <v>0.5707865168539326</v>
       </c>
     </row>
     <row r="100">
@@ -6370,45 +6376,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>427</v>
+        <v>496</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="G100" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>235</v>
+        <v>283</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.550351288056206</v>
+        <v>0.5705645161290323</v>
       </c>
     </row>
     <row r="101">
@@ -6417,45 +6423,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5692695214105793</v>
       </c>
     </row>
     <row r="102">
@@ -6464,45 +6470,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="G102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>207</v>
+      </c>
+      <c r="K102" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="9" t="n">
-        <v>218</v>
-      </c>
-      <c r="K102" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L102" s="9" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.5463659147869674</v>
+        <v>0.5691489361702128</v>
       </c>
     </row>
     <row r="103">
@@ -6511,45 +6517,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>520</v>
+        <v>455</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>234</v>
+        <v>188</v>
       </c>
       <c r="G103" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H103" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I103" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>235</v>
+      </c>
+      <c r="K103" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H103" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="I103" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="J103" s="9" t="n">
-        <v>263</v>
-      </c>
-      <c r="K103" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="L103" s="9" t="n">
-        <v>284</v>
+        <v>258</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.5461538461538461</v>
+        <v>0.567032967032967</v>
       </c>
     </row>
     <row r="104">
@@ -6558,45 +6564,45 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>455</v>
+        <v>522</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>229</v>
+        <v>287</v>
       </c>
       <c r="K104" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>248</v>
+        <v>292</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.545054945054945</v>
+        <v>0.5593869731800766</v>
       </c>
     </row>
     <row r="105">
@@ -6619,31 +6625,31 @@
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="G105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="K105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.5394736842105263</v>
+        <v>0.5577342047930284</v>
       </c>
     </row>
     <row r="106">
@@ -6652,7 +6658,7 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
@@ -6666,13 +6672,13 @@
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H106" s="9" t="n">
         <v>0</v>
@@ -6681,16 +6687,16 @@
         <v>0</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.5388349514563107</v>
+        <v>0.5513784461152882</v>
       </c>
     </row>
     <row r="107">
@@ -6699,45 +6705,45 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>325</v>
+        <v>412</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>79</v>
+        <v>170</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>173</v>
+        <v>221</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5509708737864077</v>
       </c>
     </row>
     <row r="108">
@@ -6746,45 +6752,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Regina Kesya Dumumpe</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.5323383084577115</v>
+        <v>0.5458823529411765</v>
       </c>
     </row>
     <row r="109">
@@ -6807,31 +6813,31 @@
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I109" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="K109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.5275779376498801</v>
+        <v>0.542654028436019</v>
       </c>
     </row>
     <row r="110">
@@ -6840,45 +6846,45 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>471</v>
+        <v>512</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.5265392781316348</v>
+        <v>0.537109375</v>
       </c>
     </row>
     <row r="111">
@@ -6887,45 +6893,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Regina Kesya Dumumpe</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>420</v>
+        <v>479</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5365344467640919</v>
       </c>
     </row>
     <row r="112">
@@ -6934,7 +6940,7 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Ivan Christian Sasenga</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
@@ -6948,31 +6954,31 @@
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>498</v>
+        <v>402</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>238</v>
+        <v>185</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="K112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.5220883534136547</v>
+        <v>0.5348258706467661</v>
       </c>
     </row>
     <row r="113">
@@ -6981,7 +6987,7 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Ivan Christian Sasenga</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
@@ -6995,31 +7001,31 @@
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>438</v>
+        <v>503</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.5205479452054794</v>
+        <v>0.532803180914513</v>
       </c>
     </row>
     <row r="114">
@@ -7028,45 +7034,45 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>508</v>
+        <v>408</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="G114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.5137795275590551</v>
+        <v>0.5318627450980392</v>
       </c>
     </row>
     <row r="115">
@@ -7075,45 +7081,45 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>408</v>
+        <v>471</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>206</v>
+        <v>246</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>209</v>
+        <v>248</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.5122549019607843</v>
+        <v>0.5265392781316348</v>
       </c>
     </row>
     <row r="116">
@@ -7122,45 +7128,45 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>477</v>
+        <v>438</v>
       </c>
       <c r="F116" s="9" t="n">
+        <v>209</v>
+      </c>
+      <c r="G116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>227</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" s="9" t="n">
         <v>229</v>
       </c>
-      <c r="G116" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H116" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="I116" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="J116" s="9" t="n">
-        <v>189</v>
-      </c>
-      <c r="K116" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L116" s="9" t="n">
-        <v>244</v>
-      </c>
       <c r="M116" s="12" t="n">
-        <v>0.5115303983228512</v>
+        <v>0.5228310502283106</v>
       </c>
     </row>
     <row r="117">
@@ -7169,45 +7175,45 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>454</v>
+        <v>346</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>223</v>
+        <v>166</v>
       </c>
       <c r="G117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>231</v>
+        <v>171</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.5088105726872246</v>
+        <v>0.5202312138728323</v>
       </c>
     </row>
     <row r="118">
@@ -7216,45 +7222,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>405</v>
+        <v>455</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="K118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.5012345679012346</v>
+        <v>0.5186813186813187</v>
       </c>
     </row>
     <row r="119">
@@ -7263,45 +7269,45 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="G119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="K119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.5011764705882353</v>
+        <v>0.5166666666666667</v>
       </c>
     </row>
     <row r="120">
@@ -7310,45 +7316,45 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="K120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.4987468671679198</v>
+        <v>0.5135135135135135</v>
       </c>
     </row>
     <row r="121">
@@ -7357,45 +7363,45 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>345</v>
+        <v>426</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="G121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>172</v>
+        <v>217</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0.4985507246376812</v>
+        <v>0.5093896713615024</v>
       </c>
     </row>
     <row r="122">
@@ -7404,45 +7410,45 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G122" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="K122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.4977168949771689</v>
+        <v>0.5076586433260394</v>
       </c>
     </row>
     <row r="123">
@@ -7451,45 +7457,45 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.4928229665071771</v>
+        <v>0.5068181818181818</v>
       </c>
     </row>
     <row r="124">
@@ -7498,7 +7504,7 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
@@ -7512,31 +7518,31 @@
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>416</v>
+        <v>445</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="G124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="I124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>147</v>
+        <v>222</v>
       </c>
       <c r="K124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.4927884615384615</v>
+        <v>0.5056179775280899</v>
       </c>
     </row>
     <row r="125">
@@ -7545,7 +7551,7 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
@@ -7559,31 +7565,31 @@
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.4920273348519363</v>
+        <v>0.5047619047619047</v>
       </c>
     </row>
     <row r="126">
@@ -7592,45 +7598,45 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>451</v>
+        <v>416</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="G126" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>213</v>
+        <v>147</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.5024038461538461</v>
       </c>
     </row>
     <row r="127">
@@ -7639,7 +7645,7 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -7653,31 +7659,31 @@
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.4830917874396136</v>
+        <v>0.5012224938875306</v>
       </c>
     </row>
     <row r="128">
@@ -7686,45 +7692,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>441</v>
+        <v>399</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.4807256235827664</v>
+        <v>0.4987468671679198</v>
       </c>
     </row>
     <row r="129">
@@ -7733,45 +7739,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.4717444717444718</v>
+        <v>0.4966139954853273</v>
       </c>
     </row>
     <row r="130">
@@ -7780,45 +7786,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="K130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4875283446712018</v>
       </c>
     </row>
     <row r="131">
@@ -7827,45 +7833,45 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>514</v>
+        <v>396</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>269</v>
+        <v>203</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>240</v>
+        <v>193</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.4669260700389105</v>
+        <v>0.4873737373737373</v>
       </c>
     </row>
     <row r="132">
@@ -7874,45 +7880,45 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>391</v>
+        <v>514</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.4629156010230179</v>
+        <v>0.4844357976653696</v>
       </c>
     </row>
     <row r="133">
@@ -7921,45 +7927,45 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>459</v>
+        <v>420</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H133" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="K133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.4596949891067538</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="134">
@@ -7968,45 +7974,45 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>417</v>
+        <v>459</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="G134" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="H134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="H134" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="I134" s="9" t="n">
-        <v>29</v>
-      </c>
       <c r="J134" s="9" t="n">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="K134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.4580335731414868</v>
+        <v>0.477124183006536</v>
       </c>
     </row>
     <row r="135">
@@ -8029,31 +8035,31 @@
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.4549763033175356</v>
+        <v>0.4680851063829787</v>
       </c>
     </row>
     <row r="136">
@@ -8082,25 +8088,25 @@
         <v>8</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H136" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J136" s="9" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="K136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.4427710843373494</v>
+        <v>0.4518072289156627</v>
       </c>
     </row>
   </sheetData>
@@ -8160,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.30 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8262,19 +8268,19 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2898</v>
+        <v>2934</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>2496</v>
@@ -8283,10 +8289,10 @@
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.8643892339544513</v>
+        <v>0.8534423994546694</v>
       </c>
     </row>
     <row r="8">
@@ -8295,45 +8301,45 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Simson Petiunaung</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2033</v>
+        <v>2835</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>440</v>
+        <v>626</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1528</v>
+        <v>2170</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1542</v>
+        <v>2186</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.7584849975405804</v>
+        <v>0.7710758377425044</v>
       </c>
     </row>
     <row r="9">
@@ -8342,45 +8348,45 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Simson Petiunaung</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2812</v>
+        <v>2038</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>666</v>
+        <v>436</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2076</v>
+        <v>1530</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2088</v>
+        <v>1542</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.7425320056899004</v>
+        <v>0.7566241413150148</v>
       </c>
     </row>
     <row r="10">
@@ -8389,45 +8395,45 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Charly Angel Tatontos</t>
+          <t>Sutrisno Sariang</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan, Tabukan Utara</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi, Hendri</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2906</v>
+        <v>2519</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>590</v>
+        <v>624</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2034</v>
+        <v>1862</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2131</v>
+        <v>1866</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7333103922918101</v>
+        <v>0.740770146883684</v>
       </c>
     </row>
     <row r="11">
@@ -8436,45 +8442,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Sutrisno Sariang</t>
+          <t>Charly Angel Tatontos</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan, Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Alfi, Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2505</v>
+        <v>2936</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>661</v>
+        <v>558</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>16</v>
+        <v>131</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1828</v>
+        <v>2112</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1828</v>
+        <v>2173</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7297405189620758</v>
+        <v>0.7401226158038147</v>
       </c>
     </row>
     <row r="12">
@@ -8497,31 +8503,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2854</v>
+        <v>2867</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>755</v>
+        <v>710</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I12" s="9" t="n">
         <v>8</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>2007</v>
+        <v>2079</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2015</v>
+        <v>2087</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7060266292922215</v>
+        <v>0.7279386117893268</v>
       </c>
     </row>
     <row r="13">
@@ -8530,45 +8536,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Kepulauan Marore, Tabukan Utara</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri, Michael</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2110</v>
+        <v>2911</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>676</v>
+        <v>936</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1379</v>
+        <v>1906</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1382</v>
+        <v>1914</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6549763033175355</v>
+        <v>0.6575060116798351</v>
       </c>
     </row>
     <row r="14">
@@ -8591,31 +8597,31 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2774</v>
+        <v>2803</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>913</v>
+        <v>863</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1786</v>
+        <v>1817</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1795</v>
+        <v>1830</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6470800288392213</v>
+        <v>0.6528719229397075</v>
       </c>
     </row>
     <row r="15">
@@ -8624,45 +8630,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore, Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Hendri, Michael</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2903</v>
+        <v>2119</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>991</v>
+        <v>661</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1856</v>
+        <v>1380</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1868</v>
+        <v>1382</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.6434722700654496</v>
+        <v>0.6521944313355357</v>
       </c>
     </row>
     <row r="16">
@@ -8685,31 +8691,31 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2403</v>
+        <v>2428</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>864</v>
+        <v>834</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1504</v>
+        <v>1554</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1515</v>
+        <v>1563</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.630461922596754</v>
+        <v>0.6437397034596376</v>
       </c>
     </row>
     <row r="17">
@@ -8732,31 +8738,31 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2164</v>
+        <v>2181</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>790</v>
+        <v>753</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1325</v>
+        <v>1349</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1328</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>0.6136783733826248</v>
+        <v>1362</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>0.624484181568088</v>
       </c>
     </row>
     <row r="18">
@@ -8779,31 +8785,31 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2890</v>
+        <v>2898</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1072</v>
+        <v>1053</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1730</v>
+        <v>1772</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1753</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>0.6065743944636678</v>
+        <v>1799</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>0.6207729468599034</v>
       </c>
     </row>
     <row r="19">
@@ -8826,31 +8832,31 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2825</v>
+        <v>2835</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1125</v>
+        <v>1090</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1632</v>
+        <v>1724</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>8</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1679</v>
+        <v>1738</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.5943362831858408</v>
+        <v>0.6130511463844798</v>
       </c>
     </row>
     <row r="20">
@@ -8873,31 +8879,31 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2670</v>
+        <v>2682</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1127</v>
+        <v>1073</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1519</v>
+        <v>1582</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1520</v>
+        <v>1583</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.5692883895131086</v>
+        <v>0.5902311707680835</v>
       </c>
     </row>
     <row r="21">
@@ -8906,45 +8912,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2697</v>
+        <v>2324</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1145</v>
+        <v>896</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1498</v>
+        <v>1315</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1501</v>
+        <v>1339</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.5565443084909159</v>
+        <v>0.5761617900172117</v>
       </c>
     </row>
     <row r="22">
@@ -8953,45 +8959,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Kezia Maralending</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2451</v>
+        <v>1439</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>897</v>
+        <v>338</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>35</v>
+        <v>275</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>9</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1350</v>
+        <v>802</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1359</v>
+        <v>813</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.554467564259486</v>
+        <v>0.5649756775538568</v>
       </c>
     </row>
     <row r="23">
@@ -9000,45 +9006,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2314</v>
+        <v>2727</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>951</v>
+        <v>1101</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1255</v>
+        <v>1511</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1279</v>
+        <v>1515</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.5527225583405359</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="24">
@@ -9047,45 +9053,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2546</v>
+        <v>2465</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1161</v>
+        <v>873</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>4</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1371</v>
+        <v>1355</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>1377</v>
+        <v>1359</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5408483896307934</v>
+        <v>0.5513184584178499</v>
       </c>
     </row>
     <row r="25">
@@ -9094,45 +9100,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Kezia Maralending</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>1433</v>
+        <v>2562</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>356</v>
+        <v>1127</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>294</v>
+        <v>2</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>766</v>
+        <v>1394</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>768</v>
+        <v>1397</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5359385903698535</v>
+        <v>0.5452771272443404</v>
       </c>
     </row>
     <row r="26">
@@ -9155,31 +9161,31 @@
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2413</v>
+        <v>2418</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1077</v>
+        <v>1033</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1186</v>
+        <v>1208</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1241</v>
+        <v>1268</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.5142975549108993</v>
+        <v>0.5244003308519437</v>
       </c>
     </row>
     <row r="27">
@@ -9188,45 +9194,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Olfira Sicilia Budiman</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2712</v>
+        <v>2108</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1227</v>
+        <v>965</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1389</v>
+        <v>1012</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>1394</v>
+        <v>1095</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.5140117994100295</v>
+        <v>0.5194497153700189</v>
       </c>
     </row>
     <row r="28">
@@ -9235,45 +9241,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Olfira Sicilia Budiman</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2090</v>
+        <v>2721</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>996</v>
+        <v>1211</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>967</v>
+        <v>1396</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1029</v>
+        <v>1401</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.4923444976076555</v>
+        <v>0.5148842337375965</v>
       </c>
     </row>
     <row r="29">
@@ -9296,31 +9302,31 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2065</v>
+        <v>2078</v>
       </c>
       <c r="F29" s="9" t="n">
+        <v>984</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>1003</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="9" t="n">
         <v>1016</v>
       </c>
-      <c r="G29" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="J29" s="9" t="n">
-        <v>990</v>
-      </c>
-      <c r="K29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="9" t="n">
-        <v>1011</v>
-      </c>
       <c r="M29" s="12" t="n">
-        <v>0.489588377723971</v>
+        <v>0.4889316650625601</v>
       </c>
     </row>
   </sheetData>
@@ -9371,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.30 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9418,7 +9424,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.783923941227312</v>
+        <v>0.802065404475043</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9436,7 +9442,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7723704866562009</v>
+        <v>0.7882938978829389</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9454,7 +9460,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7553259141494436</v>
+        <v>0.7697285353535354</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9472,7 +9478,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7255323725532372</v>
+        <v>0.7430703624733475</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -9490,7 +9496,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.7224233647115617</v>
+        <v>0.7293721433726245</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9504,15 +9510,15 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.6384</v>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6550724637681159</v>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9522,15 +9528,15 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tenggara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.631219512195122</v>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6448516579406632</v>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9540,15 +9546,15 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.6233538191395961</v>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6384</v>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>-2</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9568,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.6007079646017699</v>
+        <v>0.6144620811287478</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -9580,7 +9586,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.5883935434281322</v>
+        <v>0.6041746457296056</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9594,15 +9600,15 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.5596885813148789</v>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.5740097289784573</v>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>+2</t>
         </is>
       </c>
     </row>
@@ -9612,15 +9618,15 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.5531625201138755</v>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.5735483870967742</v>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9630,15 +9636,15 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.5464061409630147</v>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.5709717097170972</v>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9652,7 +9658,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.5428926647326979</v>
+        <v>0.5632754342431762</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
@@ -9670,7 +9676,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.5358327803583278</v>
+        <v>0.553198487090939</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 11.05 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 11.05 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 11.05 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 11.05 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.05 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.05 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.05 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.05 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,10 +91,6 @@
     </font>
     <font>
       <color rgb="00595959"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="8">
@@ -167,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -192,8 +188,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -594,7 +588,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 22 Juli 2026</t>
+          <t>Hari/Tanggal : 23 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -616,32 +610,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 08.16 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-37):</t>
+          <t>Target Hari Ini (H-38):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.79%</t>
+          <t>63.46%</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Hijau &gt;= 61.79%</t>
+          <t>Hijau &gt;= 63.46%</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Kuning 30.89% - 61.79%</t>
+          <t>Kuning 31.73% - 63.46%</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Merah &lt; 30.89%</t>
+          <t>Merah &lt; 31.73%</t>
         </is>
       </c>
     </row>
@@ -750,41 +744,41 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4157</v>
+        <v>4163</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1097</v>
+        <v>1079</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
         <v/>
       </c>
       <c r="F7" s="9" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G7" s="10">
         <f>F7/B7</f>
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K7" s="10">
         <f>J7/B7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2910</v>
+        <v>2912</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
@@ -798,14 +792,14 @@
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>3032</v>
+        <v>3065</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -819,62 +813,62 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1439</v>
+        <v>1456</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>338</v>
+        <v>295</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
         <v/>
       </c>
       <c r="J8" s="9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K8" s="10">
         <f>J8/B8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>802</v>
+        <v>876</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
         <v/>
       </c>
       <c r="N8" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O8" s="10">
         <f>N8/B8</f>
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>826</v>
+        <v>901</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -888,41 +882,41 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6336</v>
+        <v>6341</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1365</v>
+        <v>1340</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4611</v>
+        <v>4636</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -936,14 +930,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4877</v>
+        <v>4908</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -957,13 +951,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3212</v>
+        <v>3218</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>680</v>
+        <v>657</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -977,7 +971,7 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
@@ -991,7 +985,7 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2477</v>
+        <v>2482</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
@@ -1005,14 +999,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2532</v>
+        <v>2561</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1032,21 +1026,21 @@
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
@@ -1060,7 +1054,7 @@
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="M11" s="10">
         <f>L11/B11</f>
@@ -1074,14 +1068,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>739</v>
+        <v>748</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1095,13 +1089,13 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>23</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E12" s="10">
         <f>D12/B12</f>
@@ -1115,7 +1109,7 @@
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
@@ -1143,14 +1137,14 @@
         <v/>
       </c>
       <c r="P12" s="9" t="n">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="Q12" s="11">
         <f>P12/B12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1164,41 +1158,41 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4650</v>
+        <v>4665</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1946</v>
+        <v>1909</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>220</v>
+        <v>167</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2442</v>
+        <v>2519</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1212,14 +1206,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2667</v>
+        <v>2725</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1233,41 +1227,41 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6081</v>
+        <v>6108</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2686</v>
+        <v>2628</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3149</v>
+        <v>3263</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
@@ -1281,14 +1275,14 @@
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3364</v>
+        <v>3454</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>134</v>
+        <v>90</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1302,41 +1296,41 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8130</v>
+        <v>8167</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3385</v>
+        <v>3303</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="10">
         <f>J15/B15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4489</v>
+        <v>4643</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1350,14 +1344,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4642</v>
+        <v>4770</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>173</v>
+        <v>128</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1371,13 +1365,13 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5222</v>
+        <v>5251</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1949</v>
+        <v>1853</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
@@ -1391,21 +1385,21 @@
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>3087</v>
+        <v>3165</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1419,14 +1413,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3155</v>
+        <v>3280</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1440,41 +1434,41 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2418</v>
+        <v>2422</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1033</v>
+        <v>999</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1208</v>
+        <v>1219</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
@@ -1488,14 +1482,14 @@
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1362</v>
+        <v>1399</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1509,20 +1503,20 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9380</v>
+        <v>9424</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2310</v>
+        <v>2227</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
@@ -1536,14 +1530,14 @@
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6780</v>
+        <v>6933</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1557,14 +1551,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>6970</v>
+        <v>7119</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>224</v>
+        <v>149</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1578,13 +1572,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1598,21 +1592,21 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
         <v/>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19" s="10">
         <f>J19/B19</f>
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>907</v>
+        <v>953</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1626,14 +1620,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>932</v>
+        <v>959</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1674,14 +1668,14 @@
         <v/>
       </c>
       <c r="J20" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K20" s="10">
         <f>J20/B20</f>
         <v/>
       </c>
       <c r="L20" s="9" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M20" s="10">
         <f>L20/B20</f>
@@ -1716,13 +1710,13 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2835</v>
+        <v>2849</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1090</v>
+        <v>1060</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
@@ -1736,21 +1730,21 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1724</v>
+        <v>1743</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1764,14 +1758,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1742</v>
+        <v>1786</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1886,7 +1880,7 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1900,7 +1894,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 22 Juli 2026</t>
+          <t>Hari/Tanggal : 23 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1917,17 +1911,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 08.16 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-37):</t>
+          <t>Target Hari Ini (H-38):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.79%</t>
+          <t>63.46%</t>
         </is>
       </c>
     </row>
@@ -2116,28 +2110,28 @@
         <v>571</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.9737302977232924</v>
+        <v>0.9772329246935202</v>
       </c>
     </row>
     <row r="10">
@@ -2163,16 +2157,16 @@
         <v>530</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>6</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>478</v>
@@ -2181,10 +2175,10 @@
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.9358490566037736</v>
+        <v>0.9377358490566039</v>
       </c>
     </row>
     <row r="11">
@@ -2207,16 +2201,16 @@
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>0</v>
@@ -2228,10 +2222,10 @@
         <v>1</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.9158576051779935</v>
+        <v>0.9196141479099679</v>
       </c>
     </row>
     <row r="12">
@@ -2240,45 +2234,45 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Fitria Rianti Gorosita</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>384</v>
+        <v>511</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>338</v>
+        <v>466</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>343</v>
+        <v>466</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.8932291666666665</v>
+        <v>0.9119373776908023</v>
       </c>
     </row>
     <row r="13">
@@ -2287,45 +2281,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Alfred Jonathan</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.8818681318681318</v>
+        <v>0.8947368421052632</v>
       </c>
     </row>
     <row r="14">
@@ -2334,24 +2328,24 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Alfred Jonathan</t>
+          <t>Fitria Rianti Gorosita</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
@@ -2363,16 +2357,16 @@
         <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.8726790450928382</v>
+        <v>0.8932291666666665</v>
       </c>
     </row>
     <row r="15">
@@ -2381,45 +2375,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Clara Patricia Pangandaheng</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.8567639257294429</v>
+        <v>0.8818681318681318</v>
       </c>
     </row>
     <row r="16">
@@ -2428,45 +2422,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Clara Patricia Pangandaheng</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>507</v>
+        <v>377</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>420</v>
+        <v>307</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>425</v>
+        <v>328</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.8382642998027613</v>
+        <v>0.870026525198939</v>
       </c>
     </row>
     <row r="17">
@@ -2475,45 +2469,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Asari Prisilia Antari</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="9" t="n">
-        <v>84</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>4</v>
-      </c>
       <c r="J17" s="9" t="n">
-        <v>269</v>
+        <v>353</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8380281690140845</v>
+        <v>0.8533653846153846</v>
       </c>
     </row>
     <row r="18">
@@ -2536,16 +2530,16 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I18" s="9" t="n">
         <v>2</v>
@@ -2557,10 +2551,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8370370370370369</v>
+        <v>0.8472906403940886</v>
       </c>
     </row>
     <row r="19">
@@ -2569,7 +2563,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -2583,31 +2577,31 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>388</v>
+        <v>500</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>319</v>
+        <v>412</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>323</v>
+        <v>421</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.8324742268041238</v>
+        <v>0.8420000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -2616,45 +2610,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>415</v>
+        <v>389</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.8313253012048193</v>
+        <v>0.8406169665809768</v>
       </c>
     </row>
     <row r="21">
@@ -2663,45 +2657,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Asari Prisilia Antari</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>499</v>
+        <v>426</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>401</v>
+        <v>269</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>410</v>
+        <v>357</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.8216432865731462</v>
+        <v>0.8380281690140845</v>
       </c>
     </row>
     <row r="22">
@@ -2710,7 +2704,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -2724,31 +2718,31 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.8215962441314554</v>
+        <v>0.8317972350230414</v>
       </c>
     </row>
     <row r="23">
@@ -2757,7 +2751,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -2771,31 +2765,31 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.8213457076566125</v>
+        <v>0.8262910798122065</v>
       </c>
     </row>
     <row r="24">
@@ -2804,45 +2798,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>478</v>
+        <v>505</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.8200836820083682</v>
+        <v>0.8257425742574257</v>
       </c>
     </row>
     <row r="25">
@@ -2851,45 +2845,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>503</v>
+        <v>479</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.8091451292246521</v>
+        <v>0.8225469728601253</v>
       </c>
     </row>
     <row r="26">
@@ -2945,45 +2939,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>533</v>
+        <v>425</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>420</v>
+        <v>318</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>420</v>
+        <v>336</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.7879924953095684</v>
+        <v>0.7905882352941176</v>
       </c>
     </row>
     <row r="28">
@@ -2992,7 +2986,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Sheryl Jessica Tatontos</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -3006,31 +3000,31 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>498</v>
+        <v>533</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>336</v>
+        <v>420</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>0.7831325301204819</v>
+        <v>0.7879924953095684</v>
       </c>
     </row>
     <row r="29">
@@ -3039,24 +3033,24 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Sheryl Jessica Tatontos</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>386</v>
+        <v>498</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
@@ -3065,19 +3059,19 @@
         <v>16</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>298</v>
+        <v>390</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.7720207253886009</v>
+        <v>0.7831325301204819</v>
       </c>
     </row>
     <row r="30">
@@ -3086,7 +3080,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -3100,7 +3094,7 @@
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>96</v>
@@ -3109,22 +3103,22 @@
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7714285714285716</v>
+        <v>0.7735849056603774</v>
       </c>
     </row>
     <row r="31">
@@ -3133,45 +3127,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>424</v>
+        <v>386</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>319</v>
+        <v>281</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7570754716981132</v>
+        <v>0.7720207253886009</v>
       </c>
     </row>
     <row r="32">
@@ -3180,45 +3174,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>424</v>
+        <v>503</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>313</v>
+        <v>375</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>321</v>
+        <v>382</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.7570754716981132</v>
+        <v>0.7594433399602386</v>
       </c>
     </row>
     <row r="33">
@@ -3227,45 +3221,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>410</v>
+        <v>561</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>291</v>
+        <v>398</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>310</v>
+        <v>425</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.7575757575757575</v>
       </c>
     </row>
     <row r="34">
@@ -3274,45 +3268,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>503</v>
+        <v>424</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>378</v>
+        <v>321</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.7514910536779325</v>
+        <v>0.7570754716981132</v>
       </c>
     </row>
     <row r="35">
@@ -3321,45 +3315,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>519</v>
+        <v>410</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>375</v>
+        <v>291</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>389</v>
+        <v>310</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.7495183044315994</v>
+        <v>0.7560975609756098</v>
       </c>
     </row>
     <row r="36">
@@ -3368,45 +3362,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>560</v>
+        <v>519</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>398</v>
+        <v>375</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7392857142857143</v>
+        <v>0.7495183044315994</v>
       </c>
     </row>
     <row r="37">
@@ -3415,45 +3409,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>350</v>
+        <v>508</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>255</v>
+        <v>374</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>258</v>
+        <v>380</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7371428571428571</v>
+        <v>0.7480314960629921</v>
       </c>
     </row>
     <row r="38">
@@ -3462,45 +3456,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>544</v>
+        <v>408</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>396</v>
+        <v>302</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>400</v>
+        <v>304</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.7450980392156863</v>
       </c>
     </row>
     <row r="39">
@@ -3509,45 +3503,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>425</v>
+        <v>547</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>312</v>
+        <v>407</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7341176470588234</v>
+        <v>0.7440585009140768</v>
       </c>
     </row>
     <row r="40">
@@ -3556,45 +3550,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>507</v>
+        <v>425</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>364</v>
+        <v>291</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>370</v>
+        <v>314</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.7297830374753451</v>
+        <v>0.7388235294117647</v>
       </c>
     </row>
     <row r="41">
@@ -3603,45 +3597,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>505</v>
+        <v>350</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="G41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>255</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" s="9" t="n">
-        <v>349</v>
-      </c>
-      <c r="K41" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" s="9" t="n">
-        <v>364</v>
+        <v>258</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.7207920792079208</v>
+        <v>0.7371428571428571</v>
       </c>
     </row>
     <row r="42">
@@ -3650,45 +3644,45 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>453</v>
+        <v>392</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>323</v>
+        <v>253</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>323</v>
+        <v>286</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.7130242825607064</v>
+        <v>0.7295918367346939</v>
       </c>
     </row>
     <row r="43">
@@ -3697,45 +3691,45 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>388</v>
+        <v>458</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I43" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>253</v>
+        <v>332</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>276</v>
+        <v>333</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.711340206185567</v>
+        <v>0.7270742358078602</v>
       </c>
     </row>
     <row r="44">
@@ -3744,7 +3738,7 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -3758,31 +3752,31 @@
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>458</v>
+        <v>505</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>290</v>
+        <v>349</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>323</v>
+        <v>364</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.7052401746724891</v>
+        <v>0.7207920792079208</v>
       </c>
     </row>
     <row r="45">
@@ -3791,45 +3785,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Ruslan Ginoga</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>505</v>
+        <v>371</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>350</v>
+        <v>260</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>354</v>
+        <v>264</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.7009900990099009</v>
+        <v>0.7115902964959568</v>
       </c>
     </row>
     <row r="46">
@@ -3838,45 +3832,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Ruslan Ginoga</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>370</v>
+        <v>508</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>252</v>
+        <v>359</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>259</v>
+        <v>360</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.7</v>
+        <v>0.7086614173228347</v>
       </c>
     </row>
     <row r="47">
@@ -3885,45 +3879,45 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.697228144989339</v>
+        <v>0.7052401746724891</v>
       </c>
     </row>
     <row r="48">
@@ -3932,45 +3926,45 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>520</v>
+        <v>349</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>341</v>
+        <v>228</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>360</v>
+        <v>246</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.7048710601719198</v>
       </c>
     </row>
     <row r="49">
@@ -3979,45 +3973,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="F49" s="9" t="n">
         <v>107</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I49" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.69164265129683</v>
+        <v>0.7026315789473684</v>
       </c>
     </row>
     <row r="50">
@@ -4040,16 +4034,16 @@
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I50" s="9" t="n">
         <v>1</v>
@@ -4061,10 +4055,10 @@
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.6889460154241646</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="51">
@@ -4073,45 +4067,45 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.6856060606060607</v>
+        <v>0.6982922201138519</v>
       </c>
     </row>
     <row r="52">
@@ -4120,45 +4114,45 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>380</v>
+        <v>469</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>259</v>
+        <v>327</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.6815789473684211</v>
+        <v>0.697228144989339</v>
       </c>
     </row>
     <row r="53">
@@ -4167,45 +4161,45 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>416</v>
+        <v>510</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>221</v>
+        <v>339</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>280</v>
+        <v>348</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.673076923076923</v>
+        <v>0.6823529411764706</v>
       </c>
     </row>
     <row r="54">
@@ -4214,7 +4208,7 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
@@ -4228,31 +4222,31 @@
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.6728971962616822</v>
+        <v>0.6791208791208792</v>
       </c>
     </row>
     <row r="55">
@@ -4261,45 +4255,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>458</v>
+        <v>430</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I55" s="9" t="n">
         <v>3</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>305</v>
+        <v>270</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.6724890829694323</v>
+        <v>0.6790697674418604</v>
       </c>
     </row>
     <row r="56">
@@ -4308,45 +4302,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>289</v>
+        <v>464</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>191</v>
+        <v>314</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>194</v>
+        <v>314</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.671280276816609</v>
+        <v>0.6767241379310345</v>
       </c>
     </row>
     <row r="57">
@@ -4355,45 +4349,45 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>452</v>
+        <v>416</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.6703539823008849</v>
+        <v>0.673076923076923</v>
       </c>
     </row>
     <row r="58">
@@ -4402,45 +4396,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>406</v>
+        <v>458</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>260</v>
+        <v>305</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.6674876847290641</v>
+        <v>0.6724890829694323</v>
       </c>
     </row>
     <row r="59">
@@ -4449,45 +4443,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>452</v>
+        <v>289</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>152</v>
+        <v>95</v>
       </c>
       <c r="G59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>191</v>
+      </c>
+      <c r="K59" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J59" s="9" t="n">
-        <v>284</v>
-      </c>
-      <c r="K59" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L59" s="9" t="n">
-        <v>300</v>
+        <v>194</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6637168141592921</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="60">
@@ -4496,7 +4490,7 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
@@ -4510,31 +4504,31 @@
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>464</v>
+        <v>506</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>305</v>
+        <v>339</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.6573275862068965</v>
+        <v>0.6699604743083004</v>
       </c>
     </row>
     <row r="61">
@@ -4543,45 +4537,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I61" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.65359477124183</v>
+        <v>0.6680497925311202</v>
       </c>
     </row>
     <row r="62">
@@ -4590,45 +4584,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>502</v>
+        <v>435</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>324</v>
+        <v>278</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>328</v>
+        <v>290</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6533864541832669</v>
+        <v>0.6666666666666665</v>
       </c>
     </row>
     <row r="63">
@@ -4637,7 +4631,7 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -4651,31 +4645,31 @@
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.6505747126436782</v>
+        <v>0.6637168141592921</v>
       </c>
     </row>
     <row r="64">
@@ -4684,45 +4678,45 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>501</v>
+        <v>432</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="K64" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J64" s="9" t="n">
-        <v>298</v>
-      </c>
-      <c r="K64" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="L64" s="9" t="n">
-        <v>323</v>
+        <v>286</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.6447105788423154</v>
+        <v>0.6620370370370371</v>
       </c>
     </row>
     <row r="65">
@@ -4731,7 +4725,7 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
@@ -4745,31 +4739,31 @@
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.6412037037037037</v>
+        <v>0.6620046620046619</v>
       </c>
     </row>
     <row r="66">
@@ -4778,45 +4772,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>427</v>
+        <v>459</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="I66" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J66" s="9" t="n">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.639344262295082</v>
+        <v>0.65359477124183</v>
       </c>
     </row>
     <row r="67">
@@ -4825,45 +4819,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>625</v>
+        <v>429</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>219</v>
+        <v>148</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>394</v>
+        <v>280</v>
       </c>
       <c r="K67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>399</v>
+        <v>280</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.6384</v>
+        <v>0.6526806526806527</v>
       </c>
     </row>
     <row r="68">
@@ -4872,45 +4866,45 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.6381156316916489</v>
+        <v>0.649402390438247</v>
       </c>
     </row>
     <row r="69">
@@ -4919,45 +4913,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.6347150259067358</v>
+        <v>0.6466346153846154</v>
       </c>
     </row>
     <row r="70">
@@ -4966,45 +4960,45 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>429</v>
+        <v>471</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>0.634032634032634</v>
+        <v>0.6454352441613588</v>
       </c>
     </row>
     <row r="71">
@@ -5013,45 +5007,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>211</v>
+        <v>301</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>223</v>
+        <v>303</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>0.6335227272727273</v>
+        <v>0.6446808510638298</v>
       </c>
     </row>
     <row r="72">
@@ -5060,45 +5054,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="M72" s="11" t="n">
-        <v>0.6330097087378641</v>
+        <v>0.6423076923076924</v>
       </c>
     </row>
     <row r="73">
@@ -5107,45 +5101,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>572</v>
+        <v>484</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>11</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>360</v>
+        <v>309</v>
       </c>
       <c r="M73" s="11" t="n">
-        <v>0.6293706293706294</v>
+        <v>0.6384297520661157</v>
       </c>
     </row>
     <row r="74">
@@ -5154,45 +5148,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>441</v>
+        <v>625</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>164</v>
+        <v>219</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="I74" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J74" s="9" t="n">
-        <v>272</v>
+        <v>395</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>277</v>
+        <v>399</v>
       </c>
       <c r="M74" s="11" t="n">
-        <v>0.6281179138321995</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="75">
@@ -5201,45 +5195,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>427</v>
+        <v>546</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="K75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>268</v>
+        <v>348</v>
       </c>
       <c r="M75" s="11" t="n">
-        <v>0.6276346604215457</v>
+        <v>0.6373626373626373</v>
       </c>
     </row>
     <row r="76">
@@ -5248,45 +5242,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>478</v>
+        <v>352</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>293</v>
+        <v>211</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>299</v>
+        <v>224</v>
       </c>
       <c r="M76" s="11" t="n">
-        <v>0.6255230125523012</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="77">
@@ -5295,45 +5289,45 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="M77" s="11" t="n">
-        <v>0.6247334754797441</v>
+        <v>0.6359550561797753</v>
       </c>
     </row>
     <row r="78">
@@ -5342,45 +5336,45 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>546</v>
+        <v>518</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I78" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="M78" s="11" t="n">
-        <v>0.6245421245421245</v>
+        <v>0.6351351351351351</v>
       </c>
     </row>
     <row r="79">
@@ -5389,45 +5383,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="M79" s="11" t="n">
-        <v>0.6237623762376238</v>
+        <v>0.6347150259067358</v>
       </c>
     </row>
     <row r="80">
@@ -5436,7 +5430,7 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
@@ -5450,13 +5444,13 @@
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H80" s="9" t="n">
         <v>1</v>
@@ -5465,16 +5459,16 @@
         <v>0</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>258</v>
-      </c>
-      <c r="M80" s="11" t="n">
-        <v>0.6216867469879518</v>
+        <v>272</v>
+      </c>
+      <c r="M80" s="12" t="n">
+        <v>0.634032634032634</v>
       </c>
     </row>
     <row r="81">
@@ -5483,45 +5477,45 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>509</v>
+        <v>405</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>315</v>
-      </c>
-      <c r="M81" s="11" t="n">
-        <v>0.618860510805501</v>
+        <v>256</v>
+      </c>
+      <c r="M81" s="12" t="n">
+        <v>0.6320987654320988</v>
       </c>
     </row>
     <row r="82">
@@ -5530,45 +5524,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>418</v>
+        <v>588</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>251</v>
+        <v>335</v>
       </c>
       <c r="K82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>258</v>
+        <v>371</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.6172248803827751</v>
+        <v>0.6309523809523809</v>
       </c>
     </row>
     <row r="83">
@@ -5577,45 +5571,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>478</v>
+        <v>418</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="H83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>294</v>
+        <v>257</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>295</v>
+        <v>263</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.6171548117154811</v>
+        <v>0.6291866028708134</v>
       </c>
     </row>
     <row r="84">
@@ -5624,45 +5618,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>559</v>
+        <v>514</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>344</v>
+        <v>316</v>
       </c>
       <c r="K84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.6284046692607004</v>
       </c>
     </row>
     <row r="85">
@@ -5671,45 +5665,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>516</v>
+        <v>562</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>313</v>
+        <v>352</v>
       </c>
       <c r="K85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>317</v>
+        <v>352</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.6143410852713178</v>
+        <v>0.6263345195729537</v>
       </c>
     </row>
     <row r="86">
@@ -5718,45 +5712,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>465</v>
+        <v>325</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>176</v>
+        <v>74</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>262</v>
+        <v>202</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>284</v>
+        <v>203</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.610752688172043</v>
+        <v>0.6246153846153846</v>
       </c>
     </row>
     <row r="87">
@@ -5765,45 +5759,45 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.6088888888888889</v>
+        <v>0.6241299303944315</v>
       </c>
     </row>
     <row r="88">
@@ -5812,45 +5806,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>366</v>
+        <v>505</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>207</v>
+        <v>311</v>
       </c>
       <c r="K88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>222</v>
+        <v>315</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.6065573770491803</v>
+        <v>0.6237623762376238</v>
       </c>
     </row>
     <row r="89">
@@ -5859,45 +5853,45 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>430</v>
+        <v>465</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="I89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.6046511627906976</v>
+        <v>0.6193548387096774</v>
       </c>
     </row>
     <row r="90">
@@ -5906,45 +5900,45 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>361</v>
+        <v>475</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>211</v>
+        <v>289</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>217</v>
+        <v>294</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.6011080332409973</v>
+        <v>0.6189473684210526</v>
       </c>
     </row>
     <row r="91">
@@ -5953,45 +5947,45 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="I91" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.6</v>
+        <v>0.6181015452538632</v>
       </c>
     </row>
     <row r="92">
@@ -6000,45 +5994,45 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>402</v>
+        <v>472</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>217</v>
+        <v>258</v>
       </c>
       <c r="K92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>241</v>
+        <v>290</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.599502487562189</v>
+        <v>0.614406779661017</v>
       </c>
     </row>
     <row r="93">
@@ -6047,45 +6041,45 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.5970149253731343</v>
+        <v>0.6088888888888889</v>
       </c>
     </row>
     <row r="94">
@@ -6094,45 +6088,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>504</v>
+        <v>366</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>295</v>
+        <v>207</v>
       </c>
       <c r="K94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>300</v>
+        <v>222</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.5952380952380952</v>
+        <v>0.6065573770491803</v>
       </c>
     </row>
     <row r="95">
@@ -6141,45 +6135,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>468</v>
+        <v>402</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.594017094017094</v>
+        <v>0.6044776119402985</v>
       </c>
     </row>
     <row r="96">
@@ -6188,45 +6182,45 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H96" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I96" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I96" s="9" t="n">
-        <v>4</v>
-      </c>
       <c r="J96" s="9" t="n">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.5906183368869936</v>
+        <v>0.6016949152542372</v>
       </c>
     </row>
     <row r="97">
@@ -6235,45 +6229,45 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>471</v>
+        <v>361</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>259</v>
+        <v>211</v>
       </c>
       <c r="K97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>278</v>
+        <v>217</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.5902335456475584</v>
+        <v>0.6011080332409973</v>
       </c>
     </row>
     <row r="98">
@@ -6282,45 +6276,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>325</v>
+        <v>471</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>186</v>
+        <v>269</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>191</v>
+        <v>283</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.5876923076923077</v>
+        <v>0.6008492569002123</v>
       </c>
     </row>
     <row r="99">
@@ -6329,45 +6323,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>445</v>
+        <v>384</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="G99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="I99" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H99" s="9" t="n">
+      <c r="J99" s="9" t="n">
+        <v>219</v>
+      </c>
+      <c r="K99" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="9" t="n">
-        <v>253</v>
-      </c>
-      <c r="K99" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L99" s="9" t="n">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.5707865168539326</v>
+        <v>0.5989583333333334</v>
       </c>
     </row>
     <row r="100">
@@ -6376,45 +6370,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>496</v>
+        <v>448</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="G100" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="K100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.5705645161290323</v>
+        <v>0.5959821428571429</v>
       </c>
     </row>
     <row r="101">
@@ -6423,45 +6417,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>397</v>
+        <v>500</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="G101" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H101" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I101" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J101" s="9" t="n">
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="K101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>226</v>
+        <v>297</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.5692695214105793</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="102">
@@ -6470,45 +6464,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>376</v>
+        <v>461</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="G102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>207</v>
+        <v>273</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>214</v>
+        <v>273</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.5691489361702128</v>
+        <v>0.5921908893709328</v>
       </c>
     </row>
     <row r="103">
@@ -6517,45 +6511,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>455</v>
+        <v>399</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H103" s="9" t="n">
         <v>8</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.567032967032967</v>
+        <v>0.5864661654135338</v>
       </c>
     </row>
     <row r="104">
@@ -6578,10 +6572,10 @@
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="G104" s="9" t="n">
         <v>2</v>
@@ -6593,16 +6587,16 @@
         <v>2</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="K104" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.5593869731800766</v>
+        <v>0.5828571428571429</v>
       </c>
     </row>
     <row r="105">
@@ -6611,45 +6605,45 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.5577342047930284</v>
+        <v>0.5802197802197803</v>
       </c>
     </row>
     <row r="106">
@@ -6658,45 +6652,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>399</v>
+        <v>536</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>178</v>
+        <v>231</v>
       </c>
       <c r="G106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>284</v>
+      </c>
+      <c r="K106" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="9" t="n">
-        <v>220</v>
-      </c>
-      <c r="K106" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L106" s="9" t="n">
-        <v>220</v>
+        <v>305</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.5513784461152882</v>
+        <v>0.5690298507462687</v>
       </c>
     </row>
     <row r="107">
@@ -6705,45 +6699,45 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Regina Kesya Dumumpe</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="G107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="H107" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I107" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J107" s="9" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.5509708737864077</v>
+        <v>0.5661252900232019</v>
       </c>
     </row>
     <row r="108">
@@ -6752,45 +6746,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Regina Kesya Dumumpe</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="G108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.5458823529411765</v>
+        <v>0.5588972431077694</v>
       </c>
     </row>
     <row r="109">
@@ -6799,45 +6793,45 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="K109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.542654028436019</v>
+        <v>0.5588235294117647</v>
       </c>
     </row>
     <row r="110">
@@ -6846,45 +6840,45 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>512</v>
+        <v>412</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>237</v>
+        <v>170</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I110" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>271</v>
+        <v>221</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>275</v>
+        <v>230</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.537109375</v>
+        <v>0.558252427184466</v>
       </c>
     </row>
     <row r="111">
@@ -6893,45 +6887,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="G111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H111" s="9" t="n">
-        <v>48</v>
-      </c>
-      <c r="I111" s="9" t="n">
-        <v>15</v>
-      </c>
       <c r="J111" s="9" t="n">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.5365344467640919</v>
+        <v>0.5576470588235294</v>
       </c>
     </row>
     <row r="112">
@@ -6940,45 +6934,45 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>402</v>
+        <v>479</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>215</v>
+        <v>264</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.5348258706467661</v>
+        <v>0.5511482254697286</v>
       </c>
     </row>
     <row r="113">
@@ -7004,28 +6998,28 @@
         <v>503</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="K113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.532803180914513</v>
+        <v>0.5407554671968191</v>
       </c>
     </row>
     <row r="114">
@@ -7034,45 +7028,45 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>408</v>
+        <v>481</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>205</v>
+        <v>249</v>
       </c>
       <c r="K114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>217</v>
+        <v>258</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.5318627450980392</v>
+        <v>0.5363825363825364</v>
       </c>
     </row>
     <row r="115">
@@ -7081,45 +7075,45 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>471</v>
+        <v>422</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.5265392781316348</v>
+        <v>0.5355450236966824</v>
       </c>
     </row>
     <row r="116">
@@ -7128,7 +7122,7 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
@@ -7142,31 +7136,31 @@
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>438</v>
+        <v>402</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="G116" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.5228310502283106</v>
+        <v>0.5348258706467661</v>
       </c>
     </row>
     <row r="117">
@@ -7175,24 +7169,24 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>346</v>
+        <v>455</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>166</v>
+        <v>215</v>
       </c>
       <c r="G117" s="9" t="n">
         <v>0</v>
@@ -7204,16 +7198,16 @@
         <v>0</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.5202312138728323</v>
+        <v>0.5274725274725275</v>
       </c>
     </row>
     <row r="118">
@@ -7222,45 +7216,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.5186813186813187</v>
+        <v>0.527114967462039</v>
       </c>
     </row>
     <row r="119">
@@ -7269,45 +7263,45 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.5166666666666667</v>
+        <v>0.5228310502283106</v>
       </c>
     </row>
     <row r="120">
@@ -7330,31 +7324,31 @@
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" s="9" t="n">
         <v>13</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.5135135135135135</v>
+        <v>0.5220588235294118</v>
       </c>
     </row>
     <row r="121">
@@ -7363,45 +7357,45 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>426</v>
+        <v>346</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>209</v>
+        <v>166</v>
       </c>
       <c r="G121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>217</v>
+        <v>180</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0.5093896713615024</v>
+        <v>0.5202312138728323</v>
       </c>
     </row>
     <row r="122">
@@ -7410,45 +7404,45 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="G122" s="9" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="K122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.5076586433260394</v>
+        <v>0.5179372197309418</v>
       </c>
     </row>
     <row r="123">
@@ -7457,45 +7451,45 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.5068181818181818</v>
+        <v>0.5179372197309418</v>
       </c>
     </row>
     <row r="124">
@@ -7504,45 +7498,45 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="G124" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="K124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.5056179775280899</v>
+        <v>0.5159090909090909</v>
       </c>
     </row>
     <row r="125">
@@ -7568,13 +7562,13 @@
         <v>420</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G125" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I125" s="9" t="n">
         <v>0</v>
@@ -7586,10 +7580,10 @@
         <v>0</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.5047619047619047</v>
+        <v>0.5119047619047619</v>
       </c>
     </row>
     <row r="126">
@@ -7598,45 +7592,45 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="G126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.5024038461538461</v>
+        <v>0.5113350125944585</v>
       </c>
     </row>
     <row r="127">
@@ -7645,45 +7639,45 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.5012224938875306</v>
+        <v>0.5096153846153846</v>
       </c>
     </row>
     <row r="128">
@@ -7692,45 +7686,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="K128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.4987468671679198</v>
+        <v>0.5093896713615024</v>
       </c>
     </row>
     <row r="129">
@@ -7739,45 +7733,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.4966139954853273</v>
+        <v>0.5090497737556561</v>
       </c>
     </row>
     <row r="130">
@@ -7786,45 +7780,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>441</v>
+        <v>515</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>215</v>
+        <v>262</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4875283446712018</v>
+        <v>0.5087378640776699</v>
       </c>
     </row>
     <row r="131">
@@ -7833,45 +7827,45 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.4873737373737373</v>
+        <v>0.5061124694376528</v>
       </c>
     </row>
     <row r="132">
@@ -7880,45 +7874,45 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>514</v>
+        <v>425</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>260</v>
+        <v>198</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>249</v>
+        <v>214</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.4844357976653696</v>
+        <v>0.5035294117647059</v>
       </c>
     </row>
     <row r="133">
@@ -7927,45 +7921,45 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="K133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.4833333333333333</v>
+        <v>0.5012531328320802</v>
       </c>
     </row>
     <row r="134">
@@ -7974,45 +7968,45 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Dince Lahaube</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>459</v>
+        <v>339</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>222</v>
+        <v>7</v>
       </c>
       <c r="G134" s="9" t="n">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="H134" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>219</v>
+        <v>164</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.477124183006536</v>
+        <v>0.4837758112094395</v>
       </c>
     </row>
     <row r="135">
@@ -8021,45 +8015,45 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.4680851063829787</v>
+        <v>0.477124183006536</v>
       </c>
     </row>
     <row r="136">
@@ -8068,45 +8062,45 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Dince Lahaube</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E136" s="9" t="n">
-        <v>332</v>
+        <v>424</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>8</v>
+        <v>223</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>174</v>
+        <v>1</v>
       </c>
       <c r="H136" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136" s="9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J136" s="9" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="K136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.4518072289156627</v>
+        <v>0.4716981132075472</v>
       </c>
     </row>
   </sheetData>
@@ -8135,7 +8129,7 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8149,7 +8143,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 22 Juli 2026</t>
+          <t>Hari/Tanggal : 23 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8166,17 +8160,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 08.16 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-37):</t>
+          <t>Target Hari Ini (H-38):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.79%</t>
+          <t>63.46%</t>
         </is>
       </c>
     </row>
@@ -8268,31 +8262,31 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2934</v>
+        <v>2938</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2496</v>
+        <v>2560</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2504</v>
+        <v>2568</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.8534423994546694</v>
+        <v>0.874063989108237</v>
       </c>
     </row>
     <row r="8">
@@ -8315,31 +8309,31 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2835</v>
+        <v>2841</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>14</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>2170</v>
+        <v>2175</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>2186</v>
+        <v>2191</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.7710758377425044</v>
+        <v>0.7712073213657163</v>
       </c>
     </row>
     <row r="9">
@@ -8348,45 +8342,45 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Sutrisno Sariang</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Nusa Tabukan, Tabukan Utara</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Alfi, Hendri</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2038</v>
+        <v>2534</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>436</v>
+        <v>579</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1530</v>
+        <v>1939</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>1542</v>
+        <v>1943</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.7566241413150148</v>
+        <v>0.7667719021310182</v>
       </c>
     </row>
     <row r="10">
@@ -8395,45 +8389,45 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Sutrisno Sariang</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan, Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Alfi, Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2519</v>
+        <v>2041</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>624</v>
+        <v>433</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="I10" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>1532</v>
+      </c>
+      <c r="K10" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="J10" s="9" t="n">
-        <v>1862</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" s="9" t="n">
-        <v>1866</v>
+        <v>1541</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.740770146883684</v>
+        <v>0.7550220480156785</v>
       </c>
     </row>
     <row r="11">
@@ -8459,16 +8453,16 @@
         <v>2936</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>74</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>2112</v>
@@ -8477,10 +8471,10 @@
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>2173</v>
+        <v>2168</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7401226158038147</v>
+        <v>0.7384196185286104</v>
       </c>
     </row>
     <row r="12">
@@ -8503,31 +8497,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2867</v>
+        <v>2872</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>710</v>
+        <v>686</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>2079</v>
+        <v>2104</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2087</v>
+        <v>2114</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7279386117893268</v>
+        <v>0.7360724233983287</v>
       </c>
     </row>
     <row r="13">
@@ -8550,31 +8544,31 @@
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2911</v>
+        <v>2924</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>936</v>
+        <v>914</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1906</v>
+        <v>1950</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1914</v>
+        <v>1957</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6575060116798351</v>
+        <v>0.6692886456908345</v>
       </c>
     </row>
     <row r="14">
@@ -8583,45 +8577,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu, Tamako</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike, Mega</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2803</v>
+        <v>2439</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>863</v>
+        <v>809</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1817</v>
+        <v>1585</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1830</v>
+        <v>1599</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6528719229397075</v>
+        <v>0.6555965559655597</v>
       </c>
     </row>
     <row r="15">
@@ -8630,45 +8624,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2119</v>
+        <v>2820</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>661</v>
+        <v>844</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1380</v>
+        <v>1832</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1382</v>
+        <v>1843</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.6521944313355357</v>
+        <v>0.6535460992907801</v>
       </c>
     </row>
     <row r="16">
@@ -8677,45 +8671,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Manganitu, Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Erike, Mega</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2428</v>
+        <v>2122</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>834</v>
+        <v>646</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1554</v>
+        <v>1380</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1563</v>
+        <v>1381</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.6437397034596376</v>
+        <v>0.6508011310084825</v>
       </c>
     </row>
     <row r="17">
@@ -8724,45 +8718,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2181</v>
+        <v>2905</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>753</v>
+        <v>994</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1349</v>
+        <v>1834</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1362</v>
+        <v>1860</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.624484181568088</v>
+        <v>0.6402753872633391</v>
       </c>
     </row>
     <row r="18">
@@ -8771,45 +8765,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2898</v>
+        <v>2849</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1053</v>
+        <v>1060</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1772</v>
+        <v>1743</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1799</v>
-      </c>
-      <c r="M18" s="11" t="n">
-        <v>0.6207729468599034</v>
+        <v>1785</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>0.6265356265356266</v>
       </c>
     </row>
     <row r="19">
@@ -8818,45 +8812,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2835</v>
+        <v>2185</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1090</v>
+        <v>743</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1724</v>
+        <v>1355</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1738</v>
+        <v>1368</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.6130511463844798</v>
+        <v>0.6260869565217392</v>
       </c>
     </row>
     <row r="20">
@@ -8865,45 +8859,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Kezia Maralending</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2682</v>
+        <v>1456</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1073</v>
+        <v>295</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>22</v>
+        <v>260</v>
       </c>
       <c r="H20" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>876</v>
+      </c>
+      <c r="K20" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>1582</v>
-      </c>
-      <c r="K20" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="L20" s="9" t="n">
-        <v>1583</v>
+        <v>882</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.5902311707680835</v>
+        <v>0.6057692307692307</v>
       </c>
     </row>
     <row r="21">
@@ -8912,45 +8906,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2324</v>
+        <v>2694</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>896</v>
+        <v>1031</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1315</v>
+        <v>1630</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1339</v>
+        <v>1631</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.5761617900172117</v>
+        <v>0.605419450631032</v>
       </c>
     </row>
     <row r="22">
@@ -8959,45 +8953,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Kezia Maralending</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>1439</v>
+        <v>2470</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>338</v>
+        <v>858</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>275</v>
+        <v>29</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>802</v>
+        <v>1428</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>813</v>
+        <v>1466</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.5649756775538568</v>
+        <v>0.5935222672064777</v>
       </c>
     </row>
     <row r="23">
@@ -9006,45 +9000,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2727</v>
+        <v>2346</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1101</v>
+        <v>859</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="H23" s="9" t="n">
         <v>64</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1511</v>
+        <v>1331</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1515</v>
+        <v>1355</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5775788576300085</v>
       </c>
     </row>
     <row r="24">
@@ -9053,45 +9047,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2465</v>
+        <v>2746</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>873</v>
+        <v>1085</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1355</v>
+        <v>1530</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>1359</v>
+        <v>1536</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5513184584178499</v>
+        <v>0.5593590677348871</v>
       </c>
     </row>
     <row r="25">
@@ -9100,45 +9094,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2562</v>
+        <v>2727</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1127</v>
+        <v>1187</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1394</v>
+        <v>1483</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>1397</v>
+        <v>1487</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5452771272443404</v>
+        <v>0.5452878621195453</v>
       </c>
     </row>
     <row r="26">
@@ -9147,45 +9141,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2418</v>
+        <v>2572</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1033</v>
+        <v>1100</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1208</v>
+        <v>1398</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1268</v>
+        <v>1401</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.5244003308519437</v>
+        <v>0.5447122861586314</v>
       </c>
     </row>
     <row r="27">
@@ -9208,31 +9202,31 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2108</v>
+        <v>2123</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>965</v>
+        <v>948</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1012</v>
+        <v>1052</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>1095</v>
+        <v>1154</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.5194497153700189</v>
+        <v>0.5435704192180876</v>
       </c>
     </row>
     <row r="28">
@@ -9241,45 +9235,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2721</v>
+        <v>2422</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1211</v>
+        <v>999</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1396</v>
+        <v>1219</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1401</v>
+        <v>1278</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.5148842337375965</v>
+        <v>0.5276630883567299</v>
       </c>
     </row>
     <row r="29">
@@ -9302,31 +9296,31 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>984</v>
+        <v>968</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1003</v>
+        <v>1046</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1016</v>
+        <v>1074</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.4889316650625601</v>
+        <v>0.5165945165945166</v>
       </c>
     </row>
   </sheetData>
@@ -9360,7 +9354,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 22 Juli 2026</t>
+          <t>Hari/Tanggal : 23 Juli 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9377,17 +9371,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 08.16 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-37):</t>
+          <t>Target Hari Ini (H-38):</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>61.79%</t>
+          <t>63.46%</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9418,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.802065404475043</v>
+        <v>0.821765209940017</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9442,7 +9436,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7882938978829389</v>
+        <v>0.7958359229334991</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9460,7 +9454,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7697285353535354</v>
+        <v>0.7740104084529255</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9478,7 +9472,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7430703624733475</v>
+        <v>0.755411714770798</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -9496,7 +9490,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.7293721433726245</v>
+        <v>0.7362478981503723</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9514,11 +9508,11 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.6550724637681159</v>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>+1</t>
+        <v>0.6621751684311838</v>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9532,11 +9526,11 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.6448516579406632</v>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>+1</t>
+        <v>0.6527050610820244</v>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9552,9 +9546,9 @@
       <c r="C14" s="11" t="n">
         <v>0.6384</v>
       </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>-2</t>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9562,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.6144620811287478</v>
+        <v>0.6268866268866269</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -9586,7 +9580,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.6041746457296056</v>
+        <v>0.6246429251571129</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9604,11 +9598,11 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.5740097289784573</v>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>+2</t>
+        <v>0.6188186813186813</v>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9622,11 +9616,11 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.5735483870967742</v>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>-1</t>
+        <v>0.5841371918542336</v>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9640,11 +9634,11 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.5709717097170972</v>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>-1</t>
+        <v>0.5840577935594465</v>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9652,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.5632754342431762</v>
+        <v>0.5776218001651527</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
@@ -9676,7 +9670,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.553198487090939</v>
+        <v>0.5654878847413228</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.16 WITA</t>
+          <t>Pukul        : 08.39 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.16 WITA</t>
+          <t>Pukul        : 08.39 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.16 WITA</t>
+          <t>Pukul        : 08.39 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9371,7 +9371,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.16 WITA</t>
+          <t>Pukul        : 08.39 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,6 +91,10 @@
     </font>
     <font>
       <color rgb="00595959"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="8">
@@ -163,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -188,6 +192,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -588,7 +594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 23 Juli 2026</t>
+          <t>Hari/Tanggal : 24 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -610,32 +616,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.39 WITA</t>
+          <t>Pukul        : 11.14 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-38):</t>
+          <t>Target Hari Ini (H-39):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>63.46%</t>
+          <t>65.13%</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Hijau &gt;= 63.46%</t>
+          <t>Hijau &gt;= 65.13%</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Kuning 31.73% - 63.46%</t>
+          <t>Kuning 32.56% - 65.13%</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Merah &lt; 31.73%</t>
+          <t>Merah &lt; 32.56%</t>
         </is>
       </c>
     </row>
@@ -744,27 +750,27 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4163</v>
+        <v>4172</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1079</v>
+        <v>1040</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
         <v/>
       </c>
       <c r="F7" s="9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="10">
         <f>F7/B7</f>
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
@@ -778,7 +784,7 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2912</v>
+        <v>2992</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
@@ -792,14 +798,14 @@
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>3065</v>
+        <v>3111</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -813,41 +819,41 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1456</v>
+        <v>1466</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
         <v/>
       </c>
       <c r="J8" s="9" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="K8" s="10">
         <f>J8/B8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>876</v>
+        <v>906</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -861,14 +867,14 @@
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>901</v>
+        <v>951</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -882,41 +888,41 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6341</v>
+        <v>6361</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1340</v>
+        <v>1288</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4636</v>
+        <v>4722</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -930,14 +936,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4908</v>
+        <v>4970</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -951,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3218</v>
+        <v>3237</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>657</v>
+        <v>601</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -971,21 +977,21 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K10" s="10">
         <f>J10/B10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2482</v>
+        <v>2523</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
@@ -999,14 +1005,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2561</v>
+        <v>2636</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1020,27 +1026,27 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
@@ -1054,7 +1060,7 @@
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>724</v>
+        <v>741</v>
       </c>
       <c r="M11" s="10">
         <f>L11/B11</f>
@@ -1068,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1109,7 +1115,7 @@
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
@@ -1123,7 +1129,7 @@
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>631</v>
+        <v>686</v>
       </c>
       <c r="M12" s="10">
         <f>L12/B12</f>
@@ -1144,7 +1150,7 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1158,41 +1164,41 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4665</v>
+        <v>4724</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1909</v>
+        <v>1861</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2519</v>
+        <v>2650</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1206,14 +1212,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2725</v>
+        <v>2841</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1227,62 +1233,62 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6108</v>
+        <v>6152</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2628</v>
+        <v>2508</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3263</v>
+        <v>3356</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
         <v/>
       </c>
       <c r="N14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="10">
         <f>N14/B14</f>
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3454</v>
+        <v>3616</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>90</v>
+        <v>162</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1296,41 +1302,41 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8167</v>
+        <v>8194</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3303</v>
+        <v>3201</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K15" s="10">
         <f>J15/B15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4643</v>
+        <v>4815</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1344,14 +1350,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4770</v>
+        <v>4880</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1365,41 +1371,41 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5251</v>
+        <v>5277</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1853</v>
+        <v>1756</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>3165</v>
+        <v>3305</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1413,14 +1419,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3280</v>
+        <v>3387</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1434,62 +1440,62 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2422</v>
+        <v>2427</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>999</v>
+        <v>944</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1219</v>
+        <v>1266</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
         <v/>
       </c>
       <c r="N17" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O17" s="10">
         <f>N17/B17</f>
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1399</v>
+        <v>1447</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1503,41 +1509,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9424</v>
+        <v>9491</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2227</v>
+        <v>2070</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>162</v>
+        <v>270</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6933</v>
+        <v>7025</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1551,14 +1557,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>7119</v>
+        <v>7317</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>149</v>
+        <v>198</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1572,13 +1578,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1167</v>
+        <v>1174</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1592,14 +1598,14 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
         <v/>
       </c>
       <c r="J19" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" s="10">
         <f>J19/B19</f>
@@ -1620,14 +1626,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>959</v>
+        <v>1001</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1691,7 +1697,7 @@
       <c r="P20" s="9" t="n">
         <v>399</v>
       </c>
-      <c r="Q20" s="11">
+      <c r="Q20" s="12">
         <f>P20/B20</f>
         <v/>
       </c>
@@ -1710,13 +1716,13 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2849</v>
+        <v>2870</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1060</v>
+        <v>1016</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
@@ -1730,21 +1736,21 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1743</v>
+        <v>1798</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1758,14 +1764,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1786</v>
+        <v>1851</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1894,7 +1900,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 23 Juli 2026</t>
+          <t>Hari/Tanggal : 24 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1911,17 +1917,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.39 WITA</t>
+          <t>Pukul        : 11.14 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-38):</t>
+          <t>Target Hari Ini (H-39):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>63.46%</t>
+          <t>65.13%</t>
         </is>
       </c>
     </row>
@@ -2110,13 +2116,13 @@
         <v>571</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
@@ -2128,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.9772329246935202</v>
+        <v>0.9807355516637479</v>
       </c>
     </row>
     <row r="10">
@@ -2140,45 +2146,45 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Merry Christiani Lano</t>
+          <t>Alfred Jonathan</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>530</v>
+        <v>386</v>
       </c>
       <c r="F10" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="G10" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>16</v>
-      </c>
       <c r="I10" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>478</v>
+        <v>340</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>497</v>
+        <v>367</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.9377358490566039</v>
+        <v>0.9507772020725389</v>
       </c>
     </row>
     <row r="11">
@@ -2187,45 +2193,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Ayu Lestari Areros</t>
+          <t>Merry Christiani Lano</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>311</v>
+        <v>532</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>25</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>286</v>
+        <v>498</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.9196141479099679</v>
+        <v>0.9360902255639096</v>
       </c>
     </row>
     <row r="12">
@@ -2251,13 +2257,13 @@
         <v>511</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I12" s="9" t="n">
         <v>0</v>
@@ -2269,10 +2275,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.9119373776908023</v>
+        <v>0.9275929549902152</v>
       </c>
     </row>
     <row r="13">
@@ -2281,45 +2287,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Alfred Jonathan</t>
+          <t>Ayu Lestari Areros</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>380</v>
+        <v>311</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>340</v>
+        <v>280</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>340</v>
+        <v>286</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.9196141479099679</v>
       </c>
     </row>
     <row r="14">
@@ -2375,21 +2381,21 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Clara Patricia Pangandaheng</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>43</v>
@@ -2398,22 +2404,22 @@
         <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.8818681318681318</v>
+        <v>0.8880208333333335</v>
       </c>
     </row>
     <row r="16">
@@ -2422,45 +2428,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Clara Patricia Pangandaheng</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I16" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.870026525198939</v>
+        <v>0.8818681318681318</v>
       </c>
     </row>
     <row r="17">
@@ -2486,16 +2492,16 @@
         <v>416</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="9" t="n">
         <v>353</v>
@@ -2504,10 +2510,10 @@
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8533653846153846</v>
+        <v>0.8725961538461539</v>
       </c>
     </row>
     <row r="18">
@@ -2530,31 +2536,31 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I18" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.8673218673218673</v>
       </c>
     </row>
     <row r="19">
@@ -2563,7 +2569,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -2577,31 +2583,31 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>500</v>
+        <v>399</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>412</v>
+        <v>325</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>421</v>
+        <v>342</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.8420000000000001</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="20">
@@ -2610,7 +2616,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -2624,31 +2630,31 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>389</v>
+        <v>507</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>325</v>
+        <v>429</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>327</v>
+        <v>429</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.8406169665809768</v>
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="21">
@@ -2680,13 +2686,13 @@
         <v>2</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
@@ -2704,45 +2710,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.8317972350230414</v>
+        <v>0.8372641509433962</v>
       </c>
     </row>
     <row r="23">
@@ -2751,45 +2757,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>426</v>
+        <v>480</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>352</v>
+        <v>401</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.8262910798122065</v>
+        <v>0.8354166666666667</v>
       </c>
     </row>
     <row r="24">
@@ -2798,7 +2804,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -2812,31 +2818,31 @@
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>505</v>
+        <v>434</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>404</v>
+        <v>362</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>417</v>
+        <v>362</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.8257425742574257</v>
+        <v>0.8341013824884793</v>
       </c>
     </row>
     <row r="25">
@@ -2845,45 +2851,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>394</v>
+        <v>427</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.8225469728601253</v>
+        <v>0.833984375</v>
       </c>
     </row>
     <row r="26">
@@ -2906,16 +2912,16 @@
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>3</v>
@@ -2927,10 +2933,10 @@
         <v>1</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.8061224489795918</v>
+        <v>0.8333333333333335</v>
       </c>
     </row>
     <row r="27">
@@ -2939,45 +2945,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>318</v>
+        <v>352</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.7905882352941176</v>
+        <v>0.8262910798122065</v>
       </c>
     </row>
     <row r="28">
@@ -3000,31 +3006,31 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>0.7879924953095684</v>
+        <v>0.8014981273408239</v>
       </c>
     </row>
     <row r="29">
@@ -3033,45 +3039,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Sheryl Jessica Tatontos</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>498</v>
+        <v>427</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.7831325301204819</v>
+        <v>0.7962529274004683</v>
       </c>
     </row>
     <row r="30">
@@ -3080,45 +3086,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Sheryl Jessica Tatontos</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>424</v>
+        <v>508</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>328</v>
+        <v>403</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7735849056603774</v>
+        <v>0.7933070866141734</v>
       </c>
     </row>
     <row r="31">
@@ -3127,45 +3133,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>386</v>
+        <v>503</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>281</v>
+        <v>383</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>298</v>
+        <v>390</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7720207253886009</v>
+        <v>0.7753479125248509</v>
       </c>
     </row>
     <row r="32">
@@ -3174,45 +3180,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>503</v>
+        <v>408</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>375</v>
+        <v>290</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>382</v>
+        <v>315</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.7594433399602386</v>
+        <v>0.7720588235294117</v>
       </c>
     </row>
     <row r="33">
@@ -3221,7 +3227,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -3235,31 +3241,31 @@
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>561</v>
+        <v>386</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>398</v>
+        <v>296</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>425</v>
+        <v>298</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.7575757575757575</v>
+        <v>0.7720207253886009</v>
       </c>
     </row>
     <row r="34">
@@ -3268,45 +3274,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I34" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.7570754716981132</v>
+        <v>0.7710280373831776</v>
       </c>
     </row>
     <row r="35">
@@ -3315,45 +3321,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>410</v>
+        <v>561</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>291</v>
+        <v>424</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>310</v>
+        <v>432</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.7700534759358288</v>
       </c>
     </row>
     <row r="36">
@@ -3362,45 +3368,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>519</v>
+        <v>412</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>375</v>
+        <v>291</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>389</v>
+        <v>317</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7495183044315994</v>
+        <v>0.7694174757281553</v>
       </c>
     </row>
     <row r="37">
@@ -3409,45 +3415,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>508</v>
+        <v>429</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>374</v>
+        <v>320</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7480314960629921</v>
+        <v>0.7668997668997669</v>
       </c>
     </row>
     <row r="38">
@@ -3456,45 +3462,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>408</v>
+        <v>554</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>302</v>
+        <v>418</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>304</v>
+        <v>424</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.7450980392156863</v>
+        <v>0.7653429602888085</v>
       </c>
     </row>
     <row r="39">
@@ -3503,45 +3509,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>547</v>
+        <v>519</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>406</v>
+        <v>377</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7440585009140768</v>
+        <v>0.7495183044315994</v>
       </c>
     </row>
     <row r="40">
@@ -3550,45 +3556,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>425</v>
+        <v>511</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>291</v>
+        <v>374</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>314</v>
+        <v>380</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.7388235294117647</v>
+        <v>0.7436399217221134</v>
       </c>
     </row>
     <row r="41">
@@ -3597,45 +3603,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>350</v>
+        <v>458</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I41" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>258</v>
+        <v>339</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.7371428571428571</v>
+        <v>0.7401746724890831</v>
       </c>
     </row>
     <row r="42">
@@ -3644,45 +3650,45 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>392</v>
+        <v>350</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I42" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>255</v>
+      </c>
+      <c r="K42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="9" t="n">
-        <v>253</v>
-      </c>
-      <c r="K42" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" s="9" t="n">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.7295918367346939</v>
+        <v>0.7371428571428571</v>
       </c>
     </row>
     <row r="43">
@@ -3691,45 +3697,45 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>458</v>
+        <v>515</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>376</v>
+      </c>
+      <c r="K43" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="9" t="n">
-        <v>332</v>
-      </c>
-      <c r="K43" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" s="9" t="n">
-        <v>333</v>
+        <v>378</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.7270742358078602</v>
+        <v>0.7339805825242719</v>
       </c>
     </row>
     <row r="44">
@@ -3755,16 +3761,16 @@
         <v>505</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J44" s="9" t="n">
         <v>349</v>
@@ -3773,10 +3779,10 @@
         <v>0</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.7207920792079208</v>
+        <v>0.7306930693069308</v>
       </c>
     </row>
     <row r="45">
@@ -3785,45 +3791,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Ruslan Ginoga</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.7115902964959568</v>
+        <v>0.7295918367346939</v>
       </c>
     </row>
     <row r="46">
@@ -3832,45 +3838,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>508</v>
+        <v>458</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>359</v>
+        <v>332</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.7086614173228347</v>
+        <v>0.7292576419213974</v>
       </c>
     </row>
     <row r="47">
@@ -3879,45 +3885,45 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Ruslan Ginoga</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>458</v>
+        <v>372</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>291</v>
+        <v>260</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>323</v>
+        <v>271</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.7052401746724891</v>
+        <v>0.7284946236559139</v>
       </c>
     </row>
     <row r="48">
@@ -3940,31 +3946,31 @@
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.7048710601719198</v>
+        <v>0.71875</v>
       </c>
     </row>
     <row r="49">
@@ -3973,45 +3979,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.7026315789473684</v>
+        <v>0.7153465346534653</v>
       </c>
     </row>
     <row r="50">
@@ -4020,45 +4026,45 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>390</v>
+        <v>534</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>223</v>
+        <v>344</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>273</v>
+        <v>381</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.7</v>
+        <v>0.7134831460674157</v>
       </c>
     </row>
     <row r="51">
@@ -4067,7 +4073,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -4081,31 +4087,31 @@
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>527</v>
+        <v>471</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>341</v>
+        <v>313</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>368</v>
+        <v>336</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.6982922201138519</v>
+        <v>0.7133757961783439</v>
       </c>
     </row>
     <row r="52">
@@ -4114,45 +4120,45 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>469</v>
+        <v>383</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>327</v>
+        <v>272</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.697228144989339</v>
+        <v>0.7101827676240208</v>
       </c>
     </row>
     <row r="53">
@@ -4161,45 +4167,45 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>510</v>
+        <v>455</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>339</v>
+        <v>311</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.6823529411764706</v>
+        <v>0.6967032967032967</v>
       </c>
     </row>
     <row r="54">
@@ -4208,45 +4214,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>302</v>
+        <v>344</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>309</v>
+        <v>356</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.6791208791208792</v>
+        <v>0.6939571150097466</v>
       </c>
     </row>
     <row r="55">
@@ -4269,31 +4275,31 @@
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I55" s="9" t="n">
         <v>3</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="K55" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.6790697674418604</v>
+        <v>0.6912442396313364</v>
       </c>
     </row>
     <row r="56">
@@ -4316,13 +4322,13 @@
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H56" s="9" t="n">
         <v>0</v>
@@ -4331,16 +4337,16 @@
         <v>0</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.6767241379310345</v>
+        <v>0.6909871244635193</v>
       </c>
     </row>
     <row r="57">
@@ -4349,45 +4355,45 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.673076923076923</v>
+        <v>0.689095127610209</v>
       </c>
     </row>
     <row r="58">
@@ -4396,45 +4402,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="K58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.6724890829694323</v>
+        <v>0.6850220264317179</v>
       </c>
     </row>
     <row r="59">
@@ -4443,27 +4449,27 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>289</v>
+        <v>483</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H59" s="9" t="n">
         <v>0</v>
@@ -4472,16 +4478,16 @@
         <v>1</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>191</v>
+        <v>329</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>194</v>
+        <v>330</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.671280276816609</v>
+        <v>0.6832298136645963</v>
       </c>
     </row>
     <row r="60">
@@ -4490,45 +4496,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>506</v>
+        <v>466</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>324</v>
+        <v>281</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.6699604743083004</v>
+        <v>0.6802575107296137</v>
       </c>
     </row>
     <row r="61">
@@ -4537,45 +4543,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>482</v>
+        <v>433</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>293</v>
+      </c>
+      <c r="K61" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J61" s="9" t="n">
-        <v>296</v>
-      </c>
-      <c r="K61" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L61" s="9" t="n">
-        <v>322</v>
+        <v>294</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.6680497925311202</v>
+        <v>0.6789838337182448</v>
       </c>
     </row>
     <row r="62">
@@ -4584,45 +4590,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>435</v>
+        <v>507</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>278</v>
+        <v>342</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>290</v>
+        <v>344</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.6785009861932939</v>
       </c>
     </row>
     <row r="63">
@@ -4631,45 +4637,45 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>452</v>
+        <v>416</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.6637168141592921</v>
+        <v>0.673076923076923</v>
       </c>
     </row>
     <row r="64">
@@ -4678,45 +4684,45 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.6620370370370371</v>
+        <v>0.6724890829694323</v>
       </c>
     </row>
     <row r="65">
@@ -4725,45 +4731,45 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>429</v>
+        <v>527</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="I65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>277</v>
+        <v>329</v>
       </c>
       <c r="K65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>284</v>
+        <v>354</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.6620046620046619</v>
+        <v>0.6717267552182163</v>
       </c>
     </row>
     <row r="66">
@@ -4772,45 +4778,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>459</v>
+        <v>289</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I66" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>281</v>
+        <v>191</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>300</v>
+        <v>194</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.65359477124183</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="67">
@@ -4819,45 +4825,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>429</v>
+        <v>486</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>280</v>
+        <v>326</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.6526806526806527</v>
+        <v>0.6707818930041153</v>
       </c>
     </row>
     <row r="68">
@@ -4866,45 +4872,45 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>502</v>
+        <v>419</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I68" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>326</v>
+        <v>281</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.649402390438247</v>
+        <v>0.6706443914081146</v>
       </c>
     </row>
     <row r="69">
@@ -4913,45 +4919,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.6466346153846154</v>
+        <v>0.6705336426914154</v>
       </c>
     </row>
     <row r="70">
@@ -4960,45 +4966,45 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>471</v>
+        <v>435</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>166</v>
+        <v>128</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H70" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I70" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>0.6454352441613588</v>
+        <v>0.6666666666666665</v>
       </c>
     </row>
     <row r="71">
@@ -5007,7 +5013,7 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -5021,31 +5027,31 @@
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>470</v>
+        <v>433</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>0.6446808510638298</v>
+        <v>0.6651270207852193</v>
       </c>
     </row>
     <row r="72">
@@ -5054,7 +5060,7 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -5068,31 +5074,31 @@
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>520</v>
+        <v>473</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="M72" s="11" t="n">
-        <v>0.6423076923076924</v>
+        <v>0.6596194503171248</v>
       </c>
     </row>
     <row r="73">
@@ -5101,45 +5107,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>484</v>
+        <v>433</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>303</v>
+        <v>268</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="M73" s="11" t="n">
-        <v>0.6384297520661157</v>
+        <v>0.6581986143187067</v>
       </c>
     </row>
     <row r="74">
@@ -5148,45 +5154,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>625</v>
+        <v>472</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>219</v>
+        <v>161</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>395</v>
+        <v>309</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>399</v>
+        <v>310</v>
       </c>
       <c r="M74" s="11" t="n">
-        <v>0.6384</v>
+        <v>0.6567796610169492</v>
       </c>
     </row>
     <row r="75">
@@ -5195,45 +5201,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>546</v>
+        <v>502</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H75" s="9" t="n">
         <v>11</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="K75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="M75" s="11" t="n">
-        <v>0.6373626373626373</v>
+        <v>0.655378486055777</v>
       </c>
     </row>
     <row r="76">
@@ -5242,45 +5248,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>352</v>
+        <v>410</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>211</v>
+        <v>257</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>224</v>
+        <v>268</v>
       </c>
       <c r="M76" s="11" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.653658536585366</v>
       </c>
     </row>
     <row r="77">
@@ -5289,45 +5295,45 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>445</v>
+        <v>506</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>272</v>
+        <v>323</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="M77" s="11" t="n">
-        <v>0.6359550561797753</v>
+        <v>0.6521739130434783</v>
       </c>
     </row>
     <row r="78">
@@ -5350,31 +5356,31 @@
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I78" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="K78" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="M78" s="11" t="n">
-        <v>0.6351351351351351</v>
+        <v>0.6521739130434783</v>
       </c>
     </row>
     <row r="79">
@@ -5383,45 +5389,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>386</v>
+        <v>449</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>233</v>
+        <v>289</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>245</v>
-      </c>
-      <c r="M79" s="11" t="n">
-        <v>0.6347150259067358</v>
+        <v>291</v>
+      </c>
+      <c r="M79" s="12" t="n">
+        <v>0.6481069042316259</v>
       </c>
     </row>
     <row r="80">
@@ -5430,45 +5436,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>429</v>
+        <v>591</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="G80" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H80" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I80" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J80" s="9" t="n">
-        <v>271</v>
+        <v>381</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>272</v>
+        <v>383</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.634032634032634</v>
+        <v>0.6480541455160744</v>
       </c>
     </row>
     <row r="81">
@@ -5477,7 +5483,7 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -5491,31 +5497,31 @@
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>405</v>
+        <v>477</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>256</v>
+        <v>308</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.6320987654320988</v>
+        <v>0.6457023060796646</v>
       </c>
     </row>
     <row r="82">
@@ -5524,45 +5530,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>588</v>
+        <v>420</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>197</v>
+        <v>147</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>335</v>
+        <v>257</v>
       </c>
       <c r="K82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>371</v>
+        <v>271</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.6309523809523809</v>
+        <v>0.6452380952380953</v>
       </c>
     </row>
     <row r="83">
@@ -5571,45 +5577,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>418</v>
+        <v>520</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>257</v>
+        <v>321</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>263</v>
+        <v>335</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.6291866028708134</v>
+        <v>0.6442307692307694</v>
       </c>
     </row>
     <row r="84">
@@ -5618,45 +5624,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>514</v>
+        <v>625</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="G84" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H84" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I84" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="J84" s="9" t="n">
-        <v>316</v>
+        <v>395</v>
       </c>
       <c r="K84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>323</v>
+        <v>399</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.6284046692607004</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="85">
@@ -5665,45 +5671,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>562</v>
+        <v>467</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>352</v>
+        <v>279</v>
       </c>
       <c r="K85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>352</v>
+        <v>298</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.6263345195729537</v>
+        <v>0.6381156316916489</v>
       </c>
     </row>
     <row r="86">
@@ -5712,45 +5718,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>325</v>
+        <v>546</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>202</v>
+        <v>344</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>203</v>
+        <v>348</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.6246153846153846</v>
+        <v>0.6373626373626373</v>
       </c>
     </row>
     <row r="87">
@@ -5759,45 +5765,45 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>431</v>
+        <v>573</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>264</v>
+        <v>365</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>269</v>
+        <v>365</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.6241299303944315</v>
+        <v>0.6369982547993019</v>
       </c>
     </row>
     <row r="88">
@@ -5806,45 +5812,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>505</v>
+        <v>352</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>182</v>
+        <v>128</v>
       </c>
       <c r="G88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="H88" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I88" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="J88" s="9" t="n">
-        <v>311</v>
+        <v>216</v>
       </c>
       <c r="K88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>315</v>
+        <v>224</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.6237623762376238</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="89">
@@ -5853,45 +5859,45 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>465</v>
+        <v>386</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="K89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>288</v>
+        <v>245</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.6193548387096774</v>
+        <v>0.6347150259067358</v>
       </c>
     </row>
     <row r="90">
@@ -5900,7 +5906,7 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
@@ -5914,31 +5920,31 @@
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>475</v>
+        <v>454</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.6189473684210526</v>
+        <v>0.6343612334801763</v>
       </c>
     </row>
     <row r="91">
@@ -5947,45 +5953,45 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>453</v>
+        <v>326</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>252</v>
+        <v>205</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>280</v>
+        <v>206</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.6181015452538632</v>
+        <v>0.6319018404907976</v>
       </c>
     </row>
     <row r="92">
@@ -5994,45 +6000,45 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>472</v>
+        <v>392</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>290</v>
+        <v>246</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.614406779661017</v>
+        <v>0.6275510204081632</v>
       </c>
     </row>
     <row r="93">
@@ -6041,45 +6047,45 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.6088888888888889</v>
+        <v>0.6210526315789474</v>
       </c>
     </row>
     <row r="94">
@@ -6088,45 +6094,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="K94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.6065573770491803</v>
+        <v>0.6206896551724138</v>
       </c>
     </row>
     <row r="95">
@@ -6135,45 +6141,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>402</v>
+        <v>461</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>238</v>
+        <v>285</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>243</v>
+        <v>286</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.6044776119402985</v>
+        <v>0.6203904555314533</v>
       </c>
     </row>
     <row r="96">
@@ -6182,30 +6188,30 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I96" s="9" t="n">
         <v>2</v>
@@ -6217,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.6016949152542372</v>
+        <v>0.6203090507726269</v>
       </c>
     </row>
     <row r="97">
@@ -6229,45 +6235,45 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>361</v>
+        <v>471</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>217</v>
+        <v>291</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.6011080332409973</v>
+        <v>0.6178343949044586</v>
       </c>
     </row>
     <row r="98">
@@ -6276,45 +6282,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.6008492569002123</v>
+        <v>0.6147368421052631</v>
       </c>
     </row>
     <row r="99">
@@ -6323,45 +6329,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>384</v>
+        <v>450</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>219</v>
+        <v>269</v>
       </c>
       <c r="K99" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.5989583333333334</v>
+        <v>0.6133333333333333</v>
       </c>
     </row>
     <row r="100">
@@ -6370,45 +6376,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>448</v>
+        <v>362</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>259</v>
+        <v>216</v>
       </c>
       <c r="K100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>267</v>
+        <v>221</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.5959821428571429</v>
+        <v>0.6104972375690608</v>
       </c>
     </row>
     <row r="101">
@@ -6417,45 +6423,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>500</v>
+        <v>366</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>281</v>
+        <v>222</v>
       </c>
       <c r="K101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>297</v>
+        <v>222</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.594</v>
+        <v>0.6065573770491803</v>
       </c>
     </row>
     <row r="102">
@@ -6464,45 +6470,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>461</v>
+        <v>528</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>273</v>
+        <v>314</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>273</v>
+        <v>320</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.5921908893709328</v>
+        <v>0.6060606060606061</v>
       </c>
     </row>
     <row r="103">
@@ -6511,45 +6517,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>399</v>
+        <v>456</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.5864661654135338</v>
+        <v>0.6052631578947368</v>
       </c>
     </row>
     <row r="104">
@@ -6558,7 +6564,7 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
@@ -6572,31 +6578,31 @@
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J104" s="9" t="n">
         <v>301</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.5828571428571429</v>
+        <v>0.6048237476808905</v>
       </c>
     </row>
     <row r="105">
@@ -6605,45 +6611,45 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>455</v>
+        <v>407</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.5802197802197803</v>
+        <v>0.597051597051597</v>
       </c>
     </row>
     <row r="106">
@@ -6652,45 +6658,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>536</v>
+        <v>500</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.5690298507462687</v>
+        <v>0.596</v>
       </c>
     </row>
     <row r="107">
@@ -6713,31 +6719,31 @@
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.5661252900232019</v>
+        <v>0.5793103448275863</v>
       </c>
     </row>
     <row r="108">
@@ -6746,45 +6752,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>399</v>
+        <v>482</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>223</v>
+        <v>279</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.5588972431077694</v>
+        <v>0.578838174273859</v>
       </c>
     </row>
     <row r="109">
@@ -6793,45 +6799,45 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="K109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.5588235294117647</v>
+        <v>0.5780885780885781</v>
       </c>
     </row>
     <row r="110">
@@ -6840,7 +6846,7 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
@@ -6854,31 +6860,31 @@
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.558252427184466</v>
+        <v>0.5775</v>
       </c>
     </row>
     <row r="111">
@@ -6887,45 +6893,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="G111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.5576470588235294</v>
+        <v>0.5628997867803838</v>
       </c>
     </row>
     <row r="112">
@@ -6934,45 +6940,45 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>479</v>
+        <v>412</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>211</v>
+        <v>168</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.5511482254697286</v>
+        <v>0.5606796116504854</v>
       </c>
     </row>
     <row r="113">
@@ -6981,7 +6987,7 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Ivan Christian Sasenga</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
@@ -6995,31 +7001,31 @@
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>503</v>
+        <v>408</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>268</v>
+        <v>223</v>
       </c>
       <c r="K113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.5407554671968191</v>
+        <v>0.5588235294117647</v>
       </c>
     </row>
     <row r="114">
@@ -7028,36 +7034,36 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="K114" s="9" t="n">
         <v>0</v>
@@ -7066,7 +7072,7 @@
         <v>258</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.5363825363825364</v>
+        <v>0.5536480686695279</v>
       </c>
     </row>
     <row r="115">
@@ -7075,45 +7081,45 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>422</v>
+        <v>490</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>206</v>
+        <v>267</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.5355450236966824</v>
+        <v>0.5530612244897959</v>
       </c>
     </row>
     <row r="116">
@@ -7122,45 +7128,45 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="F116" s="9" t="n">
         <v>185</v>
       </c>
       <c r="G116" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="K116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.5348258706467661</v>
+        <v>0.5498783454987834</v>
       </c>
     </row>
     <row r="117">
@@ -7169,7 +7175,7 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
@@ -7183,31 +7189,31 @@
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="G117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.5274725274725275</v>
+        <v>0.548235294117647</v>
       </c>
     </row>
     <row r="118">
@@ -7216,45 +7222,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Ivan Christian Sasenga</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>229</v>
+        <v>272</v>
       </c>
       <c r="K118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.527114967462039</v>
+        <v>0.5467196819085487</v>
       </c>
     </row>
     <row r="119">
@@ -7263,27 +7269,27 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="9" t="n">
         <v>0</v>
@@ -7295,13 +7301,13 @@
         <v>228</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.5228310502283106</v>
+        <v>0.5428571428571428</v>
       </c>
     </row>
     <row r="120">
@@ -7310,45 +7316,45 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="K120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.5220588235294118</v>
+        <v>0.5426008968609866</v>
       </c>
     </row>
     <row r="121">
@@ -7357,45 +7363,45 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>346</v>
+        <v>452</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="G121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>171</v>
+        <v>241</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>180</v>
+        <v>245</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0.5202312138728323</v>
+        <v>0.5420353982300885</v>
       </c>
     </row>
     <row r="122">
@@ -7404,45 +7410,45 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Dince Lahaube</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>446</v>
+        <v>340</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>192</v>
+        <v>5</v>
       </c>
       <c r="G122" s="9" t="n">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.5179372197309418</v>
+        <v>0.5411764705882353</v>
       </c>
     </row>
     <row r="123">
@@ -7451,45 +7457,45 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>446</v>
+        <v>402</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.5179372197309418</v>
+        <v>0.5398009950248757</v>
       </c>
     </row>
     <row r="124">
@@ -7498,45 +7504,45 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="G124" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.5159090909090909</v>
+        <v>0.5353075170842825</v>
       </c>
     </row>
     <row r="125">
@@ -7545,7 +7551,7 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
@@ -7559,31 +7565,31 @@
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.5119047619047619</v>
+        <v>0.5350467289719626</v>
       </c>
     </row>
     <row r="126">
@@ -7592,7 +7598,7 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
@@ -7606,31 +7612,31 @@
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>397</v>
+        <v>443</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="G126" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.5113350125944585</v>
+        <v>0.5282167042889391</v>
       </c>
     </row>
     <row r="127">
@@ -7639,45 +7645,45 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>176</v>
+        <v>219</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.5096153846153846</v>
+        <v>0.5277777777777778</v>
       </c>
     </row>
     <row r="128">
@@ -7686,45 +7692,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>426</v>
+        <v>516</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>217</v>
+        <v>272</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.5093896713615024</v>
+        <v>0.5271317829457365</v>
       </c>
     </row>
     <row r="129">
@@ -7733,45 +7739,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.5090497737556561</v>
+        <v>0.5255474452554745</v>
       </c>
     </row>
     <row r="130">
@@ -7780,45 +7786,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>515</v>
+        <v>397</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>262</v>
+        <v>207</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.5087378640776699</v>
+        <v>0.5214105793450882</v>
       </c>
     </row>
     <row r="131">
@@ -7827,45 +7833,45 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>409</v>
+        <v>346</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H131" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="K131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.5061124694376528</v>
+        <v>0.5202312138728323</v>
       </c>
     </row>
     <row r="132">
@@ -7874,7 +7880,7 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
@@ -7888,31 +7894,31 @@
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.5035294117647059</v>
+        <v>0.5194508009153318</v>
       </c>
     </row>
     <row r="133">
@@ -7938,13 +7944,13 @@
         <v>399</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I133" s="9" t="n">
         <v>0</v>
@@ -7956,10 +7962,10 @@
         <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.5012531328320802</v>
+        <v>0.518796992481203</v>
       </c>
     </row>
     <row r="134">
@@ -7968,45 +7974,45 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Dince Lahaube</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>339</v>
+        <v>427</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>7</v>
+        <v>206</v>
       </c>
       <c r="G134" s="9" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H134" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>153</v>
+        <v>219</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>164</v>
+        <v>221</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.4837758112094395</v>
+        <v>0.5175644028103045</v>
       </c>
     </row>
     <row r="135">
@@ -8015,45 +8021,45 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>459</v>
+        <v>416</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.477124183006536</v>
+        <v>0.5120192307692307</v>
       </c>
     </row>
     <row r="136">
@@ -8062,45 +8068,45 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E136" s="9" t="n">
-        <v>424</v>
+        <v>459</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I136" s="9" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J136" s="9" t="n">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="K136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.4716981132075472</v>
+        <v>0.477124183006536</v>
       </c>
     </row>
   </sheetData>
@@ -8143,7 +8149,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 23 Juli 2026</t>
+          <t>Hari/Tanggal : 24 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8160,17 +8166,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.39 WITA</t>
+          <t>Pukul        : 11.14 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-38):</t>
+          <t>Target Hari Ini (H-39):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>63.46%</t>
+          <t>65.13%</t>
         </is>
       </c>
     </row>
@@ -8262,16 +8268,16 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2938</v>
+        <v>2947</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>317</v>
+        <v>279</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>1</v>
@@ -8286,7 +8292,7 @@
         <v>2568</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.874063989108237</v>
+        <v>0.8713946386155412</v>
       </c>
     </row>
     <row r="8">
@@ -8309,31 +8315,31 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2841</v>
+        <v>2853</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>608</v>
+        <v>558</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>2175</v>
+        <v>2216</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>2191</v>
+        <v>2235</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.7712073213657163</v>
+        <v>0.7833859095688749</v>
       </c>
     </row>
     <row r="9">
@@ -8356,19 +8362,19 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2534</v>
+        <v>2558</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>579</v>
+        <v>525</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9" s="9" t="n">
         <v>1939</v>
@@ -8377,10 +8383,10 @@
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.7667719021310182</v>
+        <v>0.7584050039093042</v>
       </c>
     </row>
     <row r="10">
@@ -8403,16 +8409,16 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>17</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>5</v>
@@ -8427,7 +8433,7 @@
         <v>1541</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7550220480156785</v>
+        <v>0.7539138943248532</v>
       </c>
     </row>
     <row r="11">
@@ -8436,7 +8442,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Charly Angel Tatontos</t>
+          <t>Fresly Jeica Manangkoda</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -8450,31 +8456,31 @@
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2936</v>
+        <v>2879</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>557</v>
+        <v>655</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>137</v>
+        <v>48</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>2112</v>
+        <v>2154</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7384196185286104</v>
+        <v>0.7537339353942341</v>
       </c>
     </row>
     <row r="12">
@@ -8483,7 +8489,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Fresly Jeica Manangkoda</t>
+          <t>Charly Angel Tatontos</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -8497,31 +8503,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2872</v>
+        <v>2948</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>686</v>
+        <v>547</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>2104</v>
+        <v>2147</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2114</v>
+        <v>2205</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7360724233983287</v>
+        <v>0.7479647218453188</v>
       </c>
     </row>
     <row r="13">
@@ -8530,45 +8536,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore, Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Hendri, Michael</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2924</v>
+        <v>2128</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>914</v>
+        <v>622</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1950</v>
+        <v>1460</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1957</v>
+        <v>1461</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6692886456908345</v>
+        <v>0.6865601503759399</v>
       </c>
     </row>
     <row r="14">
@@ -8577,45 +8583,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Manganitu, Tamako</t>
+          <t>Kepulauan Marore, Tabukan Utara</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Erike, Mega</t>
+          <t>Hendri, Michael</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2439</v>
+        <v>2943</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>809</v>
+        <v>870</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1585</v>
+        <v>2008</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1599</v>
+        <v>2015</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6555965559655597</v>
+        <v>0.6846755011892627</v>
       </c>
     </row>
     <row r="15">
@@ -8624,45 +8630,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu, Tamako</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike, Mega</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2820</v>
+        <v>2457</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>844</v>
+        <v>766</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1832</v>
+        <v>1628</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1843</v>
+        <v>1651</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.6535460992907801</v>
+        <v>0.6719576719576721</v>
       </c>
     </row>
     <row r="16">
@@ -8671,45 +8677,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2122</v>
+        <v>2842</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>646</v>
+        <v>788</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1380</v>
+        <v>1866</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1381</v>
+        <v>1877</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.6508011310084825</v>
+        <v>0.6604503870513723</v>
       </c>
     </row>
     <row r="17">
@@ -8718,45 +8724,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2905</v>
+        <v>2188</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>994</v>
+        <v>739</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="H17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1834</v>
+        <v>1427</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1860</v>
+        <v>1440</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.6402753872633391</v>
+        <v>0.6581352833638026</v>
       </c>
     </row>
     <row r="18">
@@ -8765,45 +8771,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2849</v>
+        <v>2918</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1060</v>
+        <v>937</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1743</v>
+        <v>1883</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1785</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>0.6265356265356266</v>
+        <v>1909</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>0.6542152159013023</v>
       </c>
     </row>
     <row r="19">
@@ -8812,45 +8818,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2185</v>
+        <v>2870</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>743</v>
+        <v>1016</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1355</v>
+        <v>1798</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1368</v>
+        <v>1839</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.6260869565217392</v>
+        <v>0.6407665505226481</v>
       </c>
     </row>
     <row r="20">
@@ -8873,31 +8879,31 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1456</v>
+        <v>1466</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>876</v>
+        <v>906</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>882</v>
+        <v>934</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.6057692307692307</v>
+        <v>0.6371077762619373</v>
       </c>
     </row>
     <row r="21">
@@ -8920,31 +8926,31 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2694</v>
+        <v>2709</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1031</v>
+        <v>991</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1630</v>
+        <v>1680</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1631</v>
+        <v>1681</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.605419450631032</v>
+        <v>0.6205241786637136</v>
       </c>
     </row>
     <row r="22">
@@ -8953,45 +8959,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2470</v>
+        <v>2359</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>858</v>
+        <v>819</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1428</v>
+        <v>1422</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1466</v>
+        <v>1447</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.5935222672064777</v>
+        <v>0.6133955065705807</v>
       </c>
     </row>
     <row r="23">
@@ -9000,45 +9006,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2346</v>
+        <v>2496</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>859</v>
+        <v>838</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1331</v>
+        <v>1468</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1355</v>
+        <v>1506</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.5775788576300085</v>
+        <v>0.6033653846153846</v>
       </c>
     </row>
     <row r="24">
@@ -9061,31 +9067,31 @@
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2746</v>
+        <v>2754</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1085</v>
+        <v>1049</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1530</v>
+        <v>1642</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>1536</v>
+        <v>1651</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5593590677348871</v>
+        <v>0.5994916485112564</v>
       </c>
     </row>
     <row r="25">
@@ -9094,45 +9100,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2727</v>
+        <v>2612</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1187</v>
+        <v>1066</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1483</v>
+        <v>1489</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>1487</v>
+        <v>1500</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5452878621195453</v>
+        <v>0.5742725880551302</v>
       </c>
     </row>
     <row r="26">
@@ -9141,45 +9147,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2572</v>
+        <v>2427</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1100</v>
+        <v>944</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1398</v>
+        <v>1266</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1401</v>
+        <v>1344</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.5447122861586314</v>
+        <v>0.553770086526576</v>
       </c>
     </row>
     <row r="27">
@@ -9188,45 +9194,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Olfira Sicilia Budiman</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2123</v>
+        <v>2731</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>948</v>
+        <v>1161</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1052</v>
+        <v>1493</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>1154</v>
+        <v>1498</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.5435704192180876</v>
+        <v>0.5485170267301355</v>
       </c>
     </row>
     <row r="28">
@@ -9235,45 +9241,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>Olfira Sicilia Budiman</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2422</v>
+        <v>2149</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>999</v>
+        <v>906</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1219</v>
+        <v>1061</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1278</v>
+        <v>1154</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.5276630883567299</v>
+        <v>0.5369939506747324</v>
       </c>
     </row>
     <row r="29">
@@ -9296,31 +9302,31 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>968</v>
+        <v>922</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1046</v>
+        <v>1088</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1074</v>
+        <v>1114</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.5165945165945166</v>
+        <v>0.5355769230769231</v>
       </c>
     </row>
   </sheetData>
@@ -9354,7 +9360,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 23 Juli 2026</t>
+          <t>Hari/Tanggal : 24 Juli 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9371,17 +9377,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.39 WITA</t>
+          <t>Pukul        : 11.14 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-38):</t>
+          <t>Target Hari Ini (H-39):</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>63.46%</t>
+          <t>65.13%</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9424,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.821765209940017</v>
+        <v>0.8526405451448043</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9436,7 +9442,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7958359229334991</v>
+        <v>0.8143342601173926</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9454,7 +9460,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7740104084529255</v>
+        <v>0.7813236912435151</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9472,7 +9478,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.755411714770798</v>
+        <v>0.7709408913707722</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -9490,7 +9496,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.7362478981503723</v>
+        <v>0.74568552253116</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9526,7 +9532,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.6527050610820244</v>
+        <v>0.6553524804177546</v>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
@@ -9540,15 +9546,15 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>0.6384</v>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>Tatoareng</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>0.6487039563437926</v>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>+3</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9568,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.6268866268866269</v>
+        <v>0.6449477351916376</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -9580,7 +9586,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.6246429251571129</v>
+        <v>0.6418419556566231</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9594,15 +9600,15 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.6188186813186813</v>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6384</v>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>-3</t>
         </is>
       </c>
     </row>
@@ -9616,7 +9622,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.5841371918542336</v>
+        <v>0.6013971210838273</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -9630,15 +9636,15 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.5840577935594465</v>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.596209311907705</v>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9648,15 +9654,15 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.5776218001651527</v>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.5955577251647547</v>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9670,7 +9676,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.5654878847413228</v>
+        <v>0.58777633289987</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.14 WITA</t>
+          <t>Pukul        : 11.25 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.14 WITA</t>
+          <t>Pukul        : 11.25 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.14 WITA</t>
+          <t>Pukul        : 11.25 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.14 WITA</t>
+          <t>Pukul        : 11.25 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,32 +616,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.25 WITA</t>
+          <t>Pukul        : 11.14 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-39):</t>
+          <t>Target Hari Ini (H-40):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>65.13%</t>
+          <t>66.80%</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Hijau &gt;= 65.13%</t>
+          <t>Hijau &gt;= 66.80%</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Kuning 32.56% - 65.13%</t>
+          <t>Kuning 33.40% - 66.80%</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Merah &lt; 32.56%</t>
+          <t>Merah &lt; 33.40%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       <c r="P11" s="9" t="n">
         <v>753</v>
       </c>
-      <c r="Q11" s="11">
+      <c r="Q11" s="12">
         <f>P11/B11</f>
         <v/>
       </c>
@@ -1145,7 +1145,7 @@
       <c r="P12" s="9" t="n">
         <v>688</v>
       </c>
-      <c r="Q12" s="11">
+      <c r="Q12" s="12">
         <f>P12/B12</f>
         <v/>
       </c>
@@ -1917,17 +1917,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.25 WITA</t>
+          <t>Pukul        : 11.14 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-39):</t>
+          <t>Target Hari Ini (H-40):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>65.13%</t>
+          <t>66.80%</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       <c r="L70" s="9" t="n">
         <v>290</v>
       </c>
-      <c r="M70" s="11" t="n">
+      <c r="M70" s="12" t="n">
         <v>0.6666666666666665</v>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       <c r="L71" s="9" t="n">
         <v>288</v>
       </c>
-      <c r="M71" s="11" t="n">
+      <c r="M71" s="12" t="n">
         <v>0.6651270207852193</v>
       </c>
     </row>
@@ -5097,7 +5097,7 @@
       <c r="L72" s="9" t="n">
         <v>312</v>
       </c>
-      <c r="M72" s="11" t="n">
+      <c r="M72" s="12" t="n">
         <v>0.6596194503171248</v>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       <c r="L73" s="9" t="n">
         <v>285</v>
       </c>
-      <c r="M73" s="11" t="n">
+      <c r="M73" s="12" t="n">
         <v>0.6581986143187067</v>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       <c r="L74" s="9" t="n">
         <v>310</v>
       </c>
-      <c r="M74" s="11" t="n">
+      <c r="M74" s="12" t="n">
         <v>0.6567796610169492</v>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       <c r="L75" s="9" t="n">
         <v>329</v>
       </c>
-      <c r="M75" s="11" t="n">
+      <c r="M75" s="12" t="n">
         <v>0.655378486055777</v>
       </c>
     </row>
@@ -5285,7 +5285,7 @@
       <c r="L76" s="9" t="n">
         <v>268</v>
       </c>
-      <c r="M76" s="11" t="n">
+      <c r="M76" s="12" t="n">
         <v>0.653658536585366</v>
       </c>
     </row>
@@ -5332,7 +5332,7 @@
       <c r="L77" s="9" t="n">
         <v>330</v>
       </c>
-      <c r="M77" s="11" t="n">
+      <c r="M77" s="12" t="n">
         <v>0.6521739130434783</v>
       </c>
     </row>
@@ -5379,7 +5379,7 @@
       <c r="L78" s="9" t="n">
         <v>345</v>
       </c>
-      <c r="M78" s="11" t="n">
+      <c r="M78" s="12" t="n">
         <v>0.6521739130434783</v>
       </c>
     </row>
@@ -8166,17 +8166,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.25 WITA</t>
+          <t>Pukul        : 11.14 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-39):</t>
+          <t>Target Hari Ini (H-40):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>65.13%</t>
+          <t>66.80%</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       <c r="L16" s="9" t="n">
         <v>1877</v>
       </c>
-      <c r="M16" s="11" t="n">
+      <c r="M16" s="12" t="n">
         <v>0.6604503870513723</v>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       <c r="L17" s="9" t="n">
         <v>1440</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" s="12" t="n">
         <v>0.6581352833638026</v>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       <c r="L18" s="9" t="n">
         <v>1909</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" s="12" t="n">
         <v>0.6542152159013023</v>
       </c>
     </row>
@@ -9377,17 +9377,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.25 WITA</t>
+          <t>Pukul        : 11.14 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-39):</t>
+          <t>Target Hari Ini (H-40):</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>65.13%</t>
+          <t>66.80%</t>
         </is>
       </c>
     </row>
@@ -9513,7 +9513,7 @@
           <t>Tabukan Selatan Tenggara</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>0.6621751684311838</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -9531,7 +9531,7 @@
           <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="12" t="n">
         <v>0.6553524804177546</v>
       </c>
       <c r="D13" s="17" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 24 Juli 2026</t>
+          <t>Hari/Tanggal : 25 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -616,32 +616,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.14 WITA</t>
+          <t>Pukul        : 11.53 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-40):</t>
+          <t>Target Hari Ini (H-41):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>66.80%</t>
+          <t>68.47%</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Hijau &gt;= 66.80%</t>
+          <t>Hijau &gt;= 68.47%</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Kuning 33.40% - 66.80%</t>
+          <t>Kuning 34.23% - 68.47%</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Merah &lt; 33.40%</t>
+          <t>Merah &lt; 34.23%</t>
         </is>
       </c>
     </row>
@@ -750,27 +750,27 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4172</v>
+        <v>4185</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1040</v>
+        <v>978</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
         <v/>
       </c>
       <c r="F7" s="9" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G7" s="10">
         <f>F7/B7</f>
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
@@ -784,7 +784,7 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2992</v>
+        <v>3025</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
@@ -798,14 +798,14 @@
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>3111</v>
+        <v>3191</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -819,27 +819,27 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>906</v>
+        <v>938</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -867,14 +867,14 @@
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>951</v>
+        <v>967</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -888,41 +888,41 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6361</v>
+        <v>6373</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1288</v>
+        <v>1268</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4722</v>
+        <v>4761</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -936,14 +936,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4970</v>
+        <v>5000</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3237</v>
+        <v>3251</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>601</v>
+        <v>558</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -977,21 +977,21 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="K10" s="10">
         <f>J10/B10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2523</v>
+        <v>2567</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
@@ -1005,14 +1005,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2636</v>
+        <v>2693</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
@@ -1046,21 +1046,21 @@
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
         <v/>
       </c>
       <c r="J11" s="9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K11" s="10">
         <f>J11/B11</f>
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="M11" s="10">
         <f>L11/B11</f>
@@ -1074,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>1039</v>
+        <v>1048</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>23</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="E12" s="10">
         <f>D12/B12</f>
@@ -1115,42 +1115,42 @@
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
         <v/>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K12" s="10">
         <f>J12/B12</f>
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="M12" s="10">
         <f>L12/B12</f>
         <v/>
       </c>
       <c r="N12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="10">
         <f>N12/B12</f>
         <v/>
       </c>
       <c r="P12" s="9" t="n">
-        <v>688</v>
+        <v>717</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/B12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1164,41 +1164,41 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4724</v>
+        <v>4745</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1861</v>
+        <v>1843</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2650</v>
+        <v>2659</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1212,14 +1212,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2841</v>
+        <v>2865</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1233,41 +1233,41 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6152</v>
+        <v>6201</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2508</v>
+        <v>2381</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>118</v>
+        <v>203</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3356</v>
+        <v>3433</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
@@ -1281,14 +1281,14 @@
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3616</v>
+        <v>3781</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1302,41 +1302,41 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8194</v>
+        <v>8237</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3201</v>
+        <v>3075</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K15" s="10">
         <f>J15/B15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4815</v>
+        <v>4986</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1350,14 +1350,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4880</v>
+        <v>5039</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1371,27 +1371,27 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5277</v>
+        <v>5297</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1756</v>
+        <v>1669</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
@@ -1405,7 +1405,7 @@
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>3305</v>
+        <v>3331</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1419,14 +1419,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3387</v>
+        <v>3477</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1440,62 +1440,62 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2427</v>
+        <v>2434</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>944</v>
+        <v>883</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1266</v>
+        <v>1327</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
         <v/>
       </c>
       <c r="N17" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O17" s="10">
         <f>N17/B17</f>
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1447</v>
+        <v>1493</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1509,41 +1509,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9491</v>
+        <v>9521</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2070</v>
+        <v>1925</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>270</v>
+        <v>147</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>7025</v>
+        <v>7334</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1557,14 +1557,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>7317</v>
+        <v>7514</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1174</v>
+        <v>1179</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1598,21 +1598,21 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
         <v/>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="10">
         <f>J19/B19</f>
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1626,14 +1626,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>1001</v>
+        <v>1033</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1716,41 +1716,41 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2870</v>
+        <v>2880</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1016</v>
+        <v>989</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
         <v/>
       </c>
       <c r="F21" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" s="10">
         <f>F21/B21</f>
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1798</v>
+        <v>1841</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1764,14 +1764,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1851</v>
+        <v>1889</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1900,7 +1900,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 24 Juli 2026</t>
+          <t>Hari/Tanggal : 25 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1917,17 +1917,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.14 WITA</t>
+          <t>Pukul        : 11.53 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-40):</t>
+          <t>Target Hari Ini (H-41):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>66.80%</t>
+          <t>68.47%</t>
         </is>
       </c>
     </row>
@@ -2113,31 +2113,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.9807355516637479</v>
+        <v>0.991304347826087</v>
       </c>
     </row>
     <row r="10">
@@ -2160,16 +2160,16 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>0</v>
@@ -2181,10 +2181,10 @@
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.9507772020725389</v>
+        <v>0.9896907216494846</v>
       </c>
     </row>
     <row r="11">
@@ -2193,45 +2193,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Merry Christiani Lano</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.9360902255639096</v>
+        <v>0.9591439688715954</v>
       </c>
     </row>
     <row r="12">
@@ -2240,45 +2240,45 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Merry Christiani Lano</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G12" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="H12" s="9" t="n">
-        <v>8</v>
-      </c>
       <c r="I12" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.9275929549902152</v>
+        <v>0.9360902255639096</v>
       </c>
     </row>
     <row r="13">
@@ -2310,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>1</v>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
@@ -2360,19 +2360,19 @@
         <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.8932291666666665</v>
+        <v>0.9145077720207254</v>
       </c>
     </row>
     <row r="15">
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>2</v>
@@ -2416,10 +2416,10 @@
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.8880208333333335</v>
+        <v>0.8937823834196891</v>
       </c>
     </row>
     <row r="16">
@@ -2442,31 +2442,31 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I16" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.8818681318681318</v>
+        <v>0.893150684931507</v>
       </c>
     </row>
     <row r="17">
@@ -2489,31 +2489,31 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8725961538461539</v>
+        <v>0.8875598086124402</v>
       </c>
     </row>
     <row r="18">
@@ -2536,16 +2536,16 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I18" s="9" t="n">
         <v>2</v>
@@ -2557,10 +2557,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8673218673218673</v>
+        <v>0.8848039215686273</v>
       </c>
     </row>
     <row r="19">
@@ -2592,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>0</v>
@@ -2645,16 +2645,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8538011695906432</v>
       </c>
     </row>
     <row r="21">
@@ -2663,45 +2663,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Asari Prisilia Antari</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>426</v>
+        <v>397</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.8380281690140845</v>
+        <v>0.8513853904282116</v>
       </c>
     </row>
     <row r="22">
@@ -2710,45 +2710,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>424</v>
+        <v>514</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>323</v>
+        <v>425</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>355</v>
+        <v>431</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.8372641509433962</v>
+        <v>0.8385214007782102</v>
       </c>
     </row>
     <row r="23">
@@ -2757,45 +2757,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>480</v>
+        <v>424</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>377</v>
+        <v>323</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>401</v>
+        <v>355</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.8354166666666667</v>
+        <v>0.8372641509433962</v>
       </c>
     </row>
     <row r="24">
@@ -2804,45 +2804,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>434</v>
+        <v>482</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>362</v>
+        <v>403</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.8341013824884793</v>
+        <v>0.8360995850622408</v>
       </c>
     </row>
     <row r="25">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Asari Prisilia Antari</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -2865,31 +2865,31 @@
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>512</v>
+        <v>426</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>422</v>
+        <v>302</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>427</v>
+        <v>356</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.833984375</v>
+        <v>0.8356807511737088</v>
       </c>
     </row>
     <row r="26">
@@ -2898,45 +2898,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>396</v>
+        <v>434</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.8333333333333335</v>
+        <v>0.8341013824884793</v>
       </c>
     </row>
     <row r="27">
@@ -2992,45 +2992,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>534</v>
+        <v>416</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>421</v>
+        <v>343</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>428</v>
+        <v>343</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>0.8014981273408239</v>
+        <v>0.8245192307692306</v>
       </c>
     </row>
     <row r="29">
@@ -3039,45 +3039,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>427</v>
+        <v>388</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>335</v>
+        <v>306</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.7962529274004683</v>
+        <v>0.8195876288659794</v>
       </c>
     </row>
     <row r="30">
@@ -3086,45 +3086,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Sheryl Jessica Tatontos</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>508</v>
+        <v>430</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>403</v>
+        <v>348</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7933070866141734</v>
+        <v>0.8093023255813954</v>
       </c>
     </row>
     <row r="31">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -3147,31 +3147,31 @@
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>383</v>
+        <v>429</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>390</v>
+        <v>429</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7753479125248509</v>
+        <v>0.8018691588785046</v>
       </c>
     </row>
     <row r="32">
@@ -3180,45 +3180,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Sheryl Jessica Tatontos</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>408</v>
+        <v>508</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>290</v>
+        <v>336</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>315</v>
+        <v>403</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.7720588235294117</v>
+        <v>0.7933070866141734</v>
       </c>
     </row>
     <row r="33">
@@ -3227,45 +3227,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>386</v>
+        <v>556</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>296</v>
+        <v>438</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>298</v>
+        <v>438</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.7720207253886009</v>
+        <v>0.7877697841726617</v>
       </c>
     </row>
     <row r="34">
@@ -3274,45 +3274,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>428</v>
+        <v>564</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>297</v>
+        <v>424</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>330</v>
+        <v>441</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.7710280373831776</v>
+        <v>0.7819148936170213</v>
       </c>
     </row>
     <row r="35">
@@ -3321,45 +3321,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>561</v>
+        <v>429</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>424</v>
+        <v>297</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>432</v>
+        <v>335</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.7700534759358288</v>
+        <v>0.7808857808857809</v>
       </c>
     </row>
     <row r="36">
@@ -3368,45 +3368,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>412</v>
+        <v>505</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>291</v>
+        <v>383</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>317</v>
+        <v>394</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7694174757281553</v>
+        <v>0.7801980198019802</v>
       </c>
     </row>
     <row r="37">
@@ -3429,31 +3429,31 @@
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7668997668997669</v>
+        <v>0.7800925925925926</v>
       </c>
     </row>
     <row r="38">
@@ -3462,45 +3462,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>554</v>
+        <v>408</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>418</v>
+        <v>290</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>424</v>
+        <v>315</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.7653429602888085</v>
+        <v>0.7720588235294117</v>
       </c>
     </row>
     <row r="39">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -3523,31 +3523,31 @@
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>519</v>
+        <v>465</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="I39" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>377</v>
+        <v>316</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>389</v>
+        <v>354</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7495183044315994</v>
+        <v>0.7612903225806451</v>
       </c>
     </row>
     <row r="40">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -3570,31 +3570,31 @@
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.7436399217221134</v>
+        <v>0.7562862669245648</v>
       </c>
     </row>
     <row r="41">
@@ -3603,45 +3603,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>458</v>
+        <v>350</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="I41" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>339</v>
+        <v>264</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.7401746724890831</v>
+        <v>0.7542857142857143</v>
       </c>
     </row>
     <row r="42">
@@ -3650,45 +3650,45 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>350</v>
+        <v>519</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I42" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>255</v>
+        <v>377</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>258</v>
+        <v>389</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.7371428571428571</v>
+        <v>0.7495183044315994</v>
       </c>
     </row>
     <row r="43">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -3711,31 +3711,31 @@
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.7339805825242719</v>
+        <v>0.7485493230174082</v>
       </c>
     </row>
     <row r="44">
@@ -3744,45 +3744,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>505</v>
+        <v>464</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.7306930693069308</v>
+        <v>0.7478448275862069</v>
       </c>
     </row>
     <row r="45">
@@ -3805,31 +3805,31 @@
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I45" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.7295918367346939</v>
+        <v>0.7468354430379747</v>
       </c>
     </row>
     <row r="46">
@@ -3838,45 +3838,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Ruslan Ginoga</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>458</v>
+        <v>373</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>332</v>
+        <v>266</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>334</v>
+        <v>278</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.7292576419213974</v>
+        <v>0.7453083109919573</v>
       </c>
     </row>
     <row r="47">
@@ -3885,45 +3885,45 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Ruslan Ginoga</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.7284946236559139</v>
+        <v>0.7372881355932204</v>
       </c>
     </row>
     <row r="48">
@@ -3932,45 +3932,45 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>352</v>
+        <v>534</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>245</v>
+        <v>390</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>253</v>
+        <v>391</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.71875</v>
+        <v>0.7322097378277154</v>
       </c>
     </row>
     <row r="49">
@@ -3979,45 +3979,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>404</v>
+        <v>505</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>247</v>
+        <v>349</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.7153465346534653</v>
+        <v>0.7306930693069308</v>
       </c>
     </row>
     <row r="50">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
@@ -4040,31 +4040,31 @@
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>534</v>
+        <v>438</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>344</v>
+        <v>280</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>381</v>
+        <v>320</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.7134831460674157</v>
+        <v>0.7305936073059359</v>
       </c>
     </row>
     <row r="51">
@@ -4087,31 +4087,31 @@
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.7133757961783439</v>
+        <v>0.7293868921775899</v>
       </c>
     </row>
     <row r="52">
@@ -4120,45 +4120,45 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I52" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.7101827676240208</v>
+        <v>0.7178217821782178</v>
       </c>
     </row>
     <row r="53">
@@ -4167,45 +4167,45 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G53" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H53" s="9" t="n">
-        <v>4</v>
-      </c>
       <c r="I53" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.6967032967032967</v>
+        <v>0.7124463519313305</v>
       </c>
     </row>
     <row r="54">
@@ -4214,45 +4214,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>344</v>
+        <v>271</v>
       </c>
       <c r="K54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>356</v>
+        <v>272</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.6939571150097466</v>
+        <v>0.7101827676240208</v>
       </c>
     </row>
     <row r="55">
@@ -4261,45 +4261,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.6912442396313364</v>
+        <v>0.7083333333333335</v>
       </c>
     </row>
     <row r="56">
@@ -4308,45 +4308,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>322</v>
+        <v>284</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.6909871244635193</v>
+        <v>0.7070484581497797</v>
       </c>
     </row>
     <row r="57">
@@ -4355,24 +4355,24 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>431</v>
+        <v>477</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>0</v>
@@ -4381,19 +4381,19 @@
         <v>4</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>292</v>
+        <v>330</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>297</v>
+        <v>337</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.689095127610209</v>
+        <v>0.7064989517819708</v>
       </c>
     </row>
     <row r="58">
@@ -4402,45 +4402,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.6850220264317179</v>
+        <v>0.703056768558952</v>
       </c>
     </row>
     <row r="59">
@@ -4449,45 +4449,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>483</v>
+        <v>514</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6832298136645963</v>
+        <v>0.6984435797665369</v>
       </c>
     </row>
     <row r="60">
@@ -4496,45 +4496,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>466</v>
+        <v>434</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="G60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.6802575107296137</v>
+        <v>0.695852534562212</v>
       </c>
     </row>
     <row r="61">
@@ -4543,45 +4543,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.6789838337182448</v>
+        <v>0.6952380952380952</v>
       </c>
     </row>
     <row r="62">
@@ -4590,45 +4590,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>507</v>
+        <v>432</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>342</v>
+        <v>299</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>344</v>
+        <v>299</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6785009861932939</v>
+        <v>0.6921296296296297</v>
       </c>
     </row>
     <row r="63">
@@ -4637,45 +4637,45 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.673076923076923</v>
+        <v>0.6889400921658987</v>
       </c>
     </row>
     <row r="64">
@@ -4684,45 +4684,45 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>458</v>
+        <v>506</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I64" s="9" t="n">
         <v>3</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="K64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>308</v>
+        <v>348</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.6724890829694323</v>
+        <v>0.6877470355731226</v>
       </c>
     </row>
     <row r="65">
@@ -4731,45 +4731,45 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="I65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="K65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.6717267552182163</v>
+        <v>0.68762278978389</v>
       </c>
     </row>
     <row r="66">
@@ -4778,45 +4778,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>289</v>
+        <v>487</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>191</v>
+        <v>330</v>
       </c>
       <c r="K66" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>194</v>
-      </c>
-      <c r="M66" s="11" t="n">
-        <v>0.671280276816609</v>
+        <v>333</v>
+      </c>
+      <c r="M66" s="12" t="n">
+        <v>0.6837782340862423</v>
       </c>
     </row>
     <row r="67">
@@ -4825,45 +4825,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>326</v>
-      </c>
-      <c r="M67" s="11" t="n">
-        <v>0.6707818930041153</v>
+        <v>330</v>
+      </c>
+      <c r="M67" s="12" t="n">
+        <v>0.6832298136645963</v>
       </c>
     </row>
     <row r="68">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -4886,31 +4886,31 @@
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>419</v>
+        <v>530</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>279</v>
+        <v>357</v>
       </c>
       <c r="K68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>281</v>
-      </c>
-      <c r="M68" s="11" t="n">
-        <v>0.6706443914081146</v>
+        <v>362</v>
+      </c>
+      <c r="M68" s="12" t="n">
+        <v>0.6830188679245282</v>
       </c>
     </row>
     <row r="69">
@@ -4919,45 +4919,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="G69" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="H69" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I69" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J69" s="9" t="n">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>289</v>
-      </c>
-      <c r="M69" s="11" t="n">
-        <v>0.6705336426914154</v>
+        <v>297</v>
+      </c>
+      <c r="M69" s="12" t="n">
+        <v>0.6827586206896552</v>
       </c>
     </row>
     <row r="70">
@@ -4966,45 +4966,45 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>435</v>
+        <v>416</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H70" s="9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="K70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.6802884615384616</v>
       </c>
     </row>
     <row r="71">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -5027,31 +5027,31 @@
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>433</v>
+        <v>466</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>0.6651270207852193</v>
+        <v>0.6802575107296137</v>
       </c>
     </row>
     <row r="72">
@@ -5060,45 +5060,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>473</v>
+        <v>504</v>
       </c>
       <c r="F72" s="9" t="n">
         <v>161</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>0.6596194503171248</v>
+        <v>0.6765873015873016</v>
       </c>
     </row>
     <row r="73">
@@ -5107,45 +5107,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>433</v>
+        <v>604</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>268</v>
+        <v>402</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>285</v>
+        <v>408</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>0.6581986143187067</v>
+        <v>0.6754966887417219</v>
       </c>
     </row>
     <row r="74">
@@ -5154,45 +5154,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="H74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>0.6567796610169492</v>
+        <v>0.6724890829694323</v>
       </c>
     </row>
     <row r="75">
@@ -5201,45 +5201,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>502</v>
+        <v>289</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c r="G75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>191</v>
+      </c>
+      <c r="K75" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H75" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="I75" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J75" s="9" t="n">
-        <v>310</v>
-      </c>
-      <c r="K75" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L75" s="9" t="n">
-        <v>329</v>
+        <v>194</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>0.655378486055777</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="76">
@@ -5248,45 +5248,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>0.653658536585366</v>
+        <v>0.6674364896073903</v>
       </c>
     </row>
     <row r="77">
@@ -5295,45 +5295,45 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6659619450317125</v>
       </c>
     </row>
     <row r="78">
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>0</v>
@@ -5371,16 +5371,16 @@
         <v>1</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="K78" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.664783427495292</v>
       </c>
     </row>
     <row r="79">
@@ -5389,45 +5389,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>449</v>
+        <v>575</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>289</v>
+        <v>379</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>291</v>
+        <v>382</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.6481069042316259</v>
+        <v>0.6643478260869565</v>
       </c>
     </row>
     <row r="80">
@@ -5436,45 +5436,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>591</v>
+        <v>469</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>381</v>
+        <v>279</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>383</v>
+        <v>310</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.6480541455160744</v>
+        <v>0.6609808102345416</v>
       </c>
     </row>
     <row r="81">
@@ -5483,45 +5483,45 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>477</v>
+        <v>521</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>258</v>
+        <v>344</v>
       </c>
       <c r="K81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.6457023060796646</v>
+        <v>0.6602687140115164</v>
       </c>
     </row>
     <row r="82">
@@ -5530,45 +5530,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>420</v>
+        <v>388</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="I82" s="9" t="n">
-        <v>5</v>
-      </c>
       <c r="J82" s="9" t="n">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="K82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.6452380952380953</v>
+        <v>0.6597938144329896</v>
       </c>
     </row>
     <row r="83">
@@ -5577,45 +5577,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>520</v>
+        <v>449</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>289</v>
+      </c>
+      <c r="K83" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J83" s="9" t="n">
-        <v>321</v>
-      </c>
-      <c r="K83" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L83" s="9" t="n">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.6442307692307694</v>
+        <v>0.6570155902004454</v>
       </c>
     </row>
     <row r="84">
@@ -5624,45 +5624,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>625</v>
+        <v>454</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>219</v>
+        <v>137</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>395</v>
+        <v>293</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>399</v>
+        <v>298</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.6384</v>
+        <v>0.6563876651982379</v>
       </c>
     </row>
     <row r="85">
@@ -5671,45 +5671,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>467</v>
+        <v>412</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>298</v>
+        <v>270</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.6381156316916489</v>
+        <v>0.6553398058252428</v>
       </c>
     </row>
     <row r="86">
@@ -5735,28 +5735,28 @@
         <v>546</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.6373626373626373</v>
+        <v>0.6501831501831502</v>
       </c>
     </row>
     <row r="87">
@@ -5765,45 +5765,45 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>573</v>
+        <v>421</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>365</v>
+        <v>257</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>365</v>
+        <v>272</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.6369982547993019</v>
+        <v>0.6460807600950119</v>
       </c>
     </row>
     <row r="88">
@@ -5812,45 +5812,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6441717791411042</v>
       </c>
     </row>
     <row r="89">
@@ -5859,45 +5859,45 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>386</v>
+        <v>486</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="K89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.6347150259067358</v>
+        <v>0.6440329218106996</v>
       </c>
     </row>
     <row r="90">
@@ -5906,45 +5906,45 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.6343612334801763</v>
+        <v>0.6427061310782239</v>
       </c>
     </row>
     <row r="91">
@@ -5953,27 +5953,27 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>326</v>
+        <v>480</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H91" s="9" t="n">
         <v>0</v>
@@ -5982,16 +5982,16 @@
         <v>0</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>205</v>
+        <v>308</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>206</v>
+        <v>308</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.6319018404907976</v>
+        <v>0.6416666666666667</v>
       </c>
     </row>
     <row r="92">
@@ -6000,45 +6000,45 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.6275510204081632</v>
+        <v>0.6414634146341462</v>
       </c>
     </row>
     <row r="93">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
@@ -6061,31 +6061,31 @@
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.6210526315789474</v>
+        <v>0.6407185628742514</v>
       </c>
     </row>
     <row r="94">
@@ -6094,45 +6094,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>406</v>
+        <v>353</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="I94" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="J94" s="9" t="n">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="K94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.6402266288951841</v>
       </c>
     </row>
     <row r="95">
@@ -6141,45 +6141,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>461</v>
+        <v>625</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>285</v>
+        <v>395</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>286</v>
+        <v>399</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.6203904555314533</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="96">
@@ -6188,24 +6188,24 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>0</v>
@@ -6214,19 +6214,19 @@
         <v>1</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="K96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.6203090507726269</v>
+        <v>0.6349892008639308</v>
       </c>
     </row>
     <row r="97">
@@ -6235,45 +6235,45 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>471</v>
+        <v>393</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>291</v>
+        <v>249</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.6178343949044586</v>
+        <v>0.6335877862595419</v>
       </c>
     </row>
     <row r="98">
@@ -6282,45 +6282,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>475</v>
+        <v>458</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I98" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.6147368421052631</v>
+        <v>0.631004366812227</v>
       </c>
     </row>
     <row r="99">
@@ -6329,45 +6329,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>450</v>
+        <v>363</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>276</v>
+        <v>229</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.6308539944903582</v>
       </c>
     </row>
     <row r="100">
@@ -6376,45 +6376,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>362</v>
+        <v>534</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>140</v>
+        <v>197</v>
       </c>
       <c r="G100" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>216</v>
+        <v>327</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>221</v>
+        <v>335</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.6104972375690608</v>
+        <v>0.6273408239700374</v>
       </c>
     </row>
     <row r="101">
@@ -6437,19 +6437,19 @@
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J101" s="9" t="n">
         <v>222</v>
@@ -6458,10 +6458,10 @@
         <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.6065573770491803</v>
+        <v>0.6267029972752044</v>
       </c>
     </row>
     <row r="102">
@@ -6470,45 +6470,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>528</v>
+        <v>476</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I102" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.6260504201680672</v>
       </c>
     </row>
     <row r="103">
@@ -6517,45 +6517,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>456</v>
+        <v>539</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>232</v>
+        <v>314</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>276</v>
+        <v>336</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.6052631578947368</v>
+        <v>0.6233766233766234</v>
       </c>
     </row>
     <row r="104">
@@ -6564,45 +6564,45 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>539</v>
+        <v>454</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="K104" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>326</v>
+        <v>282</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.6048237476808905</v>
+        <v>0.6211453744493393</v>
       </c>
     </row>
     <row r="105">
@@ -6611,45 +6611,45 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>407</v>
+        <v>456</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.597051597051597</v>
+        <v>0.6162280701754386</v>
       </c>
     </row>
     <row r="106">
@@ -6658,45 +6658,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Regina Kesya Dumumpe</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>500</v>
+        <v>438</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>282</v>
+        <v>230</v>
       </c>
       <c r="K106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.596</v>
+        <v>0.6004566210045662</v>
       </c>
     </row>
     <row r="107">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Regina Kesya Dumumpe</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
@@ -6719,31 +6719,31 @@
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="G107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I107" s="9" t="n">
         <v>4</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="K107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.5793103448275863</v>
+        <v>0.5962877030162413</v>
       </c>
     </row>
     <row r="108">
@@ -6769,28 +6769,28 @@
         <v>482</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G108" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="H108" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="I108" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>238</v>
+      </c>
+      <c r="K108" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="H108" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="I108" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="J108" s="9" t="n">
-        <v>214</v>
-      </c>
-      <c r="K108" s="9" t="n">
-        <v>6</v>
-      </c>
       <c r="L108" s="9" t="n">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.578838174273859</v>
+        <v>0.5954356846473029</v>
       </c>
     </row>
     <row r="109">
@@ -6799,45 +6799,45 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="K109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.5780885780885781</v>
+        <v>0.5932203389830508</v>
       </c>
     </row>
     <row r="110">
@@ -6846,45 +6846,45 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>400</v>
+        <v>498</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.5775</v>
+        <v>0.5923694779116466</v>
       </c>
     </row>
     <row r="111">
@@ -6893,45 +6893,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="K111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.5628997867803838</v>
+        <v>0.5873684210526315</v>
       </c>
     </row>
     <row r="112">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H112" s="9" t="n">
         <v>0</v>
@@ -6969,16 +6969,16 @@
         <v>0</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.5606796116504854</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="113">
@@ -6987,45 +6987,45 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="K113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.5588235294117647</v>
+        <v>0.5829383886255924</v>
       </c>
     </row>
     <row r="114">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
@@ -7048,31 +7048,31 @@
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>466</v>
+        <v>413</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c r="K114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.5536480686695279</v>
+        <v>0.5786924939467313</v>
       </c>
     </row>
     <row r="115">
@@ -7081,45 +7081,45 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>490</v>
+        <v>415</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>209</v>
+        <v>155</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>267</v>
+        <v>236</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.5530612244897959</v>
+        <v>0.5734939759036145</v>
       </c>
     </row>
     <row r="116">
@@ -7128,45 +7128,45 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Dince Lahaube</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>185</v>
+        <v>4</v>
       </c>
       <c r="G116" s="9" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.5498783454987834</v>
+        <v>0.5676470588235294</v>
       </c>
     </row>
     <row r="117">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
@@ -7189,31 +7189,31 @@
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>425</v>
+        <v>470</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="G117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.548235294117647</v>
+        <v>0.5659574468085107</v>
       </c>
     </row>
     <row r="118">
@@ -7222,45 +7222,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Ivan Christian Sasenga</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>503</v>
+        <v>434</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>272</v>
+        <v>220</v>
       </c>
       <c r="K118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.5467196819085487</v>
+        <v>0.5645161290322581</v>
       </c>
     </row>
     <row r="119">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
@@ -7283,31 +7283,31 @@
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>228</v>
+        <v>164</v>
       </c>
       <c r="K119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.5563218390804597</v>
       </c>
     </row>
     <row r="120">
@@ -7316,45 +7316,45 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>446</v>
+        <v>403</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="K120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.5426008968609866</v>
+        <v>0.5558312655086849</v>
       </c>
     </row>
     <row r="121">
@@ -7363,45 +7363,45 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Ivan Christian Sasenga</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>452</v>
+        <v>504</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="G121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>241</v>
+        <v>279</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0.5420353982300885</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="122">
@@ -7410,45 +7410,45 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Dince Lahaube</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>340</v>
+        <v>415</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>5</v>
+        <v>182</v>
       </c>
       <c r="G122" s="9" t="n">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.5411764705882353</v>
+        <v>0.5542168674698795</v>
       </c>
     </row>
     <row r="123">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
@@ -7471,31 +7471,31 @@
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>402</v>
+        <v>439</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="G123" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H123" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="I123" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.5398009950248757</v>
+        <v>0.5535307517084282</v>
       </c>
     </row>
     <row r="124">
@@ -7504,45 +7504,45 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="G124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.5353075170842825</v>
+        <v>0.548235294117647</v>
       </c>
     </row>
     <row r="125">
@@ -7551,45 +7551,45 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>428</v>
+        <v>351</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.5350467289719626</v>
+        <v>0.5470085470085471</v>
       </c>
     </row>
     <row r="126">
@@ -7598,45 +7598,45 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="G126" s="9" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.5282167042889391</v>
+        <v>0.5448430493273543</v>
       </c>
     </row>
     <row r="127">
@@ -7645,45 +7645,45 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.5277777777777778</v>
+        <v>0.5440528634361234</v>
       </c>
     </row>
     <row r="128">
@@ -7692,45 +7692,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>516</v>
+        <v>420</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.5271317829457365</v>
+        <v>0.5428571428571428</v>
       </c>
     </row>
     <row r="129">
@@ -7739,45 +7739,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>411</v>
+        <v>519</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>209</v>
+        <v>254</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>216</v>
+        <v>280</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.5255474452554745</v>
+        <v>0.5394990366088632</v>
       </c>
     </row>
     <row r="130">
@@ -7786,45 +7786,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>397</v>
+        <v>439</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="K130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.5214105793450882</v>
+        <v>0.5375854214123007</v>
       </c>
     </row>
     <row r="131">
@@ -7833,45 +7833,45 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>346</v>
+        <v>443</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>166</v>
+        <v>203</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I131" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J131" s="9" t="n">
-        <v>179</v>
+        <v>234</v>
       </c>
       <c r="K131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>180</v>
+        <v>235</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.5202312138728323</v>
+        <v>0.5304740406320542</v>
       </c>
     </row>
     <row r="132">
@@ -7880,45 +7880,45 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="K132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.5194508009153318</v>
+        <v>0.5302325581395348</v>
       </c>
     </row>
     <row r="133">
@@ -7941,16 +7941,16 @@
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G133" s="9" t="n">
         <v>6</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I133" s="9" t="n">
         <v>0</v>
@@ -7962,10 +7962,10 @@
         <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.518796992481203</v>
+        <v>0.5275</v>
       </c>
     </row>
     <row r="134">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
@@ -7988,10 +7988,10 @@
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="G134" s="9" t="n">
         <v>0</v>
@@ -8000,19 +8000,19 @@
         <v>0</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="K134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.5175644028103045</v>
+        <v>0.5214105793450882</v>
       </c>
     </row>
     <row r="135">
@@ -8038,13 +8038,13 @@
         <v>416</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I135" s="9" t="n">
         <v>27</v>
@@ -8056,10 +8056,10 @@
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.5120192307692307</v>
+        <v>0.5144230769230769</v>
       </c>
     </row>
     <row r="136">
@@ -8149,7 +8149,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 24 Juli 2026</t>
+          <t>Hari/Tanggal : 25 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8166,17 +8166,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.14 WITA</t>
+          <t>Pukul        : 11.53 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-40):</t>
+          <t>Target Hari Ini (H-41):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>66.80%</t>
+          <t>68.47%</t>
         </is>
       </c>
     </row>
@@ -8268,31 +8268,31 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2947</v>
+        <v>2944</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>279</v>
+        <v>230</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2560</v>
+        <v>2662</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2568</v>
+        <v>2673</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.8713946386155412</v>
+        <v>0.9079483695652173</v>
       </c>
     </row>
     <row r="8">
@@ -8315,31 +8315,31 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2853</v>
+        <v>2865</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>558</v>
+        <v>517</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>2216</v>
+        <v>2260</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>2235</v>
+        <v>2295</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.7833859095688749</v>
+        <v>0.8010471204188483</v>
       </c>
     </row>
     <row r="9">
@@ -8362,31 +8362,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2558</v>
+        <v>2572</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>525</v>
+        <v>487</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1939</v>
+        <v>2005</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>1940</v>
+        <v>2009</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.7584050039093042</v>
+        <v>0.781104199066874</v>
       </c>
     </row>
     <row r="10">
@@ -8395,45 +8395,45 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Fresly Jeica Manangkoda</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2044</v>
+        <v>2890</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>418</v>
+        <v>635</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1532</v>
+        <v>2183</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>1541</v>
+        <v>2199</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7539138943248532</v>
+        <v>0.7608996539792388</v>
       </c>
     </row>
     <row r="11">
@@ -8442,45 +8442,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Fresly Jeica Manangkoda</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2879</v>
+        <v>2047</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>655</v>
+        <v>401</v>
       </c>
       <c r="G11" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="I11" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="H11" s="9" t="n">
-        <v>48</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>16</v>
-      </c>
       <c r="J11" s="9" t="n">
-        <v>2154</v>
+        <v>1543</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>2170</v>
+        <v>1553</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7537339353942341</v>
+        <v>0.7586712261846604</v>
       </c>
     </row>
     <row r="12">
@@ -8509,25 +8509,25 @@
         <v>547</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" s="9" t="n">
         <v>119</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7479647218453188</v>
+        <v>0.7476255088195387</v>
       </c>
     </row>
     <row r="13">
@@ -8536,45 +8536,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Kepulauan Marore, Tabukan Utara</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri, Michael</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2128</v>
+        <v>2956</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>622</v>
+        <v>816</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1460</v>
+        <v>2073</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1461</v>
+        <v>2086</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6865601503759399</v>
+        <v>0.7056833558863329</v>
       </c>
     </row>
     <row r="14">
@@ -8583,45 +8583,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore, Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Hendri, Michael</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2943</v>
+        <v>2138</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>870</v>
+        <v>577</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>2008</v>
+        <v>1482</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>2015</v>
+        <v>1482</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6846755011892627</v>
+        <v>0.6931711880261928</v>
       </c>
     </row>
     <row r="15">
@@ -8644,31 +8644,31 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2457</v>
+        <v>2478</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>766</v>
+        <v>738</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1628</v>
+        <v>1689</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1651</v>
+        <v>1713</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.6719576719576721</v>
+        <v>0.6912832929782082</v>
       </c>
     </row>
     <row r="16">
@@ -8691,31 +8691,31 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2842</v>
+        <v>2853</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>788</v>
+        <v>757</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1866</v>
+        <v>1949</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1877</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>0.6604503870513723</v>
+        <v>1958</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>0.6862951279355065</v>
       </c>
     </row>
     <row r="17">
@@ -8738,31 +8738,31 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2188</v>
+        <v>2198</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>739</v>
+        <v>713</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>8</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1427</v>
+        <v>1442</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1440</v>
+        <v>1463</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.6581352833638026</v>
+        <v>0.6656050955414012</v>
       </c>
     </row>
     <row r="18">
@@ -8785,31 +8785,31 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2918</v>
+        <v>2928</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>937</v>
+        <v>892</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="I18" s="9" t="n">
         <v>24</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1883</v>
+        <v>1908</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1909</v>
+        <v>1934</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.6542152159013023</v>
+        <v>0.66051912568306</v>
       </c>
     </row>
     <row r="19">
@@ -8818,45 +8818,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Kezia Maralending</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2870</v>
+        <v>1467</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1016</v>
+        <v>272</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>3</v>
+        <v>228</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1798</v>
+        <v>938</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1839</v>
+        <v>966</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.6407665505226481</v>
+        <v>0.6584867075664621</v>
       </c>
     </row>
     <row r="20">
@@ -8865,45 +8865,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Kezia Maralending</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1466</v>
+        <v>2880</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>275</v>
+        <v>989</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>240</v>
+        <v>2</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>906</v>
+        <v>1841</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>934</v>
+        <v>1883</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.6371077762619373</v>
+        <v>0.6538194444444444</v>
       </c>
     </row>
     <row r="21">
@@ -8926,31 +8926,31 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2709</v>
+        <v>2718</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>991</v>
+        <v>958</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1680</v>
+        <v>1728</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1681</v>
+        <v>1729</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.6205241786637136</v>
+        <v>0.6361295069904341</v>
       </c>
     </row>
     <row r="22">
@@ -8959,45 +8959,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2359</v>
+        <v>2774</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>819</v>
+        <v>994</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1422</v>
+        <v>1686</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1447</v>
+        <v>1697</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.6133955065705807</v>
+        <v>0.6117519826964672</v>
       </c>
     </row>
     <row r="23">
@@ -9006,45 +9006,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2496</v>
+        <v>2369</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>838</v>
+        <v>777</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1468</v>
+        <v>1423</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1506</v>
+        <v>1448</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.6033653846153846</v>
+        <v>0.6112283663993247</v>
       </c>
     </row>
     <row r="24">
@@ -9053,45 +9053,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2754</v>
+        <v>2508</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1049</v>
+        <v>825</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>4</v>
+        <v>154</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1642</v>
+        <v>1468</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>1651</v>
+        <v>1500</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5994916485112564</v>
+        <v>0.5980861244019139</v>
       </c>
     </row>
     <row r="25">
@@ -9100,45 +9100,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2612</v>
+        <v>2434</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1066</v>
+        <v>883</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1489</v>
+        <v>1327</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>1500</v>
+        <v>1402</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5742725880551302</v>
+        <v>0.5760065735414954</v>
       </c>
     </row>
     <row r="26">
@@ -9147,45 +9147,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2427</v>
+        <v>2623</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>944</v>
+        <v>1059</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1266</v>
+        <v>1498</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1344</v>
+        <v>1510</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.553770086526576</v>
+        <v>0.5756767060617614</v>
       </c>
     </row>
     <row r="27">
@@ -9208,31 +9208,31 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2731</v>
+        <v>2745</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1161</v>
+        <v>1123</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1493</v>
+        <v>1572</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>1498</v>
+        <v>1580</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.5485170267301355</v>
+        <v>0.575591985428051</v>
       </c>
     </row>
     <row r="28">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Olfira Sicilia Budiman</t>
+          <t>B. Lenskar Diamanis</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -9255,31 +9255,31 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2149</v>
+        <v>2094</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>906</v>
+        <v>865</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1061</v>
+        <v>1110</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1154</v>
+        <v>1138</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.5369939506747324</v>
+        <v>0.5434574976122254</v>
       </c>
     </row>
     <row r="29">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>B. Lenskar Diamanis</t>
+          <t>Olfira Sicilia Budiman</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -9302,31 +9302,31 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2080</v>
+        <v>2164</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>922</v>
+        <v>864</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1088</v>
+        <v>1063</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1114</v>
+        <v>1156</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.5355769230769231</v>
+        <v>0.5341959334565619</v>
       </c>
     </row>
   </sheetData>
@@ -9360,7 +9360,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 24 Juli 2026</t>
+          <t>Hari/Tanggal : 25 Juli 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9377,17 +9377,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.14 WITA</t>
+          <t>Pukul        : 11.53 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-40):</t>
+          <t>Target Hari Ini (H-41):</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.80%</t>
+          <t>68.47%</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.8526405451448043</v>
+        <v>0.8761662425784563</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.8143342601173926</v>
+        <v>0.828360504460166</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9456,15 +9456,15 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7813236912435151</v>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.7892028148303748</v>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9474,15 +9474,15 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7709408913707722</v>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.7845598619174643</v>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.74568552253116</v>
+        <v>0.7624850657108722</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>0.6621751684311838</v>
+        <v>0.6841603053435115</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>0.6553524804177546</v>
+        <v>0.6608695652173913</v>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
@@ -9550,11 +9550,11 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>0.6487039563437926</v>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>+3</t>
+        <v>0.6591683708248125</v>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9564,15 +9564,15 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.6449477351916376</v>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6564092882763829</v>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9582,15 +9582,15 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.6418419556566231</v>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6559027777777777</v>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9606,9 +9606,9 @@
       <c r="C17" s="12" t="n">
         <v>0.6384</v>
       </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>-3</t>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9618,15 +9618,15 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.6013971210838273</v>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6133935907970419</v>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9636,11 +9636,11 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.596209311907705</v>
+        <v>0.6117518514022096</v>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
@@ -9654,15 +9654,15 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.5955577251647547</v>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>-1</t>
+        <v>0.6097403644573456</v>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9672,15 +9672,15 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.58777633289987</v>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6037934668071654</v>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>-3</t>
         </is>
       </c>
     </row>

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.53 WITA</t>
+          <t>Pukul        : 12.22 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.53 WITA</t>
+          <t>Pukul        : 12.22 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.53 WITA</t>
+          <t>Pukul        : 12.22 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.53 WITA</t>
+          <t>Pukul        : 12.22 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 12.22 WITA</t>
+          <t>Pukul        : 11.53 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 12.22 WITA</t>
+          <t>Pukul        : 11.53 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 12.22 WITA</t>
+          <t>Pukul        : 11.53 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 12.22 WITA</t>
+          <t>Pukul        : 11.53 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 25 Juli 2026</t>
+          <t>Hari/Tanggal : 26 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.53 WITA</t>
+          <t>Pukul        : 09.55 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -750,41 +750,41 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4185</v>
+        <v>4191</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>978</v>
+        <v>940</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
         <v/>
       </c>
       <c r="F7" s="9" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G7" s="10">
         <f>F7/B7</f>
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K7" s="10">
         <f>J7/B7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>3025</v>
+        <v>3044</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
@@ -798,14 +798,14 @@
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>3191</v>
+        <v>3227</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -819,27 +819,27 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1467</v>
+        <v>1479</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>938</v>
+        <v>957</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -867,14 +867,14 @@
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>967</v>
+        <v>994</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -888,41 +888,41 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6373</v>
+        <v>6393</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1268</v>
+        <v>1224</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4761</v>
+        <v>4793</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -936,14 +936,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>5000</v>
+        <v>5070</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3251</v>
+        <v>3259</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>558</v>
+        <v>519</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -977,21 +977,21 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="K10" s="10">
         <f>J10/B10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2567</v>
+        <v>2610</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
@@ -1005,14 +1005,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2693</v>
+        <v>2740</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
@@ -1046,21 +1046,21 @@
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
         <v/>
       </c>
       <c r="J11" s="9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K11" s="10">
         <f>J11/B11</f>
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="M11" s="10">
         <f>L11/B11</f>
@@ -1074,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
         <v/>
       </c>
       <c r="J12" s="9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K12" s="10">
         <f>J12/B12</f>
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="M12" s="10">
         <f>L12/B12</f>
@@ -1150,7 +1150,7 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1164,41 +1164,41 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4745</v>
+        <v>4757</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1843</v>
+        <v>1812</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2659</v>
+        <v>2718</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1212,14 +1212,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2865</v>
+        <v>2913</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1233,41 +1233,41 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6201</v>
+        <v>6230</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2381</v>
+        <v>2302</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>203</v>
+        <v>243</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3433</v>
+        <v>3507</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
@@ -1281,14 +1281,14 @@
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3781</v>
+        <v>3898</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>165</v>
+        <v>117</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1302,41 +1302,41 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8237</v>
+        <v>8264</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3075</v>
+        <v>2994</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K15" s="10">
         <f>J15/B15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4986</v>
+        <v>5082</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1350,14 +1350,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>5039</v>
+        <v>5136</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>159</v>
+        <v>97</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1371,41 +1371,41 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5297</v>
+        <v>5304</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1669</v>
+        <v>1618</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>3331</v>
+        <v>3393</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1419,14 +1419,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3477</v>
+        <v>3552</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1440,41 +1440,41 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2434</v>
+        <v>2438</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>883</v>
+        <v>849</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1327</v>
+        <v>1362</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
@@ -1488,14 +1488,14 @@
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1493</v>
+        <v>1524</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1509,41 +1509,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9521</v>
+        <v>9575</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1925</v>
+        <v>1817</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>147</v>
+        <v>61</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>7334</v>
+        <v>7580</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1557,14 +1557,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>7514</v>
+        <v>7671</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
@@ -1612,7 +1612,7 @@
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>960</v>
+        <v>1021</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1626,14 +1626,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>1033</v>
+        <v>1040</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1716,27 +1716,27 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>989</v>
+        <v>956</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
         <v/>
       </c>
       <c r="F21" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="10">
         <f>F21/B21</f>
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
@@ -1750,7 +1750,7 @@
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1841</v>
+        <v>1889</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1764,14 +1764,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1889</v>
+        <v>1935</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1900,7 +1900,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 25 Juli 2026</t>
+          <t>Hari/Tanggal : 26 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.53 WITA</t>
+          <t>Pukul        : 09.55 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Regina Mahoro</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -2066,31 +2066,31 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>426</v>
+        <v>518</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>413</v>
+        <v>513</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>423</v>
+        <v>518</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.9929577464788732</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Syamsia Makaminan</t>
+          <t>Regina Mahoro</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -2113,31 +2113,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>575</v>
+        <v>426</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>560</v>
+        <v>416</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>570</v>
+        <v>424</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.991304347826087</v>
+        <v>0.9953051643192488</v>
       </c>
     </row>
     <row r="10">
@@ -2146,45 +2146,45 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Alfred Jonathan</t>
+          <t>Syamsia Makaminan</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>388</v>
+        <v>575</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>340</v>
+        <v>561</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>384</v>
+        <v>570</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.9896907216494846</v>
+        <v>0.991304347826087</v>
       </c>
     </row>
     <row r="11">
@@ -2193,45 +2193,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Alfred Jonathan</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>514</v>
+        <v>388</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>484</v>
+        <v>369</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>493</v>
+        <v>384</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.9591439688715954</v>
+        <v>0.9896907216494846</v>
       </c>
     </row>
     <row r="12">
@@ -2240,45 +2240,45 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Merry Christiani Lano</t>
+          <t>Fitria Rianti Gorosita</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>532</v>
+        <v>389</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>480</v>
+        <v>364</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>498</v>
+        <v>367</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.9360902255639096</v>
+        <v>0.9434447300771208</v>
       </c>
     </row>
     <row r="13">
@@ -2287,45 +2287,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Ayu Lestari Areros</t>
+          <t>Merry Christiani Lano</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>311</v>
+        <v>532</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>25</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>285</v>
+        <v>480</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>286</v>
+        <v>498</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.9196141479099679</v>
+        <v>0.9360902255639096</v>
       </c>
     </row>
     <row r="14">
@@ -2334,24 +2334,24 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Fitria Rianti Gorosita</t>
+          <t>Ayu Lestari Areros</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>386</v>
+        <v>311</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
@@ -2360,19 +2360,19 @@
         <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>351</v>
+        <v>285</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>353</v>
+        <v>286</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.9145077720207254</v>
+        <v>0.9196141479099679</v>
       </c>
     </row>
     <row r="15">
@@ -2381,45 +2381,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Clara Patricia Pangandaheng</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="I15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>329</v>
+      </c>
+      <c r="K15" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J15" s="9" t="n">
-        <v>307</v>
-      </c>
-      <c r="K15" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" s="9" t="n">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.8937823834196891</v>
+        <v>0.907103825136612</v>
       </c>
     </row>
     <row r="16">
@@ -2428,21 +2428,21 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Meisye Fransiska Samau</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>39</v>
@@ -2451,22 +2451,22 @@
         <v>0</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>326</v>
+        <v>368</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.893150684931507</v>
+        <v>0.9041769041769042</v>
       </c>
     </row>
     <row r="17">
@@ -2475,45 +2475,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Clara Patricia Pangandaheng</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>418</v>
+        <v>389</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>354</v>
+        <v>302</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8875598086124402</v>
+        <v>0.897172236503856</v>
       </c>
     </row>
     <row r="18">
@@ -2522,21 +2522,21 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Meisye Fransiska Samau</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>47</v>
@@ -2545,22 +2545,22 @@
         <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8848039215686273</v>
+        <v>0.8875598086124402</v>
       </c>
     </row>
     <row r="19">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -2583,31 +2583,31 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>399</v>
+        <v>514</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>342</v>
+        <v>449</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>342</v>
+        <v>450</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8754863813229572</v>
       </c>
     </row>
     <row r="20">
@@ -2616,45 +2616,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>513</v>
+        <v>398</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>438</v>
+        <v>332</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>438</v>
+        <v>346</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.8538011695906432</v>
+        <v>0.8693467336683418</v>
       </c>
     </row>
     <row r="21">
@@ -2663,45 +2663,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.8513853904282116</v>
+        <v>0.8660049627791563</v>
       </c>
     </row>
     <row r="22">
@@ -2710,45 +2710,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>514</v>
+        <v>482</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>425</v>
+        <v>380</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.8385214007782102</v>
+        <v>0.8526970954356847</v>
       </c>
     </row>
     <row r="23">
@@ -2757,36 +2757,36 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0</v>
@@ -2795,7 +2795,7 @@
         <v>355</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.8372641509433962</v>
+        <v>0.8513189448441247</v>
       </c>
     </row>
     <row r="24">
@@ -2804,45 +2804,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>482</v>
+        <v>515</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>376</v>
+        <v>425</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>403</v>
+        <v>434</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.8360995850622408</v>
+        <v>0.8427184466019417</v>
       </c>
     </row>
     <row r="25">
@@ -2851,45 +2851,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Asari Prisilia Antari</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.8356807511737088</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="26">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Asari Prisilia Antari</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -2912,31 +2912,31 @@
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>362</v>
+        <v>302</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.8341013824884793</v>
+        <v>0.8380281690140845</v>
       </c>
     </row>
     <row r="27">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>0</v>
@@ -2974,16 +2974,16 @@
         <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.8262910798122065</v>
+        <v>0.8341013824884793</v>
       </c>
     </row>
     <row r="28">
@@ -2992,21 +2992,21 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>73</v>
@@ -3018,19 +3018,19 @@
         <v>0</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>0.8245192307692306</v>
+        <v>0.8294392523364487</v>
       </c>
     </row>
     <row r="29">
@@ -3039,45 +3039,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>388</v>
+        <v>426</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>318</v>
+        <v>352</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.8195876288659794</v>
+        <v>0.8262910798122065</v>
       </c>
     </row>
     <row r="30">
@@ -3086,45 +3086,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.8093023255813954</v>
+        <v>0.8256410256410256</v>
       </c>
     </row>
     <row r="31">
@@ -3133,27 +3133,27 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>535</v>
+        <v>556</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
         <v>0</v>
@@ -3162,16 +3162,16 @@
         <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.8018691588785046</v>
+        <v>0.8039568345323741</v>
       </c>
     </row>
     <row r="32">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Sheryl Jessica Tatontos</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -3194,31 +3194,31 @@
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>508</v>
+        <v>537</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.7933070866141734</v>
+        <v>0.7988826815642457</v>
       </c>
     </row>
     <row r="33">
@@ -3227,45 +3227,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Sheryl Jessica Tatontos</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>556</v>
+        <v>511</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>438</v>
+        <v>336</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>438</v>
+        <v>408</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.7877697841726617</v>
+        <v>0.7984344422700587</v>
       </c>
     </row>
     <row r="34">
@@ -3274,45 +3274,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>564</v>
+        <v>431</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>424</v>
+        <v>340</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>441</v>
+        <v>343</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.7819148936170213</v>
+        <v>0.7958236658932715</v>
       </c>
     </row>
     <row r="35">
@@ -3321,45 +3321,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>429</v>
+        <v>517</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>297</v>
+        <v>381</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>335</v>
+        <v>409</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.7808857808857809</v>
+        <v>0.7911025145067698</v>
       </c>
     </row>
     <row r="36">
@@ -3385,13 +3385,13 @@
         <v>505</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I36" s="9" t="n">
         <v>5</v>
@@ -3403,10 +3403,10 @@
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7801980198019802</v>
+        <v>0.7841584158415842</v>
       </c>
     </row>
     <row r="37">
@@ -3415,45 +3415,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>432</v>
+        <v>467</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7800925925925926</v>
+        <v>0.7837259100642399</v>
       </c>
     </row>
     <row r="38">
@@ -3462,45 +3462,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>408</v>
+        <v>564</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>290</v>
+        <v>424</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>315</v>
+        <v>441</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.7720588235294117</v>
+        <v>0.7819148936170213</v>
       </c>
     </row>
     <row r="39">
@@ -3509,45 +3509,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>465</v>
+        <v>433</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7612903225806451</v>
+        <v>0.7806004618937643</v>
       </c>
     </row>
     <row r="40">
@@ -3556,45 +3556,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>517</v>
+        <v>408</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>384</v>
+        <v>290</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>391</v>
+        <v>315</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.7562862669245648</v>
+        <v>0.7720588235294117</v>
       </c>
     </row>
     <row r="41">
@@ -3620,28 +3620,28 @@
         <v>350</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.7542857142857143</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="42">
@@ -3650,45 +3650,45 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Ruslan Ginoga</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>519</v>
+        <v>376</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>377</v>
+        <v>281</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>389</v>
+        <v>285</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.7495183044315994</v>
+        <v>0.7579787234042553</v>
       </c>
     </row>
     <row r="43">
@@ -3697,45 +3697,45 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>517</v>
+        <v>466</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>374</v>
+        <v>346</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.7485493230174082</v>
+        <v>0.757510729613734</v>
       </c>
     </row>
     <row r="44">
@@ -3744,45 +3744,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>464</v>
+        <v>519</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G44" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>390</v>
+      </c>
+      <c r="K44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>346</v>
-      </c>
-      <c r="K44" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" s="9" t="n">
-        <v>347</v>
+        <v>391</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.7478448275862069</v>
+        <v>0.7533718689788054</v>
       </c>
     </row>
     <row r="45">
@@ -3791,45 +3791,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>395</v>
+        <v>475</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>287</v>
+        <v>356</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>295</v>
+        <v>356</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.7468354430379747</v>
+        <v>0.7494736842105263</v>
       </c>
     </row>
     <row r="46">
@@ -3838,45 +3838,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Ruslan Ginoga</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>373</v>
+        <v>520</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>266</v>
+        <v>377</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>278</v>
+        <v>389</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.7453083109919573</v>
+        <v>0.7480769230769231</v>
       </c>
     </row>
     <row r="47">
@@ -3885,45 +3885,45 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>354</v>
+        <v>395</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.7372881355932204</v>
+        <v>0.7468354430379747</v>
       </c>
     </row>
     <row r="48">
@@ -3946,31 +3946,31 @@
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.7322097378277154</v>
+        <v>0.746268656716418</v>
       </c>
     </row>
     <row r="49">
@@ -3979,45 +3979,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>505</v>
+        <v>354</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>349</v>
+        <v>257</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>369</v>
+        <v>261</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.7306930693069308</v>
+        <v>0.7372881355932204</v>
       </c>
     </row>
     <row r="50">
@@ -4026,45 +4026,45 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>438</v>
+        <v>468</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>280</v>
+        <v>332</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.7305936073059359</v>
+        <v>0.7307692307692306</v>
       </c>
     </row>
     <row r="51">
@@ -4073,45 +4073,45 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.7293868921775899</v>
+        <v>0.7306930693069308</v>
       </c>
     </row>
     <row r="52">
@@ -4120,45 +4120,45 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>404</v>
+        <v>438</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>247</v>
+        <v>315</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.7178217821782178</v>
+        <v>0.7305936073059359</v>
       </c>
     </row>
     <row r="53">
@@ -4167,45 +4167,45 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>466</v>
+        <v>404</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="I53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>331</v>
+        <v>247</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>332</v>
+        <v>293</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.7124463519313305</v>
+        <v>0.7252475247524752</v>
       </c>
     </row>
     <row r="54">
@@ -4214,45 +4214,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>383</v>
+        <v>432</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>271</v>
+        <v>312</v>
       </c>
       <c r="K54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>272</v>
+        <v>312</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.7101827676240208</v>
+        <v>0.7222222222222221</v>
       </c>
     </row>
     <row r="55">
@@ -4261,45 +4261,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>432</v>
+        <v>483</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>298</v>
+        <v>348</v>
       </c>
       <c r="K55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>306</v>
+        <v>348</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.7083333333333335</v>
+        <v>0.7204968944099379</v>
       </c>
     </row>
     <row r="56">
@@ -4308,45 +4308,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.7070484581497797</v>
+        <v>0.7159353348729792</v>
       </c>
     </row>
     <row r="57">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
@@ -4369,31 +4369,31 @@
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.7064989517819708</v>
+        <v>0.7114967462039046</v>
       </c>
     </row>
     <row r="58">
@@ -4402,45 +4402,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>458</v>
+        <v>435</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="K58" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.703056768558952</v>
+        <v>0.7103448275862069</v>
       </c>
     </row>
     <row r="59">
@@ -4449,45 +4449,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>514</v>
+        <v>383</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>350</v>
+        <v>271</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>359</v>
+        <v>272</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6984435797665369</v>
+        <v>0.7101827676240208</v>
       </c>
     </row>
     <row r="60">
@@ -4496,45 +4496,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.695852534562212</v>
+        <v>0.7080459770114943</v>
       </c>
     </row>
     <row r="61">
@@ -4543,45 +4543,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="K61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.6952380952380952</v>
+        <v>0.7070484581497797</v>
       </c>
     </row>
     <row r="62">
@@ -4590,45 +4590,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>432</v>
+        <v>506</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="G62" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H62" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H62" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="I62" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>299</v>
+        <v>353</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6921296296296297</v>
+        <v>0.7055335968379447</v>
       </c>
     </row>
     <row r="63">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -4651,31 +4651,31 @@
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.6889400921658987</v>
+        <v>0.7054631828978623</v>
       </c>
     </row>
     <row r="64">
@@ -4684,45 +4684,45 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.6877470355731226</v>
+        <v>0.7008196721311475</v>
       </c>
     </row>
     <row r="65">
@@ -4731,45 +4731,45 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>509</v>
+        <v>556</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="K65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>350</v>
+        <v>389</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.68762278978389</v>
+        <v>0.699640287769784</v>
       </c>
     </row>
     <row r="66">
@@ -4778,45 +4778,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>487</v>
+        <v>459</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>333</v>
-      </c>
-      <c r="M66" s="12" t="n">
-        <v>0.6837782340862423</v>
+        <v>321</v>
+      </c>
+      <c r="M66" s="11" t="n">
+        <v>0.6993464052287581</v>
       </c>
     </row>
     <row r="67">
@@ -4825,45 +4825,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="K67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>330</v>
-      </c>
-      <c r="M67" s="12" t="n">
-        <v>0.6832298136645963</v>
+        <v>360</v>
+      </c>
+      <c r="M67" s="11" t="n">
+        <v>0.6990291262135923</v>
       </c>
     </row>
     <row r="68">
@@ -4872,45 +4872,45 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>530</v>
+        <v>504</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="K68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>362</v>
-      </c>
-      <c r="M68" s="12" t="n">
-        <v>0.6830188679245282</v>
+        <v>352</v>
+      </c>
+      <c r="M68" s="11" t="n">
+        <v>0.6984126984126984</v>
       </c>
     </row>
     <row r="69">
@@ -4919,45 +4919,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>435</v>
+        <v>532</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>278</v>
+        <v>359</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>297</v>
-      </c>
-      <c r="M69" s="12" t="n">
-        <v>0.6827586206896552</v>
+        <v>370</v>
+      </c>
+      <c r="M69" s="11" t="n">
+        <v>0.6954887218045113</v>
       </c>
     </row>
     <row r="70">
@@ -4966,45 +4966,45 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>416</v>
+        <v>469</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H70" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>283</v>
-      </c>
-      <c r="M70" s="12" t="n">
-        <v>0.6802884615384616</v>
+        <v>325</v>
+      </c>
+      <c r="M70" s="11" t="n">
+        <v>0.6929637526652452</v>
       </c>
     </row>
     <row r="71">
@@ -5013,45 +5013,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>466</v>
+        <v>531</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>305</v>
+        <v>363</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>317</v>
-      </c>
-      <c r="M71" s="12" t="n">
-        <v>0.6802575107296137</v>
+        <v>367</v>
+      </c>
+      <c r="M71" s="11" t="n">
+        <v>0.6911487758945385</v>
       </c>
     </row>
     <row r="72">
@@ -5060,45 +5060,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>341</v>
-      </c>
-      <c r="M72" s="12" t="n">
-        <v>0.6765873015873016</v>
+        <v>335</v>
+      </c>
+      <c r="M72" s="11" t="n">
+        <v>0.6907216494845361</v>
       </c>
     </row>
     <row r="73">
@@ -5107,45 +5107,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>604</v>
+        <v>436</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>179</v>
+        <v>118</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>408</v>
-      </c>
-      <c r="M73" s="12" t="n">
-        <v>0.6754966887417219</v>
+        <v>300</v>
+      </c>
+      <c r="M73" s="11" t="n">
+        <v>0.6880733944954129</v>
       </c>
     </row>
     <row r="74">
@@ -5154,45 +5154,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>458</v>
+        <v>509</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="H74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>305</v>
+        <v>345</v>
       </c>
       <c r="K74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>308</v>
-      </c>
-      <c r="M74" s="12" t="n">
-        <v>0.6724890829694323</v>
+        <v>350</v>
+      </c>
+      <c r="M74" s="11" t="n">
+        <v>0.68762278978389</v>
       </c>
     </row>
     <row r="75">
@@ -5201,45 +5201,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>289</v>
+        <v>471</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>191</v>
+        <v>279</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>194</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>0.671280276816609</v>
+        <v>323</v>
+      </c>
+      <c r="M75" s="11" t="n">
+        <v>0.6857749469214437</v>
       </c>
     </row>
     <row r="76">
@@ -5248,45 +5248,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>433</v>
+        <v>477</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>268</v>
+        <v>325</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>289</v>
+        <v>326</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>0.6674364896073903</v>
+        <v>0.6834381551362684</v>
       </c>
     </row>
     <row r="77">
@@ -5295,45 +5295,45 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>473</v>
+        <v>416</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>312</v>
+        <v>275</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>315</v>
+        <v>284</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0.6659619450317125</v>
+        <v>0.6826923076923077</v>
       </c>
     </row>
     <row r="78">
@@ -5342,45 +5342,45 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>531</v>
+        <v>433</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>347</v>
+        <v>269</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>353</v>
+        <v>293</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0.664783427495292</v>
+        <v>0.676674364896074</v>
       </c>
     </row>
     <row r="79">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
@@ -5403,31 +5403,31 @@
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>575</v>
+        <v>606</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="K79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.6643478260869565</v>
+        <v>0.6749174917491749</v>
       </c>
     </row>
     <row r="80">
@@ -5436,45 +5436,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>469</v>
+        <v>415</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.6609808102345416</v>
+        <v>0.6746987951807228</v>
       </c>
     </row>
     <row r="81">
@@ -5497,13 +5497,13 @@
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H81" s="9" t="n">
         <v>0</v>
@@ -5512,16 +5512,16 @@
         <v>0</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="K81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.6602687140115164</v>
+        <v>0.6730038022813687</v>
       </c>
     </row>
     <row r="82">
@@ -5530,45 +5530,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>388</v>
+        <v>581</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>247</v>
+        <v>391</v>
       </c>
       <c r="K82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>256</v>
+        <v>391</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.6597938144329896</v>
+        <v>0.6729776247848537</v>
       </c>
     </row>
     <row r="83">
@@ -5577,45 +5577,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>449</v>
+        <v>289</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>289</v>
+        <v>191</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>295</v>
+        <v>194</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.6570155902004454</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="84">
@@ -5624,45 +5624,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="K84" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.6563876651982379</v>
+        <v>0.6711111111111111</v>
       </c>
     </row>
     <row r="85">
@@ -5671,45 +5671,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>412</v>
+        <v>390</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.6553398058252428</v>
+        <v>0.6666666666666665</v>
       </c>
     </row>
     <row r="86">
@@ -5718,45 +5718,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>546</v>
+        <v>326</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>191</v>
+        <v>70</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>345</v>
+        <v>212</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>355</v>
+        <v>216</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.6501831501831502</v>
+        <v>0.6625766871165644</v>
       </c>
     </row>
     <row r="87">
@@ -5765,45 +5765,45 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>421</v>
+        <v>482</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.6460807600950119</v>
+        <v>0.6597510373443982</v>
       </c>
     </row>
     <row r="88">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
@@ -5826,31 +5826,31 @@
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>326</v>
+        <v>405</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>209</v>
+        <v>262</v>
       </c>
       <c r="K88" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>210</v>
+        <v>267</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.6441717791411042</v>
+        <v>0.6592592592592592</v>
       </c>
     </row>
     <row r="89">
@@ -5859,45 +5859,45 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>486</v>
+        <v>463</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="K89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.6440329218106996</v>
+        <v>0.6544276457883369</v>
       </c>
     </row>
     <row r="90">
@@ -5906,45 +5906,45 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>473</v>
+        <v>422</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I90" s="9" t="n">
         <v>5</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.6427061310782239</v>
+        <v>0.6540284360189574</v>
       </c>
     </row>
     <row r="91">
@@ -5953,45 +5953,45 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>480</v>
+        <v>414</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>308</v>
+        <v>245</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>308</v>
+        <v>270</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.6416666666666667</v>
+        <v>0.6521739130434783</v>
       </c>
     </row>
     <row r="92">
@@ -6000,45 +6000,45 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>410</v>
+        <v>457</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>245</v>
+        <v>296</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.6414634146341462</v>
+        <v>0.6520787746170679</v>
       </c>
     </row>
     <row r="93">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
@@ -6061,31 +6061,31 @@
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>501</v>
+        <v>477</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="G93" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="H93" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="I93" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H93" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I93" s="9" t="n">
-        <v>4</v>
-      </c>
       <c r="J93" s="9" t="n">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.6407185628742514</v>
+        <v>0.6498951781970649</v>
       </c>
     </row>
     <row r="94">
@@ -6094,45 +6094,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>353</v>
+        <v>489</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>218</v>
+        <v>258</v>
       </c>
       <c r="K94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>226</v>
+        <v>317</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.6402266288951841</v>
+        <v>0.6482617586912065</v>
       </c>
     </row>
     <row r="95">
@@ -6141,45 +6141,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>625</v>
+        <v>458</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>399</v>
+        <v>296</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.6384</v>
+        <v>0.6462882096069869</v>
       </c>
     </row>
     <row r="96">
@@ -6188,45 +6188,45 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.6349892008639308</v>
+        <v>0.6427061310782239</v>
       </c>
     </row>
     <row r="97">
@@ -6235,45 +6235,45 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>393</v>
+        <v>354</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.6335877862595419</v>
+        <v>0.6412429378531074</v>
       </c>
     </row>
     <row r="98">
@@ -6282,45 +6282,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>458</v>
+        <v>501</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.631004366812227</v>
+        <v>0.6407185628742514</v>
       </c>
     </row>
     <row r="99">
@@ -6329,45 +6329,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>363</v>
+        <v>538</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>216</v>
+        <v>338</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>229</v>
+        <v>344</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.6308539944903582</v>
+        <v>0.6394052044609665</v>
       </c>
     </row>
     <row r="100">
@@ -6376,45 +6376,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>534</v>
+        <v>625</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="G100" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>327</v>
+        <v>395</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>335</v>
+        <v>399</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.6273408239700374</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="101">
@@ -6423,45 +6423,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>367</v>
+        <v>542</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>222</v>
+        <v>322</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>230</v>
+        <v>344</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.6267029972752044</v>
+        <v>0.6346863468634686</v>
       </c>
     </row>
     <row r="102">
@@ -6470,45 +6470,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>476</v>
+        <v>363</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>293</v>
+        <v>216</v>
       </c>
       <c r="K102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.6260504201680672</v>
+        <v>0.6336088154269972</v>
       </c>
     </row>
     <row r="103">
@@ -6517,45 +6517,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>539</v>
+        <v>457</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>314</v>
+        <v>261</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>336</v>
+        <v>289</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.6233766233766234</v>
+        <v>0.6323851203501094</v>
       </c>
     </row>
     <row r="104">
@@ -6564,45 +6564,45 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>454</v>
+        <v>367</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>282</v>
+        <v>230</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.6211453744493393</v>
+        <v>0.6267029972752044</v>
       </c>
     </row>
     <row r="105">
@@ -6611,45 +6611,45 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>232</v>
+        <v>285</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.6162280701754386</v>
+        <v>0.6266375545851528</v>
       </c>
     </row>
     <row r="106">
@@ -6658,45 +6658,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Regina Kesya Dumumpe</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="K106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.6004566210045662</v>
+        <v>0.6240963855421687</v>
       </c>
     </row>
     <row r="107">
@@ -6705,45 +6705,45 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>431</v>
+        <v>498</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I107" s="9" t="n">
         <v>4</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="K107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.5962877030162413</v>
+        <v>0.6224899598393574</v>
       </c>
     </row>
     <row r="108">
@@ -6752,45 +6752,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Regina Kesya Dumumpe</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>482</v>
+        <v>442</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.5954356846473029</v>
+        <v>0.6063348416289592</v>
       </c>
     </row>
     <row r="109">
@@ -6799,45 +6799,45 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.5932203389830508</v>
+        <v>0.6041666666666666</v>
       </c>
     </row>
     <row r="110">
@@ -6846,45 +6846,45 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>498</v>
+        <v>414</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.5923694779116466</v>
+        <v>0.6014492753623188</v>
       </c>
     </row>
     <row r="111">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
@@ -6907,31 +6907,31 @@
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>475</v>
+        <v>424</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="K111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.5873684210526315</v>
+        <v>0.6014150943396226</v>
       </c>
     </row>
     <row r="112">
@@ -6940,45 +6940,45 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>400</v>
+        <v>479</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="K112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>234</v>
+        <v>288</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.585</v>
+        <v>0.6012526096033403</v>
       </c>
     </row>
     <row r="113">
@@ -6987,45 +6987,45 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="G113" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>248</v>
+      </c>
+      <c r="K113" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="9" t="n">
-        <v>245</v>
-      </c>
-      <c r="K113" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L113" s="9" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.5829383886255924</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="114">
@@ -7034,36 +7034,36 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="G114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="K114" s="9" t="n">
         <v>0</v>
@@ -7072,7 +7072,7 @@
         <v>239</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.5786924939467313</v>
+        <v>0.5975</v>
       </c>
     </row>
     <row r="115">
@@ -7081,45 +7081,45 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>415</v>
+        <v>484</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>238</v>
+        <v>289</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.5734939759036145</v>
+        <v>0.5971074380165289</v>
       </c>
     </row>
     <row r="116">
@@ -7128,45 +7128,45 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Dince Lahaube</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>340</v>
+        <v>437</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>4</v>
+        <v>181</v>
       </c>
       <c r="G116" s="9" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>193</v>
+        <v>256</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.5676470588235294</v>
+        <v>0.585812356979405</v>
       </c>
     </row>
     <row r="117">
@@ -7175,45 +7175,45 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>470</v>
+        <v>415</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.5659574468085107</v>
+        <v>0.5807228915662651</v>
       </c>
     </row>
     <row r="118">
@@ -7222,45 +7222,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Dince Lahaube</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>434</v>
+        <v>340</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>187</v>
+        <v>4</v>
       </c>
       <c r="G118" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="H118" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H118" s="9" t="n">
-        <v>24</v>
-      </c>
       <c r="I118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>193</v>
+      </c>
+      <c r="K118" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J118" s="9" t="n">
-        <v>220</v>
-      </c>
-      <c r="K118" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L118" s="9" t="n">
-        <v>245</v>
+        <v>196</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.5645161290322581</v>
+        <v>0.5764705882352941</v>
       </c>
     </row>
     <row r="119">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
@@ -7283,31 +7283,31 @@
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="K119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.5563218390804597</v>
+        <v>0.5759637188208617</v>
       </c>
     </row>
     <row r="120">
@@ -7316,45 +7316,45 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>403</v>
+        <v>438</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>224</v>
+        <v>164</v>
       </c>
       <c r="K120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.5558312655086849</v>
+        <v>0.5707762557077626</v>
       </c>
     </row>
     <row r="121">
@@ -7363,45 +7363,45 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Ivan Christian Sasenga</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>504</v>
+        <v>470</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="G121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>279</v>
+        <v>245</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5680851063829787</v>
       </c>
     </row>
     <row r="122">
@@ -7410,45 +7410,45 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G122" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="K122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.5542168674698795</v>
+        <v>0.5668316831683168</v>
       </c>
     </row>
     <row r="123">
@@ -7474,28 +7474,28 @@
         <v>439</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G123" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I123" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.5535307517084282</v>
+        <v>0.5603644646924829</v>
       </c>
     </row>
     <row r="124">
@@ -7504,45 +7504,45 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>425</v>
+        <v>520</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="G124" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>233</v>
+        <v>290</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.548235294117647</v>
+        <v>0.5576923076923077</v>
       </c>
     </row>
     <row r="125">
@@ -7551,24 +7551,24 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Ivan Christian Sasenga</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>351</v>
+        <v>504</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>159</v>
+        <v>224</v>
       </c>
       <c r="G125" s="9" t="n">
         <v>0</v>
@@ -7577,19 +7577,19 @@
         <v>0</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>189</v>
+        <v>279</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>192</v>
+        <v>280</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.5470085470085471</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="126">
@@ -7598,45 +7598,45 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G126" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.5448430493273543</v>
+        <v>0.5550351288056206</v>
       </c>
     </row>
     <row r="127">
@@ -7645,45 +7645,45 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>454</v>
+        <v>427</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.5440528634361234</v>
+        <v>0.5480093676814989</v>
       </c>
     </row>
     <row r="128">
@@ -7692,45 +7692,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>420</v>
+        <v>351</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>189</v>
+      </c>
+      <c r="K128" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="9" t="n">
-        <v>227</v>
-      </c>
-      <c r="K128" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L128" s="9" t="n">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.5470085470085471</v>
       </c>
     </row>
     <row r="129">
@@ -7739,45 +7739,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.5394990366088632</v>
+        <v>0.545054945054945</v>
       </c>
     </row>
     <row r="130">
@@ -7786,45 +7786,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="K130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.5375854214123007</v>
+        <v>0.5436241610738255</v>
       </c>
     </row>
     <row r="131">
@@ -7850,13 +7850,13 @@
         <v>443</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I131" s="9" t="n">
         <v>1</v>
@@ -7868,10 +7868,10 @@
         <v>0</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.5304740406320542</v>
+        <v>0.5395033860045146</v>
       </c>
     </row>
     <row r="132">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
@@ -7894,31 +7894,31 @@
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="G132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="K132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.5302325581395348</v>
+        <v>0.5365239294710328</v>
       </c>
     </row>
     <row r="133">
@@ -7927,45 +7927,45 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="K133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.5275</v>
+        <v>0.531322505800464</v>
       </c>
     </row>
     <row r="134">
@@ -7974,45 +7974,45 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="G134" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H134" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.5214105793450882</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="135">
@@ -8149,7 +8149,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 25 Juli 2026</t>
+          <t>Hari/Tanggal : 26 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.53 WITA</t>
+          <t>Pukul        : 09.55 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8268,31 +8268,31 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2944</v>
+        <v>2966</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2662</v>
+        <v>2704</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2673</v>
+        <v>2716</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.9079483695652173</v>
+        <v>0.9157113958192852</v>
       </c>
     </row>
     <row r="8">
@@ -8315,31 +8315,31 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2865</v>
+        <v>2870</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>517</v>
+        <v>479</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>2260</v>
+        <v>2308</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>2295</v>
+        <v>2351</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.8010471204188483</v>
+        <v>0.8191637630662021</v>
       </c>
     </row>
     <row r="9">
@@ -8362,31 +8362,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2572</v>
+        <v>2583</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>487</v>
+        <v>470</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2005</v>
+        <v>2068</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2009</v>
+        <v>2069</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.781104199066874</v>
+        <v>0.8010065814943864</v>
       </c>
     </row>
     <row r="10">
@@ -8395,45 +8395,45 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Fresly Jeica Manangkoda</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2890</v>
+        <v>2049</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>635</v>
+        <v>381</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2183</v>
+        <v>1562</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2199</v>
+        <v>1569</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7608996539792388</v>
+        <v>0.7657393850658858</v>
       </c>
     </row>
     <row r="11">
@@ -8442,45 +8442,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Fresly Jeica Manangkoda</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2047</v>
+        <v>2903</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>401</v>
+        <v>597</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1543</v>
+        <v>2202</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1553</v>
+        <v>2221</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7586712261846604</v>
+        <v>0.7650706166035135</v>
       </c>
     </row>
     <row r="12">
@@ -8503,31 +8503,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2948</v>
+        <v>2953</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>2149</v>
+        <v>2162</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2204</v>
+        <v>2216</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7476255088195387</v>
+        <v>0.7504232983406705</v>
       </c>
     </row>
     <row r="13">
@@ -8536,45 +8536,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore, Tabukan Utara</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Hendri, Michael</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2956</v>
+        <v>2867</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>816</v>
+        <v>726</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>2073</v>
+        <v>2092</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2086</v>
+        <v>2101</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.7056833558863329</v>
+        <v>0.7328217649110569</v>
       </c>
     </row>
     <row r="14">
@@ -8583,45 +8583,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Kepulauan Marore, Tabukan Utara</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri, Michael</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2138</v>
+        <v>2966</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>577</v>
+        <v>769</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1482</v>
+        <v>2132</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1482</v>
+        <v>2144</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6931711880261928</v>
+        <v>0.7228590694538098</v>
       </c>
     </row>
     <row r="15">
@@ -8644,31 +8644,31 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2478</v>
+        <v>2488</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>738</v>
+        <v>712</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1689</v>
+        <v>1720</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1713</v>
+        <v>1737</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.6912832929782082</v>
+        <v>0.6981511254019293</v>
       </c>
     </row>
     <row r="16">
@@ -8677,45 +8677,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2853</v>
+        <v>2142</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>757</v>
+        <v>559</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1949</v>
+        <v>1482</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1958</v>
+        <v>1482</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.6862951279355065</v>
+        <v>0.6918767507002801</v>
       </c>
     </row>
     <row r="17">
@@ -8724,45 +8724,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2198</v>
+        <v>2932</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>713</v>
+        <v>853</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1442</v>
+        <v>1954</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1463</v>
+        <v>1979</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.6656050955414012</v>
+        <v>0.6749658935879945</v>
       </c>
     </row>
     <row r="18">
@@ -8771,45 +8771,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2928</v>
+        <v>2199</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>892</v>
+        <v>710</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1908</v>
+        <v>1453</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1934</v>
+        <v>1481</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.66051912568306</v>
+        <v>0.6734879490677581</v>
       </c>
     </row>
     <row r="19">
@@ -8818,45 +8818,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Kezia Maralending</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1467</v>
+        <v>2892</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>272</v>
+        <v>956</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>228</v>
+        <v>1</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>938</v>
+        <v>1889</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>966</v>
+        <v>1931</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.6584867075664621</v>
+        <v>0.6677040110650069</v>
       </c>
     </row>
     <row r="20">
@@ -8865,45 +8865,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Kezia Maralending</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2880</v>
+        <v>1479</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>989</v>
+        <v>263</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>2</v>
+        <v>222</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1841</v>
+        <v>957</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1883</v>
+        <v>985</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.6538194444444444</v>
+        <v>0.6659905341446923</v>
       </c>
     </row>
     <row r="21">
@@ -8926,31 +8926,31 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2718</v>
+        <v>2728</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>958</v>
+        <v>913</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1728</v>
+        <v>1779</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1729</v>
+        <v>1780</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.6361295069904341</v>
+        <v>0.6524926686217009</v>
       </c>
     </row>
     <row r="22">
@@ -8973,31 +8973,31 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2774</v>
+        <v>2780</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>994</v>
+        <v>975</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1686</v>
+        <v>1731</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1697</v>
+        <v>1739</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.6117519826964672</v>
+        <v>0.6255395683453238</v>
       </c>
     </row>
     <row r="23">
@@ -9020,31 +9020,31 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2369</v>
+        <v>2372</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1423</v>
+        <v>1439</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1448</v>
+        <v>1471</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.6112283663993247</v>
+        <v>0.6201517706576728</v>
       </c>
     </row>
     <row r="24">
@@ -9053,45 +9053,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2508</v>
+        <v>2632</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>825</v>
+        <v>1035</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1468</v>
+        <v>1557</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>1500</v>
+        <v>1569</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5980861244019139</v>
+        <v>0.5961246200607903</v>
       </c>
     </row>
     <row r="25">
@@ -9100,45 +9100,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2434</v>
+        <v>2514</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>883</v>
+        <v>817</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>91</v>
+        <v>171</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1327</v>
+        <v>1463</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>1402</v>
+        <v>1498</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5760065735414954</v>
+        <v>0.5958631662688942</v>
       </c>
     </row>
     <row r="26">
@@ -9147,45 +9147,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2623</v>
+        <v>2438</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1059</v>
+        <v>849</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1498</v>
+        <v>1362</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1510</v>
+        <v>1447</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.5756767060617614</v>
+        <v>0.5935192780968006</v>
       </c>
     </row>
     <row r="27">
@@ -9208,16 +9208,16 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2745</v>
+        <v>2756</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1123</v>
+        <v>1106</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="I27" s="9" t="n">
         <v>8</v>
@@ -9232,7 +9232,7 @@
         <v>1580</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.575591985428051</v>
+        <v>0.5732946298984035</v>
       </c>
     </row>
     <row r="28">
@@ -9255,31 +9255,31 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2094</v>
+        <v>2104</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>865</v>
+        <v>830</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1110</v>
+        <v>1144</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1138</v>
+        <v>1178</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.5434574976122254</v>
+        <v>0.5598859315589354</v>
       </c>
     </row>
     <row r="29">
@@ -9302,31 +9302,31 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2164</v>
+        <v>2175</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>864</v>
+        <v>842</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1063</v>
+        <v>1072</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.5341959334565619</v>
+        <v>0.5374712643678161</v>
       </c>
     </row>
   </sheetData>
@@ -9360,7 +9360,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 25 Juli 2026</t>
+          <t>Hari/Tanggal : 26 Juli 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.53 WITA</t>
+          <t>Pukul        : 09.55 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.8761662425784563</v>
+        <v>0.8798646362098139</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.828360504460166</v>
+        <v>0.8407486959189936</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9460,11 +9460,11 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7892028148303748</v>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>+1</t>
+        <v>0.8011488250652742</v>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9478,11 +9478,11 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7845598619174643</v>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>-1</t>
+        <v>0.7930549038010324</v>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.7624850657108722</v>
+        <v>0.7699832975423526</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9528,15 +9528,15 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>0.6608695652173913</v>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.672075726842461</v>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9546,15 +9546,15 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>0.6591683708248125</v>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6696832579185519</v>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9564,11 +9564,11 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.6564092882763829</v>
+        <v>0.6690871369294605</v>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
@@ -9582,15 +9582,15 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.6559027777777777</v>
+        <v>0.6637706342311034</v>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
     </row>
@@ -9618,15 +9618,15 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.6133935907970419</v>
+        <v>0.6256821829855538</v>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
     </row>
@@ -9636,15 +9636,15 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.6117518514022096</v>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>+1</t>
+        <v>0.6251025430680885</v>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9654,15 +9654,15 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.6097403644573456</v>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>+1</t>
+        <v>0.6214908034849952</v>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9676,11 +9676,11 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.6037934668071654</v>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>-3</t>
+        <v>0.6123607315535001</v>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.55 WITA</t>
+          <t>Pukul        : 10.07 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.55 WITA</t>
+          <t>Pukul        : 10.07 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.55 WITA</t>
+          <t>Pukul        : 10.07 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.55 WITA</t>
+          <t>Pukul        : 10.07 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 26 Juli 2026</t>
+          <t>Hari/Tanggal : 27 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -616,32 +616,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 10.07 WITA</t>
+          <t>Pukul        : 08.08 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-41):</t>
+          <t>Target Hari Ini (H-42):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>68.47%</t>
+          <t>70.14%</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Hijau &gt;= 68.47%</t>
+          <t>Hijau &gt;= 70.14%</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Kuning 34.23% - 68.47%</t>
+          <t>Kuning 35.07% - 70.14%</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Merah &lt; 34.23%</t>
+          <t>Merah &lt; 35.07%</t>
         </is>
       </c>
     </row>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4191</v>
+        <v>4199</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
@@ -770,21 +770,21 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" s="10">
         <f>J7/B7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>3044</v>
+        <v>3052</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
@@ -798,14 +798,14 @@
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>3227</v>
+        <v>3248</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -819,41 +819,41 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1479</v>
+        <v>1484</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>263</v>
+        <v>213</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
         <v/>
       </c>
       <c r="J8" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K8" s="10">
         <f>J8/B8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>957</v>
+        <v>1020</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -867,14 +867,14 @@
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>994</v>
-      </c>
-      <c r="Q8" s="12">
+        <v>1054</v>
+      </c>
+      <c r="Q8" s="11">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -888,41 +888,41 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6393</v>
+        <v>6402</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1224</v>
+        <v>1206</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4793</v>
+        <v>4824</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -936,14 +936,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>5070</v>
+        <v>5107</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3259</v>
+        <v>3272</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>519</v>
+        <v>476</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -977,21 +977,21 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="K10" s="10">
         <f>J10/B10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2610</v>
+        <v>2685</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
@@ -1005,14 +1005,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2740</v>
+        <v>2796</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1032,28 +1032,28 @@
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
         <v/>
       </c>
       <c r="J11" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K11" s="10">
         <f>J11/B11</f>
@@ -1074,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1115,14 +1115,14 @@
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
         <v/>
       </c>
       <c r="J12" s="9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K12" s="10">
         <f>J12/B12</f>
@@ -1164,13 +1164,13 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4757</v>
+        <v>4772</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1812</v>
+        <v>1767</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
@@ -1184,14 +1184,14 @@
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>154</v>
+        <v>221</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
@@ -1205,21 +1205,21 @@
         <v/>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O13" s="10">
         <f>N13/B13</f>
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2913</v>
+        <v>2973</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1233,41 +1233,41 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6230</v>
+        <v>6240</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2302</v>
+        <v>2276</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3507</v>
+        <v>3590</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
@@ -1281,14 +1281,14 @@
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3898</v>
+        <v>3943</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1302,41 +1302,41 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8264</v>
+        <v>8275</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2994</v>
+        <v>2945</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K15" s="10">
         <f>J15/B15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>5082</v>
+        <v>5130</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1350,14 +1350,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>5136</v>
+        <v>5212</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1371,41 +1371,41 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5304</v>
+        <v>5312</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1618</v>
+        <v>1590</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>3393</v>
+        <v>3511</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1419,14 +1419,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3552</v>
+        <v>3610</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1446,35 +1446,35 @@
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1362</v>
+        <v>1393</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
@@ -1488,14 +1488,14 @@
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1524</v>
+        <v>1529</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1509,41 +1509,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9575</v>
+        <v>9603</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1817</v>
+        <v>1761</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>7580</v>
+        <v>7699</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1557,14 +1557,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>7671</v>
+        <v>7774</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
@@ -1612,7 +1612,7 @@
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1021</v>
+        <v>1048</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1626,14 +1626,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>1040</v>
+        <v>1051</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1716,13 +1716,13 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2892</v>
+        <v>2900</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>956</v>
+        <v>929</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
@@ -1736,21 +1736,21 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1889</v>
+        <v>1926</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1764,14 +1764,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1935</v>
+        <v>1970</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1900,7 +1900,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 26 Juli 2026</t>
+          <t>Hari/Tanggal : 27 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1917,17 +1917,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 10.07 WITA</t>
+          <t>Pukul        : 08.08 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-41):</t>
+          <t>Target Hari Ini (H-42):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>68.47%</t>
+          <t>70.14%</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Siti Maryam Madonsa</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>561</v>
+        <v>518</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0</v>
@@ -2028,19 +2028,19 @@
         <v>0</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>557</v>
+        <v>518</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>561</v>
+        <v>518</v>
       </c>
       <c r="M7" s="11" t="n">
         <v>1</v>
@@ -2052,21 +2052,21 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Alfred Jonathan</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>518</v>
+        <v>389</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0</v>
@@ -2075,19 +2075,19 @@
         <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>513</v>
+        <v>389</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>518</v>
+        <v>389</v>
       </c>
       <c r="M8" s="11" t="n">
         <v>1</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Regina Mahoro</t>
+          <t>Siti Maryam Madonsa</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -2113,31 +2113,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>426</v>
+        <v>561</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>416</v>
+        <v>561</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>424</v>
+        <v>561</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.9953051643192488</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Syamsia Makaminan</t>
+          <t>Regina Mahoro</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -2160,31 +2160,31 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>575</v>
+        <v>426</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>561</v>
+        <v>418</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>570</v>
+        <v>424</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.991304347826087</v>
+        <v>0.9953051643192488</v>
       </c>
     </row>
     <row r="11">
@@ -2193,45 +2193,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Alfred Jonathan</t>
+          <t>Syamsia Makaminan</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>388</v>
+        <v>575</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>369</v>
+        <v>569</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>384</v>
+        <v>570</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.9896907216494846</v>
+        <v>0.991304347826087</v>
       </c>
     </row>
     <row r="12">
@@ -2257,7 +2257,7 @@
         <v>389</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>0</v>
@@ -2269,16 +2269,16 @@
         <v>3</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.9434447300771208</v>
+        <v>0.9511568123393316</v>
       </c>
     </row>
     <row r="13">
@@ -2301,13 +2301,13 @@
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H13" s="9" t="n">
         <v>16</v>
@@ -2325,7 +2325,7 @@
         <v>498</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.9360902255639096</v>
+        <v>0.9325842696629213</v>
       </c>
     </row>
     <row r="14">
@@ -2348,16 +2348,16 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>0</v>
@@ -2369,10 +2369,10 @@
         <v>1</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.9196141479099679</v>
+        <v>0.923076923076923</v>
       </c>
     </row>
     <row r="15">
@@ -2381,45 +2381,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Meisye Fransiska Samau</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>366</v>
+        <v>412</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>332</v>
+        <v>379</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.907103825136612</v>
+        <v>0.9199029126213593</v>
       </c>
     </row>
     <row r="16">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Meisye Fransiska Samau</t>
+          <t>Clara Patricia Pangandaheng</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -2442,31 +2442,31 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>359</v>
+        <v>302</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.9041769041769042</v>
+        <v>0.9104859335038362</v>
       </c>
     </row>
     <row r="17">
@@ -2475,45 +2475,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Clara Patricia Pangandaheng</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>389</v>
+        <v>366</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>302</v>
+        <v>329</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.897172236503856</v>
+        <v>0.907103825136612</v>
       </c>
     </row>
     <row r="18">
@@ -2522,45 +2522,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>418</v>
+        <v>515</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>371</v>
+        <v>457</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>371</v>
+        <v>460</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8875598086124402</v>
+        <v>0.8932038834951457</v>
       </c>
     </row>
     <row r="19">
@@ -2569,45 +2569,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>514</v>
+        <v>418</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>449</v>
+        <v>371</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>450</v>
+        <v>371</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.8754863813229572</v>
+        <v>0.8875598086124402</v>
       </c>
     </row>
     <row r="20">
@@ -2633,28 +2633,28 @@
         <v>398</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.8693467336683418</v>
+        <v>0.8819095477386935</v>
       </c>
     </row>
     <row r="21">
@@ -2677,31 +2677,31 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.8660049627791563</v>
+        <v>0.8737864077669903</v>
       </c>
     </row>
     <row r="22">
@@ -2710,45 +2710,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>482</v>
+        <v>427</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>380</v>
+        <v>359</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>411</v>
+        <v>369</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.8526970954356847</v>
+        <v>0.8641686182669788</v>
       </c>
     </row>
     <row r="23">
@@ -2757,45 +2757,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>417</v>
+        <v>482</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>355</v>
+        <v>411</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.8513189448441247</v>
+        <v>0.8526970954356847</v>
       </c>
     </row>
     <row r="24">
@@ -2804,45 +2804,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>515</v>
+        <v>431</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="H24" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>6</v>
-      </c>
       <c r="J24" s="9" t="n">
-        <v>425</v>
+        <v>359</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>434</v>
+        <v>367</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.8427184466019417</v>
+        <v>0.851508120649652</v>
       </c>
     </row>
     <row r="25">
@@ -2851,45 +2851,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.84</v>
+        <v>0.8513189448441247</v>
       </c>
     </row>
     <row r="26">
@@ -2898,45 +2898,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Asari Prisilia Antari</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.8380281690140845</v>
+        <v>0.8455882352941176</v>
       </c>
     </row>
     <row r="27">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -2959,31 +2959,31 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
+        <v>515</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>429</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="9" t="n">
         <v>434</v>
       </c>
-      <c r="F27" s="9" t="n">
-        <v>72</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>362</v>
-      </c>
-      <c r="K27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="9" t="n">
-        <v>362</v>
-      </c>
       <c r="M27" s="11" t="n">
-        <v>0.8341013824884793</v>
+        <v>0.8427184466019417</v>
       </c>
     </row>
     <row r="28">
@@ -2992,45 +2992,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Asari Prisilia Antari</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>347</v>
+        <v>302</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>0.8294392523364487</v>
+        <v>0.8380281690140845</v>
       </c>
     </row>
     <row r="29">
@@ -3039,45 +3039,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>426</v>
+        <v>393</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>352</v>
+        <v>306</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.8262910798122065</v>
+        <v>0.8371501272264631</v>
       </c>
     </row>
     <row r="30">
@@ -3086,45 +3086,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>390</v>
+        <v>434</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>306</v>
+        <v>362</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.8256410256410256</v>
+        <v>0.8341013824884793</v>
       </c>
     </row>
     <row r="31">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>556</v>
+        <v>426</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
@@ -3162,16 +3162,16 @@
         <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>447</v>
+        <v>352</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>447</v>
+        <v>352</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.8039568345323741</v>
+        <v>0.8262910798122065</v>
       </c>
     </row>
     <row r="32">
@@ -3180,27 +3180,27 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H32" s="9" t="n">
         <v>0</v>
@@ -3209,16 +3209,16 @@
         <v>0</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>429</v>
+        <v>456</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>429</v>
+        <v>456</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.7988826815642457</v>
+        <v>0.8172043010752688</v>
       </c>
     </row>
     <row r="33">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Sheryl Jessica Tatontos</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -3241,31 +3241,31 @@
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>511</v>
+        <v>538</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>336</v>
+        <v>432</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.7984344422700587</v>
+        <v>0.8104089219330856</v>
       </c>
     </row>
     <row r="34">
@@ -3274,45 +3274,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>431</v>
+        <v>517</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>340</v>
+        <v>411</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>343</v>
+        <v>417</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.7958236658932715</v>
+        <v>0.8065764023210832</v>
       </c>
     </row>
     <row r="35">
@@ -3321,45 +3321,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.7911025145067698</v>
+        <v>0.8062622309197651</v>
       </c>
     </row>
     <row r="36">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Sheryl Jessica Tatontos</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -3382,31 +3382,31 @@
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>383</v>
+        <v>336</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7841584158415842</v>
+        <v>0.7984344422700587</v>
       </c>
     </row>
     <row r="37">
@@ -3415,45 +3415,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>467</v>
+        <v>431</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7837259100642399</v>
+        <v>0.7981438515081206</v>
       </c>
     </row>
     <row r="38">
@@ -3462,45 +3462,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>564</v>
+        <v>433</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="G38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>424</v>
+        <v>332</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>441</v>
+        <v>342</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.7819148936170213</v>
+        <v>0.789838337182448</v>
       </c>
     </row>
     <row r="39">
@@ -3509,45 +3509,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>433</v>
+        <v>566</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>332</v>
+        <v>424</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>338</v>
+        <v>446</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7806004618937643</v>
+        <v>0.7879858657243817</v>
       </c>
     </row>
     <row r="40">
@@ -3556,45 +3556,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>408</v>
+        <v>467</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>290</v>
+        <v>339</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>315</v>
+        <v>366</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.7720588235294117</v>
+        <v>0.7837259100642399</v>
       </c>
     </row>
     <row r="41">
@@ -3603,45 +3603,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>350</v>
+        <v>537</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>262</v>
+        <v>401</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>266</v>
+        <v>417</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.76</v>
+        <v>0.776536312849162</v>
       </c>
     </row>
     <row r="42">
@@ -3650,45 +3650,45 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Ruslan Ginoga</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>376</v>
+        <v>472</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>281</v>
+        <v>365</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>285</v>
+        <v>366</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.7579787234042553</v>
+        <v>0.7754237288135593</v>
       </c>
     </row>
     <row r="43">
@@ -3697,45 +3697,45 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>466</v>
+        <v>519</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G43" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>401</v>
+      </c>
+      <c r="K43" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="9" t="n">
-        <v>346</v>
-      </c>
-      <c r="K43" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" s="9" t="n">
-        <v>353</v>
+        <v>402</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.757510729613734</v>
+        <v>0.7745664739884393</v>
       </c>
     </row>
     <row r="44">
@@ -3744,45 +3744,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Ruslan Ginoga</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>519</v>
+        <v>377</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>390</v>
+        <v>288</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>391</v>
+        <v>291</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.7533718689788054</v>
+        <v>0.7718832891246684</v>
       </c>
     </row>
     <row r="45">
@@ -3791,45 +3791,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>475</v>
+        <v>350</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>356</v>
+        <v>262</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>356</v>
+        <v>269</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.7494736842105263</v>
+        <v>0.7685714285714286</v>
       </c>
     </row>
     <row r="46">
@@ -3838,45 +3838,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>520</v>
+        <v>478</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>389</v>
+        <v>366</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.7480769230769231</v>
+        <v>0.7656903765690377</v>
       </c>
     </row>
     <row r="47">
@@ -3885,45 +3885,45 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
+        <v>520</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="I47" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>377</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="9" t="n">
         <v>395</v>
       </c>
-      <c r="F47" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="G47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="J47" s="9" t="n">
-        <v>289</v>
-      </c>
-      <c r="K47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="9" t="n">
-        <v>295</v>
-      </c>
       <c r="M47" s="11" t="n">
-        <v>0.7468354430379747</v>
+        <v>0.7596153846153846</v>
       </c>
     </row>
     <row r="48">
@@ -3932,45 +3932,45 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>536</v>
+        <v>395</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>400</v>
+        <v>289</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>400</v>
+        <v>295</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.746268656716418</v>
+        <v>0.7468354430379747</v>
       </c>
     </row>
     <row r="49">
@@ -3996,13 +3996,13 @@
         <v>354</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I49" s="9" t="n">
         <v>0</v>
@@ -4014,10 +4014,10 @@
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.7372881355932204</v>
+        <v>0.7429378531073446</v>
       </c>
     </row>
     <row r="50">
@@ -4026,45 +4026,45 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>468</v>
+        <v>432</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.7307692307692306</v>
+        <v>0.7384259259259259</v>
       </c>
     </row>
     <row r="51">
@@ -4073,45 +4073,45 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>505</v>
+        <v>483</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.7306930693069308</v>
+        <v>0.7370600414078674</v>
       </c>
     </row>
     <row r="52">
@@ -4120,45 +4120,45 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>438</v>
+        <v>469</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>315</v>
+        <v>343</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.7305936073059359</v>
+        <v>0.7313432835820897</v>
       </c>
     </row>
     <row r="53">
@@ -4167,45 +4167,45 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>404</v>
+        <v>505</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>247</v>
+        <v>349</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>293</v>
+        <v>369</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.7252475247524752</v>
+        <v>0.7306930693069308</v>
       </c>
     </row>
     <row r="54">
@@ -4214,45 +4214,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.7222222222222221</v>
+        <v>0.7305936073059359</v>
       </c>
     </row>
     <row r="55">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
@@ -4275,31 +4275,31 @@
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>328</v>
+      </c>
+      <c r="K55" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="9" t="n">
-        <v>348</v>
-      </c>
-      <c r="K55" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" s="9" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.7204968944099379</v>
+        <v>0.7278617710583153</v>
       </c>
     </row>
     <row r="56">
@@ -4308,45 +4308,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>433</v>
+        <v>404</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>310</v>
+        <v>247</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.7159353348729792</v>
+        <v>0.7252475247524752</v>
       </c>
     </row>
     <row r="57">
@@ -4355,45 +4355,45 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>461</v>
+        <v>434</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.7114967462039046</v>
+        <v>0.7188940092165899</v>
       </c>
     </row>
     <row r="58">
@@ -4402,45 +4402,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.7103448275862069</v>
+        <v>0.7167755991285403</v>
       </c>
     </row>
     <row r="59">
@@ -4449,45 +4449,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>383</v>
+        <v>422</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.7101827676240208</v>
+        <v>0.7156398104265402</v>
       </c>
     </row>
     <row r="60">
@@ -4496,45 +4496,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.7080459770114943</v>
+        <v>0.7155963302752294</v>
       </c>
     </row>
     <row r="61">
@@ -4543,45 +4543,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>454</v>
+        <v>383</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="K61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>321</v>
+        <v>274</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.7070484581497797</v>
+        <v>0.7154046997389034</v>
       </c>
     </row>
     <row r="62">
@@ -4590,45 +4590,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>506</v>
+        <v>435</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="G62" s="9" t="n">
         <v>7</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>357</v>
+        <v>310</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.7055335968379447</v>
+        <v>0.7126436781609197</v>
       </c>
     </row>
     <row r="63">
@@ -4637,45 +4637,45 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>421</v>
+        <v>511</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>295</v>
+        <v>345</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>297</v>
+        <v>363</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.7054631828978623</v>
+        <v>0.7103718199608611</v>
       </c>
     </row>
     <row r="64">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
@@ -4698,31 +4698,31 @@
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>488</v>
+        <v>533</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>339</v>
+        <v>373</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.7008196721311475</v>
+        <v>0.7091932457786116</v>
       </c>
     </row>
     <row r="65">
@@ -4731,45 +4731,45 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>556</v>
+        <v>454</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>352</v>
+        <v>293</v>
       </c>
       <c r="K65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>389</v>
+        <v>321</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.699640287769784</v>
+        <v>0.7070484581497797</v>
       </c>
     </row>
     <row r="66">
@@ -4778,27 +4778,27 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>459</v>
+        <v>506</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="H66" s="9" t="n">
         <v>0</v>
@@ -4807,16 +4807,16 @@
         <v>3</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="K66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.6993464052287581</v>
+        <v>0.7055335968379447</v>
       </c>
     </row>
     <row r="67">
@@ -4825,45 +4825,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>515</v>
+        <v>326</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H67" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>227</v>
+      </c>
+      <c r="K67" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I67" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J67" s="9" t="n">
-        <v>350</v>
-      </c>
-      <c r="K67" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L67" s="9" t="n">
-        <v>360</v>
+        <v>230</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.6990291262135923</v>
+        <v>0.7055214723926381</v>
       </c>
     </row>
     <row r="68">
@@ -4872,45 +4872,45 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G68" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H68" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H68" s="9" t="n">
-        <v>25</v>
-      </c>
       <c r="I68" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.6984126984126984</v>
+        <v>0.7052845528455285</v>
       </c>
     </row>
     <row r="69">
@@ -4919,45 +4919,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
         <v>532</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.6954887218045113</v>
+        <v>0.7048872180451127</v>
       </c>
     </row>
     <row r="70">
@@ -4966,45 +4966,45 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H70" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>325</v>
-      </c>
-      <c r="M70" s="11" t="n">
-        <v>0.6929637526652452</v>
+        <v>338</v>
+      </c>
+      <c r="M70" s="12" t="n">
+        <v>0.6997929606625258</v>
       </c>
     </row>
     <row r="71">
@@ -5013,45 +5013,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>531</v>
+        <v>556</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>367</v>
-      </c>
-      <c r="M71" s="11" t="n">
-        <v>0.6911487758945385</v>
+        <v>389</v>
+      </c>
+      <c r="M71" s="12" t="n">
+        <v>0.699640287769784</v>
       </c>
     </row>
     <row r="72">
@@ -5060,45 +5060,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>485</v>
+        <v>515</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>335</v>
-      </c>
-      <c r="M72" s="11" t="n">
-        <v>0.6907216494845361</v>
+        <v>360</v>
+      </c>
+      <c r="M72" s="12" t="n">
+        <v>0.6990291262135923</v>
       </c>
     </row>
     <row r="73">
@@ -5107,45 +5107,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>436</v>
+        <v>504</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>284</v>
+        <v>338</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>300</v>
-      </c>
-      <c r="M73" s="11" t="n">
-        <v>0.6880733944954129</v>
+        <v>352</v>
+      </c>
+      <c r="M73" s="12" t="n">
+        <v>0.6984126984126984</v>
       </c>
     </row>
     <row r="74">
@@ -5154,45 +5154,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>509</v>
+        <v>469</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>350</v>
-      </c>
-      <c r="M74" s="11" t="n">
-        <v>0.68762278978389</v>
+        <v>326</v>
+      </c>
+      <c r="M74" s="12" t="n">
+        <v>0.6950959488272921</v>
       </c>
     </row>
     <row r="75">
@@ -5201,45 +5201,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="I75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>323</v>
-      </c>
-      <c r="M75" s="11" t="n">
-        <v>0.6857749469214437</v>
+        <v>301</v>
+      </c>
+      <c r="M75" s="12" t="n">
+        <v>0.6935483870967742</v>
       </c>
     </row>
     <row r="76">
@@ -5248,45 +5248,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>325</v>
+        <v>278</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>0.6834381551362684</v>
+        <v>0.693446088794926</v>
       </c>
     </row>
     <row r="77">
@@ -5309,16 +5309,16 @@
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I77" s="9" t="n">
         <v>0</v>
@@ -5330,10 +5330,10 @@
         <v>0</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0.6826923076923077</v>
+        <v>0.6930455635491607</v>
       </c>
     </row>
     <row r="78">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -5356,31 +5356,31 @@
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>433</v>
+        <v>485</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>269</v>
+        <v>334</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>293</v>
+        <v>336</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0.676674364896074</v>
+        <v>0.6927835051546392</v>
       </c>
     </row>
     <row r="79">
@@ -5389,45 +5389,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>606</v>
+        <v>477</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>405</v>
+        <v>328</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>409</v>
+        <v>329</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.6749174917491749</v>
+        <v>0.689727463312369</v>
       </c>
     </row>
     <row r="80">
@@ -5436,45 +5436,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>415</v>
+        <v>582</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>277</v>
+        <v>401</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>280</v>
+        <v>401</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.6746987951807228</v>
+        <v>0.6890034364261168</v>
       </c>
     </row>
     <row r="81">
@@ -5483,45 +5483,45 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>526</v>
+        <v>436</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>354</v>
+        <v>284</v>
       </c>
       <c r="K81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>354</v>
+        <v>300</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.6730038022813687</v>
+        <v>0.6880733944954129</v>
       </c>
     </row>
     <row r="82">
@@ -5530,45 +5530,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>581</v>
+        <v>410</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>391</v>
+        <v>280</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>391</v>
+        <v>282</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.6729776247848537</v>
+        <v>0.6878048780487805</v>
       </c>
     </row>
     <row r="83">
@@ -5577,45 +5577,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>289</v>
+        <v>451</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>299</v>
+      </c>
+      <c r="K83" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J83" s="9" t="n">
-        <v>191</v>
-      </c>
-      <c r="K83" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="L83" s="9" t="n">
-        <v>194</v>
+        <v>307</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.671280276816609</v>
+        <v>0.6807095343680709</v>
       </c>
     </row>
     <row r="84">
@@ -5624,45 +5624,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>450</v>
+        <v>526</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>302</v>
+        <v>357</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.6711111111111111</v>
+        <v>0.6787072243346007</v>
       </c>
     </row>
     <row r="85">
@@ -5671,45 +5671,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>390</v>
+        <v>606</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>247</v>
+        <v>408</v>
       </c>
       <c r="K85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>260</v>
+        <v>409</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.6749174917491749</v>
       </c>
     </row>
     <row r="86">
@@ -5718,45 +5718,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>326</v>
+        <v>415</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="K86" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>216</v>
+        <v>280</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.6625766871165644</v>
+        <v>0.6746987951807228</v>
       </c>
     </row>
     <row r="87">
@@ -5765,24 +5765,24 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>482</v>
+        <v>289</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>0</v>
@@ -5791,19 +5791,19 @@
         <v>0</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>318</v>
+        <v>191</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>318</v>
+        <v>194</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.6597510373443982</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="88">
@@ -5812,45 +5812,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J88" s="9" t="n">
+        <v>250</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="9" t="n">
         <v>262</v>
       </c>
-      <c r="K88" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L88" s="9" t="n">
-        <v>267</v>
-      </c>
       <c r="M88" s="12" t="n">
-        <v>0.6592592592592592</v>
+        <v>0.670076726342711</v>
       </c>
     </row>
     <row r="89">
@@ -5859,45 +5859,45 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.6544276457883369</v>
+        <v>0.6673960612691466</v>
       </c>
     </row>
     <row r="90">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
@@ -5920,31 +5920,31 @@
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.6540284360189574</v>
+        <v>0.6594202898550725</v>
       </c>
     </row>
     <row r="91">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
@@ -5967,31 +5967,31 @@
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>414</v>
+        <v>460</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I91" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>245</v>
+        <v>300</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6565217391304347</v>
       </c>
     </row>
     <row r="92">
@@ -6000,45 +6000,45 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>457</v>
+        <v>540</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>132</v>
+        <v>185</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>296</v>
+        <v>349</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>298</v>
+        <v>354</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.6520787746170679</v>
+        <v>0.6555555555555556</v>
       </c>
     </row>
     <row r="93">
@@ -6047,45 +6047,45 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>477</v>
+        <v>547</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>293</v>
+        <v>334</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>310</v>
+        <v>358</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.6498951781970649</v>
+        <v>0.6544789762340036</v>
       </c>
     </row>
     <row r="94">
@@ -6094,45 +6094,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>489</v>
+        <v>463</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>258</v>
+        <v>302</v>
       </c>
       <c r="K94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.6482617586912065</v>
+        <v>0.6544276457883369</v>
       </c>
     </row>
     <row r="95">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
@@ -6155,31 +6155,31 @@
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>458</v>
+        <v>422</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>294</v>
+        <v>257</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.6462882096069869</v>
+        <v>0.6540284360189574</v>
       </c>
     </row>
     <row r="96">
@@ -6188,45 +6188,45 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.6427061310782239</v>
+        <v>0.6519916142557652</v>
       </c>
     </row>
     <row r="97">
@@ -6235,45 +6235,45 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>354</v>
+        <v>489</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>218</v>
+        <v>258</v>
       </c>
       <c r="K97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>227</v>
+        <v>317</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.6412429378531074</v>
+        <v>0.6482617586912065</v>
       </c>
     </row>
     <row r="98">
@@ -6282,45 +6282,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>501</v>
+        <v>473</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G98" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H98" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>294</v>
+      </c>
+      <c r="K98" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H98" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I98" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J98" s="9" t="n">
-        <v>315</v>
-      </c>
-      <c r="K98" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L98" s="9" t="n">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.6407185628742514</v>
+        <v>0.6427061310782239</v>
       </c>
     </row>
     <row r="99">
@@ -6329,45 +6329,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>538</v>
+        <v>354</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>193</v>
+        <v>127</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>338</v>
+        <v>218</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>344</v>
+        <v>227</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.6394052044609665</v>
+        <v>0.6412429378531074</v>
       </c>
     </row>
     <row r="100">
@@ -6376,45 +6376,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>625</v>
+        <v>501</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="G100" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" s="9" t="n">
         <v>4</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>395</v>
+        <v>316</v>
       </c>
       <c r="K100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>399</v>
+        <v>321</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.6384</v>
+        <v>0.6407185628742514</v>
       </c>
     </row>
     <row r="101">
@@ -6423,45 +6423,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>542</v>
+        <v>625</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>322</v>
+        <v>395</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.6346863468634686</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="102">
@@ -6470,45 +6470,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>363</v>
+        <v>498</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>216</v>
+        <v>303</v>
       </c>
       <c r="K102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>230</v>
+        <v>316</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.6336088154269972</v>
+        <v>0.6345381526104418</v>
       </c>
     </row>
     <row r="103">
@@ -6517,45 +6517,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>457</v>
+        <v>363</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>261</v>
+        <v>216</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>289</v>
+        <v>230</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.6323851203501094</v>
+        <v>0.6336088154269972</v>
       </c>
     </row>
     <row r="104">
@@ -6564,45 +6564,45 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>367</v>
+        <v>457</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>230</v>
+        <v>289</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.6267029972752044</v>
+        <v>0.6323851203501094</v>
       </c>
     </row>
     <row r="105">
@@ -6628,7 +6628,7 @@
         <v>458</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G105" s="9" t="n">
         <v>1</v>
@@ -6640,16 +6640,16 @@
         <v>1</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K105" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.6266375545851528</v>
+        <v>0.62882096069869</v>
       </c>
     </row>
     <row r="106">
@@ -6658,45 +6658,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>415</v>
+        <v>367</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="K106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.6240963855421687</v>
+        <v>0.6267029972752044</v>
       </c>
     </row>
     <row r="107">
@@ -6705,45 +6705,45 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>498</v>
+        <v>415</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="K107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>310</v>
+        <v>259</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.6224899598393574</v>
+        <v>0.6240963855421687</v>
       </c>
     </row>
     <row r="108">
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G108" s="9" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>33</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J108" s="9" t="n">
         <v>230</v>
@@ -6787,10 +6787,10 @@
         <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.6063348416289592</v>
+        <v>0.6094808126410836</v>
       </c>
     </row>
     <row r="109">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>432</v>
+        <v>479</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H109" s="9" t="n">
         <v>9</v>
@@ -6828,16 +6828,16 @@
         <v>7</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="K109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6075156576200418</v>
       </c>
     </row>
     <row r="110">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
@@ -6860,31 +6860,31 @@
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.6014492753623188</v>
+        <v>0.6041666666666666</v>
       </c>
     </row>
     <row r="111">
@@ -6893,45 +6893,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J111" s="9" t="n">
         <v>245</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.6014150943396226</v>
+        <v>0.6033057851239669</v>
       </c>
     </row>
     <row r="112">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
@@ -6954,31 +6954,31 @@
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>479</v>
+        <v>414</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>265</v>
+        <v>220</v>
       </c>
       <c r="K112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.6012526096033403</v>
+        <v>0.6014492753623188</v>
       </c>
     </row>
     <row r="113">
@@ -7001,31 +7001,31 @@
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K113" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.6</v>
+        <v>0.6014319809069213</v>
       </c>
     </row>
     <row r="114">
@@ -7034,45 +7034,45 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="K114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.5975</v>
+        <v>0.6014150943396226</v>
       </c>
     </row>
     <row r="115">
@@ -7081,45 +7081,45 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>484</v>
+        <v>400</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.5971074380165289</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="116">
@@ -7145,28 +7145,28 @@
         <v>437</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="K116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.585812356979405</v>
+        <v>0.5949656750572082</v>
       </c>
     </row>
     <row r="117">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
@@ -7189,31 +7189,31 @@
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>415</v>
+        <v>446</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.5807228915662651</v>
+        <v>0.5896860986547086</v>
       </c>
     </row>
     <row r="118">
@@ -7222,45 +7222,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Dince Lahaube</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>340</v>
+        <v>438</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>4</v>
+        <v>169</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>196</v>
+        <v>258</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.5764705882352941</v>
+        <v>0.589041095890411</v>
       </c>
     </row>
     <row r="119">
@@ -7269,45 +7269,45 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>441</v>
+        <v>472</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.5759637188208617</v>
+        <v>0.5847457627118644</v>
       </c>
     </row>
     <row r="120">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
@@ -7330,31 +7330,31 @@
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="K120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.5707762557077626</v>
+        <v>0.5807228915662651</v>
       </c>
     </row>
     <row r="121">
@@ -7363,45 +7363,45 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Dince Lahaube</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>470</v>
+        <v>340</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>203</v>
+        <v>4</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="H121" s="9" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>245</v>
+        <v>195</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>267</v>
+        <v>197</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0.5680851063829787</v>
+        <v>0.5794117647058824</v>
       </c>
     </row>
     <row r="122">
@@ -7410,45 +7410,45 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="G122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="K122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.5668316831683168</v>
+        <v>0.5689277899343544</v>
       </c>
     </row>
     <row r="123">
@@ -7457,45 +7457,45 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.5603644646924829</v>
+        <v>0.5683962264150944</v>
       </c>
     </row>
     <row r="124">
@@ -7504,45 +7504,45 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>520</v>
+        <v>404</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="G124" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>290</v>
+        <v>229</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.5576923076923077</v>
+        <v>0.5668316831683168</v>
       </c>
     </row>
     <row r="125">
@@ -7551,45 +7551,45 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Ivan Christian Sasenga</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>504</v>
+        <v>520</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I125" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>255</v>
+      </c>
+      <c r="K125" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J125" s="9" t="n">
-        <v>279</v>
-      </c>
-      <c r="K125" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L125" s="9" t="n">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5615384615384615</v>
       </c>
     </row>
     <row r="126">
@@ -7598,45 +7598,45 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>427</v>
+        <v>451</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="G126" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.5550351288056206</v>
+        <v>0.5609756097560976</v>
       </c>
     </row>
     <row r="127">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -7659,31 +7659,31 @@
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.5480093676814989</v>
+        <v>0.5603644646924829</v>
       </c>
     </row>
     <row r="128">
@@ -7692,45 +7692,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Ivan Christian Sasenga</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>351</v>
+        <v>504</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="G128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>189</v>
+        <v>281</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>192</v>
+        <v>282</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.5470085470085471</v>
+        <v>0.5595238095238095</v>
       </c>
     </row>
     <row r="129">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
@@ -7753,31 +7753,31 @@
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>455</v>
+        <v>428</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="G129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.545054945054945</v>
+        <v>0.5584112149532711</v>
       </c>
     </row>
     <row r="130">
@@ -7786,45 +7786,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="F130" s="9" t="n">
         <v>179</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="K130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.5436241610738255</v>
+        <v>0.5560747663551402</v>
       </c>
     </row>
     <row r="131">
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G131" s="9" t="n">
         <v>3</v>
@@ -7862,16 +7862,16 @@
         <v>1</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="K131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.5395033860045146</v>
+        <v>0.5528089887640449</v>
       </c>
     </row>
     <row r="132">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
@@ -7894,31 +7894,31 @@
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>397</v>
+        <v>431</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="G132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="K132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.5365239294710328</v>
+        <v>0.5522041763341067</v>
       </c>
     </row>
     <row r="133">
@@ -7927,24 +7927,24 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>431</v>
+        <v>351</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>202</v>
+        <v>159</v>
       </c>
       <c r="G133" s="9" t="n">
         <v>0</v>
@@ -7956,16 +7956,16 @@
         <v>2</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.531322505800464</v>
+        <v>0.5470085470085471</v>
       </c>
     </row>
     <row r="134">
@@ -7974,45 +7974,45 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G134" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H134" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="K134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.53</v>
+        <v>0.5365239294710328</v>
       </c>
     </row>
     <row r="135">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
@@ -8035,31 +8035,31 @@
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.5144230769230769</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="136">
@@ -8149,7 +8149,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 26 Juli 2026</t>
+          <t>Hari/Tanggal : 27 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8166,17 +8166,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 10.07 WITA</t>
+          <t>Pukul        : 08.08 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-41):</t>
+          <t>Target Hari Ini (H-42):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>68.47%</t>
+          <t>70.14%</t>
         </is>
       </c>
     </row>
@@ -8271,28 +8271,28 @@
         <v>2966</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2704</v>
+        <v>2746</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2716</v>
+        <v>2754</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.9157113958192852</v>
+        <v>0.9285232636547539</v>
       </c>
     </row>
     <row r="8">
@@ -8315,31 +8315,31 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2870</v>
+        <v>2881</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>479</v>
+        <v>441</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>2308</v>
+        <v>2383</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>2351</v>
+        <v>2436</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.8191637630662021</v>
+        <v>0.8455397431447415</v>
       </c>
     </row>
     <row r="9">
@@ -8362,31 +8362,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2583</v>
+        <v>2601</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>470</v>
+        <v>445</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2068</v>
+        <v>2132</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2069</v>
+        <v>2137</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.8010065814943864</v>
+        <v>0.8216070742022299</v>
       </c>
     </row>
     <row r="10">
@@ -8395,45 +8395,45 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Fresly Jeica Manangkoda</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2049</v>
+        <v>2909</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>381</v>
+        <v>587</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1562</v>
+        <v>2222</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>1569</v>
+        <v>2244</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7657393850658858</v>
+        <v>0.7713991062220694</v>
       </c>
     </row>
     <row r="11">
@@ -8442,45 +8442,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Fresly Jeica Manangkoda</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2903</v>
+        <v>2050</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>597</v>
+        <v>380</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>2202</v>
+        <v>1571</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>2221</v>
+        <v>1579</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7650706166035135</v>
+        <v>0.7702439024390244</v>
       </c>
     </row>
     <row r="12">
@@ -8503,31 +8503,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2953</v>
+        <v>2955</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I12" s="9" t="n">
         <v>54</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>2162</v>
+        <v>2170</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2216</v>
+        <v>2224</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7504232983406705</v>
+        <v>0.7526226734348562</v>
       </c>
     </row>
     <row r="13">
@@ -8550,31 +8550,31 @@
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2867</v>
+        <v>2873</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>726</v>
+        <v>698</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I13" s="9" t="n">
         <v>5</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>2092</v>
+        <v>2105</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2101</v>
+        <v>2114</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.7328217649110569</v>
+        <v>0.7358162199791159</v>
       </c>
     </row>
     <row r="14">
@@ -8597,31 +8597,31 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2966</v>
+        <v>2972</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>769</v>
+        <v>758</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>2132</v>
+        <v>2159</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>2144</v>
+        <v>2169</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.7228590694538098</v>
+        <v>0.7298115746971736</v>
       </c>
     </row>
     <row r="15">
@@ -8630,45 +8630,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Kezia Maralending</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Manganitu, Tamako</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Erike, Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2488</v>
+        <v>1484</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>712</v>
+        <v>213</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>29</v>
+        <v>217</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1720</v>
+        <v>1020</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1737</v>
+        <v>1049</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.6981511254019293</v>
+        <v>0.7068733153638814</v>
       </c>
     </row>
     <row r="16">
@@ -8677,45 +8677,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Manganitu, Tamako</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike, Mega</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2142</v>
+        <v>2493</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>559</v>
+        <v>695</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1482</v>
+        <v>1749</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1482</v>
+        <v>1760</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.6918767507002801</v>
+        <v>0.7059767348576013</v>
       </c>
     </row>
     <row r="17">
@@ -8738,31 +8738,31 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1954</v>
+        <v>2014</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1979</v>
+        <v>2041</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.6749658935879945</v>
+        <v>0.6958745311967269</v>
       </c>
     </row>
     <row r="18">
@@ -8771,45 +8771,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2199</v>
+        <v>2149</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>710</v>
+        <v>547</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1453</v>
+        <v>1481</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
         <v>1481</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.6734879490677581</v>
+        <v>0.6891577477896697</v>
       </c>
     </row>
     <row r="19">
@@ -8832,31 +8832,31 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2892</v>
+        <v>2900</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>956</v>
+        <v>929</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1889</v>
+        <v>1926</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>8</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1931</v>
+        <v>1970</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.6677040110650069</v>
+        <v>0.6793103448275862</v>
       </c>
     </row>
     <row r="20">
@@ -8865,45 +8865,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Kezia Maralending</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1479</v>
+        <v>2199</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>263</v>
+        <v>707</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>222</v>
+        <v>6</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>957</v>
+        <v>1453</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>985</v>
+        <v>1475</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.6659905341446923</v>
+        <v>0.6707594361073216</v>
       </c>
     </row>
     <row r="21">
@@ -8926,31 +8926,31 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2728</v>
+        <v>2732</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>913</v>
+        <v>890</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1779</v>
+        <v>1812</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1780</v>
+        <v>1813</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.6524926686217009</v>
+        <v>0.6636163982430454</v>
       </c>
     </row>
     <row r="22">
@@ -8959,45 +8959,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2780</v>
+        <v>2379</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>975</v>
+        <v>739</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1731</v>
+        <v>1497</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1739</v>
+        <v>1525</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.6255395683453238</v>
+        <v>0.641025641025641</v>
       </c>
     </row>
     <row r="23">
@@ -9006,45 +9006,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2372</v>
+        <v>2784</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>765</v>
+        <v>957</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1439</v>
+        <v>1736</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1471</v>
+        <v>1744</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.6201517706576728</v>
+        <v>0.6264367816091954</v>
       </c>
     </row>
     <row r="24">
@@ -9053,45 +9053,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2632</v>
+        <v>2438</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1035</v>
+        <v>847</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1557</v>
+        <v>1393</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>1569</v>
+        <v>1479</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5961246200607903</v>
+        <v>0.6066447908121411</v>
       </c>
     </row>
     <row r="25">
@@ -9100,45 +9100,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2514</v>
+        <v>2638</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>817</v>
+        <v>1013</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>171</v>
+        <v>51</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1463</v>
+        <v>1557</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>1498</v>
+        <v>1570</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5958631662688942</v>
+        <v>0.5951478392721758</v>
       </c>
     </row>
     <row r="26">
@@ -9147,45 +9147,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2438</v>
+        <v>2525</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>849</v>
+        <v>789</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1362</v>
+        <v>1463</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1447</v>
+        <v>1490</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.5935192780968006</v>
+        <v>0.5900990099009901</v>
       </c>
     </row>
     <row r="27">
@@ -9194,45 +9194,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>B. Lenskar Diamanis</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2756</v>
+        <v>2104</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1106</v>
+        <v>823</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1572</v>
+        <v>1197</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>1580</v>
+        <v>1232</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.5732946298984035</v>
+        <v>0.5855513307984791</v>
       </c>
     </row>
     <row r="28">
@@ -9241,45 +9241,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>B. Lenskar Diamanis</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2104</v>
+        <v>2759</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>830</v>
+        <v>1098</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1144</v>
+        <v>1582</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1178</v>
+        <v>1589</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.5598859315589354</v>
+        <v>0.5759333091699891</v>
       </c>
     </row>
     <row r="29">
@@ -9302,31 +9302,31 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2175</v>
+        <v>2181</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="I29" s="9" t="n">
         <v>97</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.5374712643678161</v>
+        <v>0.5378266850068776</v>
       </c>
     </row>
   </sheetData>
@@ -9360,7 +9360,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 26 Juli 2026</t>
+          <t>Hari/Tanggal : 27 Juli 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9377,17 +9377,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 10.07 WITA</t>
+          <t>Pukul        : 08.08 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-41):</t>
+          <t>Target Hari Ini (H-42):</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>68.47%</t>
+          <t>70.14%</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.8798646362098139</v>
+        <v>0.887668918918919</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.8407486959189936</v>
+        <v>0.8545232273838631</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.8011488250652742</v>
+        <v>0.8095386858273457</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7930549038010324</v>
+        <v>0.7977194626679163</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.7699832975423526</v>
+        <v>0.773517504167659</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9510,15 +9510,15 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tenggara</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>0.6841603053435115</v>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>Tatoareng</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>0.7102425876010782</v>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9528,15 +9528,15 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>0.672075726842461</v>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>+1</t>
+        <v>0.6841603053435115</v>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9550,11 +9550,11 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>0.6696832579185519</v>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>+1</t>
+        <v>0.6795933734939759</v>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9568,11 +9568,11 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.6690871369294605</v>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>+1</t>
+        <v>0.6793103448275862</v>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9586,11 +9586,11 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.6637706342311034</v>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>-3</t>
+        <v>0.6681146828844483</v>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9622,11 +9622,11 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.6256821829855538</v>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>+2</t>
+        <v>0.6318910256410256</v>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9636,15 +9636,15 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.6251025430680885</v>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>-1</t>
+        <v>0.6298489425981874</v>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9654,11 +9654,11 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.6214908034849952</v>
+        <v>0.6271534044298606</v>
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.6123607315535001</v>
+        <v>0.6230092204526404</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.08 WITA</t>
+          <t>Pukul        : 08.18 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.08 WITA</t>
+          <t>Pukul        : 08.18 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.08 WITA</t>
+          <t>Pukul        : 08.18 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.08 WITA</t>
+          <t>Pukul        : 08.18 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 27 Juli 2026</t>
+          <t>Hari/Tanggal : 28 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -616,32 +616,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.18 WITA</t>
+          <t>Pukul        : 08.16 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-42):</t>
+          <t>Target Hari Ini (H-44):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>70.14%</t>
+          <t>73.48%</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Hijau &gt;= 70.14%</t>
+          <t>Hijau &gt;= 73.48%</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Kuning 35.07% - 70.14%</t>
+          <t>Kuning 36.74% - 73.48%</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Merah &lt; 35.07%</t>
+          <t>Merah &lt; 36.74%</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       <c r="P8" s="9" t="n">
         <v>1054</v>
       </c>
-      <c r="Q8" s="11">
+      <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
@@ -1844,7 +1844,7 @@
         <f>SUM(P7:P21)</f>
         <v/>
       </c>
-      <c r="Q22" s="11">
+      <c r="Q22" s="12">
         <f>P22/B22</f>
         <v/>
       </c>
@@ -1900,7 +1900,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 27 Juli 2026</t>
+          <t>Hari/Tanggal : 28 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1917,17 +1917,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.18 WITA</t>
+          <t>Pukul        : 08.16 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-42):</t>
+          <t>Target Hari Ini (H-44):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>70.14%</t>
+          <t>73.48%</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       <c r="L52" s="9" t="n">
         <v>343</v>
       </c>
-      <c r="M52" s="11" t="n">
+      <c r="M52" s="12" t="n">
         <v>0.7313432835820897</v>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       <c r="L53" s="9" t="n">
         <v>369</v>
       </c>
-      <c r="M53" s="11" t="n">
+      <c r="M53" s="12" t="n">
         <v>0.7306930693069308</v>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       <c r="L54" s="9" t="n">
         <v>320</v>
       </c>
-      <c r="M54" s="11" t="n">
+      <c r="M54" s="12" t="n">
         <v>0.7305936073059359</v>
       </c>
     </row>
@@ -4298,7 +4298,7 @@
       <c r="L55" s="9" t="n">
         <v>337</v>
       </c>
-      <c r="M55" s="11" t="n">
+      <c r="M55" s="12" t="n">
         <v>0.7278617710583153</v>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       <c r="L56" s="9" t="n">
         <v>293</v>
       </c>
-      <c r="M56" s="11" t="n">
+      <c r="M56" s="12" t="n">
         <v>0.7252475247524752</v>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       <c r="L57" s="9" t="n">
         <v>312</v>
       </c>
-      <c r="M57" s="11" t="n">
+      <c r="M57" s="12" t="n">
         <v>0.7188940092165899</v>
       </c>
     </row>
@@ -4439,7 +4439,7 @@
       <c r="L58" s="9" t="n">
         <v>329</v>
       </c>
-      <c r="M58" s="11" t="n">
+      <c r="M58" s="12" t="n">
         <v>0.7167755991285403</v>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       <c r="L59" s="9" t="n">
         <v>302</v>
       </c>
-      <c r="M59" s="11" t="n">
+      <c r="M59" s="12" t="n">
         <v>0.7156398104265402</v>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       <c r="L60" s="9" t="n">
         <v>312</v>
       </c>
-      <c r="M60" s="11" t="n">
+      <c r="M60" s="12" t="n">
         <v>0.7155963302752294</v>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       <c r="L61" s="9" t="n">
         <v>274</v>
       </c>
-      <c r="M61" s="11" t="n">
+      <c r="M61" s="12" t="n">
         <v>0.7154046997389034</v>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       <c r="L62" s="9" t="n">
         <v>310</v>
       </c>
-      <c r="M62" s="11" t="n">
+      <c r="M62" s="12" t="n">
         <v>0.7126436781609197</v>
       </c>
     </row>
@@ -4674,7 +4674,7 @@
       <c r="L63" s="9" t="n">
         <v>363</v>
       </c>
-      <c r="M63" s="11" t="n">
+      <c r="M63" s="12" t="n">
         <v>0.7103718199608611</v>
       </c>
     </row>
@@ -4721,7 +4721,7 @@
       <c r="L64" s="9" t="n">
         <v>378</v>
       </c>
-      <c r="M64" s="11" t="n">
+      <c r="M64" s="12" t="n">
         <v>0.7091932457786116</v>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       <c r="L65" s="9" t="n">
         <v>321</v>
       </c>
-      <c r="M65" s="11" t="n">
+      <c r="M65" s="12" t="n">
         <v>0.7070484581497797</v>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       <c r="L66" s="9" t="n">
         <v>357</v>
       </c>
-      <c r="M66" s="11" t="n">
+      <c r="M66" s="12" t="n">
         <v>0.7055335968379447</v>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       <c r="L67" s="9" t="n">
         <v>230</v>
       </c>
-      <c r="M67" s="11" t="n">
+      <c r="M67" s="12" t="n">
         <v>0.7055214723926381</v>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       <c r="L68" s="9" t="n">
         <v>347</v>
       </c>
-      <c r="M68" s="11" t="n">
+      <c r="M68" s="12" t="n">
         <v>0.7052845528455285</v>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       <c r="L69" s="9" t="n">
         <v>375</v>
       </c>
-      <c r="M69" s="11" t="n">
+      <c r="M69" s="12" t="n">
         <v>0.7048872180451127</v>
       </c>
     </row>
@@ -8149,7 +8149,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 27 Juli 2026</t>
+          <t>Hari/Tanggal : 28 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8166,17 +8166,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.18 WITA</t>
+          <t>Pukul        : 08.16 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-42):</t>
+          <t>Target Hari Ini (H-44):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>70.14%</t>
+          <t>73.48%</t>
         </is>
       </c>
     </row>
@@ -8620,7 +8620,7 @@
       <c r="L14" s="9" t="n">
         <v>2169</v>
       </c>
-      <c r="M14" s="11" t="n">
+      <c r="M14" s="12" t="n">
         <v>0.7298115746971736</v>
       </c>
     </row>
@@ -8667,7 +8667,7 @@
       <c r="L15" s="9" t="n">
         <v>1049</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" s="12" t="n">
         <v>0.7068733153638814</v>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       <c r="L16" s="9" t="n">
         <v>1760</v>
       </c>
-      <c r="M16" s="11" t="n">
+      <c r="M16" s="12" t="n">
         <v>0.7059767348576013</v>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 27 Juli 2026</t>
+          <t>Hari/Tanggal : 28 Juli 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9377,17 +9377,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.18 WITA</t>
+          <t>Pukul        : 08.16 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-42):</t>
+          <t>Target Hari Ini (H-44):</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>70.14%</t>
+          <t>73.48%</t>
         </is>
       </c>
     </row>
@@ -9513,7 +9513,7 @@
           <t>Tatoareng</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>0.7102425876010782</v>
       </c>
       <c r="D12" s="18" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 28 Juli 2026</t>
+          <t>Hari/Tanggal : 29 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.16 WITA</t>
+          <t>Pukul        : 07.45 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -750,62 +750,62 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4199</v>
+        <v>4246</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>927</v>
+        <v>682</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
         <v/>
       </c>
       <c r="F7" s="9" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G7" s="10">
         <f>F7/B7</f>
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>188</v>
+        <v>4</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K7" s="10">
         <f>J7/B7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>3052</v>
+        <v>3505</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
         <v/>
       </c>
       <c r="N7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O7" s="10">
         <f>N7/B7</f>
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>3248</v>
+        <v>3523</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -819,41 +819,41 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1484</v>
+        <v>1490</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
         <v/>
       </c>
       <c r="J8" s="9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K8" s="10">
         <f>J8/B8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1020</v>
+        <v>1066</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -867,14 +867,14 @@
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>1054</v>
-      </c>
-      <c r="Q8" s="12">
+        <v>1106</v>
+      </c>
+      <c r="Q8" s="11">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6402</v>
+        <v>6479</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1206</v>
+        <v>982</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
@@ -908,21 +908,21 @@
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>207</v>
+        <v>410</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4824</v>
+        <v>4927</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -936,14 +936,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>5107</v>
+        <v>5408</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>37</v>
+        <v>301</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3272</v>
+        <v>3304</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>476</v>
+        <v>401</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -977,42 +977,42 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="K10" s="10">
         <f>J10/B10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2685</v>
+        <v>2768</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
         <v/>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O10" s="10">
         <f>N10/B10</f>
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2796</v>
+        <v>2903</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1026,41 +1026,41 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>376</v>
+        <v>328</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
         <v/>
       </c>
       <c r="J11" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K11" s="10">
         <f>J11/B11</f>
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>750</v>
+        <v>801</v>
       </c>
       <c r="M11" s="10">
         <f>L11/B11</f>
@@ -1074,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>769</v>
+        <v>815</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>1048</v>
+        <v>1063</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>23</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="E12" s="10">
         <f>D12/B12</f>
@@ -1115,42 +1115,42 @@
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
         <v/>
       </c>
       <c r="J12" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K12" s="10">
         <f>J12/B12</f>
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>703</v>
+        <v>752</v>
       </c>
       <c r="M12" s="10">
         <f>L12/B12</f>
         <v/>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="10">
         <f>N12/B12</f>
         <v/>
       </c>
       <c r="P12" s="9" t="n">
-        <v>717</v>
+        <v>762</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/B12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1164,62 +1164,62 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4772</v>
+        <v>4801</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1767</v>
+        <v>1662</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>221</v>
+        <v>287</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2718</v>
+        <v>2794</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
         <v/>
       </c>
       <c r="N13" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O13" s="10">
         <f>N13/B13</f>
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2973</v>
+        <v>3112</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1233,62 +1233,62 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6240</v>
+        <v>6322</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2276</v>
+        <v>2041</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>210</v>
+        <v>286</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3590</v>
+        <v>3776</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
         <v/>
       </c>
       <c r="N14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="10">
         <f>N14/B14</f>
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3943</v>
+        <v>4245</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>45</v>
+        <v>302</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1302,41 +1302,41 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8275</v>
+        <v>8415</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2945</v>
+        <v>2678</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K15" s="10">
         <f>J15/B15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>5130</v>
+        <v>5525</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1350,14 +1350,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>5212</v>
+        <v>5591</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>76</v>
+        <v>379</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1371,62 +1371,62 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5312</v>
+        <v>5353</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1590</v>
+        <v>1440</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>3511</v>
+        <v>3658</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
         <v/>
       </c>
       <c r="N16" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O16" s="10">
         <f>N16/B16</f>
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3610</v>
+        <v>3774</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1440,62 +1440,62 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2438</v>
+        <v>2443</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>847</v>
+        <v>766</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1393</v>
+        <v>1513</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
         <v/>
       </c>
       <c r="N17" s="9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O17" s="10">
         <f>N17/B17</f>
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1529</v>
+        <v>1594</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1509,41 +1509,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9603</v>
+        <v>9699</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1761</v>
+        <v>1472</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>7699</v>
+        <v>8065</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1557,14 +1557,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>7774</v>
+        <v>8153</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>103</v>
+        <v>379</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
@@ -1612,7 +1612,7 @@
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1048</v>
+        <v>1065</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1626,14 +1626,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>1051</v>
+        <v>1083</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1647,20 +1647,20 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>8</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E20" s="10">
         <f>D20/B20</f>
         <v/>
       </c>
       <c r="F20" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G20" s="10">
         <f>F20/B20</f>
@@ -1674,14 +1674,14 @@
         <v/>
       </c>
       <c r="J20" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" s="10">
         <f>J20/B20</f>
         <v/>
       </c>
       <c r="L20" s="9" t="n">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="M20" s="10">
         <f>L20/B20</f>
@@ -1695,14 +1695,14 @@
         <v/>
       </c>
       <c r="P20" s="9" t="n">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="Q20" s="12">
         <f>P20/B20</f>
         <v/>
       </c>
       <c r="R20" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S20" s="10">
         <f>R20/B20</f>
@@ -1716,13 +1716,13 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2900</v>
+        <v>2915</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>929</v>
+        <v>851</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
@@ -1736,21 +1736,21 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1926</v>
+        <v>2017</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1764,14 +1764,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1970</v>
+        <v>2063</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1844,7 +1844,7 @@
         <f>SUM(P7:P21)</f>
         <v/>
       </c>
-      <c r="Q22" s="12">
+      <c r="Q22" s="11">
         <f>P22/B22</f>
         <v/>
       </c>
@@ -1900,7 +1900,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 28 Juli 2026</t>
+          <t>Hari/Tanggal : 29 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.16 WITA</t>
+          <t>Pukul        : 07.45 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2160,16 +2160,16 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>0</v>
@@ -2181,10 +2181,10 @@
         <v>6</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.9953051643192488</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2193,45 +2193,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Syamsia Makaminan</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>575</v>
+        <v>372</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>369</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>372</v>
+      </c>
+      <c r="M11" s="11" t="n">
         <v>1</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>569</v>
-      </c>
-      <c r="K11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="9" t="n">
-        <v>570</v>
-      </c>
-      <c r="M11" s="11" t="n">
-        <v>0.991304347826087</v>
       </c>
     </row>
     <row r="12">
@@ -2240,45 +2240,45 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Fitria Rianti Gorosita</t>
+          <t>Syamsia Makaminan</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>389</v>
+        <v>581</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>367</v>
+        <v>568</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>370</v>
+        <v>578</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.9511568123393316</v>
+        <v>0.9948364888123923</v>
       </c>
     </row>
     <row r="13">
@@ -2287,45 +2287,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Merry Christiani Lano</t>
+          <t>Fitria Rianti Gorosita</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>534</v>
+        <v>392</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>480</v>
+        <v>370</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>498</v>
+        <v>379</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.9325842696629213</v>
+        <v>0.9668367346938775</v>
       </c>
     </row>
     <row r="14">
@@ -2348,31 +2348,31 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.923076923076923</v>
+        <v>0.9534161490683229</v>
       </c>
     </row>
     <row r="15">
@@ -2395,31 +2395,31 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.9199029126213593</v>
+        <v>0.9493975903614458</v>
       </c>
     </row>
     <row r="16">
@@ -2428,45 +2428,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Clara Patricia Pangandaheng</t>
+          <t>Merry Christiani Lano</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>391</v>
+        <v>536</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>302</v>
+        <v>481</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>356</v>
+        <v>501</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.9104859335038362</v>
+        <v>0.9347014925373134</v>
       </c>
     </row>
     <row r="17">
@@ -2475,45 +2475,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Clara Patricia Pangandaheng</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
+        <v>396</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>302</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="9" t="n">
         <v>366</v>
       </c>
-      <c r="F17" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>329</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="9" t="n">
-        <v>332</v>
-      </c>
       <c r="M17" s="11" t="n">
-        <v>0.907103825136612</v>
+        <v>0.9242424242424242</v>
       </c>
     </row>
     <row r="18">
@@ -2522,45 +2522,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>515</v>
+        <v>400</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>363</v>
+      </c>
+      <c r="K18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="9" t="n">
-        <v>457</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" s="9" t="n">
-        <v>460</v>
+        <v>368</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8932038834951457</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="19">
@@ -2583,31 +2583,31 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.8875598086124402</v>
+        <v>0.9192399049881235</v>
       </c>
     </row>
     <row r="20">
@@ -2616,45 +2616,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>398</v>
+        <v>517</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>341</v>
+        <v>469</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>351</v>
+        <v>472</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.8819095477386935</v>
+        <v>0.9129593810444874</v>
       </c>
     </row>
     <row r="21">
@@ -2663,45 +2663,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>412</v>
+        <v>486</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>346</v>
+        <v>439</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>360</v>
+        <v>440</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.8737864077669903</v>
+        <v>0.9053497942386831</v>
       </c>
     </row>
     <row r="22">
@@ -2710,45 +2710,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.8641686182669788</v>
+        <v>0.8995215311004785</v>
       </c>
     </row>
     <row r="23">
@@ -2757,30 +2757,30 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>482</v>
+        <v>423</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>0</v>
@@ -2789,13 +2789,13 @@
         <v>380</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.8526970954356847</v>
+        <v>0.8983451536643026</v>
       </c>
     </row>
     <row r="24">
@@ -2804,45 +2804,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>431</v>
+        <v>398</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.851508120649652</v>
+        <v>0.8944723618090452</v>
       </c>
     </row>
     <row r="25">
@@ -2851,45 +2851,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.8513189448441247</v>
+        <v>0.8906976744186046</v>
       </c>
     </row>
     <row r="26">
@@ -2898,45 +2898,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>318</v>
+        <v>352</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>345</v>
+        <v>382</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.8455882352941176</v>
+        <v>0.8904428904428905</v>
       </c>
     </row>
     <row r="27">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Asari Prisilia Antari</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -2959,31 +2959,31 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>515</v>
+        <v>426</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>429</v>
+        <v>316</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>434</v>
+        <v>377</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.8427184466019417</v>
+        <v>0.8849765258215964</v>
       </c>
     </row>
     <row r="28">
@@ -2992,45 +2992,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Asari Prisilia Antari</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>0.8380281690140845</v>
+        <v>0.8823529411764706</v>
       </c>
     </row>
     <row r="29">
@@ -3039,45 +3039,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>393</v>
+        <v>444</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>306</v>
+        <v>370</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.8371501272264631</v>
+        <v>0.8626126126126126</v>
       </c>
     </row>
     <row r="30">
@@ -3086,45 +3086,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>434</v>
+        <v>566</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>362</v>
+        <v>482</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>362</v>
+        <v>488</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.8341013824884793</v>
+        <v>0.8621908127208481</v>
       </c>
     </row>
     <row r="31">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -3147,31 +3147,31 @@
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>426</v>
+        <v>518</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>352</v>
+        <v>429</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>352</v>
+        <v>444</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.8262910798122065</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="32">
@@ -3180,45 +3180,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>558</v>
+        <v>435</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>456</v>
+        <v>362</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>456</v>
+        <v>370</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.8172043010752688</v>
+        <v>0.850574712643678</v>
       </c>
     </row>
     <row r="33">
@@ -3227,45 +3227,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.8104089219330856</v>
+        <v>0.8500948766603416</v>
       </c>
     </row>
     <row r="34">
@@ -3274,45 +3274,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>517</v>
+        <v>539</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>417</v>
+        <v>455</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.8065764023210832</v>
+        <v>0.8441558441558441</v>
       </c>
     </row>
     <row r="35">
@@ -3335,31 +3335,31 @@
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.8062622309197651</v>
+        <v>0.8423076923076923</v>
       </c>
     </row>
     <row r="36">
@@ -3368,45 +3368,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Sheryl Jessica Tatontos</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>511</v>
+        <v>570</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>336</v>
+        <v>476</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>408</v>
+        <v>477</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7984344422700587</v>
+        <v>0.8368421052631579</v>
       </c>
     </row>
     <row r="37">
@@ -3415,21 +3415,21 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Sheryl Jessica Tatontos</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>431</v>
+        <v>529</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>87</v>
@@ -3438,22 +3438,22 @@
         <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>344</v>
+        <v>442</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7981438515081206</v>
+        <v>0.8355387523629489</v>
       </c>
     </row>
     <row r="38">
@@ -3462,45 +3462,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>342</v>
+        <v>393</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.789838337182448</v>
+        <v>0.8326271186440678</v>
       </c>
     </row>
     <row r="39">
@@ -3509,45 +3509,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>566</v>
+        <v>352</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>424</v>
+        <v>291</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>446</v>
+        <v>292</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7879858657243817</v>
+        <v>0.8295454545454546</v>
       </c>
     </row>
     <row r="40">
@@ -3556,45 +3556,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>339</v>
+        <v>398</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>366</v>
+        <v>399</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.7837259100642399</v>
+        <v>0.822680412371134</v>
       </c>
     </row>
     <row r="41">
@@ -3603,45 +3603,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>537</v>
+        <v>357</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>401</v>
+        <v>292</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>417</v>
+        <v>292</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.776536312849162</v>
+        <v>0.8179271708683473</v>
       </c>
     </row>
     <row r="42">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -3664,31 +3664,31 @@
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>472</v>
+        <v>542</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>365</v>
+        <v>432</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>366</v>
+        <v>441</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.7754237288135593</v>
+        <v>0.8136531365313653</v>
       </c>
     </row>
     <row r="43">
@@ -3697,45 +3697,45 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>519</v>
+        <v>431</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>401</v>
+        <v>346</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>402</v>
+        <v>350</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.8120649651972158</v>
       </c>
     </row>
     <row r="44">
@@ -3758,31 +3758,31 @@
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.7718832891246684</v>
+        <v>0.8100263852242745</v>
       </c>
     </row>
     <row r="45">
@@ -3791,45 +3791,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>350</v>
+        <v>535</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>262</v>
+        <v>390</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>269</v>
+        <v>430</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.7685714285714286</v>
+        <v>0.8037383177570093</v>
       </c>
     </row>
     <row r="46">
@@ -3838,45 +3838,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>478</v>
+        <v>434</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J46" s="9" t="n">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.7656903765690377</v>
+        <v>0.7995391705069125</v>
       </c>
     </row>
     <row r="47">
@@ -3885,45 +3885,45 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.7596153846153846</v>
+        <v>0.7958333333333333</v>
       </c>
     </row>
     <row r="48">
@@ -3932,45 +3932,45 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>395</v>
+        <v>525</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I48" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>289</v>
+        <v>413</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>295</v>
+        <v>415</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.7468354430379747</v>
+        <v>0.7904761904761906</v>
       </c>
     </row>
     <row r="49">
@@ -3979,45 +3979,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>257</v>
+        <v>315</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>263</v>
+        <v>316</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.7429378531073446</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="50">
@@ -4026,45 +4026,45 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>432</v>
+        <v>473</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>313</v>
+        <v>368</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.7384259259259259</v>
+        <v>0.788583509513742</v>
       </c>
     </row>
     <row r="51">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -4087,31 +4087,31 @@
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>483</v>
+        <v>427</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.7370600414078674</v>
+        <v>0.7845433255269321</v>
       </c>
     </row>
     <row r="52">
@@ -4120,36 +4120,36 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0</v>
@@ -4157,8 +4157,8 @@
       <c r="L52" s="9" t="n">
         <v>343</v>
       </c>
-      <c r="M52" s="12" t="n">
-        <v>0.7313432835820897</v>
+      <c r="M52" s="11" t="n">
+        <v>0.7813211845102505</v>
       </c>
     </row>
     <row r="53">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -4181,31 +4181,31 @@
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>505</v>
+        <v>466</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>369</v>
-      </c>
-      <c r="M53" s="12" t="n">
-        <v>0.7306930693069308</v>
+        <v>362</v>
+      </c>
+      <c r="M53" s="11" t="n">
+        <v>0.776824034334764</v>
       </c>
     </row>
     <row r="54">
@@ -4214,45 +4214,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>438</v>
+        <v>509</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>314</v>
+        <v>356</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>320</v>
-      </c>
-      <c r="M54" s="12" t="n">
-        <v>0.7305936073059359</v>
+        <v>395</v>
+      </c>
+      <c r="M54" s="11" t="n">
+        <v>0.7760314341846758</v>
       </c>
     </row>
     <row r="55">
@@ -4261,45 +4261,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>463</v>
+        <v>434</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>337</v>
-      </c>
-      <c r="M55" s="12" t="n">
-        <v>0.7278617710583153</v>
+        <v>335</v>
+      </c>
+      <c r="M55" s="11" t="n">
+        <v>0.771889400921659</v>
       </c>
     </row>
     <row r="56">
@@ -4308,45 +4308,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>404</v>
+        <v>486</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>247</v>
+        <v>368</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>293</v>
-      </c>
-      <c r="M56" s="12" t="n">
-        <v>0.7252475247524752</v>
+        <v>373</v>
+      </c>
+      <c r="M56" s="11" t="n">
+        <v>0.7674897119341564</v>
       </c>
     </row>
     <row r="57">
@@ -4355,45 +4355,45 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>434</v>
+        <v>475</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>310</v>
+        <v>364</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>312</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>0.7188940092165899</v>
+        <v>364</v>
+      </c>
+      <c r="M57" s="11" t="n">
+        <v>0.7663157894736841</v>
       </c>
     </row>
     <row r="58">
@@ -4402,45 +4402,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="H58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>329</v>
-      </c>
-      <c r="M58" s="12" t="n">
-        <v>0.7167755991285403</v>
+        <v>359</v>
+      </c>
+      <c r="M58" s="11" t="n">
+        <v>0.7638297872340426</v>
       </c>
     </row>
     <row r="59">
@@ -4449,45 +4449,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>335</v>
+      </c>
+      <c r="K59" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I59" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="9" t="n">
-        <v>300</v>
-      </c>
-      <c r="K59" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L59" s="9" t="n">
-        <v>302</v>
-      </c>
-      <c r="M59" s="12" t="n">
-        <v>0.7156398104265402</v>
+        <v>336</v>
+      </c>
+      <c r="M59" s="11" t="n">
+        <v>0.7619047619047619</v>
       </c>
     </row>
     <row r="60">
@@ -4496,45 +4496,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="G60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>312</v>
-      </c>
-      <c r="M60" s="12" t="n">
-        <v>0.7155963302752294</v>
+        <v>358</v>
+      </c>
+      <c r="M60" s="11" t="n">
+        <v>0.7600849256900213</v>
       </c>
     </row>
     <row r="61">
@@ -4543,45 +4543,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>383</v>
+        <v>437</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>271</v>
+        <v>331</v>
       </c>
       <c r="K61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>274</v>
-      </c>
-      <c r="M61" s="12" t="n">
-        <v>0.7154046997389034</v>
+        <v>331</v>
+      </c>
+      <c r="M61" s="11" t="n">
+        <v>0.7574370709382151</v>
       </c>
     </row>
     <row r="62">
@@ -4590,45 +4590,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>310</v>
-      </c>
-      <c r="M62" s="12" t="n">
-        <v>0.7126436781609197</v>
+        <v>334</v>
+      </c>
+      <c r="M62" s="11" t="n">
+        <v>0.750561797752809</v>
       </c>
     </row>
     <row r="63">
@@ -4637,45 +4637,45 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>511</v>
+        <v>457</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>363</v>
-      </c>
-      <c r="M63" s="12" t="n">
-        <v>0.7103718199608611</v>
+        <v>343</v>
+      </c>
+      <c r="M63" s="11" t="n">
+        <v>0.7505470459518599</v>
       </c>
     </row>
     <row r="64">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
@@ -4698,31 +4698,31 @@
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>533</v>
+        <v>443</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>378</v>
-      </c>
-      <c r="M64" s="12" t="n">
-        <v>0.7091932457786116</v>
+        <v>330</v>
+      </c>
+      <c r="M64" s="11" t="n">
+        <v>0.7449209932279911</v>
       </c>
     </row>
     <row r="65">
@@ -4731,45 +4731,45 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>454</v>
+        <v>537</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>293</v>
+        <v>396</v>
       </c>
       <c r="K65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>321</v>
-      </c>
-      <c r="M65" s="12" t="n">
-        <v>0.7070484581497797</v>
+        <v>400</v>
+      </c>
+      <c r="M65" s="11" t="n">
+        <v>0.74487895716946</v>
       </c>
     </row>
     <row r="66">
@@ -4778,45 +4778,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="K66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>357</v>
-      </c>
-      <c r="M66" s="12" t="n">
-        <v>0.7055335968379447</v>
+        <v>360</v>
+      </c>
+      <c r="M66" s="11" t="n">
+        <v>0.7438016528925619</v>
       </c>
     </row>
     <row r="67">
@@ -4825,45 +4825,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>326</v>
+        <v>404</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>230</v>
-      </c>
-      <c r="M67" s="12" t="n">
-        <v>0.7055214723926381</v>
+        <v>300</v>
+      </c>
+      <c r="M67" s="11" t="n">
+        <v>0.7425742574257426</v>
       </c>
     </row>
     <row r="68">
@@ -4872,45 +4872,45 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>492</v>
+        <v>565</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>347</v>
-      </c>
-      <c r="M68" s="12" t="n">
-        <v>0.7052845528455285</v>
+        <v>419</v>
+      </c>
+      <c r="M68" s="11" t="n">
+        <v>0.7415929203539823</v>
       </c>
     </row>
     <row r="69">
@@ -4919,45 +4919,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>532</v>
+        <v>503</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="9" t="n">
+        <v>371</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L69" s="9" t="n">
         <v>373</v>
       </c>
-      <c r="K69" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="9" t="n">
-        <v>375</v>
-      </c>
-      <c r="M69" s="12" t="n">
-        <v>0.7048872180451127</v>
+      <c r="M69" s="11" t="n">
+        <v>0.7415506958250497</v>
       </c>
     </row>
     <row r="70">
@@ -4966,24 +4966,24 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>483</v>
+        <v>532</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>0</v>
@@ -4992,19 +4992,19 @@
         <v>0</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>338</v>
+        <v>391</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>338</v>
-      </c>
-      <c r="M70" s="12" t="n">
-        <v>0.6997929606625258</v>
+        <v>393</v>
+      </c>
+      <c r="M70" s="11" t="n">
+        <v>0.7387218045112782</v>
       </c>
     </row>
     <row r="71">
@@ -5013,45 +5013,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>556</v>
+        <v>593</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>355</v>
+        <v>435</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>389</v>
-      </c>
-      <c r="M71" s="12" t="n">
-        <v>0.699640287769784</v>
+        <v>438</v>
+      </c>
+      <c r="M71" s="11" t="n">
+        <v>0.7386172006745363</v>
       </c>
     </row>
     <row r="72">
@@ -5060,45 +5060,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>515</v>
+        <v>416</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>351</v>
+        <v>305</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>360</v>
-      </c>
-      <c r="M72" s="12" t="n">
-        <v>0.6990291262135923</v>
+        <v>307</v>
+      </c>
+      <c r="M72" s="11" t="n">
+        <v>0.7379807692307694</v>
       </c>
     </row>
     <row r="73">
@@ -5107,45 +5107,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I73" s="9" t="n">
-        <v>11</v>
-      </c>
       <c r="J73" s="9" t="n">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>0.6984126984126984</v>
+        <v>0.733201581027668</v>
       </c>
     </row>
     <row r="74">
@@ -5154,45 +5154,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>469</v>
+        <v>519</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>325</v>
+        <v>367</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>326</v>
+        <v>379</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>0.6950959488272921</v>
+        <v>0.7302504816955684</v>
       </c>
     </row>
     <row r="75">
@@ -5201,45 +5201,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>434</v>
+        <v>326</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>297</v>
+        <v>237</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>0.6935483870967742</v>
+        <v>0.7300613496932516</v>
       </c>
     </row>
     <row r="76">
@@ -5248,45 +5248,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>473</v>
+        <v>385</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>328</v>
+        <v>281</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>0.693446088794926</v>
+        <v>0.7298701298701299</v>
       </c>
     </row>
     <row r="77">
@@ -5295,45 +5295,45 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>417</v>
+        <v>514</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>275</v>
+        <v>365</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>289</v>
+        <v>371</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0.6930455635491607</v>
+        <v>0.7217898832684824</v>
       </c>
     </row>
     <row r="78">
@@ -5342,45 +5342,45 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>485</v>
+        <v>393</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>334</v>
+        <v>269</v>
       </c>
       <c r="K78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0.6927835051546392</v>
+        <v>0.7201017811704835</v>
       </c>
     </row>
     <row r="79">
@@ -5389,45 +5389,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>477</v>
+        <v>537</v>
       </c>
       <c r="F79" s="9" t="n">
         <v>148</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>328</v>
+        <v>380</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>329</v>
+        <v>384</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.689727463312369</v>
+        <v>0.7150837988826815</v>
       </c>
     </row>
     <row r="80">
@@ -5436,45 +5436,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>582</v>
+        <v>504</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>401</v>
+        <v>351</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>401</v>
+        <v>360</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.6890034364261168</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="81">
@@ -5483,45 +5483,45 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.6880733944954129</v>
+        <v>0.7133182844243793</v>
       </c>
     </row>
     <row r="82">
@@ -5530,45 +5530,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>410</v>
+        <v>482</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>280</v>
+        <v>342</v>
       </c>
       <c r="K82" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>282</v>
+        <v>343</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.6878048780487805</v>
+        <v>0.7116182572614107</v>
       </c>
     </row>
     <row r="83">
@@ -5577,45 +5577,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>299</v>
+        <v>328</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.6807095343680709</v>
+        <v>0.7063829787234043</v>
       </c>
     </row>
     <row r="84">
@@ -5624,45 +5624,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>526</v>
+        <v>456</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>357</v>
+        <v>311</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>357</v>
+        <v>322</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.6787072243346007</v>
+        <v>0.7061403508771931</v>
       </c>
     </row>
     <row r="85">
@@ -5671,45 +5671,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>606</v>
+        <v>550</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H85" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I85" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>364</v>
+      </c>
+      <c r="K85" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="9" t="n">
-        <v>408</v>
-      </c>
-      <c r="K85" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L85" s="9" t="n">
-        <v>409</v>
+        <v>387</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.6749174917491749</v>
+        <v>0.7036363636363636</v>
       </c>
     </row>
     <row r="86">
@@ -5718,45 +5718,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>415</v>
+        <v>211</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>277</v>
+        <v>144</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>280</v>
+        <v>148</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.6746987951807228</v>
+        <v>0.7014218009478674</v>
       </c>
     </row>
     <row r="87">
@@ -5765,45 +5765,45 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>289</v>
+        <v>419</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>191</v>
+        <v>271</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>194</v>
+        <v>292</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.671280276816609</v>
+        <v>0.6968973747016708</v>
       </c>
     </row>
     <row r="88">
@@ -5812,45 +5812,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="K88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.670076726342711</v>
+        <v>0.6959619952494062</v>
       </c>
     </row>
     <row r="89">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
@@ -5873,31 +5873,31 @@
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>298</v>
+        <v>331</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.6673960612691466</v>
+        <v>0.69375</v>
       </c>
     </row>
     <row r="90">
@@ -5906,45 +5906,45 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>414</v>
+        <v>487</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I90" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>245</v>
+        <v>335</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>273</v>
+        <v>337</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.6594202898550725</v>
+        <v>0.6919917864476386</v>
       </c>
     </row>
     <row r="91">
@@ -5953,45 +5953,45 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>460</v>
+        <v>354</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>300</v>
+        <v>229</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>302</v>
+        <v>242</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.6565217391304347</v>
+        <v>0.6836158192090396</v>
       </c>
     </row>
     <row r="92">
@@ -6000,45 +6000,45 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>540</v>
+        <v>461</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>185</v>
+        <v>115</v>
       </c>
       <c r="G92" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="H92" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I92" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="J92" s="9" t="n">
-        <v>349</v>
+        <v>305</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>354</v>
+        <v>315</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.6555555555555556</v>
+        <v>0.6832971800433839</v>
       </c>
     </row>
     <row r="93">
@@ -6047,45 +6047,45 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>547</v>
+        <v>468</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.6544789762340036</v>
+        <v>0.6794871794871795</v>
       </c>
     </row>
     <row r="94">
@@ -6094,45 +6094,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>463</v>
+        <v>543</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>302</v>
+        <v>362</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.6544276457883369</v>
+        <v>0.6758747697974218</v>
       </c>
     </row>
     <row r="95">
@@ -6141,45 +6141,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.6540284360189574</v>
+        <v>0.6746987951807228</v>
       </c>
     </row>
     <row r="96">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
@@ -6202,31 +6202,31 @@
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>477</v>
+        <v>635</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>293</v>
+        <v>419</v>
       </c>
       <c r="K96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>311</v>
+        <v>428</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.6519916142557652</v>
+        <v>0.6740157480314961</v>
       </c>
     </row>
     <row r="97">
@@ -6235,45 +6235,45 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>489</v>
+        <v>289</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>151</v>
+        <v>95</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="I97" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>191</v>
+      </c>
+      <c r="K97" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J97" s="9" t="n">
-        <v>258</v>
-      </c>
-      <c r="K97" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L97" s="9" t="n">
-        <v>317</v>
+        <v>194</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.6482617586912065</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="98">
@@ -6282,45 +6282,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>473</v>
+        <v>502</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="G98" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="H98" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="I98" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="H98" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I98" s="9" t="n">
-        <v>7</v>
-      </c>
       <c r="J98" s="9" t="n">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>304</v>
+        <v>336</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.6427061310782239</v>
+        <v>0.6693227091633466</v>
       </c>
     </row>
     <row r="99">
@@ -6329,45 +6329,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>354</v>
+        <v>493</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="K99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>227</v>
+        <v>327</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.6412429378531074</v>
+        <v>0.6632860040567951</v>
       </c>
     </row>
     <row r="100">
@@ -6376,45 +6376,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>501</v>
+        <v>475</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="G100" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>311</v>
+      </c>
+      <c r="K100" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I100" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J100" s="9" t="n">
-        <v>316</v>
-      </c>
-      <c r="K100" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L100" s="9" t="n">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.6407185628742514</v>
+        <v>0.6631578947368421</v>
       </c>
     </row>
     <row r="101">
@@ -6423,45 +6423,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>625</v>
+        <v>418</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>219</v>
+        <v>141</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>395</v>
+        <v>226</v>
       </c>
       <c r="K101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>399</v>
+        <v>277</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.6384</v>
+        <v>0.6626794258373205</v>
       </c>
     </row>
     <row r="102">
@@ -6470,45 +6470,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F102" s="9" t="n">
         <v>168</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="K102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.6345381526104418</v>
+        <v>0.6613545816733066</v>
       </c>
     </row>
     <row r="103">
@@ -6517,45 +6517,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>363</v>
+        <v>464</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>216</v>
+        <v>299</v>
       </c>
       <c r="K103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>230</v>
+        <v>306</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.6336088154269972</v>
+        <v>0.6594827586206897</v>
       </c>
     </row>
     <row r="104">
@@ -6564,45 +6564,45 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>457</v>
+        <v>422</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.6323851203501094</v>
+        <v>0.6587677725118484</v>
       </c>
     </row>
     <row r="105">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
@@ -6625,31 +6625,31 @@
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>458</v>
+        <v>422</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="G105" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H105" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H105" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="I105" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.62882096069869</v>
+        <v>0.6540284360189574</v>
       </c>
     </row>
     <row r="106">
@@ -6658,45 +6658,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="K106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.6267029972752044</v>
+        <v>0.6538461538461539</v>
       </c>
     </row>
     <row r="107">
@@ -6705,45 +6705,45 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.6240963855421687</v>
+        <v>0.6533957845433256</v>
       </c>
     </row>
     <row r="108">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Regina Kesya Dumumpe</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
@@ -6766,31 +6766,31 @@
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>443</v>
+        <v>416</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="K108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.6094808126410836</v>
+        <v>0.6514423076923077</v>
       </c>
     </row>
     <row r="109">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Regina Kesya Dumumpe</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
@@ -6813,31 +6813,31 @@
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="K109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.6075156576200418</v>
+        <v>0.6477024070021882</v>
       </c>
     </row>
     <row r="110">
@@ -6846,45 +6846,45 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>432</v>
+        <v>626</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>245</v>
+        <v>401</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>261</v>
+        <v>404</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.645367412140575</v>
       </c>
     </row>
     <row r="111">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
@@ -6907,31 +6907,31 @@
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>484</v>
+        <v>458</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.6033057851239669</v>
+        <v>0.6419213973799127</v>
       </c>
     </row>
     <row r="112">
@@ -6940,45 +6940,45 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>414</v>
+        <v>373</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="G112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="K112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.6014492753623188</v>
+        <v>0.6407506702412868</v>
       </c>
     </row>
     <row r="113">
@@ -6987,45 +6987,45 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>419</v>
+        <v>487</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>252</v>
+        <v>311</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.6014319809069213</v>
+        <v>0.6386036960985626</v>
       </c>
     </row>
     <row r="114">
@@ -7034,45 +7034,45 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>247</v>
+        <v>289</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.6014150943396226</v>
+        <v>0.6384297520661157</v>
       </c>
     </row>
     <row r="115">
@@ -7098,7 +7098,7 @@
         <v>400</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="G115" s="9" t="n">
         <v>0</v>
@@ -7110,16 +7110,16 @@
         <v>0</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.6</v>
+        <v>0.6375</v>
       </c>
     </row>
     <row r="116">
@@ -7142,31 +7142,31 @@
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="G116" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="K116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.5949656750572082</v>
+        <v>0.6343115124153499</v>
       </c>
     </row>
     <row r="117">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
@@ -7189,31 +7189,31 @@
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="G117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="I117" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H117" s="9" t="n">
-        <v>49</v>
-      </c>
-      <c r="I117" s="9" t="n">
-        <v>34</v>
-      </c>
       <c r="J117" s="9" t="n">
-        <v>180</v>
+        <v>253</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.5896860986547086</v>
+        <v>0.632420091324201</v>
       </c>
     </row>
     <row r="118">
@@ -7222,45 +7222,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="G118" s="9" t="n">
         <v>11</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.589041095890411</v>
+        <v>0.6312056737588653</v>
       </c>
     </row>
     <row r="119">
@@ -7269,45 +7269,45 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>472</v>
+        <v>450</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.5847457627118644</v>
+        <v>0.6311111111111111</v>
       </c>
     </row>
     <row r="120">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
@@ -7330,31 +7330,31 @@
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>232</v>
+        <v>170</v>
       </c>
       <c r="K120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.5807228915662651</v>
+        <v>0.6230248306997742</v>
       </c>
     </row>
     <row r="121">
@@ -7363,45 +7363,45 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Dince Lahaube</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>340</v>
+        <v>433</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>4</v>
+        <v>165</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="H121" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>195</v>
+        <v>261</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>197</v>
+        <v>268</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0.5794117647058824</v>
+        <v>0.6189376443418014</v>
       </c>
     </row>
     <row r="122">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
@@ -7424,31 +7424,31 @@
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="G122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.5689277899343544</v>
+        <v>0.6181434599156118</v>
       </c>
     </row>
     <row r="123">
@@ -7457,45 +7457,45 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>184</v>
+        <v>238</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>241</v>
+        <v>279</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.5683962264150944</v>
+        <v>0.6172566371681416</v>
       </c>
     </row>
     <row r="124">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Ivan Christian Sasenga</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
@@ -7518,31 +7518,31 @@
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>404</v>
+        <v>506</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="G124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>224</v>
+        <v>311</v>
       </c>
       <c r="K124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>229</v>
+        <v>311</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.5668316831683168</v>
+        <v>0.6146245059288538</v>
       </c>
     </row>
     <row r="125">
@@ -7565,31 +7565,31 @@
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I125" s="9" t="n">
         <v>20</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.5615384615384615</v>
+        <v>0.6053639846743295</v>
       </c>
     </row>
     <row r="126">
@@ -7598,45 +7598,45 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>451</v>
+        <v>400</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="G126" s="9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="127">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -7659,31 +7659,31 @@
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="G127" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H127" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H127" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="I127" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.5603644646924829</v>
+        <v>0.6017699115044248</v>
       </c>
     </row>
     <row r="128">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Ivan Christian Sasenga</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
@@ -7706,31 +7706,31 @@
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>504</v>
+        <v>477</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I128" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J128" s="9" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="K128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.5595238095238095</v>
+        <v>0.6016771488469602</v>
       </c>
     </row>
     <row r="129">
@@ -7739,45 +7739,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="G129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="I129" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J129" s="9" t="n">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.5584112149532711</v>
+        <v>0.5975903614457831</v>
       </c>
     </row>
     <row r="130">
@@ -7786,45 +7786,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Dince Lahaube</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>428</v>
+        <v>340</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>179</v>
+        <v>3</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.5560747663551402</v>
+        <v>0.5911764705882353</v>
       </c>
     </row>
     <row r="131">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
@@ -7847,31 +7847,31 @@
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I131" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.5528089887640449</v>
+        <v>0.5891647855530474</v>
       </c>
     </row>
     <row r="132">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
@@ -7894,31 +7894,31 @@
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>431</v>
+        <v>399</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="G132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="K132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.5522041763341067</v>
+        <v>0.5839598997493735</v>
       </c>
     </row>
     <row r="133">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G133" s="9" t="n">
         <v>0</v>
@@ -7953,19 +7953,19 @@
         <v>0</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.5470085470085471</v>
+        <v>0.5830985915492958</v>
       </c>
     </row>
     <row r="134">
@@ -7974,24 +7974,24 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>397</v>
+        <v>461</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="G134" s="9" t="n">
         <v>0</v>
@@ -8000,19 +8000,19 @@
         <v>0</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>213</v>
+        <v>264</v>
       </c>
       <c r="K134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>213</v>
+        <v>266</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.5365239294710328</v>
+        <v>0.5770065075921909</v>
       </c>
     </row>
     <row r="135">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
@@ -8035,31 +8035,31 @@
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="F135" s="9" t="n">
+        <v>180</v>
+      </c>
+      <c r="G135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="I135" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J135" s="9" t="n">
         <v>183</v>
       </c>
-      <c r="G135" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H135" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="I135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" s="9" t="n">
-        <v>197</v>
-      </c>
       <c r="K135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.53</v>
+        <v>0.5754716981132075</v>
       </c>
     </row>
     <row r="136">
@@ -8068,45 +8068,45 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E136" s="9" t="n">
-        <v>459</v>
+        <v>433</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H136" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I136" s="9" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J136" s="9" t="n">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="K136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.477124183006536</v>
+        <v>0.5750577367205543</v>
       </c>
     </row>
   </sheetData>
@@ -8149,7 +8149,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 28 Juli 2026</t>
+          <t>Hari/Tanggal : 29 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.16 WITA</t>
+          <t>Pukul        : 07.45 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8268,31 +8268,31 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2966</v>
+        <v>2995</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>212</v>
+        <v>132</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2746</v>
+        <v>2843</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2754</v>
+        <v>2852</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.9285232636547539</v>
+        <v>0.9522537562604341</v>
       </c>
     </row>
     <row r="8">
@@ -8301,45 +8301,45 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Simson Petiunaung</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2881</v>
+        <v>2082</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>441</v>
+        <v>248</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>2383</v>
+        <v>1781</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>2436</v>
+        <v>1795</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.8455397431447415</v>
+        <v>0.8621517771373679</v>
       </c>
     </row>
     <row r="9">
@@ -8348,45 +8348,45 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Sutrisno Sariang</t>
+          <t>Simson Petiunaung</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan, Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Alfi, Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2601</v>
+        <v>2908</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>445</v>
+        <v>371</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2132</v>
+        <v>2466</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2137</v>
+        <v>2504</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.8216070742022299</v>
+        <v>0.8610729023383769</v>
       </c>
     </row>
     <row r="10">
@@ -8395,45 +8395,45 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Fresly Jeica Manangkoda</t>
+          <t>Sutrisno Sariang</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan, Tabukan Utara</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi, Hendri</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2909</v>
+        <v>2617</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>587</v>
+        <v>384</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2222</v>
+        <v>2204</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2244</v>
+        <v>2209</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7713991062220694</v>
+        <v>0.8440962934658005</v>
       </c>
     </row>
     <row r="11">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -8456,31 +8456,31 @@
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2050</v>
+        <v>2164</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>380</v>
+        <v>434</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1571</v>
+        <v>1724</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1579</v>
+        <v>1724</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7702439024390244</v>
+        <v>0.7966728280961184</v>
       </c>
     </row>
     <row r="12">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Charly Angel Tatontos</t>
+          <t>Fresly Jeica Manangkoda</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -8503,31 +8503,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2955</v>
+        <v>2939</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>539</v>
+        <v>482</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>2170</v>
+        <v>2239</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2224</v>
+        <v>2255</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7526226734348562</v>
+        <v>0.7672677781558354</v>
       </c>
     </row>
     <row r="13">
@@ -8550,31 +8550,31 @@
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2873</v>
+        <v>2904</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>698</v>
+        <v>637</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>2105</v>
+        <v>2209</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2114</v>
+        <v>2216</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.7358162199791159</v>
+        <v>0.7630853994490359</v>
       </c>
     </row>
     <row r="14">
@@ -8583,45 +8583,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Charly Angel Tatontos</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore, Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Hendri, Michael</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2972</v>
+        <v>3001</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>758</v>
+        <v>438</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>5</v>
+        <v>217</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>2159</v>
+        <v>2238</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>2169</v>
-      </c>
-      <c r="M14" s="12" t="n">
-        <v>0.7298115746971736</v>
+        <v>2290</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>0.7630789736754415</v>
       </c>
     </row>
     <row r="15">
@@ -8630,45 +8630,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Kezia Maralending</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Kepulauan Marore, Tabukan Utara</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Hendri, Michael</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>1484</v>
+        <v>2998</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>213</v>
+        <v>638</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>217</v>
+        <v>60</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1020</v>
+        <v>2275</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1049</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>0.7068733153638814</v>
+        <v>2281</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>0.7608405603735824</v>
       </c>
     </row>
     <row r="16">
@@ -8691,31 +8691,31 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2493</v>
+        <v>2526</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>695</v>
+        <v>610</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>25</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1749</v>
+        <v>1855</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1760</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>0.7059767348576013</v>
+        <v>1874</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>0.7418844022169437</v>
       </c>
     </row>
     <row r="17">
@@ -8724,45 +8724,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Kezia Maralending</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2933</v>
+        <v>1490</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>851</v>
+        <v>185</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>41</v>
+        <v>199</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>2014</v>
+        <v>1066</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>2041</v>
+        <v>1092</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.6958745311967269</v>
+        <v>0.7328859060402685</v>
       </c>
     </row>
     <row r="18">
@@ -8771,45 +8771,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2149</v>
+        <v>2955</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>547</v>
+        <v>761</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1481</v>
+        <v>2099</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1481</v>
+        <v>2132</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.6891577477896697</v>
+        <v>0.7214890016920473</v>
       </c>
     </row>
     <row r="19">
@@ -8818,45 +8818,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2900</v>
+        <v>2754</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>929</v>
+        <v>776</v>
       </c>
       <c r="G19" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>1949</v>
+      </c>
+      <c r="K19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>1926</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>8</v>
-      </c>
       <c r="L19" s="9" t="n">
-        <v>1970</v>
+        <v>1950</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.6793103448275862</v>
+        <v>0.7080610021786492</v>
       </c>
     </row>
     <row r="20">
@@ -8865,45 +8865,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2199</v>
+        <v>2915</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>707</v>
+        <v>851</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1453</v>
+        <v>2017</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1475</v>
+        <v>2056</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.6707594361073216</v>
+        <v>0.7053173241852487</v>
       </c>
     </row>
     <row r="21">
@@ -8912,45 +8912,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2732</v>
+        <v>2219</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>890</v>
+        <v>629</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1812</v>
+        <v>1553</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1813</v>
+        <v>1564</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.6636163982430454</v>
+        <v>0.7048219918882378</v>
       </c>
     </row>
     <row r="22">
@@ -8973,31 +8973,31 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2379</v>
+        <v>2398</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>739</v>
+        <v>679</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1497</v>
+        <v>1559</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1525</v>
+        <v>1589</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.641025641025641</v>
+        <v>0.6626355296080066</v>
       </c>
     </row>
     <row r="23">
@@ -9006,45 +9006,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2784</v>
+        <v>2443</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>957</v>
+        <v>766</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1736</v>
+        <v>1513</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1744</v>
+        <v>1591</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.6264367816091954</v>
+        <v>0.6512484650020467</v>
       </c>
     </row>
     <row r="24">
@@ -9053,45 +9053,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2438</v>
+        <v>2829</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>847</v>
+        <v>882</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1393</v>
+        <v>1806</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>1479</v>
+        <v>1813</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.6066447908121411</v>
+        <v>0.6408624955814776</v>
       </c>
     </row>
     <row r="25">
@@ -9100,45 +9100,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2638</v>
+        <v>2832</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1557</v>
+        <v>1770</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>1570</v>
+        <v>1781</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5951478392721758</v>
+        <v>0.6288841807909604</v>
       </c>
     </row>
     <row r="26">
@@ -9147,45 +9147,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2525</v>
+        <v>2661</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>789</v>
+        <v>952</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1463</v>
+        <v>1654</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1490</v>
+        <v>1670</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.5900990099009901</v>
+        <v>0.6275836151822624</v>
       </c>
     </row>
     <row r="27">
@@ -9208,31 +9208,31 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2104</v>
+        <v>2125</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>823</v>
+        <v>716</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1197</v>
+        <v>1268</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>1232</v>
+        <v>1325</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.5855513307984791</v>
+        <v>0.6235294117647059</v>
       </c>
     </row>
     <row r="28">
@@ -9241,45 +9241,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2759</v>
+        <v>2536</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1098</v>
+        <v>740</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>38</v>
+        <v>307</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1582</v>
+        <v>1442</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1589</v>
+        <v>1464</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.5759333091699891</v>
+        <v>0.5772870662460567</v>
       </c>
     </row>
     <row r="29">
@@ -9302,31 +9302,31 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2181</v>
+        <v>2210</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>838</v>
+        <v>777</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1076</v>
+        <v>1103</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1173</v>
+        <v>1213</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.5378266850068776</v>
+        <v>0.548868778280543</v>
       </c>
     </row>
   </sheetData>
@@ -9360,7 +9360,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 28 Juli 2026</t>
+          <t>Hari/Tanggal : 29 Juli 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 08.16 WITA</t>
+          <t>Pukul        : 07.45 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.887668918918919</v>
+        <v>0.9108494533221194</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.8545232273838631</v>
+        <v>0.8786319612590799</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.8095386858273457</v>
+        <v>0.8406021239303021</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7977194626679163</v>
+        <v>0.8346967124556258</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.773517504167659</v>
+        <v>0.8297220913801224</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9513,12 +9513,12 @@
           <t>Tatoareng</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
-        <v>0.7102425876010782</v>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>+1</t>
+      <c r="C12" s="11" t="n">
+        <v>0.7422818791946308</v>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9532,11 +9532,11 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>0.6841603053435115</v>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>-1</t>
+        <v>0.7168391345249294</v>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9546,15 +9546,15 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>0.6795933734939759</v>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.7077186963979417</v>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9564,15 +9564,15 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.6793103448275862</v>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.7050252195030824</v>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.6681146828844483</v>
+        <v>0.7050173010380623</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9600,15 +9600,15 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.6384</v>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6714647263524202</v>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9618,15 +9618,15 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.6318910256410256</v>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6644087938205585</v>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9636,11 +9636,11 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.6298489425981874</v>
+        <v>0.6524764633647154</v>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
@@ -9654,15 +9654,15 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.6271534044298606</v>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>-1</t>
+        <v>0.6481982920224953</v>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9672,15 +9672,15 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.6230092204526404</v>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.645367412140575</v>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>-4</t>
         </is>
       </c>
     </row>

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 07.45 WITA</t>
+          <t>Pukul        : 07.55 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 07.45 WITA</t>
+          <t>Pukul        : 07.55 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 07.45 WITA</t>
+          <t>Pukul        : 07.55 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 07.45 WITA</t>
+          <t>Pukul        : 07.55 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Morning.xlsx
+++ b/dashboard/public/Report_Dashboard_Morning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 29 Juli 2026</t>
+          <t>Hari/Tanggal : 31 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -616,32 +616,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 07.55 WITA</t>
+          <t>Pukul        : 07.45 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-44):</t>
+          <t>Target Hari Ini (H-46):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>73.48%</t>
+          <t>76.82%</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Hijau &gt;= 73.48%</t>
+          <t>Hijau &gt;= 76.82%</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Kuning 36.74% - 73.48%</t>
+          <t>Kuning 38.41% - 76.82%</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Merah &lt; 36.74%</t>
+          <t>Merah &lt; 38.41%</t>
         </is>
       </c>
     </row>
@@ -750,41 +750,41 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4246</v>
+        <v>4291</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>682</v>
+        <v>504</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
         <v/>
       </c>
       <c r="F7" s="9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" s="10">
         <f>F7/B7</f>
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K7" s="10">
         <f>J7/B7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>3505</v>
+        <v>3710</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
@@ -798,14 +798,14 @@
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>3523</v>
+        <v>3747</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>275</v>
+        <v>187</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -819,41 +819,41 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
         <v/>
       </c>
       <c r="J8" s="9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K8" s="10">
         <f>J8/B8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1066</v>
+        <v>1157</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -867,14 +867,14 @@
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>1106</v>
+        <v>1185</v>
       </c>
       <c r="Q8" s="11">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -888,41 +888,41 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6479</v>
+        <v>6541</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>982</v>
+        <v>776</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>410</v>
+        <v>524</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4927</v>
+        <v>5070</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -936,14 +936,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>5408</v>
+        <v>5667</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>301</v>
+        <v>237</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3304</v>
+        <v>3355</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>401</v>
+        <v>302</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -977,21 +977,21 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="K10" s="10">
         <f>J10/B10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2768</v>
+        <v>2972</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
@@ -1005,14 +1005,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2903</v>
+        <v>3053</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1026,41 +1026,41 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1156</v>
+        <v>1166</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>28</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>328</v>
+        <v>272</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
         <v/>
       </c>
       <c r="J11" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11" s="10">
         <f>J11/B11</f>
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>801</v>
+        <v>858</v>
       </c>
       <c r="M11" s="10">
         <f>L11/B11</f>
@@ -1074,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>815</v>
+        <v>885</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>1063</v>
+        <v>1079</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>23</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>301</v>
+        <v>232</v>
       </c>
       <c r="E12" s="10">
         <f>D12/B12</f>
@@ -1115,7 +1115,7 @@
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
@@ -1129,7 +1129,7 @@
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>752</v>
+        <v>841</v>
       </c>
       <c r="M12" s="10">
         <f>L12/B12</f>
@@ -1143,14 +1143,14 @@
         <v/>
       </c>
       <c r="P12" s="9" t="n">
-        <v>762</v>
-      </c>
-      <c r="Q12" s="12">
+        <v>847</v>
+      </c>
+      <c r="Q12" s="11">
         <f>P12/B12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1164,62 +1164,62 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4801</v>
+        <v>4872</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1662</v>
+        <v>1497</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>287</v>
+        <v>187</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2794</v>
+        <v>3091</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
         <v/>
       </c>
       <c r="N13" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O13" s="10">
         <f>N13/B13</f>
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>3112</v>
+        <v>3344</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>139</v>
+        <v>191</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1233,62 +1233,62 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6322</v>
+        <v>6444</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2041</v>
+        <v>1746</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>286</v>
+        <v>384</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3776</v>
+        <v>4080</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
         <v/>
       </c>
       <c r="N14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O14" s="10">
         <f>N14/B14</f>
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>4245</v>
+        <v>4680</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>302</v>
+        <v>350</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1302,62 +1302,62 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8415</v>
+        <v>8569</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2678</v>
+        <v>2354</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K15" s="10">
         <f>J15/B15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>5525</v>
+        <v>5980</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
         <v/>
       </c>
       <c r="N15" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O15" s="10">
         <f>N15/B15</f>
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>5591</v>
+        <v>6086</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>379</v>
+        <v>434</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1371,41 +1371,41 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5353</v>
+        <v>5407</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1440</v>
+        <v>1214</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>3658</v>
+        <v>3850</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1419,14 +1419,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3774</v>
+        <v>4039</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>164</v>
+        <v>244</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1440,41 +1440,41 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2443</v>
+        <v>2458</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>766</v>
+        <v>636</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1513</v>
+        <v>1605</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
@@ -1488,14 +1488,14 @@
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1594</v>
+        <v>1733</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1509,41 +1509,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9699</v>
+        <v>9828</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1472</v>
+        <v>1151</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>8065</v>
+        <v>8479</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1557,14 +1557,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>8153</v>
+        <v>8593</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1189</v>
+        <v>1194</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
@@ -1612,7 +1612,7 @@
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1065</v>
+        <v>1115</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1626,14 +1626,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>1083</v>
+        <v>1119</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1647,20 +1647,20 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>8</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E20" s="10">
         <f>D20/B20</f>
         <v/>
       </c>
       <c r="F20" s="9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G20" s="10">
         <f>F20/B20</f>
@@ -1674,14 +1674,14 @@
         <v/>
       </c>
       <c r="J20" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20" s="10">
         <f>J20/B20</f>
         <v/>
       </c>
       <c r="L20" s="9" t="n">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="M20" s="10">
         <f>L20/B20</f>
@@ -1695,14 +1695,14 @@
         <v/>
       </c>
       <c r="P20" s="9" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q20" s="12">
         <f>P20/B20</f>
         <v/>
       </c>
       <c r="R20" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S20" s="10">
         <f>R20/B20</f>
@@ -1716,41 +1716,41 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2915</v>
+        <v>2933</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>851</v>
+        <v>754</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
         <v/>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="10">
         <f>F21/B21</f>
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>2017</v>
+        <v>2146</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1764,14 +1764,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>2063</v>
+        <v>2179</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1886,7 +1886,7 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1900,7 +1900,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 29 Juli 2026</t>
+          <t>Hari/Tanggal : 31 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1917,17 +1917,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 07.55 WITA</t>
+          <t>Pukul        : 07.45 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-44):</t>
+          <t>Target Hari Ini (H-46):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>73.48%</t>
+          <t>76.82%</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="M7" s="11" t="n">
         <v>1</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Regina Mahoro</t>
+          <t>Syamsia Makaminan</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>427</v>
+        <v>583</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0</v>
@@ -2169,19 +2169,19 @@
         <v>0</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>418</v>
+        <v>582</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>427</v>
+        <v>583</v>
       </c>
       <c r="M10" s="11" t="n">
         <v>1</v>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Syamsia Makaminan</t>
+          <t>Regina Mahoro</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -2254,31 +2254,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>581</v>
+        <v>427</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>568</v>
+        <v>421</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>578</v>
+        <v>427</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.9948364888123923</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2287,45 +2287,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Fitria Rianti Gorosita</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>370</v>
+        <v>421</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>379</v>
+        <v>421</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.9668367346938775</v>
+        <v>0.9859484777517564</v>
       </c>
     </row>
     <row r="14">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
@@ -2360,19 +2360,19 @@
         <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.9534161490683229</v>
+        <v>0.9846153846153847</v>
       </c>
     </row>
     <row r="15">
@@ -2395,31 +2395,31 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>7</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.9493975903614458</v>
+        <v>0.9808612440191388</v>
       </c>
     </row>
     <row r="16">
@@ -2428,45 +2428,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Merry Christiani Lano</t>
+          <t>Fitria Rianti Gorosita</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>536</v>
+        <v>393</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>481</v>
+        <v>382</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>501</v>
+        <v>384</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.9347014925373134</v>
+        <v>0.9770992366412213</v>
       </c>
     </row>
     <row r="17">
@@ -2475,45 +2475,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Clara Patricia Pangandaheng</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>302</v>
+        <v>384</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.9242424242424242</v>
+        <v>0.9750623441396509</v>
       </c>
     </row>
     <row r="18">
@@ -2522,45 +2522,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>363</v>
+        <v>405</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>368</v>
+        <v>409</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.92</v>
+        <v>0.9623529411764706</v>
       </c>
     </row>
     <row r="19">
@@ -2569,45 +2569,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>421</v>
+        <v>521</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>376</v>
+        <v>495</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>387</v>
+        <v>497</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.9192399049881235</v>
+        <v>0.9539347408829175</v>
       </c>
     </row>
     <row r="20">
@@ -2616,45 +2616,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Clara Patricia Pangandaheng</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>517</v>
+        <v>401</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>469</v>
+        <v>340</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>472</v>
+        <v>382</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.9129593810444874</v>
+        <v>0.9526184538653366</v>
       </c>
     </row>
     <row r="21">
@@ -2663,27 +2663,27 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>486</v>
+        <v>408</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21" s="9" t="n">
         <v>0</v>
@@ -2692,16 +2692,16 @@
         <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>439</v>
+        <v>383</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>440</v>
+        <v>384</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.9053497942386831</v>
+        <v>0.9411764705882352</v>
       </c>
     </row>
     <row r="22">
@@ -2710,45 +2710,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Merry Christiani Lano</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>418</v>
+        <v>539</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>375</v>
+        <v>492</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>376</v>
+        <v>506</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.8995215311004785</v>
+        <v>0.9387755102040817</v>
       </c>
     </row>
     <row r="23">
@@ -2757,24 +2757,24 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0</v>
@@ -2783,19 +2783,19 @@
         <v>0</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.8983451536643026</v>
+        <v>0.9364303178484108</v>
       </c>
     </row>
     <row r="24">
@@ -2804,45 +2804,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>398</v>
+        <v>433</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>355</v>
+        <v>399</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>356</v>
+        <v>402</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.8944723618090452</v>
+        <v>0.9284064665127021</v>
       </c>
     </row>
     <row r="25">
@@ -2851,45 +2851,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>430</v>
+        <v>492</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>455</v>
+      </c>
+      <c r="K25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="9" t="n">
-        <v>374</v>
-      </c>
-      <c r="K25" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" s="9" t="n">
-        <v>383</v>
+        <v>456</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.8906976744186046</v>
+        <v>0.926829268292683</v>
       </c>
     </row>
     <row r="26">
@@ -2898,45 +2898,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>352</v>
+        <v>403</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.8904428904428905</v>
+        <v>0.9243119266055045</v>
       </c>
     </row>
     <row r="27">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Asari Prisilia Antari</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -2959,31 +2959,31 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>316</v>
+        <v>364</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.8849765258215964</v>
+        <v>0.9122401847575058</v>
       </c>
     </row>
     <row r="28">
@@ -2992,45 +2992,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>408</v>
+        <v>572</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>333</v>
+        <v>513</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>360</v>
+        <v>518</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.9055944055944056</v>
       </c>
     </row>
     <row r="29">
@@ -3039,45 +3039,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Sheryl Jessica Tatontos</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>444</v>
+        <v>540</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>383</v>
+        <v>489</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.8626126126126126</v>
+        <v>0.9055555555555556</v>
       </c>
     </row>
     <row r="30">
@@ -3086,45 +3086,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Asari Prisilia Antari</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>566</v>
+        <v>426</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>482</v>
+        <v>321</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>488</v>
+        <v>382</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.8621908127208481</v>
+        <v>0.8967136150234741</v>
       </c>
     </row>
     <row r="31">
@@ -3147,31 +3147,31 @@
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="I31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8925143953934742</v>
       </c>
     </row>
     <row r="32">
@@ -3180,45 +3180,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>435</v>
+        <v>464</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>362</v>
+        <v>404</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>370</v>
+        <v>414</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.850574712643678</v>
+        <v>0.8922413793103449</v>
       </c>
     </row>
     <row r="33">
@@ -3241,13 +3241,13 @@
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H33" s="9" t="n">
         <v>1</v>
@@ -3256,16 +3256,16 @@
         <v>5</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.8500948766603416</v>
+        <v>0.8849056603773584</v>
       </c>
     </row>
     <row r="34">
@@ -3288,31 +3288,31 @@
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.8441558441558441</v>
+        <v>0.8795620437956204</v>
       </c>
     </row>
     <row r="35">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -3335,31 +3335,31 @@
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>520</v>
+        <v>436</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>398</v>
+        <v>362</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>438</v>
+        <v>382</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.8423076923076923</v>
+        <v>0.8761467889908257</v>
       </c>
     </row>
     <row r="36">
@@ -3368,45 +3368,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>570</v>
+        <v>497</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>430</v>
+      </c>
+      <c r="K36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>476</v>
-      </c>
-      <c r="K36" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" s="9" t="n">
-        <v>477</v>
+        <v>435</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.8368421052631579</v>
+        <v>0.8752515090543259</v>
       </c>
     </row>
     <row r="37">
@@ -3415,45 +3415,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Sheryl Jessica Tatontos</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>529</v>
+        <v>362</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>442</v>
+        <v>316</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.8355387523629489</v>
+        <v>0.8729281767955801</v>
       </c>
     </row>
     <row r="38">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -3476,31 +3476,31 @@
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>472</v>
+        <v>529</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>339</v>
+        <v>398</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>393</v>
+        <v>460</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.8326271186440678</v>
+        <v>0.8695652173913043</v>
       </c>
     </row>
     <row r="39">
@@ -3509,45 +3509,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>352</v>
+        <v>478</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>291</v>
+        <v>344</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>292</v>
+        <v>413</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.8295454545454546</v>
+        <v>0.8640167364016736</v>
       </c>
     </row>
     <row r="40">
@@ -3556,45 +3556,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>485</v>
+        <v>541</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>399</v>
+        <v>466</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.822680412371134</v>
+        <v>0.8613678373382625</v>
       </c>
     </row>
     <row r="41">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -3617,31 +3617,31 @@
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>357</v>
+        <v>576</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>292</v>
+        <v>494</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>292</v>
+        <v>495</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.8179271708683473</v>
+        <v>0.859375</v>
       </c>
     </row>
     <row r="42">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -3664,31 +3664,31 @@
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>542</v>
+        <v>477</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>432</v>
+        <v>409</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>441</v>
+        <v>409</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.8136531365313653</v>
+        <v>0.8574423480083857</v>
       </c>
     </row>
     <row r="43">
@@ -3697,45 +3697,45 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>431</v>
+        <v>352</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>346</v>
+        <v>300</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.8120649651972158</v>
+        <v>0.8551136363636364</v>
       </c>
     </row>
     <row r="44">
@@ -3744,45 +3744,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Ruslan Ginoga</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>379</v>
+        <v>489</v>
       </c>
       <c r="F44" s="9" t="n">
         <v>72</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>300</v>
+        <v>416</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>307</v>
+        <v>416</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.8100263852242745</v>
+        <v>0.8507157464212679</v>
       </c>
     </row>
     <row r="45">
@@ -3791,45 +3791,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="I45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>390</v>
+        <v>438</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>430</v>
+        <v>467</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.8037383177570093</v>
+        <v>0.8506375227686703</v>
       </c>
     </row>
     <row r="46">
@@ -3838,45 +3838,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Ruslan Ginoga</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>434</v>
+        <v>380</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.7995391705069125</v>
+        <v>0.8447368421052631</v>
       </c>
     </row>
     <row r="47">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
@@ -3899,31 +3899,31 @@
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>480</v>
+        <v>435</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="G47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>359</v>
+      </c>
+      <c r="K47" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="9" t="n">
-        <v>382</v>
-      </c>
-      <c r="K47" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" s="9" t="n">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.7958333333333333</v>
+        <v>0.8436781609195401</v>
       </c>
     </row>
     <row r="48">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>22</v>
@@ -3961,16 +3961,16 @@
         <v>1</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>413</v>
+        <v>443</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.7904761904761906</v>
+        <v>0.8428030303030303</v>
       </c>
     </row>
     <row r="49">
@@ -3979,45 +3979,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>400</v>
+        <v>437</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>315</v>
+        <v>364</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>316</v>
+        <v>366</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.79</v>
+        <v>0.8375286041189931</v>
       </c>
     </row>
     <row r="50">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
@@ -4040,31 +4040,31 @@
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.788583509513742</v>
+        <v>0.8322147651006712</v>
       </c>
     </row>
     <row r="51">
@@ -4073,45 +4073,45 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.7845433255269321</v>
+        <v>0.8300492610837439</v>
       </c>
     </row>
     <row r="52">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
@@ -4134,31 +4134,31 @@
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.7813211845102505</v>
+        <v>0.8198614318706697</v>
       </c>
     </row>
     <row r="53">
@@ -4167,45 +4167,45 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.776824034334764</v>
+        <v>0.8189473684210526</v>
       </c>
     </row>
     <row r="54">
@@ -4214,45 +4214,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>509</v>
+        <v>458</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="K54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.7760314341846758</v>
+        <v>0.8187772925764192</v>
       </c>
     </row>
     <row r="55">
@@ -4261,45 +4261,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="K55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>335</v>
+        <v>379</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.771889400921659</v>
+        <v>0.8168103448275862</v>
       </c>
     </row>
     <row r="56">
@@ -4308,45 +4308,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>486</v>
+        <v>513</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>373</v>
+        <v>418</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.7674897119341564</v>
+        <v>0.8148148148148148</v>
       </c>
     </row>
     <row r="57">
@@ -4355,45 +4355,45 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>475</v>
+        <v>326</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>364</v>
+        <v>256</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>364</v>
+        <v>264</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.7663157894736841</v>
+        <v>0.8098159509202454</v>
       </c>
     </row>
     <row r="58">
@@ -4402,45 +4402,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>470</v>
+        <v>442</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.7638297872340426</v>
+        <v>0.8076923076923077</v>
       </c>
     </row>
     <row r="59">
@@ -4463,10 +4463,10 @@
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="G59" s="9" t="n">
         <v>0</v>
@@ -4478,16 +4478,16 @@
         <v>0</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.8026905829596412</v>
       </c>
     </row>
     <row r="60">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
@@ -4510,31 +4510,31 @@
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="G60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>349</v>
+        <v>394</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>358</v>
+        <v>394</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.7600849256900213</v>
+        <v>0.8024439918533605</v>
       </c>
     </row>
     <row r="61">
@@ -4560,7 +4560,7 @@
         <v>437</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="G61" s="9" t="n">
         <v>1</v>
@@ -4572,16 +4572,16 @@
         <v>0</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="K61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.7574370709382151</v>
+        <v>0.7986270022883295</v>
       </c>
     </row>
     <row r="62">
@@ -4590,45 +4590,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>445</v>
+        <v>495</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>333</v>
+        <v>393</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>334</v>
+        <v>393</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.750561797752809</v>
+        <v>0.7939393939393939</v>
       </c>
     </row>
     <row r="63">
@@ -4637,45 +4637,45 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.7505470459518599</v>
+        <v>0.7905982905982906</v>
       </c>
     </row>
     <row r="64">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
@@ -4698,31 +4698,31 @@
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>443</v>
+        <v>544</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>320</v>
+        <v>429</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>330</v>
+        <v>430</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.7449209932279911</v>
+        <v>0.7904411764705883</v>
       </c>
     </row>
     <row r="65">
@@ -4731,45 +4731,45 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>537</v>
+        <v>470</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>396</v>
+        <v>368</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.74487895716946</v>
+        <v>0.7851063829787234</v>
       </c>
     </row>
     <row r="66">
@@ -4778,45 +4778,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>484</v>
+        <v>506</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="K66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.7438016528925619</v>
+        <v>0.7845849802371542</v>
       </c>
     </row>
     <row r="67">
@@ -4825,45 +4825,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>404</v>
+        <v>361</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="K67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.7425742574257426</v>
+        <v>0.781163434903047</v>
       </c>
     </row>
     <row r="68">
@@ -4872,45 +4872,45 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>565</v>
+        <v>419</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>419</v>
+        <v>327</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.7415929203539823</v>
+        <v>0.7804295942720764</v>
       </c>
     </row>
     <row r="69">
@@ -4919,45 +4919,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>371</v>
+        <v>307</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>373</v>
+        <v>312</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.7415506958250497</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="70">
@@ -4966,45 +4966,45 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>532</v>
+        <v>483</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H70" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I70" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>391</v>
+        <v>351</v>
       </c>
       <c r="K70" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>0.7387218045112782</v>
+        <v>0.7784679089026915</v>
       </c>
     </row>
     <row r="71">
@@ -5013,45 +5013,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>593</v>
+        <v>388</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>435</v>
+        <v>296</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>438</v>
+        <v>302</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>0.7386172006745363</v>
+        <v>0.7783505154639175</v>
       </c>
     </row>
     <row r="72">
@@ -5060,45 +5060,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="M72" s="11" t="n">
-        <v>0.7379807692307694</v>
+        <v>0.7777777777777779</v>
       </c>
     </row>
     <row r="73">
@@ -5107,45 +5107,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>506</v>
+        <v>485</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>371</v>
-      </c>
-      <c r="M73" s="12" t="n">
-        <v>0.733201581027668</v>
+        <v>377</v>
+      </c>
+      <c r="M73" s="11" t="n">
+        <v>0.7773195876288661</v>
       </c>
     </row>
     <row r="74">
@@ -5154,45 +5154,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>519</v>
+        <v>450</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H74" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I74" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I74" s="9" t="n">
-        <v>9</v>
-      </c>
       <c r="J74" s="9" t="n">
-        <v>367</v>
+        <v>330</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>379</v>
-      </c>
-      <c r="M74" s="12" t="n">
-        <v>0.7302504816955684</v>
+        <v>349</v>
+      </c>
+      <c r="M74" s="11" t="n">
+        <v>0.7755555555555556</v>
       </c>
     </row>
     <row r="75">
@@ -5201,45 +5201,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>326</v>
+        <v>600</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>237</v>
+        <v>464</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>238</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>0.7300613496932516</v>
+        <v>465</v>
+      </c>
+      <c r="M75" s="11" t="n">
+        <v>0.775</v>
       </c>
     </row>
     <row r="76">
@@ -5248,45 +5248,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>385</v>
+        <v>510</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>281</v>
+        <v>391</v>
       </c>
       <c r="K76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>281</v>
-      </c>
-      <c r="M76" s="12" t="n">
-        <v>0.7298701298701299</v>
+        <v>395</v>
+      </c>
+      <c r="M76" s="11" t="n">
+        <v>0.7745098039215687</v>
       </c>
     </row>
     <row r="77">
@@ -5295,45 +5295,45 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>514</v>
+        <v>549</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>365</v>
+        <v>425</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>371</v>
-      </c>
-      <c r="M77" s="12" t="n">
-        <v>0.7217898832684824</v>
+        <v>425</v>
+      </c>
+      <c r="M77" s="11" t="n">
+        <v>0.7741347905282332</v>
       </c>
     </row>
     <row r="78">
@@ -5342,45 +5342,45 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>393</v>
+        <v>569</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>269</v>
+        <v>377</v>
       </c>
       <c r="K78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>283</v>
-      </c>
-      <c r="M78" s="12" t="n">
-        <v>0.7201017811704835</v>
+        <v>440</v>
+      </c>
+      <c r="M78" s="11" t="n">
+        <v>0.773286467486819</v>
       </c>
     </row>
     <row r="79">
@@ -5389,45 +5389,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>380</v>
+        <v>409</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>384</v>
-      </c>
-      <c r="M79" s="12" t="n">
-        <v>0.7150837988826815</v>
+        <v>411</v>
+      </c>
+      <c r="M79" s="11" t="n">
+        <v>0.7682242990654206</v>
       </c>
     </row>
     <row r="80">
@@ -5436,45 +5436,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7679671457905544</v>
       </c>
     </row>
     <row r="81">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -5497,31 +5497,31 @@
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>443</v>
+        <v>492</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>303</v>
+        <v>349</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>316</v>
+        <v>377</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.7133182844243793</v>
+        <v>0.766260162601626</v>
       </c>
     </row>
     <row r="82">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>0</v>
@@ -5556,19 +5556,19 @@
         <v>0</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>342</v>
+        <v>390</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>343</v>
+        <v>396</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.7116182572614107</v>
+        <v>0.7600767754318618</v>
       </c>
     </row>
     <row r="83">
@@ -5577,45 +5577,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>470</v>
+        <v>508</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H83" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>380</v>
+      </c>
+      <c r="K83" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I83" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J83" s="9" t="n">
-        <v>328</v>
-      </c>
-      <c r="K83" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L83" s="9" t="n">
-        <v>332</v>
+        <v>385</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.7063829787234043</v>
+        <v>0.7578740157480314</v>
       </c>
     </row>
     <row r="84">
@@ -5624,45 +5624,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>456</v>
+        <v>485</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>322</v>
+        <v>366</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.7061403508771931</v>
+        <v>0.7546391752577319</v>
       </c>
     </row>
     <row r="85">
@@ -5671,45 +5671,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>550</v>
+        <v>428</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>364</v>
+        <v>300</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>387</v>
+        <v>322</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.7036363636363636</v>
+        <v>0.7523364485981309</v>
       </c>
     </row>
     <row r="86">
@@ -5718,45 +5718,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>211</v>
+        <v>457</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>144</v>
+        <v>340</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>148</v>
+        <v>341</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.7014218009478674</v>
+        <v>0.7461706783369803</v>
       </c>
     </row>
     <row r="87">
@@ -5765,45 +5765,45 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.6968973747016708</v>
+        <v>0.7442396313364056</v>
       </c>
     </row>
     <row r="88">
@@ -5812,45 +5812,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>274</v>
+        <v>327</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>293</v>
+        <v>332</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.6959619952494062</v>
+        <v>0.7410714285714286</v>
       </c>
     </row>
     <row r="89">
@@ -5859,45 +5859,45 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>480</v>
+        <v>555</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>331</v>
+        <v>393</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>333</v>
+        <v>411</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.69375</v>
+        <v>0.7405405405405405</v>
       </c>
     </row>
     <row r="90">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
@@ -5920,31 +5920,31 @@
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>335</v>
+        <v>383</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>337</v>
+        <v>385</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.6919917864476386</v>
+        <v>0.7291666666666665</v>
       </c>
     </row>
     <row r="91">
@@ -5953,45 +5953,45 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>354</v>
+        <v>640</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>229</v>
+        <v>435</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>242</v>
+        <v>466</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.6836158192090396</v>
+        <v>0.728125</v>
       </c>
     </row>
     <row r="92">
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I92" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.6832971800433839</v>
+        <v>0.7247311827956989</v>
       </c>
     </row>
     <row r="93">
@@ -6047,45 +6047,45 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>468</v>
+        <v>429</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>315</v>
+        <v>260</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.6794871794871795</v>
+        <v>0.7226107226107226</v>
       </c>
     </row>
     <row r="94">
@@ -6094,45 +6094,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>543</v>
+        <v>511</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.6758747697974218</v>
+        <v>0.7221135029354209</v>
       </c>
     </row>
     <row r="95">
@@ -6141,45 +6141,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>277</v>
+        <v>251</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.6746987951807228</v>
+        <v>0.7220902612826603</v>
       </c>
     </row>
     <row r="96">
@@ -6188,45 +6188,45 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>635</v>
+        <v>425</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>419</v>
+        <v>276</v>
       </c>
       <c r="K96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>428</v>
+        <v>306</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.6740157480314961</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="97">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>289</v>
+        <v>546</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>0</v>
@@ -6261,19 +6261,19 @@
         <v>0</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>191</v>
+        <v>390</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>194</v>
+        <v>393</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.671280276816609</v>
+        <v>0.7197802197802197</v>
       </c>
     </row>
     <row r="98">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
@@ -6296,31 +6296,31 @@
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>502</v>
+        <v>471</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.6693227091633466</v>
+        <v>0.7197452229299363</v>
       </c>
     </row>
     <row r="99">
@@ -6329,45 +6329,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>253</v>
+        <v>349</v>
       </c>
       <c r="K99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.6632860040567951</v>
+        <v>0.7123015873015873</v>
       </c>
     </row>
     <row r="100">
@@ -6390,31 +6390,31 @@
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="G100" s="9" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I100" s="9" t="n">
         <v>3</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="K100" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.6631578947368421</v>
+        <v>0.7107438016528925</v>
       </c>
     </row>
     <row r="101">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
@@ -6437,31 +6437,31 @@
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>418</v>
+        <v>445</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="K101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>277</v>
+        <v>316</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.6626794258373205</v>
+        <v>0.7101123595505618</v>
       </c>
     </row>
     <row r="102">
@@ -6470,45 +6470,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>502</v>
+        <v>431</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>168</v>
+        <v>116</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>329</v>
+        <v>292</v>
       </c>
       <c r="K102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>332</v>
+        <v>306</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.6613545816733066</v>
+        <v>0.7099767981438515</v>
       </c>
     </row>
     <row r="103">
@@ -6517,45 +6517,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>464</v>
+        <v>383</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="K103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.6594827586206897</v>
+        <v>0.7075718015665796</v>
       </c>
     </row>
     <row r="104">
@@ -6564,45 +6564,45 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>422</v>
+        <v>485</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="G104" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="H104" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I104" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>307</v>
+      </c>
+      <c r="K104" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H104" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="I104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="9" t="n">
-        <v>262</v>
-      </c>
-      <c r="K104" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L104" s="9" t="n">
-        <v>278</v>
+        <v>343</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.6587677725118484</v>
+        <v>0.7072164948453609</v>
       </c>
     </row>
     <row r="105">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
@@ -6625,31 +6625,31 @@
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>422</v>
+        <v>467</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G105" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="H105" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="I105" s="9" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>263</v>
+        <v>324</v>
       </c>
       <c r="K105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>276</v>
+        <v>330</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.6540284360189574</v>
+        <v>0.7066381156316917</v>
       </c>
     </row>
     <row r="106">
@@ -6658,45 +6658,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>364</v>
+        <v>434</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>237</v>
+        <v>291</v>
       </c>
       <c r="K106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>238</v>
+        <v>305</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.7027649769585254</v>
       </c>
     </row>
     <row r="107">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
@@ -6719,31 +6719,31 @@
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>427</v>
+        <v>501</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G107" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>336</v>
+      </c>
+      <c r="K107" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H107" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="I107" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="J107" s="9" t="n">
-        <v>260</v>
-      </c>
-      <c r="K107" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L107" s="9" t="n">
-        <v>279</v>
+        <v>351</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.6533957845433256</v>
+        <v>0.7005988023952096</v>
       </c>
     </row>
     <row r="108">
@@ -6752,45 +6752,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>416</v>
+        <v>366</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="K108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.6514423076923077</v>
+        <v>0.6939890710382514</v>
       </c>
     </row>
     <row r="109">
@@ -6813,31 +6813,31 @@
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>457</v>
+        <v>481</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="K109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>296</v>
+        <v>333</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.6477024070021882</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="110">
@@ -6846,45 +6846,45 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>626</v>
+        <v>509</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>213</v>
+        <v>144</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>401</v>
+        <v>281</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>404</v>
+        <v>349</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.645367412140575</v>
+        <v>0.6856581532416502</v>
       </c>
     </row>
     <row r="111">
@@ -6893,45 +6893,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>458</v>
+        <v>400</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.6419213973799127</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -6940,45 +6940,45 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>373</v>
+        <v>417</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.6407506702412868</v>
+        <v>0.6810551558752997</v>
       </c>
     </row>
     <row r="113">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
@@ -7001,31 +7001,31 @@
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>487</v>
+        <v>450</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>296</v>
+        <v>209</v>
       </c>
       <c r="K113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.6386036960985626</v>
+        <v>0.6777777777777778</v>
       </c>
     </row>
     <row r="114">
@@ -7034,45 +7034,45 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="F114" s="9" t="n">
         <v>154</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.6384297520661157</v>
+        <v>0.6736401673640168</v>
       </c>
     </row>
     <row r="115">
@@ -7081,45 +7081,45 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>400</v>
+        <v>355</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="G115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.6375</v>
+        <v>0.6732394366197183</v>
       </c>
     </row>
     <row r="116">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
@@ -7145,28 +7145,28 @@
         <v>443</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="G116" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.6343115124153499</v>
+        <v>0.672686230248307</v>
       </c>
     </row>
     <row r="117">
@@ -7175,45 +7175,45 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>438</v>
+        <v>289</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>161</v>
+        <v>95</v>
       </c>
       <c r="G117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I117" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>253</v>
+        <v>191</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>277</v>
+        <v>194</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.632420091324201</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="118">
@@ -7236,31 +7236,31 @@
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="K118" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.6312056737588653</v>
+        <v>0.6697038724373576</v>
       </c>
     </row>
     <row r="119">
@@ -7283,31 +7283,31 @@
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="M119" s="